--- a/upload/input.xlsx
+++ b/upload/input.xlsx
@@ -1,29 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vostok-1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A40BBCB-38A2-4C09-89CF-D2E00109B3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7965"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Networkall" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet name="AVR" sheetId="3" r:id="rId2"/>
+    <sheet name="AVR_Inputs" sheetId="4" r:id="rId3"/>
+    <sheet name="AVR_Outputs" sheetId="5" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$188</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="360">
   <si>
     <t>id</t>
   </si>
@@ -85,9 +94,6 @@
     <t>Помещение 1</t>
   </si>
   <si>
-    <t>Резерв</t>
-  </si>
-  <si>
     <t>ДГУ</t>
   </si>
   <si>
@@ -199,9 +205,6 @@
     <t>Остальное (по умолчанию)</t>
   </si>
   <si>
-    <t>Напряжение снято</t>
-  </si>
-  <si>
     <t>Отключен</t>
   </si>
   <si>
@@ -211,9 +214,6 @@
     <t>QF1 1 с.ш. 380 кВ ТП21</t>
   </si>
   <si>
-    <t>Точрасп ГРЩ1 QS1 1 с.ш. ППУ/ 1QF 1 с.ш. ГРЩ1</t>
-  </si>
-  <si>
     <t>QS1 1 с.ш. ППУ</t>
   </si>
   <si>
@@ -223,24 +223,12 @@
     <t>QF2 2 с.ш. 380 кВ ТП21</t>
   </si>
   <si>
-    <t>Точрасп ГРЩ 1 QS2 2 с.ш. ППУ/ 2QF 2 с.ш. ГРЩ1</t>
-  </si>
-  <si>
-    <t>Точрасп ГРЩ1 QS2 2 с.ш. ППУ/ 2QF 2 с.ш. ГРЩ1</t>
-  </si>
-  <si>
     <t>QS2 2 с.ш. ППУ</t>
   </si>
   <si>
-    <t>Точрасп ДГУ 1250 кВА в ППУ QF3 1 с.ш. ППУ QF6 2 с.ш. ППУ</t>
-  </si>
-  <si>
     <t>QF6 2 с.ш. ППУ</t>
   </si>
   <si>
-    <t>Точрасп QF2 ТП к ППУ QF2 1 с.ш. ППУ/ QF5 1 с.ш. ППУ</t>
-  </si>
-  <si>
     <t>QF2 1 с.ш. ППУ</t>
   </si>
   <si>
@@ -262,9 +250,6 @@
     <t>ДГУ 1250 кВА</t>
   </si>
   <si>
-    <t>Точрасп ДГУ 1250 кВА в ГРЩ1</t>
-  </si>
-  <si>
     <t>QF3 1 с.ш. ППУ</t>
   </si>
   <si>
@@ -541,9 +526,6 @@
     <t>АПвВнг(А)-LS- 5х(4х240) L=135 м</t>
   </si>
   <si>
-    <t>н3-ППУ - ППГнг(А)-FRHF-2 (5х240)</t>
-  </si>
-  <si>
     <t>н1-ППУ-п-61,68-0,85-110,25-50-3083,75-0,36 ППГнг(А)-FRHF-5х120</t>
   </si>
   <si>
@@ -655,27 +637,9 @@
     <t>ШП6 - 2500А (E-LINE КХA) 882,41-0,85-1577,3-127-1586-1,6</t>
   </si>
   <si>
-    <t>Точрасп ГРЩ1 QS1 1 с.ш. ППУ /1QF 1 с.ш. ГРЩ1</t>
-  </si>
-  <si>
-    <t>Точрасп ППУ QF1 1 с.ш. ППУ /QF4 2 с.ш. ППУ</t>
-  </si>
-  <si>
-    <t>Точрасп ГРЩ1 QS2 2 с.ш. ППУ /2QF 2 с.ш. ГРЩ1</t>
-  </si>
-  <si>
-    <t>Точрасп ППУ QF2 1 с.ш. ППУ/ QF5 2 с.ш. ППУ</t>
-  </si>
-  <si>
-    <t>Точрасп ДГУ 1250 кВА в ГРЩ1 QF3 2 с.ш. ГРЩ1/ Точрасп ДГУ 1250 кВА в ППУ</t>
-  </si>
-  <si>
     <t>3QF 2 с.ш. ГРЩ1</t>
   </si>
   <si>
-    <t>Точрасп ДГУ 1250 кВА в ППУ QF3 1 с.ш. ППУ/ QF6 2 с.ш. ППУ</t>
-  </si>
-  <si>
     <t>QF1 1 с.ш. ППУ ППУ-ТЦ</t>
   </si>
   <si>
@@ -1022,18 +986,152 @@
   </si>
   <si>
     <t>ППУ-п</t>
+  </si>
+  <si>
+    <t>Узел 1QF 1 с.ш. ГРЩ1/QS1 1 с.ш. ППУ ГРЩ1</t>
+  </si>
+  <si>
+    <t>Учет Pi 1 с.ш. ГРЩ1</t>
+  </si>
+  <si>
+    <t>Учет Pqs1 ППУ</t>
+  </si>
+  <si>
+    <t>Узел 2QF 2 с.ш. ГРЩ1 /QS2 2 с.ш. ППУ</t>
+  </si>
+  <si>
+    <t>Учет Piqs2 ППУ</t>
+  </si>
+  <si>
+    <t>Узел QF2 1 с.ш. ППУ/ QF5 2 с.ш. ППУ</t>
+  </si>
+  <si>
+    <t>Узуч 1 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
+  </si>
+  <si>
+    <t>Узуч 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
+  </si>
+  <si>
+    <t>Узел QF3 2 с.ш. ГРЩ1/ Узел QF3 1 с.ш. ППУ/QF6 2 с.ш. ППУ ГРЩ1</t>
+  </si>
+  <si>
+    <t>Узел QF3 1 с.ш. ППУ/QF6 2 с.ш. ППУ</t>
+  </si>
+  <si>
+    <t>ДГУ1250</t>
+  </si>
+  <si>
+    <t>AUTO</t>
+  </si>
+  <si>
+    <t>АВР между вводами ППУ</t>
+  </si>
+  <si>
+    <t>АВР ППУ</t>
+  </si>
+  <si>
+    <t>avr2</t>
+  </si>
+  <si>
+    <t>Автоматический ввод резерва ГРЩ1</t>
+  </si>
+  <si>
+    <t>avr1</t>
+  </si>
+  <si>
+    <t>delay_sec</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>ELECTRICAL</t>
+  </si>
+  <si>
+    <t>SECONDARY</t>
+  </si>
+  <si>
+    <t>PRIMARY</t>
+  </si>
+  <si>
+    <t>DGU</t>
+  </si>
+  <si>
+    <t>signal</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>element</t>
+  </si>
+  <si>
+    <t>avr_id</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>CLOSE</t>
+  </si>
+  <si>
+    <t>RESERVE_BREAKER</t>
+  </si>
+  <si>
+    <t>MAIN_BREAKER</t>
+  </si>
+  <si>
+    <t>DGU_BREAKER</t>
+  </si>
+  <si>
+    <t>action_off</t>
+  </si>
+  <si>
+    <t>action_on</t>
+  </si>
+  <si>
+    <t>АВР 1 с.ш. ГРЩ1</t>
+  </si>
+  <si>
+    <t>Резерв1</t>
+  </si>
+  <si>
+    <t>Резерв2</t>
+  </si>
+  <si>
+    <t>Резерв3</t>
+  </si>
+  <si>
+    <t>Резерв4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1070,8 +1168,39 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1090,8 +1219,14 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A86E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1127,46 +1262,155 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1506,8 +1750,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K982"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K985"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
@@ -1523,7 +1767,7 @@
     <col min="11" max="11" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="16.5" thickBot="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1778,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1558,24 +1802,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
+    <row r="2" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>297</v>
+      <c r="E2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>282</v>
       </c>
       <c r="G2">
         <v>1000</v>
@@ -1591,24 +1835,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
+    <row r="3" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>298</v>
+      <c r="E3" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>283</v>
       </c>
       <c r="G3">
         <v>630</v>
@@ -1621,27 +1865,27 @@
       </c>
       <c r="J3" s="1"/>
       <c r="K3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="26.25">
-      <c r="A4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="27" thickBot="1">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>61</v>
+      <c r="C4" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="G4">
         <v>250</v>
@@ -1657,24 +1901,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="26.25">
-      <c r="A5">
+    <row r="5" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>61</v>
+      <c r="E5" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="G5">
         <v>160</v>
@@ -1690,24 +1934,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.25">
-      <c r="A6">
+    <row r="6" spans="1:11" ht="27" thickBot="1">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>61</v>
+      <c r="C6" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="G6">
         <v>500</v>
@@ -1716,32 +1960,28 @@
         <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="C7" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="F7" s="21"/>
       <c r="G7">
         <v>1000</v>
       </c>
@@ -1753,27 +1993,27 @@
       </c>
       <c r="J7" s="1"/>
       <c r="K7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="26.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>61</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A8" s="17">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="G8">
         <v>16</v>
@@ -1782,1033 +2022,1159 @@
         <v>3.5</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="26.25">
-      <c r="B9" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A9" s="20"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="21"/>
+      <c r="J9" s="1"/>
+      <c r="K9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="27" thickBot="1">
+      <c r="A10" s="17">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="C10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="27" thickBot="1">
+      <c r="A11" s="17">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="26.25">
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="26.25">
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>65</v>
+      <c r="F11" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="26.25">
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>65</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="27" thickBot="1">
+      <c r="A12" s="17">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A13" s="17">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="27" thickBot="1">
+      <c r="A14" s="17">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="26.25">
-      <c r="B14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>299</v>
+      <c r="B14" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="J14" s="12"/>
-    </row>
-    <row r="15" spans="1:11" ht="30">
-      <c r="B15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>299</v>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30.75" thickBot="1">
+      <c r="A15" s="17">
+        <v>12</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="K15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="26.25">
-      <c r="B16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>65</v>
-      </c>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="F16" s="21"/>
       <c r="J16" s="1"/>
       <c r="K16" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="26.25">
-      <c r="B17" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A17" s="17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="C17" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>65</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>72</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A18" s="17">
+        <v>16</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" ht="30">
-      <c r="B19" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30.75" thickBot="1">
+      <c r="A19" s="17">
+        <v>17</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="K19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30.75" thickBot="1">
+      <c r="A20" s="17">
+        <v>18</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="K19" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" ht="30">
-      <c r="B20" s="1" t="s">
+      <c r="J20" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="K20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A21" s="17">
+        <v>19</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="K20" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="9"/>
+      <c r="F21" s="19" t="s">
+        <v>67</v>
+      </c>
       <c r="J21" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="K21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
-      <c r="B22" s="1" t="s">
+    <row r="22" spans="1:11" ht="30.75" thickBot="1">
+      <c r="A22" s="17">
+        <v>20</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="J22" s="1" t="s">
-        <v>327</v>
+      <c r="C22" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="J22" s="29" t="s">
+        <v>355</v>
       </c>
       <c r="K22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>299</v>
-      </c>
+    <row r="23" spans="1:11" ht="27" thickBot="1">
+      <c r="A23" s="17">
+        <v>21</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F23" s="21"/>
       <c r="J23" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="K23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="26.25">
-      <c r="B24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>299</v>
+    <row r="24" spans="1:11" ht="26.25" thickBot="1">
+      <c r="A24" s="23">
+        <v>23</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>284</v>
       </c>
       <c r="J24" s="13"/>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>299</v>
-      </c>
+      <c r="K24" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="26.25" thickBot="1">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="27"/>
       <c r="J25" s="1"/>
       <c r="K25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="26.25">
-      <c r="B26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>299</v>
-      </c>
+    <row r="26" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A26" s="26"/>
+      <c r="B26" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="27"/>
       <c r="J26" s="1"/>
       <c r="K26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="26.25">
-      <c r="B27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>299</v>
-      </c>
+    <row r="27" spans="1:11" ht="26.25" thickBot="1">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="F27" s="27"/>
       <c r="J27" s="1"/>
       <c r="K27" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" ht="30">
-      <c r="B28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>328</v>
-      </c>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="27"/>
+      <c r="J28" s="1"/>
       <c r="K28" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" ht="30">
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A29" s="26"/>
+      <c r="B29" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>328</v>
-      </c>
+      <c r="D29" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="27"/>
+      <c r="J29" s="1"/>
       <c r="K29" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="30">
-      <c r="B30" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" s="27"/>
+      <c r="J30" s="1"/>
+      <c r="K30" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A31" s="26"/>
+      <c r="B31" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="K30" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" ht="26.25">
-      <c r="B31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="C31" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="27"/>
       <c r="J31" s="1"/>
       <c r="K31" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" ht="26.25">
-      <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30">
+      <c r="A32">
+        <v>27</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="J32" s="1"/>
+        <v>284</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="K32" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="30">
+      <c r="A33">
+        <v>28</v>
+      </c>
       <c r="B33" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="J33" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="K33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30">
+      <c r="A34">
+        <v>29</v>
+      </c>
       <c r="B34" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="J34" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="K34" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="26.25">
+      <c r="A35">
+        <v>30</v>
+      </c>
       <c r="B35" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>302</v>
+        <v>287</v>
+      </c>
+      <c r="G35">
+        <v>63</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="26.25">
+      <c r="A36">
+        <v>31</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>302</v>
+        <v>287</v>
+      </c>
+      <c r="G36">
+        <v>63</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="26.25">
+      <c r="A37">
+        <v>32</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>302</v>
+        <v>287</v>
+      </c>
+      <c r="G37">
+        <v>63</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="26.25">
+      <c r="A38">
+        <v>33</v>
+      </c>
       <c r="B38" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>302</v>
+        <v>287</v>
+      </c>
+      <c r="G38">
+        <v>63</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="26.25">
+      <c r="A39">
+        <v>34</v>
+      </c>
       <c r="B39" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>303</v>
+        <v>206</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G39">
+        <v>63</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="26.25">
+      <c r="A40">
+        <v>35</v>
+      </c>
       <c r="B40" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>303</v>
+        <v>207</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G40">
+        <v>63</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="26.25">
+      <c r="A41">
+        <v>36</v>
+      </c>
       <c r="B41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>303</v>
+      <c r="C41" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G41">
+        <v>63</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="51.75">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="26.25">
+      <c r="A42">
+        <v>37</v>
+      </c>
       <c r="B42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>304</v>
+        <v>18</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G42">
+        <v>63</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="26.25">
+      <c r="A43">
+        <v>38</v>
+      </c>
       <c r="B43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>303</v>
+      <c r="C43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="26.25">
+      <c r="A44">
+        <v>39</v>
+      </c>
       <c r="B44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>303</v>
+      <c r="C44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="26.25">
+      <c r="A45">
+        <v>40</v>
+      </c>
       <c r="B45" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>303</v>
+        <v>212</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="51.75">
+      <c r="A46">
+        <v>41</v>
+      </c>
       <c r="B46" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="26.25">
+      <c r="A47">
+        <v>42</v>
+      </c>
       <c r="B47" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="26.25">
+      <c r="A48">
+        <v>43</v>
+      </c>
       <c r="B48" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="26.25">
+      <c r="A49">
+        <v>44</v>
+      </c>
       <c r="B49" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="26.25">
+      <c r="A50">
+        <v>45</v>
+      </c>
       <c r="B50" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="26.25">
+      <c r="A51">
+        <v>46</v>
+      </c>
       <c r="B51" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="26.25">
+      <c r="A52">
+        <v>47</v>
+      </c>
       <c r="B52" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" ht="26.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="26.25">
+      <c r="A53">
+        <v>48</v>
+      </c>
       <c r="B53" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="G53">
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="26.25">
+      <c r="A54">
+        <v>49</v>
+      </c>
       <c r="B54" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="G54">
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="26.25">
+      <c r="A55">
+        <v>50</v>
+      </c>
       <c r="B55" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G55">
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="26.25">
+      <c r="A56">
+        <v>51</v>
+      </c>
       <c r="B56" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="G56">
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="26.25">
+      <c r="A57">
+        <v>52</v>
+      </c>
       <c r="B57" s="1" t="s">
         <v>18</v>
       </c>
@@ -2816,13 +3182,13 @@
         <v>16</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="G57">
         <v>120</v>
@@ -2832,7 +3198,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="2:11">
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>53</v>
+      </c>
       <c r="B58" s="1" t="s">
         <v>18</v>
       </c>
@@ -2840,13 +3209,13 @@
         <v>16</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="G58">
         <v>120</v>
@@ -2856,7 +3225,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="2:11">
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>54</v>
+      </c>
       <c r="B59" s="1" t="s">
         <v>18</v>
       </c>
@@ -2864,13 +3236,13 @@
         <v>16</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="G59">
         <v>120</v>
@@ -2880,7 +3252,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="2:11">
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>55</v>
+      </c>
       <c r="B60" s="1" t="s">
         <v>18</v>
       </c>
@@ -2888,13 +3263,13 @@
         <v>16</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="G60">
         <v>120</v>
@@ -2904,7 +3279,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="2:11">
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>56</v>
+      </c>
       <c r="B61" s="1" t="s">
         <v>18</v>
       </c>
@@ -2912,13 +3290,13 @@
         <v>16</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="G61">
         <v>120</v>
@@ -2928,7 +3306,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="2:11">
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>57</v>
+      </c>
       <c r="B62" s="1" t="s">
         <v>18</v>
       </c>
@@ -2936,13 +3317,13 @@
         <v>16</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="G62">
         <v>120</v>
@@ -2952,7 +3333,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="2:11">
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>58</v>
+      </c>
       <c r="B63" s="1" t="s">
         <v>18</v>
       </c>
@@ -2960,13 +3344,13 @@
         <v>16</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="G63">
         <v>120</v>
@@ -2976,21 +3360,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="2:11">
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>59</v>
+      </c>
       <c r="B64" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="G64">
         <v>120</v>
@@ -3000,21 +3387,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="2:11">
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>60</v>
+      </c>
       <c r="B65" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="G65">
         <v>120</v>
@@ -3024,21 +3414,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="2:11">
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>61</v>
+      </c>
       <c r="B66" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="G66">
         <v>120</v>
@@ -3048,21 +3441,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="2:11">
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>62</v>
+      </c>
       <c r="B67" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="G67">
         <v>120</v>
@@ -3072,21 +3468,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="2:11">
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>63</v>
+      </c>
       <c r="B68" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="G68">
         <v>120</v>
@@ -3096,21 +3495,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="2:11">
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>64</v>
+      </c>
       <c r="B69" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G69">
         <v>120</v>
@@ -3120,21 +3522,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="2:11">
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>65</v>
+      </c>
       <c r="B70" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="G70">
         <v>120</v>
@@ -3144,21 +3549,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="2:11">
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>66</v>
+      </c>
       <c r="B71" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G71">
         <v>120</v>
@@ -3168,21 +3576,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="2:11">
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>67</v>
+      </c>
       <c r="B72" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="G72">
         <v>120</v>
@@ -3192,21 +3603,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="2:11">
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>68</v>
+      </c>
       <c r="B73" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="G73">
         <v>120</v>
@@ -3216,2252 +3630,2649 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="26.25">
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>69</v>
+      </c>
       <c r="B74" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>305</v>
+        <v>142</v>
+      </c>
+      <c r="G74">
+        <v>120</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="2:11" ht="26.25">
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>70</v>
+      </c>
       <c r="B75" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>305</v>
+        <v>143</v>
+      </c>
+      <c r="G75">
+        <v>120</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="2:11">
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>71</v>
+      </c>
       <c r="B76" s="1" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F76" s="9"/>
-      <c r="J76" s="1" t="s">
-        <v>329</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G76">
+        <v>120</v>
+      </c>
+      <c r="J76" s="1"/>
       <c r="K76" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="2:11" ht="64.5">
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>72</v>
+      </c>
       <c r="B77" s="1" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>306</v>
+        <v>145</v>
+      </c>
+      <c r="G77">
+        <v>120</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="26.25">
+      <c r="A78">
+        <v>73</v>
+      </c>
       <c r="B78" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>88</v>
+        <v>290</v>
+      </c>
+      <c r="G78">
+        <v>200</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="26.25">
+      <c r="A79">
+        <v>74</v>
+      </c>
       <c r="B79" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>75</v>
+      </c>
       <c r="B80" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J80" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="F80" s="9"/>
+      <c r="J80" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="K80" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="64.5">
+      <c r="A81">
+        <v>76</v>
+      </c>
       <c r="B81" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>77</v>
+      </c>
       <c r="B82" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="J82" s="1"/>
       <c r="K82" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>78</v>
+      </c>
       <c r="B83" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="J83" s="1"/>
       <c r="K83" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>79</v>
+      </c>
       <c r="B84" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>307</v>
+        <v>80</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>80</v>
+      </c>
       <c r="B85" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>81</v>
+      </c>
       <c r="B86" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="J86" s="12"/>
+        <v>80</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="K86" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>82</v>
+      </c>
       <c r="B87" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="J87" s="12"/>
+        <v>81</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="K87" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="26.25">
+      <c r="A88">
+        <v>83</v>
+      </c>
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="J88" s="12"/>
+        <v>292</v>
+      </c>
+      <c r="J88" s="1"/>
       <c r="K88" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="26.25">
+      <c r="A89">
+        <v>84</v>
+      </c>
       <c r="B89" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="J89" s="12"/>
+        <v>292</v>
+      </c>
+      <c r="J89" s="1"/>
       <c r="K89" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="26.25">
+      <c r="A90">
+        <v>85</v>
+      </c>
       <c r="B90" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J90" s="12"/>
       <c r="K90" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="26.25">
+      <c r="A91">
+        <v>86</v>
+      </c>
       <c r="B91" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J91" s="12"/>
       <c r="K91" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="26.25">
+      <c r="A92">
+        <v>87</v>
+      </c>
       <c r="B92" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J92" s="12"/>
       <c r="K92" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="26.25">
+      <c r="A93">
+        <v>88</v>
+      </c>
       <c r="B93" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J93" s="12"/>
       <c r="K93" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="26.25">
+      <c r="A94">
+        <v>89</v>
+      </c>
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J94" s="12"/>
       <c r="K94" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="26.25">
+      <c r="A95">
+        <v>90</v>
+      </c>
       <c r="B95" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J95" s="12"/>
       <c r="K95" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="26.25">
+      <c r="A96">
+        <v>91</v>
+      </c>
       <c r="B96" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J96" s="12"/>
       <c r="K96" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="26.25">
+      <c r="A97">
+        <v>92</v>
+      </c>
       <c r="B97" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J97" s="12"/>
       <c r="K97" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="26.25">
+      <c r="A98">
+        <v>93</v>
+      </c>
       <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J98" s="12"/>
       <c r="K98" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="26.25">
+      <c r="A99">
+        <v>94</v>
+      </c>
       <c r="B99" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J99" s="12"/>
       <c r="K99" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="26.25">
+      <c r="A100">
+        <v>95</v>
+      </c>
       <c r="B100" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J100" s="12"/>
       <c r="K100" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="26.25">
+      <c r="A101">
+        <v>96</v>
+      </c>
       <c r="B101" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J101" s="12"/>
       <c r="K101" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="26.25">
+      <c r="A102">
+        <v>97</v>
+      </c>
       <c r="B102" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="26.25">
+      <c r="A103">
+        <v>98</v>
+      </c>
       <c r="B103" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J103" s="12"/>
       <c r="K103" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="26.25">
+      <c r="A104">
+        <v>99</v>
+      </c>
       <c r="B104" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J104" s="12"/>
       <c r="K104" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="26.25">
+      <c r="A105">
+        <v>100</v>
+      </c>
       <c r="B105" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J105" s="12"/>
       <c r="K105" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="26.25">
+      <c r="A106">
+        <v>101</v>
+      </c>
       <c r="B106" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>175</v>
+        <v>13</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="J106" s="12"/>
       <c r="K106" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="26.25">
+      <c r="A107">
+        <v>102</v>
+      </c>
       <c r="B107" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="J107" s="12"/>
       <c r="K107" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="26.25">
+      <c r="A108">
+        <v>103</v>
+      </c>
       <c r="B108" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>177</v>
+        <v>86</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="J108" s="12"/>
       <c r="K108" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="26.25">
+      <c r="A109">
+        <v>104</v>
+      </c>
       <c r="B109" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>178</v>
+        <v>86</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>253</v>
+        <v>108</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="J109" s="12"/>
       <c r="K109" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="26.25">
+      <c r="A110">
+        <v>105</v>
+      </c>
       <c r="B110" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>179</v>
+        <v>87</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="J110" s="12"/>
       <c r="K110" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="26.25">
+      <c r="A111">
+        <v>106</v>
+      </c>
       <c r="B111" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>180</v>
+        <v>88</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="J111" s="12"/>
       <c r="K111" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="26.25">
+      <c r="A112">
+        <v>107</v>
+      </c>
       <c r="B112" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="J112" s="12"/>
       <c r="K112" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="113" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="26.25">
+      <c r="A113">
+        <v>108</v>
+      </c>
       <c r="B113" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="J113" s="12"/>
       <c r="K113" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="114" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="26.25">
+      <c r="A114">
+        <v>109</v>
+      </c>
       <c r="B114" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="J114" s="12"/>
       <c r="K114" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="115" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="26.25">
+      <c r="A115">
+        <v>110</v>
+      </c>
       <c r="B115" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="J115" s="12"/>
       <c r="K115" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="116" spans="2:11" ht="39">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="26.25">
+      <c r="A116">
+        <v>111</v>
+      </c>
       <c r="B116" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="J116" s="12"/>
       <c r="K116" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="117" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="26.25">
+      <c r="A117">
+        <v>112</v>
+      </c>
       <c r="B117" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D117" s="9"/>
-      <c r="E117" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="F117" s="9"/>
+        <v>94</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>300</v>
+      </c>
       <c r="J117" s="12"/>
       <c r="K117" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="118" spans="2:11" ht="64.5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="26.25">
+      <c r="A118">
+        <v>113</v>
+      </c>
       <c r="B118" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="J118" s="12"/>
       <c r="K118" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="119" spans="2:11" ht="64.5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="26.25">
+      <c r="A119">
+        <v>114</v>
+      </c>
       <c r="B119" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="J119" s="12"/>
       <c r="K119" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="120" spans="2:11" ht="51.75">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="39">
+      <c r="A120">
+        <v>115</v>
+      </c>
       <c r="B120" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="J120" s="12"/>
       <c r="K120" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="121" spans="2:11" ht="39">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121">
+        <v>116</v>
+      </c>
       <c r="B121" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>322</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D121" s="9"/>
+      <c r="E121" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F121" s="9"/>
       <c r="J121" s="12"/>
       <c r="K121" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="122" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="64.5">
+      <c r="A122">
+        <v>117</v>
+      </c>
       <c r="B122" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D122" s="9"/>
-      <c r="E122" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="F122" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>304</v>
+      </c>
       <c r="J122" s="12"/>
       <c r="K122" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="123" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="64.5">
+      <c r="A123">
+        <v>118</v>
+      </c>
       <c r="B123" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="J123" s="12"/>
       <c r="K123" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="124" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="51.75">
+      <c r="A124">
+        <v>119</v>
+      </c>
       <c r="B124" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="J124" s="12"/>
       <c r="K124" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="125" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="39">
+      <c r="A125">
+        <v>120</v>
+      </c>
       <c r="B125" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="J125" s="12"/>
       <c r="K125" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="126" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126">
+        <v>121</v>
+      </c>
       <c r="B126" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D126" s="9"/>
       <c r="E126" s="5" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="F126" s="9"/>
       <c r="J126" s="12"/>
       <c r="K126" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="127" spans="2:11" ht="26.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="26.25">
+      <c r="A127">
+        <v>122</v>
+      </c>
       <c r="B127" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F127" s="9"/>
+        <v>181</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>308</v>
+      </c>
       <c r="J127" s="12"/>
       <c r="K127" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="128" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="26.25">
+      <c r="A128">
+        <v>123</v>
+      </c>
       <c r="B128" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>117</v>
+      <c r="C128" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J128" s="12" t="s">
-        <v>327</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="J128" s="12"/>
       <c r="K128" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="129" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="26.25">
+      <c r="A129">
+        <v>124</v>
+      </c>
       <c r="B129" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C129" s="5" t="s">
-        <v>118</v>
+      <c r="C129" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J129" s="12" t="s">
-        <v>327</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J129" s="12"/>
       <c r="K129" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="130" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130">
+        <v>125</v>
+      </c>
       <c r="B130" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>168</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D130" s="9"/>
       <c r="E130" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="F130" s="9"/>
       <c r="J130" s="12"/>
       <c r="K130" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="131" spans="2:11">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="26.25">
+      <c r="A131">
+        <v>126</v>
+      </c>
       <c r="B131" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>120</v>
+        <v>11</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>118</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="F131" s="9"/>
       <c r="J131" s="12"/>
       <c r="K131" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="132" spans="2:11" ht="39">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132">
+        <v>128</v>
+      </c>
       <c r="B132" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J132" s="12"/>
+        <v>62</v>
+      </c>
+      <c r="J132" s="12" t="s">
+        <v>312</v>
+      </c>
       <c r="K132" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="2:11" ht="26.25">
-      <c r="B133" s="1"/>
+    <row r="133" spans="1:11">
+      <c r="A133">
+        <v>129</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C133" s="5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F133" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="J133" s="12"/>
-    </row>
-    <row r="134" spans="2:11" ht="26.25">
+      <c r="K133" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134">
+        <v>130</v>
+      </c>
       <c r="B134" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="J134" s="12"/>
-    </row>
-    <row r="135" spans="2:11" ht="26.25">
+      <c r="K134" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="39">
+      <c r="A135">
+        <v>131</v>
+      </c>
       <c r="B135" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J135" s="12"/>
-    </row>
-    <row r="136" spans="2:11" ht="26.25">
-      <c r="B136" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="K135" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="26.25">
+      <c r="A136">
+        <v>132</v>
+      </c>
+      <c r="B136" s="1"/>
       <c r="C136" s="5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="F136" s="9"/>
       <c r="J136" s="12"/>
     </row>
-    <row r="137" spans="2:11" ht="26.25">
+    <row r="137" spans="1:11" ht="26.25">
+      <c r="A137">
+        <v>133</v>
+      </c>
       <c r="B137" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J137" s="12"/>
     </row>
-    <row r="138" spans="2:11" ht="26.25">
+    <row r="138" spans="1:11" ht="26.25">
+      <c r="A138">
+        <v>134</v>
+      </c>
       <c r="B138" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J138" s="12"/>
     </row>
-    <row r="139" spans="2:11" ht="26.25">
+    <row r="139" spans="1:11" ht="26.25">
+      <c r="A139">
+        <v>135</v>
+      </c>
       <c r="B139" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J139" s="12"/>
     </row>
-    <row r="140" spans="2:11" ht="26.25">
+    <row r="140" spans="1:11" ht="26.25">
+      <c r="A140">
+        <v>136</v>
+      </c>
       <c r="B140" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J140" s="12"/>
     </row>
-    <row r="141" spans="2:11" ht="26.25">
+    <row r="141" spans="1:11" ht="26.25">
+      <c r="A141">
+        <v>137</v>
+      </c>
       <c r="B141" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J141" s="12"/>
     </row>
-    <row r="142" spans="2:11" ht="26.25">
+    <row r="142" spans="1:11" ht="26.25">
+      <c r="A142">
+        <v>138</v>
+      </c>
       <c r="B142" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J142" s="12"/>
     </row>
-    <row r="143" spans="2:11" ht="26.25">
+    <row r="143" spans="1:11" ht="26.25">
+      <c r="A143">
+        <v>139</v>
+      </c>
       <c r="B143" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D143" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E143" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E143" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="F143" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J143" s="12"/>
     </row>
-    <row r="144" spans="2:11">
+    <row r="144" spans="1:11" ht="26.25">
+      <c r="A144">
+        <v>140</v>
+      </c>
       <c r="B144" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C144" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E144" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D144" s="9"/>
-      <c r="E144" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="F144" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J144" s="12"/>
     </row>
-    <row r="145" spans="2:10">
+    <row r="145" spans="1:10" ht="26.25">
+      <c r="A145">
+        <v>141</v>
+      </c>
       <c r="B145" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C145" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E145" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D145" s="9"/>
-      <c r="E145" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="F145" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J145" s="12"/>
     </row>
-    <row r="146" spans="2:10">
+    <row r="146" spans="1:10" ht="26.25">
+      <c r="A146">
+        <v>142</v>
+      </c>
       <c r="B146" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C146" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E146" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D146" s="9"/>
-      <c r="E146" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F146" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J146" s="12"/>
     </row>
-    <row r="147" spans="2:10">
+    <row r="147" spans="1:10">
+      <c r="A147">
+        <v>143</v>
+      </c>
       <c r="B147" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D147" s="9"/>
       <c r="E147" s="5" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J147" s="12"/>
     </row>
-    <row r="148" spans="2:10">
+    <row r="148" spans="1:10">
+      <c r="A148">
+        <v>144</v>
+      </c>
       <c r="B148" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D148" s="9"/>
       <c r="E148" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J148" s="12"/>
     </row>
-    <row r="149" spans="2:10">
+    <row r="149" spans="1:10">
+      <c r="A149">
+        <v>145</v>
+      </c>
       <c r="B149" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D149" s="9"/>
       <c r="E149" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J149" s="12"/>
     </row>
-    <row r="150" spans="2:10">
+    <row r="150" spans="1:10">
+      <c r="A150">
+        <v>146</v>
+      </c>
       <c r="B150" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D150" s="9"/>
       <c r="E150" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J150" s="12"/>
     </row>
-    <row r="151" spans="2:10">
+    <row r="151" spans="1:10">
+      <c r="A151">
+        <v>147</v>
+      </c>
       <c r="B151" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D151" s="9"/>
       <c r="E151" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J151" s="12"/>
     </row>
-    <row r="152" spans="2:10">
+    <row r="152" spans="1:10">
+      <c r="A152">
+        <v>148</v>
+      </c>
       <c r="B152" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D152" s="9"/>
       <c r="E152" s="5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J152" s="12"/>
     </row>
-    <row r="153" spans="2:10">
+    <row r="153" spans="1:10">
+      <c r="A153">
+        <v>149</v>
+      </c>
       <c r="B153" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D153" s="9"/>
       <c r="E153" s="5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J153" s="12"/>
     </row>
-    <row r="154" spans="2:10">
+    <row r="154" spans="1:10">
+      <c r="A154">
+        <v>150</v>
+      </c>
       <c r="B154" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D154" s="9"/>
       <c r="E154" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J154" s="12"/>
     </row>
-    <row r="155" spans="2:10" ht="26.25">
+    <row r="155" spans="1:10">
+      <c r="A155">
+        <v>151</v>
+      </c>
       <c r="B155" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C155" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D155" s="9"/>
+      <c r="E155" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D155" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E155" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="F155" s="5" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J155" s="12"/>
     </row>
-    <row r="156" spans="2:10" ht="26.25">
+    <row r="156" spans="1:10">
+      <c r="A156">
+        <v>152</v>
+      </c>
       <c r="B156" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C156" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D156" s="9"/>
+      <c r="E156" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="F156" s="5" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="J156" s="12"/>
     </row>
-    <row r="157" spans="2:10" ht="26.25">
+    <row r="157" spans="1:10">
+      <c r="A157">
+        <v>153</v>
+      </c>
       <c r="B157" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C157" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D157" s="9"/>
+      <c r="E157" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D157" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E157" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="F157" s="5" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="J157" s="12"/>
     </row>
-    <row r="158" spans="2:10" ht="26.25">
+    <row r="158" spans="1:10" ht="26.25">
+      <c r="A158">
+        <v>154</v>
+      </c>
       <c r="B158" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="J158" s="12"/>
     </row>
-    <row r="159" spans="2:10" ht="26.25">
+    <row r="159" spans="1:10" ht="26.25">
+      <c r="A159">
+        <v>155</v>
+      </c>
       <c r="B159" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="J159" s="12"/>
     </row>
-    <row r="160" spans="2:10" ht="26.25">
+    <row r="160" spans="1:10" ht="26.25">
+      <c r="A160">
+        <v>156</v>
+      </c>
       <c r="B160" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J160" s="12"/>
     </row>
-    <row r="161" spans="2:11" ht="26.25">
+    <row r="161" spans="1:11" ht="26.25">
+      <c r="A161">
+        <v>157</v>
+      </c>
       <c r="B161" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J161" s="12"/>
     </row>
-    <row r="162" spans="2:11" ht="26.25">
+    <row r="162" spans="1:11" ht="26.25">
+      <c r="A162">
+        <v>158</v>
+      </c>
       <c r="B162" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J162" s="12"/>
     </row>
-    <row r="163" spans="2:11" ht="26.25">
+    <row r="163" spans="1:11" ht="26.25">
+      <c r="A163">
+        <v>159</v>
+      </c>
       <c r="B163" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="J163" s="12"/>
     </row>
-    <row r="164" spans="2:11" ht="26.25">
+    <row r="164" spans="1:11" ht="26.25">
+      <c r="A164">
+        <v>160</v>
+      </c>
       <c r="B164" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="J164" s="12"/>
     </row>
-    <row r="165" spans="2:11" ht="26.25">
+    <row r="165" spans="1:11" ht="26.25">
+      <c r="A165">
+        <v>161</v>
+      </c>
       <c r="B165" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="J165" s="12"/>
     </row>
-    <row r="166" spans="2:11" ht="39">
+    <row r="166" spans="1:11" ht="26.25">
+      <c r="A166">
+        <v>162</v>
+      </c>
       <c r="B166" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="J166" s="12"/>
-      <c r="K166" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="167" spans="2:11" ht="26.25">
+    </row>
+    <row r="167" spans="1:11" ht="26.25">
+      <c r="A167">
+        <v>163</v>
+      </c>
       <c r="B167" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="J167" s="12"/>
-      <c r="K167" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="168" spans="2:11">
+    </row>
+    <row r="168" spans="1:11" ht="26.25">
+      <c r="A168">
+        <v>164</v>
+      </c>
       <c r="B168" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D168" s="9"/>
+        <v>136</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="E168" s="5" t="s">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J168" s="12"/>
-      <c r="K168" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="169" spans="2:11">
+    </row>
+    <row r="169" spans="1:11" ht="39">
+      <c r="A169">
+        <v>165</v>
+      </c>
       <c r="B169" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D169" s="9"/>
+        <v>137</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="E169" s="5" t="s">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="J169" s="12"/>
       <c r="K169" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="2:11" ht="26.25">
+    <row r="170" spans="1:11" ht="26.25">
+      <c r="A170">
+        <v>166</v>
+      </c>
       <c r="B170" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="J170" s="12"/>
       <c r="K170" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="2:11" ht="26.25">
+    <row r="171" spans="1:11">
+      <c r="A171">
+        <v>167</v>
+      </c>
       <c r="B171" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>284</v>
+        <v>139</v>
+      </c>
+      <c r="D171" s="9"/>
+      <c r="E171" s="30" t="s">
+        <v>356</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="J171" s="12"/>
       <c r="K171" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="2:11" ht="26.25">
+    <row r="172" spans="1:11">
+      <c r="A172">
+        <v>168</v>
+      </c>
       <c r="B172" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>285</v>
+        <v>140</v>
+      </c>
+      <c r="D172" s="9"/>
+      <c r="E172" s="30" t="s">
+        <v>357</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="J172" s="12"/>
       <c r="K172" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="2:11" ht="39">
+    <row r="173" spans="1:11" ht="26.25">
+      <c r="A173">
+        <v>169</v>
+      </c>
       <c r="B173" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="J173" s="12"/>
       <c r="K173" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="2:11">
+    <row r="174" spans="1:11" ht="26.25">
+      <c r="A174">
+        <v>170</v>
+      </c>
       <c r="B174" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J174" s="12"/>
       <c r="K174" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="2:11" ht="26.25">
+    <row r="175" spans="1:11" ht="26.25">
+      <c r="A175">
+        <v>171</v>
+      </c>
       <c r="B175" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="J175" s="12"/>
       <c r="K175" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="2:11" ht="39">
+    <row r="176" spans="1:11" ht="39">
+      <c r="A176">
+        <v>172</v>
+      </c>
       <c r="B176" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="J176" s="12"/>
       <c r="K176" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="2:11" ht="26.25">
+    <row r="177" spans="1:11">
+      <c r="A177">
+        <v>173</v>
+      </c>
       <c r="B177" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="J177" s="12"/>
       <c r="K177" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="2:11">
+    <row r="178" spans="1:11" ht="26.25">
+      <c r="A178">
+        <v>174</v>
+      </c>
       <c r="B178" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D178" s="9"/>
+        <v>146</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="E178" s="5" t="s">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="J178" s="12"/>
       <c r="K178" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="2:11">
+    <row r="179" spans="1:11" ht="39">
+      <c r="A179">
+        <v>175</v>
+      </c>
       <c r="B179" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D179" s="9"/>
+        <v>147</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>195</v>
+      </c>
       <c r="E179" s="5" t="s">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="J179" s="12"/>
       <c r="K179" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="2:11">
+    <row r="180" spans="1:11" ht="26.25">
+      <c r="A180">
+        <v>176</v>
+      </c>
       <c r="B180" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J180" s="12"/>
       <c r="K180" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="2:11" ht="26.25">
+    <row r="181" spans="1:11">
+      <c r="A181">
+        <v>177</v>
+      </c>
       <c r="B181" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>292</v>
+        <v>149</v>
+      </c>
+      <c r="D181" s="9"/>
+      <c r="E181" s="30" t="s">
+        <v>358</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="J181" s="12"/>
       <c r="K181" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="2:11" ht="26.25">
+    <row r="182" spans="1:11">
+      <c r="A182">
+        <v>178</v>
+      </c>
       <c r="B182" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>293</v>
+        <v>150</v>
+      </c>
+      <c r="D182" s="9"/>
+      <c r="E182" s="30" t="s">
+        <v>359</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="J182" s="12"/>
       <c r="K182" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="2:11" ht="39">
+    <row r="183" spans="1:11">
+      <c r="A183">
+        <v>179</v>
+      </c>
       <c r="B183" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="J183" s="12"/>
       <c r="K183" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="2:11" ht="26.25">
+    <row r="184" spans="1:11" ht="26.25">
+      <c r="A184">
+        <v>180</v>
+      </c>
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="J184" s="12"/>
       <c r="K184" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="2:11">
+    <row r="185" spans="1:11" ht="26.25">
+      <c r="A185">
+        <v>181</v>
+      </c>
       <c r="B185" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="J185" s="12"/>
       <c r="K185" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="2:11">
-      <c r="B186" s="2"/>
-      <c r="C186" s="7"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-      <c r="F186" s="7"/>
-      <c r="J186" s="2"/>
-    </row>
-    <row r="187" spans="2:11">
-      <c r="B187" s="2"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="2"/>
-      <c r="J187" s="2"/>
-    </row>
-    <row r="188" spans="2:11">
-      <c r="B188" s="2"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-      <c r="F188" s="2"/>
-      <c r="J188" s="2"/>
-    </row>
-    <row r="189" spans="2:11">
+    <row r="186" spans="1:11" ht="39">
+      <c r="A186">
+        <v>182</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J186" s="12"/>
+      <c r="K186" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" ht="26.25">
+      <c r="A187">
+        <v>183</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J187" s="12"/>
+      <c r="K187" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
+      <c r="A188">
+        <v>184</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J188" s="12"/>
+      <c r="K188" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
       <c r="B189" s="2"/>
-      <c r="C189" s="8"/>
+      <c r="C189" s="7"/>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
-      <c r="F189" s="2"/>
+      <c r="F189" s="7"/>
       <c r="J189" s="2"/>
     </row>
-    <row r="190" spans="2:11">
+    <row r="190" spans="1:11">
       <c r="B190" s="2"/>
       <c r="C190" s="8"/>
       <c r="D190" s="8"/>
@@ -5469,7 +6280,7 @@
       <c r="F190" s="2"/>
       <c r="J190" s="2"/>
     </row>
-    <row r="191" spans="2:11">
+    <row r="191" spans="1:11">
       <c r="B191" s="2"/>
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
@@ -5477,7 +6288,7 @@
       <c r="F191" s="2"/>
       <c r="J191" s="2"/>
     </row>
-    <row r="192" spans="2:11">
+    <row r="192" spans="1:11">
       <c r="B192" s="2"/>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
@@ -11805,33 +12616,366 @@
       <c r="F982" s="2"/>
       <c r="J982" s="2"/>
     </row>
+    <row r="983" spans="2:10">
+      <c r="B983" s="2"/>
+      <c r="C983" s="8"/>
+      <c r="D983" s="8"/>
+      <c r="E983" s="8"/>
+      <c r="F983" s="2"/>
+      <c r="J983" s="2"/>
+    </row>
+    <row r="984" spans="2:10">
+      <c r="B984" s="2"/>
+      <c r="C984" s="8"/>
+      <c r="D984" s="8"/>
+      <c r="E984" s="8"/>
+      <c r="F984" s="2"/>
+      <c r="J984" s="2"/>
+    </row>
+    <row r="985" spans="2:10">
+      <c r="B985" s="2"/>
+      <c r="C985" s="8"/>
+      <c r="D985" s="8"/>
+      <c r="E985" s="8"/>
+      <c r="F985" s="2"/>
+      <c r="J985" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K185"/>
+  <autoFilter ref="A1:K188" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:A8 G1:I8 K1:K4 K7:K8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1 G1:I8 K1:K2 K4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB44FB6-2D9C-462D-8166-BBD7988F794F}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="35.875" style="28" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="28" customWidth="1"/>
+    <col min="5" max="5" width="10.875" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75">
+      <c r="A2" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="E2" s="28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75">
+      <c r="A3" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="E3" s="28">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4F93C2-76B9-4D86-B331-CF1832D6CC4D}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="28" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="28" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75">
+      <c r="A1" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75">
+      <c r="A2" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="28">
+        <v>1</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75">
+      <c r="A3" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="28">
+        <v>2</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75">
+      <c r="A4" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="28">
+        <v>3</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75">
+      <c r="A5" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="28">
+        <v>1</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
+      <c r="A6" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="28">
+        <v>2</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34DC4CD5-FFCD-4786-B8F6-61620E430AB5}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="18.875" style="28" customWidth="1"/>
+    <col min="4" max="5" width="10.875" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75">
+      <c r="A1" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75">
+      <c r="A2" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75">
+      <c r="A3" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75">
+      <c r="A4" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75">
+      <c r="A5" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
+      <c r="A6" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
     <col min="2" max="2" width="50.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -11839,31 +12983,31 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -11871,47 +13015,47 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.75">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -11919,103 +13063,103 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -12023,60 +13167,60 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" t="s">
         <v>46</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.75">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.75">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>50</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.75">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>52</v>
       </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.75">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>54</v>
       </c>
-      <c r="B31" t="s">
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/upload/input.xlsx
+++ b/upload/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED6FBFB-F392-4F42-9AF9-A396944F21FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBE94AF-2BDD-433E-9A3C-FCC319DC2256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Instructions" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$207</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="380">
   <si>
     <t>id</t>
   </si>
@@ -271,9 +271,6 @@
     <t>4QF 1 с.ш. ГРЩ1</t>
   </si>
   <si>
-    <t>QF18 2 с.ш. ППУ</t>
-  </si>
-  <si>
     <t>QF1 ввод ППУ-п</t>
   </si>
   <si>
@@ -946,9 +943,6 @@
     <t>Узуч 1 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
   </si>
   <si>
-    <t>Узуч 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
-  </si>
-  <si>
     <t>Узел QF3 2 с.ш. ГРЩ1/ Узел QF3 1 с.ш. ППУ/QF6 2 с.ш. ППУ ГРЩ1</t>
   </si>
   <si>
@@ -1087,9 +1081,6 @@
     <t>QF13 2 с.ш. ШАУ-П ППУ</t>
   </si>
   <si>
-    <t>QF1 1 с.ш.-ТЦ</t>
-  </si>
-  <si>
     <t>QF1 1 с.ш.-ТЦ ППУ</t>
   </si>
   <si>
@@ -1150,9 +1141,6 @@
     <t>нагрузка 10</t>
   </si>
   <si>
-    <t>нагрузка 11</t>
-  </si>
-  <si>
     <t>нагрузка 12</t>
   </si>
   <si>
@@ -1181,6 +1169,9 @@
   </si>
   <si>
     <t>Кабель 5*4</t>
+  </si>
+  <si>
+    <t>Учет 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K985"/>
+  <dimension ref="A1:K983"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
@@ -1760,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>4</v>
@@ -1801,7 +1792,7 @@
         <v>59</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G2" s="5">
         <v>1000</v>
@@ -1834,7 +1825,7 @@
         <v>62</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G3" s="5">
         <v>630</v>
@@ -1861,10 +1852,10 @@
         <v>59</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>59</v>
@@ -1891,13 +1882,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>59</v>
@@ -1924,10 +1915,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>60</v>
@@ -1957,13 +1948,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="5">
@@ -1991,10 +1982,10 @@
         <v>60</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>59</v>
@@ -2010,22 +2001,22 @@
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="26.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="5"/>
@@ -2033,7 +2024,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
       <c r="K9" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26.25">
@@ -2047,7 +2038,7 @@
         <v>61</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>73</v>
@@ -2060,7 +2051,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="26.25">
@@ -2074,7 +2065,7 @@
         <v>61</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>66</v>
@@ -2087,7 +2078,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="26.25">
@@ -2101,10 +2092,10 @@
         <v>62</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>62</v>
@@ -2125,13 +2116,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>62</v>
@@ -2141,7 +2132,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="26.25">
@@ -2152,10 +2143,10 @@
         <v>18</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>63</v>
@@ -2182,10 +2173,10 @@
         <v>63</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>62</v>
@@ -2194,10 +2185,10 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2206,13 +2197,13 @@
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="5"/>
@@ -2220,7 +2211,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
       <c r="K16" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2231,10 +2222,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>65</v>
@@ -2247,7 +2238,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="6"/>
       <c r="K17" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2258,10 +2249,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>67</v>
@@ -2274,7 +2265,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30">
@@ -2288,7 +2279,7 @@
         <v>65</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>74</v>
@@ -2300,10 +2291,10 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30">
@@ -2317,7 +2308,7 @@
         <v>66</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>75</v>
@@ -2329,10 +2320,10 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2346,7 +2337,7 @@
         <v>67</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>75</v>
@@ -2358,7 +2349,7 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>17</v>
@@ -2372,20 +2363,20 @@
         <v>11</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>17</v>
@@ -2399,20 +2390,22 @@
         <v>11</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F23" s="16"/>
+        <v>379</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>17</v>
@@ -2429,20 +2422,20 @@
         <v>71</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="22"/>
       <c r="K24" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5">
@@ -2451,10 +2444,10 @@
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E25" s="21" t="s">
         <v>70</v>
@@ -2476,10 +2469,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>76</v>
@@ -2499,13 +2492,13 @@
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="5"/>
@@ -2522,10 +2515,10 @@
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E28" s="21" t="s">
         <v>72</v>
@@ -2536,7 +2529,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="6"/>
       <c r="K28" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2550,7 +2543,7 @@
         <v>72</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E29" s="21" t="s">
         <v>74</v>
@@ -2561,7 +2554,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="6"/>
       <c r="K29" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2570,10 +2563,10 @@
       </c>
       <c r="B30" s="23"/>
       <c r="C30" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E30" s="21" t="s">
         <v>64</v>
@@ -2584,7 +2577,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="6"/>
       <c r="K30" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2598,7 +2591,7 @@
         <v>64</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>75</v>
@@ -2609,7 +2602,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="6"/>
       <c r="K31" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30">
@@ -2623,22 +2616,22 @@
         <v>72</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30">
@@ -2652,22 +2645,22 @@
         <v>65</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="30">
@@ -2681,22 +2674,22 @@
         <v>73</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="26.25">
@@ -2710,20 +2703,20 @@
         <v>74</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6"/>
       <c r="K35" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="26.25">
@@ -2737,20 +2730,20 @@
         <v>74</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
       <c r="K36" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="26.25">
@@ -2764,20 +2757,20 @@
         <v>74</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
       <c r="K37" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="26.25">
@@ -2791,20 +2784,20 @@
         <v>74</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="6"/>
       <c r="K38" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="26.25">
@@ -2818,20 +2811,20 @@
         <v>74</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="6"/>
       <c r="K39" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="26.25">
@@ -2845,20 +2838,20 @@
         <v>74</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="6"/>
       <c r="K40" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="26.25">
@@ -2872,20 +2865,20 @@
         <v>74</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="6"/>
       <c r="K41" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="26.25">
@@ -2899,20 +2892,20 @@
         <v>74</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="6"/>
       <c r="K42" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="26.25">
@@ -2926,20 +2919,20 @@
         <v>75</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="6"/>
       <c r="K43" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="26.25">
@@ -2953,20 +2946,20 @@
         <v>75</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="26.25">
@@ -2980,20 +2973,20 @@
         <v>75</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="6"/>
       <c r="K45" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="51.75">
@@ -3007,20 +3000,20 @@
         <v>72</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="6"/>
       <c r="K46" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="26.25">
@@ -3034,20 +3027,20 @@
         <v>75</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="6"/>
       <c r="K47" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="26.25">
@@ -3061,20 +3054,20 @@
         <v>75</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="6"/>
       <c r="K48" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="26.25">
@@ -3088,20 +3081,20 @@
         <v>75</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="6"/>
       <c r="K49" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="26.25">
@@ -3115,20 +3108,20 @@
         <v>75</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="6"/>
       <c r="K50" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="26.25">
@@ -3142,20 +3135,20 @@
         <v>75</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="6"/>
       <c r="K51" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="26.25">
@@ -3169,20 +3162,20 @@
         <v>75</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="6"/>
       <c r="K52" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="26.25">
@@ -3196,20 +3189,20 @@
         <v>75</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="6"/>
       <c r="K53" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="26.25">
@@ -3223,20 +3216,20 @@
         <v>75</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="6"/>
       <c r="K54" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="26.25">
@@ -3250,20 +3243,20 @@
         <v>75</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="6"/>
       <c r="K55" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="26.25">
@@ -3277,20 +3270,20 @@
         <v>75</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="6"/>
       <c r="K56" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="26.25">
@@ -3304,13 +3297,13 @@
         <v>16</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G57" s="5">
         <v>120</v>
@@ -3333,13 +3326,13 @@
         <v>16</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G58" s="5">
         <v>120</v>
@@ -3362,13 +3355,13 @@
         <v>16</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G59" s="5">
         <v>120</v>
@@ -3391,13 +3384,13 @@
         <v>16</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G60" s="5">
         <v>120</v>
@@ -3420,13 +3413,13 @@
         <v>16</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G61" s="5">
         <v>120</v>
@@ -3449,13 +3442,13 @@
         <v>16</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G62" s="5">
         <v>120</v>
@@ -3478,13 +3471,13 @@
         <v>16</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G63" s="5">
         <v>120</v>
@@ -3507,13 +3500,13 @@
         <v>16</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G64" s="5">
         <v>120</v>
@@ -3536,13 +3529,13 @@
         <v>16</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G65" s="5">
         <v>120</v>
@@ -3565,13 +3558,13 @@
         <v>16</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G66" s="5">
         <v>120</v>
@@ -3594,13 +3587,13 @@
         <v>16</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G67" s="5">
         <v>120</v>
@@ -3623,13 +3616,13 @@
         <v>76</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G68" s="5">
         <v>120</v>
@@ -3652,13 +3645,13 @@
         <v>76</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G69" s="5">
         <v>120</v>
@@ -3681,13 +3674,13 @@
         <v>76</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G70" s="5">
         <v>120</v>
@@ -3710,13 +3703,13 @@
         <v>76</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G71" s="5">
         <v>120</v>
@@ -3739,13 +3732,13 @@
         <v>76</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G72" s="5">
         <v>120</v>
@@ -3768,13 +3761,13 @@
         <v>76</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G73" s="5">
         <v>120</v>
@@ -3797,13 +3790,13 @@
         <v>76</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G74" s="5">
         <v>120</v>
@@ -3826,13 +3819,13 @@
         <v>76</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G75" s="5">
         <v>120</v>
@@ -3855,13 +3848,13 @@
         <v>76</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G76" s="5">
         <v>120</v>
@@ -3884,13 +3877,13 @@
         <v>76</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G77" s="5">
         <v>120</v>
@@ -3913,13 +3906,13 @@
         <v>16</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G78" s="5">
         <v>200</v>
@@ -3942,13 +3935,13 @@
         <v>77</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>78</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -3969,7 +3962,7 @@
         <v>78</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>76</v>
@@ -3979,7 +3972,7 @@
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>17</v>
@@ -3993,23 +3986,23 @@
         <v>57</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="6"/>
       <c r="K81" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4020,23 +4013,23 @@
         <v>11</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="6"/>
       <c r="K82" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4047,23 +4040,23 @@
         <v>57</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="6"/>
       <c r="K83" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -4074,23 +4067,23 @@
         <v>11</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="6"/>
       <c r="K84" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -4101,23 +4094,23 @@
         <v>57</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="6"/>
       <c r="K85" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4128,25 +4121,25 @@
         <v>11</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -4157,25 +4150,25 @@
         <v>57</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="26.25">
@@ -4186,23 +4179,23 @@
         <v>11</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="6"/>
       <c r="K88" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="26.25">
@@ -4213,23 +4206,23 @@
         <v>11</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="6"/>
       <c r="K89" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="26.25">
@@ -4240,23 +4233,23 @@
         <v>11</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="18"/>
       <c r="K90" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="26.25">
@@ -4267,23 +4260,23 @@
         <v>11</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="18"/>
       <c r="K91" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="26.25">
@@ -4294,23 +4287,23 @@
         <v>11</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="18"/>
       <c r="K92" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="26.25">
@@ -4321,23 +4314,23 @@
         <v>11</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="18"/>
       <c r="K93" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="26.25">
@@ -4348,23 +4341,23 @@
         <v>11</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="18"/>
       <c r="K94" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="26.25">
@@ -4375,23 +4368,23 @@
         <v>11</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="18"/>
       <c r="K95" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="26.25">
@@ -4402,23 +4395,23 @@
         <v>11</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="18"/>
       <c r="K96" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="26.25">
@@ -4429,23 +4422,23 @@
         <v>11</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="18"/>
       <c r="K97" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="26.25">
@@ -4456,23 +4449,23 @@
         <v>11</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="18"/>
       <c r="K98" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="26.25">
@@ -4483,23 +4476,23 @@
         <v>57</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="18"/>
       <c r="K99" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="26.25">
@@ -4510,23 +4503,23 @@
         <v>11</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="18"/>
       <c r="K100" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="26.25">
@@ -4537,23 +4530,23 @@
         <v>11</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="18"/>
       <c r="K101" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="26.25">
@@ -4564,23 +4557,23 @@
         <v>11</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="18"/>
       <c r="K102" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="26.25">
@@ -4591,23 +4584,23 @@
         <v>11</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="18"/>
       <c r="K103" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="26.25">
@@ -4618,23 +4611,23 @@
         <v>57</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="18"/>
       <c r="K104" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="26.25">
@@ -4645,23 +4638,23 @@
         <v>11</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="18"/>
       <c r="K105" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="26.25">
@@ -4672,23 +4665,23 @@
         <v>11</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="18"/>
       <c r="K106" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="26.25">
@@ -4699,23 +4692,23 @@
         <v>11</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="18"/>
       <c r="K107" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="26.25">
@@ -4726,23 +4719,23 @@
         <v>57</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="18"/>
       <c r="K108" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="26.25">
@@ -4753,23 +4746,23 @@
         <v>11</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="18"/>
       <c r="K109" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="26.25">
@@ -4780,23 +4773,23 @@
         <v>11</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="18"/>
       <c r="K110" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="26.25">
@@ -4807,23 +4800,23 @@
         <v>11</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="18"/>
       <c r="K111" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="26.25">
@@ -4834,23 +4827,23 @@
         <v>11</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="18"/>
       <c r="K112" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="26.25">
@@ -4861,23 +4854,23 @@
         <v>11</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="18"/>
       <c r="K113" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="26.25">
@@ -4888,23 +4881,23 @@
         <v>11</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="18"/>
       <c r="K114" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="26.25">
@@ -4915,23 +4908,23 @@
         <v>11</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="18"/>
       <c r="K115" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="26.25">
@@ -4942,23 +4935,23 @@
         <v>11</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="18"/>
       <c r="K116" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="26.25">
@@ -4969,23 +4962,23 @@
         <v>11</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="18"/>
       <c r="K117" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="26.25">
@@ -4996,23 +4989,23 @@
         <v>11</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="18"/>
       <c r="K118" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="26.25">
@@ -5023,23 +5016,23 @@
         <v>11</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="18"/>
       <c r="K119" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="39">
@@ -5050,23 +5043,23 @@
         <v>11</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="18"/>
       <c r="K120" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -5077,11 +5070,11 @@
         <v>57</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D121" s="25"/>
       <c r="E121" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F121" s="25"/>
       <c r="G121" s="5"/>
@@ -5089,7 +5082,7 @@
       <c r="I121" s="5"/>
       <c r="J121" s="18"/>
       <c r="K121" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="64.5">
@@ -5100,23 +5093,23 @@
         <v>11</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="18"/>
       <c r="K122" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="64.5">
@@ -5127,23 +5120,23 @@
         <v>11</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="18"/>
       <c r="K123" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="51.75">
@@ -5154,23 +5147,23 @@
         <v>11</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="18"/>
       <c r="K124" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="39">
@@ -5181,23 +5174,23 @@
         <v>11</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="18"/>
       <c r="K125" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5208,11 +5201,11 @@
         <v>57</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D126" s="25"/>
       <c r="E126" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F126" s="25"/>
       <c r="G126" s="5"/>
@@ -5220,7 +5213,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="18"/>
       <c r="K126" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="26.25">
@@ -5231,23 +5224,23 @@
         <v>11</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="18"/>
       <c r="K127" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="26.25">
@@ -5258,23 +5251,23 @@
         <v>11</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="18"/>
       <c r="K128" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="26.25">
@@ -5285,23 +5278,23 @@
         <v>11</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="18"/>
       <c r="K129" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5312,11 +5305,11 @@
         <v>57</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D130" s="25"/>
       <c r="E130" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F130" s="25"/>
       <c r="G130" s="5"/>
@@ -5324,7 +5317,7 @@
       <c r="I130" s="5"/>
       <c r="J130" s="18"/>
       <c r="K130" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="26.25">
@@ -5335,13 +5328,13 @@
         <v>11</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F131" s="25"/>
       <c r="G131" s="5"/>
@@ -5349,41 +5342,39 @@
       <c r="I131" s="5"/>
       <c r="J131" s="18"/>
       <c r="K131" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="13">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C132" s="9" t="s">
         <v>110</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
-      <c r="J132" s="18" t="s">
-        <v>291</v>
-      </c>
+      <c r="J132" s="18"/>
       <c r="K132" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="13">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>18</v>
@@ -5392,10 +5383,10 @@
         <v>111</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>109</v>
@@ -5408,24 +5399,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" ht="39">
       <c r="A134" s="13">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C134" s="9" t="s">
         <v>112</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -5435,48 +5426,46 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="39">
+    <row r="135" spans="1:11" ht="26.25">
       <c r="A135" s="13">
-        <v>134</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B135" s="6"/>
       <c r="C135" s="9" t="s">
         <v>113</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F135" s="9" t="s">
-        <v>113</v>
-      </c>
+      <c r="F135" s="25"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="18"/>
-      <c r="K135" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="K135" s="5"/>
     </row>
     <row r="136" spans="1:11" ht="26.25">
       <c r="A136" s="13">
-        <v>135</v>
-      </c>
-      <c r="B136" s="6"/>
+        <v>136</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C136" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F136" s="25"/>
+      <c r="F136" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -5485,7 +5474,7 @@
     </row>
     <row r="137" spans="1:11" ht="26.25">
       <c r="A137" s="13">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>18</v>
@@ -5494,13 +5483,13 @@
         <v>115</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>116</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -5510,7 +5499,7 @@
     </row>
     <row r="138" spans="1:11" ht="26.25">
       <c r="A138" s="13">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>18</v>
@@ -5519,13 +5508,13 @@
         <v>116</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>117</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -5535,7 +5524,7 @@
     </row>
     <row r="139" spans="1:11" ht="26.25">
       <c r="A139" s="13">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>18</v>
@@ -5544,13 +5533,13 @@
         <v>117</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>118</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -5560,7 +5549,7 @@
     </row>
     <row r="140" spans="1:11" ht="26.25">
       <c r="A140" s="13">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>18</v>
@@ -5569,13 +5558,13 @@
         <v>118</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>119</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -5585,7 +5574,7 @@
     </row>
     <row r="141" spans="1:11" ht="26.25">
       <c r="A141" s="13">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>18</v>
@@ -5594,13 +5583,13 @@
         <v>119</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>120</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -5610,7 +5599,7 @@
     </row>
     <row r="142" spans="1:11" ht="26.25">
       <c r="A142" s="13">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>18</v>
@@ -5619,13 +5608,13 @@
         <v>120</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>121</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -5635,7 +5624,7 @@
     </row>
     <row r="143" spans="1:11" ht="26.25">
       <c r="A143" s="13">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>18</v>
@@ -5644,13 +5633,13 @@
         <v>121</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>122</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -5660,7 +5649,7 @@
     </row>
     <row r="144" spans="1:11" ht="26.25">
       <c r="A144" s="13">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>18</v>
@@ -5669,13 +5658,13 @@
         <v>122</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>123</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -5685,7 +5674,7 @@
     </row>
     <row r="145" spans="1:11" ht="26.25">
       <c r="A145" s="13">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>18</v>
@@ -5694,13 +5683,13 @@
         <v>123</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>124</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -5708,24 +5697,22 @@
       <c r="J145" s="18"/>
       <c r="K145" s="5"/>
     </row>
-    <row r="146" spans="1:11" ht="26.25">
+    <row r="146" spans="1:11">
       <c r="A146" s="13">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D146" s="9" t="s">
         <v>114</v>
       </c>
+      <c r="D146" s="25"/>
       <c r="E146" s="9" t="s">
         <v>125</v>
       </c>
       <c r="F146" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -5735,7 +5722,7 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="13">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>11</v>
@@ -5748,7 +5735,7 @@
         <v>126</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
@@ -5758,7 +5745,7 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="13">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>11</v>
@@ -5771,7 +5758,7 @@
         <v>127</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
@@ -5781,7 +5768,7 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="13">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>11</v>
@@ -5794,7 +5781,7 @@
         <v>128</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
@@ -5804,7 +5791,7 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="13">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>11</v>
@@ -5817,7 +5804,7 @@
         <v>129</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
@@ -5827,7 +5814,7 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="13">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>11</v>
@@ -5840,7 +5827,7 @@
         <v>130</v>
       </c>
       <c r="F151" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
@@ -5850,7 +5837,7 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="13">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>11</v>
@@ -5863,7 +5850,7 @@
         <v>131</v>
       </c>
       <c r="F152" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
@@ -5873,7 +5860,7 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="13">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>11</v>
@@ -5886,7 +5873,7 @@
         <v>132</v>
       </c>
       <c r="F153" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
@@ -5896,7 +5883,7 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="13">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>11</v>
@@ -5909,7 +5896,7 @@
         <v>133</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
@@ -5919,7 +5906,7 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="13">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>11</v>
@@ -5932,7 +5919,7 @@
         <v>134</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -5942,7 +5929,7 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="13">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>11</v>
@@ -5955,7 +5942,7 @@
         <v>135</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
@@ -5963,9 +5950,9 @@
       <c r="J156" s="18"/>
       <c r="K156" s="5"/>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" ht="26.25">
       <c r="A157" s="13">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>11</v>
@@ -5973,12 +5960,14 @@
       <c r="C157" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D157" s="25"/>
+      <c r="D157" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="E157" s="9" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="F157" s="9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
@@ -5988,7 +5977,7 @@
     </row>
     <row r="158" spans="1:11" ht="26.25">
       <c r="A158" s="13">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>11</v>
@@ -5997,7 +5986,7 @@
         <v>126</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E158" s="9" t="s">
         <v>234</v>
@@ -6013,7 +6002,7 @@
     </row>
     <row r="159" spans="1:11" ht="26.25">
       <c r="A159" s="13">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>11</v>
@@ -6022,7 +6011,7 @@
         <v>127</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>235</v>
@@ -6038,7 +6027,7 @@
     </row>
     <row r="160" spans="1:11" ht="26.25">
       <c r="A160" s="13">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>11</v>
@@ -6047,7 +6036,7 @@
         <v>128</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E160" s="9" t="s">
         <v>236</v>
@@ -6063,7 +6052,7 @@
     </row>
     <row r="161" spans="1:11" ht="26.25">
       <c r="A161" s="13">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>11</v>
@@ -6072,7 +6061,7 @@
         <v>129</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>237</v>
@@ -6088,7 +6077,7 @@
     </row>
     <row r="162" spans="1:11" ht="26.25">
       <c r="A162" s="13">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>11</v>
@@ -6097,7 +6086,7 @@
         <v>130</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E162" s="9" t="s">
         <v>238</v>
@@ -6113,7 +6102,7 @@
     </row>
     <row r="163" spans="1:11" ht="26.25">
       <c r="A163" s="13">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>11</v>
@@ -6122,7 +6111,7 @@
         <v>131</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>239</v>
@@ -6138,7 +6127,7 @@
     </row>
     <row r="164" spans="1:11" ht="26.25">
       <c r="A164" s="13">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>11</v>
@@ -6147,7 +6136,7 @@
         <v>132</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>240</v>
@@ -6163,7 +6152,7 @@
     </row>
     <row r="165" spans="1:11" ht="26.25">
       <c r="A165" s="13">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>11</v>
@@ -6172,7 +6161,7 @@
         <v>133</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>241</v>
@@ -6188,7 +6177,7 @@
     </row>
     <row r="166" spans="1:11" ht="26.25">
       <c r="A166" s="13">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>11</v>
@@ -6197,7 +6186,7 @@
         <v>134</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E166" s="9" t="s">
         <v>242</v>
@@ -6213,7 +6202,7 @@
     </row>
     <row r="167" spans="1:11" ht="26.25">
       <c r="A167" s="13">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>11</v>
@@ -6222,7 +6211,7 @@
         <v>135</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>243</v>
@@ -6236,9 +6225,9 @@
       <c r="J167" s="18"/>
       <c r="K167" s="5"/>
     </row>
-    <row r="168" spans="1:11" ht="26.25">
+    <row r="168" spans="1:11" ht="39">
       <c r="A168" s="13">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>11</v>
@@ -6259,11 +6248,13 @@
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="18"/>
-      <c r="K168" s="5"/>
-    </row>
-    <row r="169" spans="1:11" ht="39">
+      <c r="K168" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="26.25">
       <c r="A169" s="13">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>11</v>
@@ -6288,21 +6279,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="26.25">
+    <row r="170" spans="1:11">
       <c r="A170" s="13">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C170" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D170" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E170" s="9" t="s">
-        <v>246</v>
+      <c r="D170" s="25"/>
+      <c r="E170" s="26" t="s">
+        <v>333</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>138</v>
@@ -6317,7 +6306,7 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="13">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>57</v>
@@ -6327,7 +6316,7 @@
       </c>
       <c r="D171" s="25"/>
       <c r="E171" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>139</v>
@@ -6340,19 +6329,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" ht="26.25">
       <c r="A172" s="13">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C172" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D172" s="25"/>
-      <c r="E172" s="26" t="s">
-        <v>336</v>
+      <c r="D172" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>140</v>
@@ -6367,7 +6358,7 @@
     </row>
     <row r="173" spans="1:11" ht="26.25">
       <c r="A173" s="13">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>11</v>
@@ -6394,7 +6385,7 @@
     </row>
     <row r="174" spans="1:11" ht="26.25">
       <c r="A174" s="13">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>11</v>
@@ -6419,9 +6410,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="26.25">
+    <row r="175" spans="1:11" ht="39">
       <c r="A175" s="13">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>11</v>
@@ -6446,9 +6437,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="39">
+    <row r="176" spans="1:11">
       <c r="A176" s="13">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>11</v>
@@ -6473,9 +6464,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" ht="26.25">
       <c r="A177" s="13">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>11</v>
@@ -6500,9 +6491,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="26.25">
+    <row r="178" spans="1:11" ht="39">
       <c r="A178" s="13">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>11</v>
@@ -6527,9 +6518,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="39">
+    <row r="179" spans="1:11" ht="26.25">
       <c r="A179" s="13">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>11</v>
@@ -6554,21 +6545,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="26.25">
+    <row r="180" spans="1:11">
       <c r="A180" s="13">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C180" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D180" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>254</v>
+      <c r="D180" s="25"/>
+      <c r="E180" s="26" t="s">
+        <v>335</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>148</v>
@@ -6583,7 +6572,7 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="13">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>57</v>
@@ -6593,7 +6582,7 @@
       </c>
       <c r="D181" s="25"/>
       <c r="E181" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>149</v>
@@ -6608,17 +6597,19 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="13">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C182" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D182" s="25"/>
-      <c r="E182" s="26" t="s">
-        <v>338</v>
+      <c r="D182" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>150</v>
@@ -6631,9 +6622,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" ht="26.25">
       <c r="A183" s="13">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>11</v>
@@ -6642,7 +6633,7 @@
         <v>151</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>255</v>
@@ -6660,7 +6651,7 @@
     </row>
     <row r="184" spans="1:11" ht="26.25">
       <c r="A184" s="13">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>11</v>
@@ -6685,9 +6676,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="26.25">
+    <row r="185" spans="1:11" ht="39">
       <c r="A185" s="13">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>11</v>
@@ -6712,9 +6703,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="39">
+    <row r="186" spans="1:11" ht="26.25">
       <c r="A186" s="13">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>11</v>
@@ -6739,9 +6730,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="26.25">
+    <row r="187" spans="1:11">
       <c r="A187" s="13">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>11</v>
@@ -6750,7 +6741,7 @@
         <v>155</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>259</v>
@@ -6768,48 +6759,48 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="13">
-        <v>187</v>
-      </c>
-      <c r="B188" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D188" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="E188" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="F188" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
+        <v>349</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F188" s="11"/>
+      <c r="G188" s="5">
+        <v>63</v>
+      </c>
+      <c r="H188" s="5">
+        <v>15</v>
+      </c>
       <c r="I188" s="5"/>
-      <c r="J188" s="18"/>
-      <c r="K188" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="J188" s="8"/>
+      <c r="K188" s="5"/>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="13">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="F189" s="11"/>
+        <v>359</v>
+      </c>
+      <c r="F189" s="8"/>
       <c r="G189" s="5">
         <v>63</v>
       </c>
@@ -6818,23 +6809,25 @@
       </c>
       <c r="I189" s="5"/>
       <c r="J189" s="8"/>
-      <c r="K189" s="5"/>
+      <c r="K189" s="5" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="13">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="5">
@@ -6846,24 +6839,24 @@
       <c r="I190" s="5"/>
       <c r="J190" s="8"/>
       <c r="K190" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="13">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F191" s="8"/>
       <c r="G191" s="5">
@@ -6875,24 +6868,24 @@
       <c r="I191" s="5"/>
       <c r="J191" s="8"/>
       <c r="K191" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="13">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="5">
@@ -6904,24 +6897,24 @@
       <c r="I192" s="5"/>
       <c r="J192" s="8"/>
       <c r="K192" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="13">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F193" s="8"/>
       <c r="G193" s="5">
@@ -6933,24 +6926,24 @@
       <c r="I193" s="5"/>
       <c r="J193" s="8"/>
       <c r="K193" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="13">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="5">
@@ -6962,24 +6955,24 @@
       <c r="I194" s="5"/>
       <c r="J194" s="8"/>
       <c r="K194" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="13">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="5">
@@ -6991,24 +6984,24 @@
       <c r="I195" s="5"/>
       <c r="J195" s="8"/>
       <c r="K195" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="13">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B196" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="5">
@@ -7020,24 +7013,24 @@
       <c r="I196" s="5"/>
       <c r="J196" s="8"/>
       <c r="K196" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="13">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B197" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="5">
@@ -7049,24 +7042,24 @@
       <c r="I197" s="5"/>
       <c r="J197" s="8"/>
       <c r="K197" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="13">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C198" s="9" t="s">
-        <v>340</v>
+      <c r="C198" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="5">
@@ -7078,24 +7071,24 @@
       <c r="I198" s="5"/>
       <c r="J198" s="8"/>
       <c r="K198" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="13">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F199" s="8"/>
       <c r="G199" s="5">
@@ -7106,11 +7099,13 @@
       </c>
       <c r="I199" s="5"/>
       <c r="J199" s="8"/>
-      <c r="K199" s="5"/>
+      <c r="K199" s="5" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="13">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>11</v>
@@ -7119,10 +7114,10 @@
         <v>341</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="5">
@@ -7134,12 +7129,12 @@
       <c r="I200" s="5"/>
       <c r="J200" s="8"/>
       <c r="K200" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="13">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>11</v>
@@ -7148,10 +7143,10 @@
         <v>342</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="5">
@@ -7163,12 +7158,12 @@
       <c r="I201" s="5"/>
       <c r="J201" s="8"/>
       <c r="K201" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="13">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>11</v>
@@ -7177,10 +7172,10 @@
         <v>343</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="5">
@@ -7192,12 +7187,12 @@
       <c r="I202" s="5"/>
       <c r="J202" s="8"/>
       <c r="K202" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="13">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>11</v>
@@ -7206,10 +7201,10 @@
         <v>344</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F203" s="8"/>
       <c r="G203" s="5">
@@ -7221,12 +7216,12 @@
       <c r="I203" s="5"/>
       <c r="J203" s="8"/>
       <c r="K203" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="13">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>11</v>
@@ -7235,10 +7230,10 @@
         <v>345</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="F204" s="8"/>
       <c r="G204" s="5">
@@ -7250,12 +7245,12 @@
       <c r="I204" s="5"/>
       <c r="J204" s="8"/>
       <c r="K204" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="13">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>11</v>
@@ -7264,10 +7259,10 @@
         <v>346</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F205" s="8"/>
       <c r="G205" s="5">
@@ -7279,12 +7274,12 @@
       <c r="I205" s="5"/>
       <c r="J205" s="8"/>
       <c r="K205" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="13">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>11</v>
@@ -7293,10 +7288,10 @@
         <v>347</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="5">
@@ -7308,12 +7303,12 @@
       <c r="I206" s="5"/>
       <c r="J206" s="8"/>
       <c r="K206" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="13">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>11</v>
@@ -7322,10 +7317,10 @@
         <v>348</v>
       </c>
       <c r="D207" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F207" s="8"/>
       <c r="G207" s="5">
@@ -7337,68 +7332,26 @@
       <c r="I207" s="5"/>
       <c r="J207" s="8"/>
       <c r="K207" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="208" spans="1:11">
-      <c r="A208" s="13">
-        <v>207</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C208" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D208" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E208" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="F208" s="8"/>
-      <c r="G208" s="5">
-        <v>63</v>
-      </c>
-      <c r="H208" s="5">
-        <v>15</v>
-      </c>
-      <c r="I208" s="5"/>
-      <c r="J208" s="8"/>
-      <c r="K208" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="209" spans="1:11">
-      <c r="A209" s="13">
-        <v>208</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C209" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="D209" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E209" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="F209" s="8"/>
-      <c r="G209" s="5">
-        <v>63</v>
-      </c>
-      <c r="H209" s="5">
-        <v>15</v>
-      </c>
-      <c r="I209" s="5"/>
-      <c r="J209" s="8"/>
-      <c r="K209" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11">
+      <c r="B208" s="1"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="1"/>
+      <c r="J208" s="1"/>
+    </row>
+    <row r="209" spans="2:10">
+      <c r="B209" s="1"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="1"/>
+      <c r="J209" s="1"/>
+    </row>
+    <row r="210" spans="2:10">
       <c r="B210" s="1"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -7406,7 +7359,7 @@
       <c r="F210" s="1"/>
       <c r="J210" s="1"/>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="2:10">
       <c r="B211" s="1"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
@@ -7414,7 +7367,7 @@
       <c r="F211" s="1"/>
       <c r="J211" s="1"/>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="2:10">
       <c r="B212" s="1"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
@@ -7422,7 +7375,7 @@
       <c r="F212" s="1"/>
       <c r="J212" s="1"/>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="2:10">
       <c r="B213" s="1"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
@@ -7430,7 +7383,7 @@
       <c r="F213" s="1"/>
       <c r="J213" s="1"/>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="2:10">
       <c r="B214" s="1"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
@@ -7438,7 +7391,7 @@
       <c r="F214" s="1"/>
       <c r="J214" s="1"/>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="2:10">
       <c r="B215" s="1"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -7446,7 +7399,7 @@
       <c r="F215" s="1"/>
       <c r="J215" s="1"/>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="2:10">
       <c r="B216" s="1"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
@@ -7454,7 +7407,7 @@
       <c r="F216" s="1"/>
       <c r="J216" s="1"/>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="2:10">
       <c r="B217" s="1"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
@@ -7462,7 +7415,7 @@
       <c r="F217" s="1"/>
       <c r="J217" s="1"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="2:10">
       <c r="B218" s="1"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
@@ -7470,7 +7423,7 @@
       <c r="F218" s="1"/>
       <c r="J218" s="1"/>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="2:10">
       <c r="B219" s="1"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
@@ -7478,7 +7431,7 @@
       <c r="F219" s="1"/>
       <c r="J219" s="1"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="2:10">
       <c r="B220" s="1"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
@@ -7486,7 +7439,7 @@
       <c r="F220" s="1"/>
       <c r="J220" s="1"/>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="2:10">
       <c r="B221" s="1"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
@@ -7494,7 +7447,7 @@
       <c r="F221" s="1"/>
       <c r="J221" s="1"/>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="2:10">
       <c r="B222" s="1"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
@@ -7502,7 +7455,7 @@
       <c r="F222" s="1"/>
       <c r="J222" s="1"/>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="2:10">
       <c r="B223" s="1"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
@@ -7510,7 +7463,7 @@
       <c r="F223" s="1"/>
       <c r="J223" s="1"/>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="2:10">
       <c r="B224" s="1"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -13590,24 +13543,8 @@
       <c r="F983" s="1"/>
       <c r="J983" s="1"/>
     </row>
-    <row r="984" spans="2:10">
-      <c r="B984" s="1"/>
-      <c r="C984" s="3"/>
-      <c r="D984" s="3"/>
-      <c r="E984" s="3"/>
-      <c r="F984" s="1"/>
-      <c r="J984" s="1"/>
-    </row>
-    <row r="985" spans="2:10">
-      <c r="B985" s="1"/>
-      <c r="C985" s="3"/>
-      <c r="D985" s="3"/>
-      <c r="E985" s="3"/>
-      <c r="F985" s="1"/>
-      <c r="J985" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K209" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -13634,30 +13571,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E2" s="4">
         <v>0.5</v>
@@ -13665,16 +13602,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E3" s="4">
         <v>0.3</v>
@@ -13700,104 +13637,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -13819,104 +13756,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/upload/input.xlsx
+++ b/upload/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBE94AF-2BDD-433E-9A3C-FCC319DC2256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ACD2A2-439E-4B4B-8644-0147C88EB27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="379">
   <si>
     <t>id</t>
   </si>
@@ -925,9 +925,6 @@
     <t>Узел 1QF 1 с.ш. ГРЩ1/QS1 1 с.ш. ППУ ГРЩ1</t>
   </si>
   <si>
-    <t>Учет Pi 1 с.ш. ГРЩ1</t>
-  </si>
-  <si>
     <t>Учет Pqs1 ППУ</t>
   </si>
   <si>
@@ -940,9 +937,6 @@
     <t>Узел QF2 1 с.ш. ППУ/ QF5 2 с.ш. ППУ</t>
   </si>
   <si>
-    <t>Узуч 1 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
-  </si>
-  <si>
     <t>Узел QF3 2 с.ш. ГРЩ1/ Узел QF3 1 с.ш. ППУ/QF6 2 с.ш. ППУ ГРЩ1</t>
   </si>
   <si>
@@ -1172,6 +1166,9 @@
   </si>
   <si>
     <t>Учет 2 с.ш. ГРЩ1 ART-03 PQRS, 5(10)A 5000/5 ГРЩ1</t>
+  </si>
+  <si>
+    <t>Учет Pi 1 с.ш. ART-03 PQRS, 5(10)A 5000/5  ГРЩ1</t>
   </si>
 </sst>
 </file>
@@ -1724,6 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K983"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
@@ -1775,7 +1773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" hidden="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1808,7 +1806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1841,7 +1839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26.25">
+    <row r="4" spans="1:11" ht="26.25" hidden="1">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1871,10 +1869,10 @@
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" hidden="1">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1907,7 +1905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.25">
+    <row r="6" spans="1:11" ht="26.25" hidden="1">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -1940,7 +1938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" ht="30" hidden="1">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -1954,7 +1952,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="5">
@@ -1966,86 +1964,82 @@
       <c r="I7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="6"/>
+      <c r="J7" s="19" t="s">
+        <v>330</v>
+      </c>
       <c r="K7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="13">
-        <v>7</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>11</v>
-      </c>
+    <row r="8" spans="1:11" ht="26.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="15" t="s">
-        <v>60</v>
+        <v>378</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="5">
         <v>16</v>
       </c>
-      <c r="H8" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="6"/>
       <c r="K8" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="26.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" hidden="1">
       <c r="A9" s="13">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>11</v>
+      </c>
       <c r="C9" s="15" t="s">
-        <v>298</v>
+        <v>60</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+        <v>297</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="26.25">
+    <row r="10" spans="1:11" ht="26.25" hidden="1">
       <c r="A10" s="13">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>18</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B10" s="17"/>
       <c r="C10" s="15" t="s">
-        <v>61</v>
+        <v>297</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>59</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F10" s="16"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -2054,9 +2048,9 @@
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="26.25">
+    <row r="11" spans="1:11" ht="26.25" hidden="1">
       <c r="A11" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>18</v>
@@ -2068,7 +2062,7 @@
         <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>59</v>
@@ -2081,48 +2075,48 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="26.25">
+    <row r="12" spans="1:11" ht="26.25" hidden="1">
       <c r="A12" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
       <c r="K12" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="26.25" hidden="1">
       <c r="A13" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>299</v>
+        <v>62</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>109</v>
+        <v>298</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>62</v>
@@ -2132,24 +2126,24 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="26.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" hidden="1">
       <c r="A14" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>62</v>
@@ -2157,26 +2151,26 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="18"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="26.25" hidden="1">
       <c r="A15" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>63</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>300</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>62</v>
@@ -2184,55 +2178,55 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="18" t="s">
-        <v>289</v>
-      </c>
+      <c r="J15" s="18"/>
       <c r="K15" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" ht="30" hidden="1">
       <c r="A16" s="13">
-        <v>15</v>
-      </c>
-      <c r="B16" s="17"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>11</v>
+      </c>
       <c r="C16" s="15" t="s">
-        <v>300</v>
+        <v>63</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="F16" s="16"/>
+        <v>299</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="18" t="s">
+        <v>289</v>
+      </c>
       <c r="K16" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="13">
-        <v>16</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B17" s="17"/>
       <c r="C17" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>62</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="F17" s="16"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2241,21 +2235,21 @@
         <v>294</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" hidden="1">
       <c r="A18" s="13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>62</v>
@@ -2268,53 +2262,51 @@
         <v>294</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="30">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" s="13">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>57</v>
-      </c>
       <c r="C19" s="15" t="s">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="18" t="s">
-        <v>289</v>
-      </c>
+      <c r="J19" s="6"/>
       <c r="K19" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="30">
+    <row r="20" spans="1:11" ht="30" hidden="1">
       <c r="A20" s="13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -2326,15 +2318,15 @@
         <v>294</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="30" hidden="1">
       <c r="A21" s="13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>159</v>
@@ -2343,46 +2335,48 @@
         <v>75</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="6" t="s">
-        <v>290</v>
+      <c r="J21" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" s="13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="F22" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>67</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="19" t="s">
-        <v>332</v>
+      <c r="J22" s="6" t="s">
+        <v>290</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="26.25">
+    <row r="23" spans="1:11" ht="26.25" hidden="1">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -2396,7 +2390,7 @@
         <v>159</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>62</v>
@@ -2411,7 +2405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="25.5">
+    <row r="24" spans="1:11" ht="25.5" hidden="1">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -2425,7 +2419,7 @@
         <v>162</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>262</v>
@@ -2435,16 +2429,16 @@
       <c r="I24" s="5"/>
       <c r="J24" s="22"/>
       <c r="K24" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="25.5">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="25.5" hidden="1">
       <c r="A25" s="13">
         <v>24</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>159</v>
@@ -2461,7 +2455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -2486,19 +2480,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="25.5">
+    <row r="27" spans="1:11" ht="25.5" hidden="1">
       <c r="A27" s="13">
         <v>26</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="5"/>
@@ -2509,13 +2503,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" hidden="1">
       <c r="A28" s="13">
         <v>27</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>159</v>
@@ -2532,7 +2526,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" hidden="1">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -2557,13 +2551,13 @@
         <v>294</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" hidden="1">
       <c r="A30" s="13">
         <v>29</v>
       </c>
       <c r="B30" s="23"/>
       <c r="C30" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>159</v>
@@ -2580,7 +2574,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" hidden="1">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -2605,7 +2599,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="30">
+    <row r="32" spans="1:11" ht="30" hidden="1">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -2634,7 +2628,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="30">
+    <row r="33" spans="1:11" ht="30" hidden="1">
       <c r="A33" s="13">
         <v>32</v>
       </c>
@@ -2663,7 +2657,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="30">
+    <row r="34" spans="1:11" ht="30" hidden="1">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -2692,7 +2686,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="26.25">
+    <row r="35" spans="1:11" ht="26.25" hidden="1">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -2706,7 +2700,7 @@
         <v>159</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>265</v>
@@ -2719,7 +2713,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="26.25">
+    <row r="36" spans="1:11" ht="26.25" hidden="1">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -2733,7 +2727,7 @@
         <v>159</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>265</v>
@@ -2746,7 +2740,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="26.25">
+    <row r="37" spans="1:11" ht="26.25" hidden="1">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -2760,7 +2754,7 @@
         <v>159</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>265</v>
@@ -2773,7 +2767,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="26.25">
+    <row r="38" spans="1:11" ht="26.25" hidden="1">
       <c r="A38" s="13">
         <v>37</v>
       </c>
@@ -2787,7 +2781,7 @@
         <v>159</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>265</v>
@@ -2800,7 +2794,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="26.25">
+    <row r="39" spans="1:11" ht="26.25" hidden="1">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -2814,7 +2808,7 @@
         <v>159</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>265</v>
@@ -2827,7 +2821,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="26.25">
+    <row r="40" spans="1:11" ht="26.25" hidden="1">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -2841,7 +2835,7 @@
         <v>159</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>265</v>
@@ -2854,7 +2848,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="26.25">
+    <row r="41" spans="1:11" ht="26.25" hidden="1">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -2868,7 +2862,7 @@
         <v>159</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>265</v>
@@ -2881,7 +2875,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="26.25">
+    <row r="42" spans="1:11" ht="26.25" hidden="1">
       <c r="A42" s="13">
         <v>41</v>
       </c>
@@ -2895,7 +2889,7 @@
         <v>159</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>265</v>
@@ -2908,7 +2902,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="26.25">
+    <row r="43" spans="1:11" ht="26.25" hidden="1">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -2922,7 +2916,7 @@
         <v>159</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F43" s="24" t="s">
         <v>266</v>
@@ -2935,7 +2929,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="26.25">
+    <row r="44" spans="1:11" ht="26.25" hidden="1">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -2949,7 +2943,7 @@
         <v>159</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F44" s="24" t="s">
         <v>266</v>
@@ -2962,7 +2956,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="26.25">
+    <row r="45" spans="1:11" ht="26.25" hidden="1">
       <c r="A45" s="13">
         <v>44</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>159</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F45" s="24" t="s">
         <v>266</v>
@@ -2989,7 +2983,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="51.75">
+    <row r="46" spans="1:11" ht="51.75" hidden="1">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -3016,7 +3010,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="26.25">
+    <row r="47" spans="1:11" ht="26.25" hidden="1">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -3030,7 +3024,7 @@
         <v>159</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>266</v>
@@ -3043,7 +3037,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="26.25">
+    <row r="48" spans="1:11" ht="26.25" hidden="1">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -3057,7 +3051,7 @@
         <v>159</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>266</v>
@@ -3070,7 +3064,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="26.25">
+    <row r="49" spans="1:11" ht="26.25" hidden="1">
       <c r="A49" s="13">
         <v>48</v>
       </c>
@@ -3084,7 +3078,7 @@
         <v>159</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>266</v>
@@ -3097,7 +3091,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="26.25">
+    <row r="50" spans="1:11" ht="26.25" hidden="1">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -3111,7 +3105,7 @@
         <v>159</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>266</v>
@@ -3124,7 +3118,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="26.25">
+    <row r="51" spans="1:11" ht="26.25" hidden="1">
       <c r="A51" s="13">
         <v>50</v>
       </c>
@@ -3138,7 +3132,7 @@
         <v>159</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>266</v>
@@ -3151,7 +3145,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="26.25">
+    <row r="52" spans="1:11" ht="26.25" hidden="1">
       <c r="A52" s="13">
         <v>51</v>
       </c>
@@ -3165,7 +3159,7 @@
         <v>159</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>266</v>
@@ -3178,7 +3172,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="26.25">
+    <row r="53" spans="1:11" ht="26.25" hidden="1">
       <c r="A53" s="13">
         <v>52</v>
       </c>
@@ -3192,7 +3186,7 @@
         <v>159</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>266</v>
@@ -3205,7 +3199,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="26.25">
+    <row r="54" spans="1:11" ht="26.25" hidden="1">
       <c r="A54" s="13">
         <v>53</v>
       </c>
@@ -3219,7 +3213,7 @@
         <v>159</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>266</v>
@@ -3232,7 +3226,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="26.25">
+    <row r="55" spans="1:11" ht="26.25" hidden="1">
       <c r="A55" s="13">
         <v>54</v>
       </c>
@@ -3246,7 +3240,7 @@
         <v>159</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>266</v>
@@ -3259,7 +3253,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="26.25">
+    <row r="56" spans="1:11" ht="26.25" hidden="1">
       <c r="A56" s="13">
         <v>55</v>
       </c>
@@ -3273,7 +3267,7 @@
         <v>159</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>266</v>
@@ -3286,7 +3280,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="26.25">
+    <row r="57" spans="1:11" ht="26.25" hidden="1">
       <c r="A57" s="13">
         <v>56</v>
       </c>
@@ -3315,7 +3309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" hidden="1">
       <c r="A58" s="13">
         <v>57</v>
       </c>
@@ -3344,7 +3338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" hidden="1">
       <c r="A59" s="13">
         <v>58</v>
       </c>
@@ -3373,7 +3367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="13">
         <v>59</v>
       </c>
@@ -3402,7 +3396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" hidden="1">
       <c r="A61" s="13">
         <v>60</v>
       </c>
@@ -3431,7 +3425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" hidden="1">
       <c r="A62" s="13">
         <v>61</v>
       </c>
@@ -3460,7 +3454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="13">
         <v>62</v>
       </c>
@@ -3489,7 +3483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" hidden="1">
       <c r="A64" s="13">
         <v>63</v>
       </c>
@@ -3518,7 +3512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" hidden="1">
       <c r="A65" s="13">
         <v>64</v>
       </c>
@@ -3547,7 +3541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" hidden="1">
       <c r="A66" s="13">
         <v>65</v>
       </c>
@@ -3576,7 +3570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" hidden="1">
       <c r="A67" s="13">
         <v>66</v>
       </c>
@@ -3605,7 +3599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -3634,7 +3628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" s="13">
         <v>68</v>
       </c>
@@ -3663,7 +3657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" s="13">
         <v>69</v>
       </c>
@@ -3692,7 +3686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -3721,7 +3715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="13">
         <v>71</v>
       </c>
@@ -3750,7 +3744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="13">
         <v>72</v>
       </c>
@@ -3779,7 +3773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="13">
         <v>73</v>
       </c>
@@ -3808,7 +3802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="13">
         <v>74</v>
       </c>
@@ -3837,7 +3831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="13">
         <v>75</v>
       </c>
@@ -3866,7 +3860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" hidden="1">
       <c r="A77" s="13">
         <v>76</v>
       </c>
@@ -3895,7 +3889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="26.25">
+    <row r="78" spans="1:11" ht="26.25" hidden="1">
       <c r="A78" s="13">
         <v>77</v>
       </c>
@@ -3924,7 +3918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="26.25">
+    <row r="79" spans="1:11" ht="26.25" hidden="1">
       <c r="A79" s="13">
         <v>78</v>
       </c>
@@ -3951,7 +3945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" hidden="1">
       <c r="A80" s="13">
         <v>79</v>
       </c>
@@ -3978,7 +3972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="64.5">
+    <row r="81" spans="1:11" ht="64.5" hidden="1">
       <c r="A81" s="13">
         <v>80</v>
       </c>
@@ -3986,7 +3980,7 @@
         <v>57</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>164</v>
@@ -4005,7 +3999,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" hidden="1">
       <c r="A82" s="13">
         <v>81</v>
       </c>
@@ -4032,7 +4026,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="13">
         <v>82</v>
       </c>
@@ -4059,7 +4053,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="13">
         <v>83</v>
       </c>
@@ -4086,7 +4080,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" s="13">
         <v>84</v>
       </c>
@@ -4113,7 +4107,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" s="13">
         <v>85</v>
       </c>
@@ -4142,7 +4136,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" s="13">
         <v>86</v>
       </c>
@@ -4171,7 +4165,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="26.25">
+    <row r="88" spans="1:11" ht="26.25" hidden="1">
       <c r="A88" s="13">
         <v>87</v>
       </c>
@@ -4198,7 +4192,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="26.25">
+    <row r="89" spans="1:11" ht="26.25" hidden="1">
       <c r="A89" s="13">
         <v>88</v>
       </c>
@@ -4225,7 +4219,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="26.25">
+    <row r="90" spans="1:11" ht="26.25" hidden="1">
       <c r="A90" s="13">
         <v>89</v>
       </c>
@@ -4252,7 +4246,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="26.25">
+    <row r="91" spans="1:11" ht="26.25" hidden="1">
       <c r="A91" s="13">
         <v>90</v>
       </c>
@@ -4279,7 +4273,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="26.25">
+    <row r="92" spans="1:11" ht="26.25" hidden="1">
       <c r="A92" s="13">
         <v>91</v>
       </c>
@@ -4306,7 +4300,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="26.25">
+    <row r="93" spans="1:11" ht="26.25" hidden="1">
       <c r="A93" s="13">
         <v>92</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="26.25">
+    <row r="94" spans="1:11" ht="26.25" hidden="1">
       <c r="A94" s="13">
         <v>93</v>
       </c>
@@ -4360,7 +4354,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="26.25">
+    <row r="95" spans="1:11" ht="26.25" hidden="1">
       <c r="A95" s="13">
         <v>94</v>
       </c>
@@ -4387,7 +4381,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="26.25">
+    <row r="96" spans="1:11" ht="26.25" hidden="1">
       <c r="A96" s="13">
         <v>95</v>
       </c>
@@ -4414,7 +4408,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="26.25">
+    <row r="97" spans="1:11" ht="26.25" hidden="1">
       <c r="A97" s="13">
         <v>96</v>
       </c>
@@ -4441,7 +4435,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="26.25">
+    <row r="98" spans="1:11" ht="26.25" hidden="1">
       <c r="A98" s="13">
         <v>97</v>
       </c>
@@ -4468,7 +4462,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="26.25">
+    <row r="99" spans="1:11" ht="26.25" hidden="1">
       <c r="A99" s="13">
         <v>98</v>
       </c>
@@ -4495,7 +4489,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="26.25">
+    <row r="100" spans="1:11" ht="26.25" hidden="1">
       <c r="A100" s="13">
         <v>99</v>
       </c>
@@ -4522,7 +4516,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="26.25">
+    <row r="101" spans="1:11" ht="26.25" hidden="1">
       <c r="A101" s="13">
         <v>100</v>
       </c>
@@ -4549,7 +4543,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="26.25">
+    <row r="102" spans="1:11" ht="26.25" hidden="1">
       <c r="A102" s="13">
         <v>101</v>
       </c>
@@ -4576,7 +4570,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="26.25">
+    <row r="103" spans="1:11" ht="26.25" hidden="1">
       <c r="A103" s="13">
         <v>102</v>
       </c>
@@ -4603,7 +4597,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="26.25">
+    <row r="104" spans="1:11" ht="26.25" hidden="1">
       <c r="A104" s="13">
         <v>103</v>
       </c>
@@ -4630,7 +4624,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="26.25">
+    <row r="105" spans="1:11" ht="26.25" hidden="1">
       <c r="A105" s="13">
         <v>104</v>
       </c>
@@ -4657,7 +4651,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="26.25">
+    <row r="106" spans="1:11" ht="26.25" hidden="1">
       <c r="A106" s="13">
         <v>105</v>
       </c>
@@ -4684,7 +4678,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="26.25">
+    <row r="107" spans="1:11" ht="26.25" hidden="1">
       <c r="A107" s="13">
         <v>106</v>
       </c>
@@ -4711,7 +4705,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="26.25">
+    <row r="108" spans="1:11" ht="26.25" hidden="1">
       <c r="A108" s="13">
         <v>107</v>
       </c>
@@ -4738,7 +4732,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="26.25">
+    <row r="109" spans="1:11" ht="26.25" hidden="1">
       <c r="A109" s="13">
         <v>108</v>
       </c>
@@ -4765,7 +4759,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="26.25">
+    <row r="110" spans="1:11" ht="26.25" hidden="1">
       <c r="A110" s="13">
         <v>109</v>
       </c>
@@ -4792,7 +4786,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="26.25">
+    <row r="111" spans="1:11" ht="26.25" hidden="1">
       <c r="A111" s="13">
         <v>110</v>
       </c>
@@ -4819,7 +4813,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="26.25">
+    <row r="112" spans="1:11" ht="26.25" hidden="1">
       <c r="A112" s="13">
         <v>111</v>
       </c>
@@ -4846,7 +4840,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="26.25">
+    <row r="113" spans="1:11" ht="26.25" hidden="1">
       <c r="A113" s="13">
         <v>112</v>
       </c>
@@ -4873,7 +4867,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="26.25">
+    <row r="114" spans="1:11" ht="26.25" hidden="1">
       <c r="A114" s="13">
         <v>113</v>
       </c>
@@ -4900,7 +4894,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="26.25">
+    <row r="115" spans="1:11" ht="26.25" hidden="1">
       <c r="A115" s="13">
         <v>114</v>
       </c>
@@ -4927,7 +4921,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="26.25">
+    <row r="116" spans="1:11" ht="26.25" hidden="1">
       <c r="A116" s="13">
         <v>115</v>
       </c>
@@ -4954,7 +4948,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="26.25">
+    <row r="117" spans="1:11" ht="26.25" hidden="1">
       <c r="A117" s="13">
         <v>116</v>
       </c>
@@ -4981,7 +4975,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="26.25">
+    <row r="118" spans="1:11" ht="26.25" hidden="1">
       <c r="A118" s="13">
         <v>117</v>
       </c>
@@ -5008,7 +5002,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="26.25">
+    <row r="119" spans="1:11" ht="26.25" hidden="1">
       <c r="A119" s="13">
         <v>118</v>
       </c>
@@ -5035,7 +5029,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="39">
+    <row r="120" spans="1:11" ht="39" hidden="1">
       <c r="A120" s="13">
         <v>119</v>
       </c>
@@ -5062,7 +5056,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" s="13">
         <v>120</v>
       </c>
@@ -5085,7 +5079,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="64.5">
+    <row r="122" spans="1:11" ht="64.5" hidden="1">
       <c r="A122" s="13">
         <v>121</v>
       </c>
@@ -5112,7 +5106,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="64.5">
+    <row r="123" spans="1:11" ht="64.5" hidden="1">
       <c r="A123" s="13">
         <v>122</v>
       </c>
@@ -5139,7 +5133,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="51.75">
+    <row r="124" spans="1:11" ht="51.75" hidden="1">
       <c r="A124" s="13">
         <v>123</v>
       </c>
@@ -5166,7 +5160,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="39">
+    <row r="125" spans="1:11" ht="39" hidden="1">
       <c r="A125" s="13">
         <v>124</v>
       </c>
@@ -5193,7 +5187,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" hidden="1">
       <c r="A126" s="13">
         <v>125</v>
       </c>
@@ -5216,7 +5210,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="26.25">
+    <row r="127" spans="1:11" ht="26.25" hidden="1">
       <c r="A127" s="13">
         <v>126</v>
       </c>
@@ -5243,7 +5237,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="26.25">
+    <row r="128" spans="1:11" ht="26.25" hidden="1">
       <c r="A128" s="13">
         <v>127</v>
       </c>
@@ -5270,7 +5264,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="26.25">
+    <row r="129" spans="1:11" ht="26.25" hidden="1">
       <c r="A129" s="13">
         <v>128</v>
       </c>
@@ -5297,7 +5291,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" hidden="1">
       <c r="A130" s="13">
         <v>129</v>
       </c>
@@ -5320,7 +5314,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="26.25">
+    <row r="131" spans="1:11" ht="26.25" hidden="1">
       <c r="A131" s="13">
         <v>130</v>
       </c>
@@ -5345,7 +5339,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" hidden="1">
       <c r="A132" s="13">
         <v>132</v>
       </c>
@@ -5372,7 +5366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" hidden="1">
       <c r="A133" s="13">
         <v>133</v>
       </c>
@@ -5399,7 +5393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="39">
+    <row r="134" spans="1:11" ht="39" hidden="1">
       <c r="A134" s="13">
         <v>134</v>
       </c>
@@ -5426,7 +5420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="26.25">
+    <row r="135" spans="1:11" ht="26.25" hidden="1">
       <c r="A135" s="13">
         <v>135</v>
       </c>
@@ -5447,7 +5441,7 @@
       <c r="J135" s="18"/>
       <c r="K135" s="5"/>
     </row>
-    <row r="136" spans="1:11" ht="26.25">
+    <row r="136" spans="1:11" ht="26.25" hidden="1">
       <c r="A136" s="13">
         <v>136</v>
       </c>
@@ -5472,7 +5466,7 @@
       <c r="J136" s="18"/>
       <c r="K136" s="5"/>
     </row>
-    <row r="137" spans="1:11" ht="26.25">
+    <row r="137" spans="1:11" ht="26.25" hidden="1">
       <c r="A137" s="13">
         <v>137</v>
       </c>
@@ -5497,7 +5491,7 @@
       <c r="J137" s="18"/>
       <c r="K137" s="5"/>
     </row>
-    <row r="138" spans="1:11" ht="26.25">
+    <row r="138" spans="1:11" ht="26.25" hidden="1">
       <c r="A138" s="13">
         <v>138</v>
       </c>
@@ -5522,7 +5516,7 @@
       <c r="J138" s="18"/>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="1:11" ht="26.25">
+    <row r="139" spans="1:11" ht="26.25" hidden="1">
       <c r="A139" s="13">
         <v>139</v>
       </c>
@@ -5547,7 +5541,7 @@
       <c r="J139" s="18"/>
       <c r="K139" s="5"/>
     </row>
-    <row r="140" spans="1:11" ht="26.25">
+    <row r="140" spans="1:11" ht="26.25" hidden="1">
       <c r="A140" s="13">
         <v>140</v>
       </c>
@@ -5572,7 +5566,7 @@
       <c r="J140" s="18"/>
       <c r="K140" s="5"/>
     </row>
-    <row r="141" spans="1:11" ht="26.25">
+    <row r="141" spans="1:11" ht="26.25" hidden="1">
       <c r="A141" s="13">
         <v>141</v>
       </c>
@@ -5597,7 +5591,7 @@
       <c r="J141" s="18"/>
       <c r="K141" s="5"/>
     </row>
-    <row r="142" spans="1:11" ht="26.25">
+    <row r="142" spans="1:11" ht="26.25" hidden="1">
       <c r="A142" s="13">
         <v>142</v>
       </c>
@@ -5622,7 +5616,7 @@
       <c r="J142" s="18"/>
       <c r="K142" s="5"/>
     </row>
-    <row r="143" spans="1:11" ht="26.25">
+    <row r="143" spans="1:11" ht="26.25" hidden="1">
       <c r="A143" s="13">
         <v>143</v>
       </c>
@@ -5647,7 +5641,7 @@
       <c r="J143" s="18"/>
       <c r="K143" s="5"/>
     </row>
-    <row r="144" spans="1:11" ht="26.25">
+    <row r="144" spans="1:11" ht="26.25" hidden="1">
       <c r="A144" s="13">
         <v>144</v>
       </c>
@@ -5672,7 +5666,7 @@
       <c r="J144" s="18"/>
       <c r="K144" s="5"/>
     </row>
-    <row r="145" spans="1:11" ht="26.25">
+    <row r="145" spans="1:11" ht="26.25" hidden="1">
       <c r="A145" s="13">
         <v>145</v>
       </c>
@@ -5697,7 +5691,7 @@
       <c r="J145" s="18"/>
       <c r="K145" s="5"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" hidden="1">
       <c r="A146" s="13">
         <v>146</v>
       </c>
@@ -5720,7 +5714,7 @@
       <c r="J146" s="18"/>
       <c r="K146" s="5"/>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147" s="13">
         <v>147</v>
       </c>
@@ -5743,7 +5737,7 @@
       <c r="J147" s="18"/>
       <c r="K147" s="5"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" hidden="1">
       <c r="A148" s="13">
         <v>148</v>
       </c>
@@ -5766,7 +5760,7 @@
       <c r="J148" s="18"/>
       <c r="K148" s="5"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="13">
         <v>149</v>
       </c>
@@ -5789,7 +5783,7 @@
       <c r="J149" s="18"/>
       <c r="K149" s="5"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" hidden="1">
       <c r="A150" s="13">
         <v>150</v>
       </c>
@@ -5812,7 +5806,7 @@
       <c r="J150" s="18"/>
       <c r="K150" s="5"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" hidden="1">
       <c r="A151" s="13">
         <v>151</v>
       </c>
@@ -5835,7 +5829,7 @@
       <c r="J151" s="18"/>
       <c r="K151" s="5"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152" s="13">
         <v>152</v>
       </c>
@@ -5858,7 +5852,7 @@
       <c r="J152" s="18"/>
       <c r="K152" s="5"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153" s="13">
         <v>153</v>
       </c>
@@ -5881,7 +5875,7 @@
       <c r="J153" s="18"/>
       <c r="K153" s="5"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154" s="13">
         <v>154</v>
       </c>
@@ -5904,7 +5898,7 @@
       <c r="J154" s="18"/>
       <c r="K154" s="5"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" hidden="1">
       <c r="A155" s="13">
         <v>155</v>
       </c>
@@ -5927,7 +5921,7 @@
       <c r="J155" s="18"/>
       <c r="K155" s="5"/>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156" s="13">
         <v>156</v>
       </c>
@@ -5950,7 +5944,7 @@
       <c r="J156" s="18"/>
       <c r="K156" s="5"/>
     </row>
-    <row r="157" spans="1:11" ht="26.25">
+    <row r="157" spans="1:11" ht="26.25" hidden="1">
       <c r="A157" s="13">
         <v>157</v>
       </c>
@@ -5975,7 +5969,7 @@
       <c r="J157" s="18"/>
       <c r="K157" s="5"/>
     </row>
-    <row r="158" spans="1:11" ht="26.25">
+    <row r="158" spans="1:11" ht="26.25" hidden="1">
       <c r="A158" s="13">
         <v>158</v>
       </c>
@@ -6000,7 +5994,7 @@
       <c r="J158" s="18"/>
       <c r="K158" s="5"/>
     </row>
-    <row r="159" spans="1:11" ht="26.25">
+    <row r="159" spans="1:11" ht="26.25" hidden="1">
       <c r="A159" s="13">
         <v>159</v>
       </c>
@@ -6025,7 +6019,7 @@
       <c r="J159" s="18"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="1:11" ht="26.25">
+    <row r="160" spans="1:11" ht="26.25" hidden="1">
       <c r="A160" s="13">
         <v>160</v>
       </c>
@@ -6050,7 +6044,7 @@
       <c r="J160" s="18"/>
       <c r="K160" s="5"/>
     </row>
-    <row r="161" spans="1:11" ht="26.25">
+    <row r="161" spans="1:11" ht="26.25" hidden="1">
       <c r="A161" s="13">
         <v>161</v>
       </c>
@@ -6075,7 +6069,7 @@
       <c r="J161" s="18"/>
       <c r="K161" s="5"/>
     </row>
-    <row r="162" spans="1:11" ht="26.25">
+    <row r="162" spans="1:11" ht="26.25" hidden="1">
       <c r="A162" s="13">
         <v>162</v>
       </c>
@@ -6100,7 +6094,7 @@
       <c r="J162" s="18"/>
       <c r="K162" s="5"/>
     </row>
-    <row r="163" spans="1:11" ht="26.25">
+    <row r="163" spans="1:11" ht="26.25" hidden="1">
       <c r="A163" s="13">
         <v>163</v>
       </c>
@@ -6125,7 +6119,7 @@
       <c r="J163" s="18"/>
       <c r="K163" s="5"/>
     </row>
-    <row r="164" spans="1:11" ht="26.25">
+    <row r="164" spans="1:11" ht="26.25" hidden="1">
       <c r="A164" s="13">
         <v>164</v>
       </c>
@@ -6150,7 +6144,7 @@
       <c r="J164" s="18"/>
       <c r="K164" s="5"/>
     </row>
-    <row r="165" spans="1:11" ht="26.25">
+    <row r="165" spans="1:11" ht="26.25" hidden="1">
       <c r="A165" s="13">
         <v>165</v>
       </c>
@@ -6175,7 +6169,7 @@
       <c r="J165" s="18"/>
       <c r="K165" s="5"/>
     </row>
-    <row r="166" spans="1:11" ht="26.25">
+    <row r="166" spans="1:11" ht="26.25" hidden="1">
       <c r="A166" s="13">
         <v>166</v>
       </c>
@@ -6200,7 +6194,7 @@
       <c r="J166" s="18"/>
       <c r="K166" s="5"/>
     </row>
-    <row r="167" spans="1:11" ht="26.25">
+    <row r="167" spans="1:11" ht="26.25" hidden="1">
       <c r="A167" s="13">
         <v>167</v>
       </c>
@@ -6225,7 +6219,7 @@
       <c r="J167" s="18"/>
       <c r="K167" s="5"/>
     </row>
-    <row r="168" spans="1:11" ht="39">
+    <row r="168" spans="1:11" ht="39" hidden="1">
       <c r="A168" s="13">
         <v>168</v>
       </c>
@@ -6252,7 +6246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="26.25">
+    <row r="169" spans="1:11" ht="26.25" hidden="1">
       <c r="A169" s="13">
         <v>169</v>
       </c>
@@ -6279,7 +6273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" s="13">
         <v>170</v>
       </c>
@@ -6291,7 +6285,7 @@
       </c>
       <c r="D170" s="25"/>
       <c r="E170" s="26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>138</v>
@@ -6304,7 +6298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" s="13">
         <v>171</v>
       </c>
@@ -6316,7 +6310,7 @@
       </c>
       <c r="D171" s="25"/>
       <c r="E171" s="26" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>139</v>
@@ -6329,7 +6323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="26.25">
+    <row r="172" spans="1:11" ht="26.25" hidden="1">
       <c r="A172" s="13">
         <v>172</v>
       </c>
@@ -6356,7 +6350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="26.25">
+    <row r="173" spans="1:11" ht="26.25" hidden="1">
       <c r="A173" s="13">
         <v>173</v>
       </c>
@@ -6383,7 +6377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="26.25">
+    <row r="174" spans="1:11" ht="26.25" hidden="1">
       <c r="A174" s="13">
         <v>174</v>
       </c>
@@ -6410,7 +6404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="39">
+    <row r="175" spans="1:11" ht="39" hidden="1">
       <c r="A175" s="13">
         <v>175</v>
       </c>
@@ -6437,7 +6431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" s="13">
         <v>176</v>
       </c>
@@ -6464,7 +6458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="26.25">
+    <row r="177" spans="1:11" ht="26.25" hidden="1">
       <c r="A177" s="13">
         <v>177</v>
       </c>
@@ -6491,7 +6485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="39">
+    <row r="178" spans="1:11" ht="39" hidden="1">
       <c r="A178" s="13">
         <v>178</v>
       </c>
@@ -6518,7 +6512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="26.25">
+    <row r="179" spans="1:11" ht="26.25" hidden="1">
       <c r="A179" s="13">
         <v>179</v>
       </c>
@@ -6545,7 +6539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" s="13">
         <v>180</v>
       </c>
@@ -6557,7 +6551,7 @@
       </c>
       <c r="D180" s="25"/>
       <c r="E180" s="26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>148</v>
@@ -6570,7 +6564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" s="13">
         <v>181</v>
       </c>
@@ -6582,7 +6576,7 @@
       </c>
       <c r="D181" s="25"/>
       <c r="E181" s="26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>149</v>
@@ -6595,7 +6589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" s="13">
         <v>182</v>
       </c>
@@ -6622,7 +6616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="26.25">
+    <row r="183" spans="1:11" ht="26.25" hidden="1">
       <c r="A183" s="13">
         <v>183</v>
       </c>
@@ -6649,7 +6643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="26.25">
+    <row r="184" spans="1:11" ht="26.25" hidden="1">
       <c r="A184" s="13">
         <v>184</v>
       </c>
@@ -6676,7 +6670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="39">
+    <row r="185" spans="1:11" ht="39" hidden="1">
       <c r="A185" s="13">
         <v>185</v>
       </c>
@@ -6703,7 +6697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="26.25">
+    <row r="186" spans="1:11" ht="26.25" hidden="1">
       <c r="A186" s="13">
         <v>186</v>
       </c>
@@ -6730,7 +6724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" s="13">
         <v>187</v>
       </c>
@@ -6757,7 +6751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" s="13">
         <v>188</v>
       </c>
@@ -6765,13 +6759,13 @@
         <v>11</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F188" s="11"/>
       <c r="G188" s="5">
@@ -6784,7 +6778,7 @@
       <c r="J188" s="8"/>
       <c r="K188" s="5"/>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" s="13">
         <v>189</v>
       </c>
@@ -6792,13 +6786,13 @@
         <v>11</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F189" s="8"/>
       <c r="G189" s="5">
@@ -6813,7 +6807,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" s="13">
         <v>190</v>
       </c>
@@ -6821,13 +6815,13 @@
         <v>11</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="5">
@@ -6842,7 +6836,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" s="13">
         <v>191</v>
       </c>
@@ -6850,13 +6844,13 @@
         <v>11</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F191" s="8"/>
       <c r="G191" s="5">
@@ -6871,7 +6865,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" s="13">
         <v>192</v>
       </c>
@@ -6879,13 +6873,13 @@
         <v>11</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="5">
@@ -6900,7 +6894,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" hidden="1">
       <c r="A193" s="13">
         <v>193</v>
       </c>
@@ -6908,13 +6902,13 @@
         <v>11</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F193" s="8"/>
       <c r="G193" s="5">
@@ -6929,7 +6923,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" hidden="1">
       <c r="A194" s="13">
         <v>194</v>
       </c>
@@ -6937,13 +6931,13 @@
         <v>11</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="5">
@@ -6958,7 +6952,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" hidden="1">
       <c r="A195" s="13">
         <v>195</v>
       </c>
@@ -6966,13 +6960,13 @@
         <v>11</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="5">
@@ -6987,7 +6981,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" hidden="1">
       <c r="A196" s="13">
         <v>196</v>
       </c>
@@ -6995,13 +6989,13 @@
         <v>11</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="5">
@@ -7016,7 +7010,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" hidden="1">
       <c r="A197" s="13">
         <v>197</v>
       </c>
@@ -7024,13 +7018,13 @@
         <v>11</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="5">
@@ -7045,7 +7039,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" hidden="1">
       <c r="A198" s="13">
         <v>199</v>
       </c>
@@ -7053,13 +7047,13 @@
         <v>11</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="5">
@@ -7074,7 +7068,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" hidden="1">
       <c r="A199" s="13">
         <v>200</v>
       </c>
@@ -7082,13 +7076,13 @@
         <v>11</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F199" s="8"/>
       <c r="G199" s="5">
@@ -7103,7 +7097,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" hidden="1">
       <c r="A200" s="13">
         <v>201</v>
       </c>
@@ -7111,13 +7105,13 @@
         <v>11</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="5">
@@ -7132,7 +7126,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" hidden="1">
       <c r="A201" s="13">
         <v>202</v>
       </c>
@@ -7140,13 +7134,13 @@
         <v>11</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="5">
@@ -7161,7 +7155,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" hidden="1">
       <c r="A202" s="13">
         <v>203</v>
       </c>
@@ -7169,13 +7163,13 @@
         <v>11</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="5">
@@ -7190,7 +7184,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" hidden="1">
       <c r="A203" s="13">
         <v>204</v>
       </c>
@@ -7198,13 +7192,13 @@
         <v>11</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F203" s="8"/>
       <c r="G203" s="5">
@@ -7219,7 +7213,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" hidden="1">
       <c r="A204" s="13">
         <v>205</v>
       </c>
@@ -7227,13 +7221,13 @@
         <v>11</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F204" s="8"/>
       <c r="G204" s="5">
@@ -7248,7 +7242,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" hidden="1">
       <c r="A205" s="13">
         <v>206</v>
       </c>
@@ -7256,13 +7250,13 @@
         <v>11</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F205" s="8"/>
       <c r="G205" s="5">
@@ -7277,7 +7271,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" hidden="1">
       <c r="A206" s="13">
         <v>207</v>
       </c>
@@ -7285,13 +7279,13 @@
         <v>11</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="5">
@@ -7306,7 +7300,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" hidden="1">
       <c r="A207" s="13">
         <v>208</v>
       </c>
@@ -7314,13 +7308,13 @@
         <v>11</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D207" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F207" s="8"/>
       <c r="G207" s="5">
@@ -13544,11 +13538,17 @@
       <c r="J983" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Учет Pi 1 с.ш. ГРЩ1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1 G1:I8 K1:K2 K4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1 G9:I9 K1:K2 G1:I7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13571,30 +13571,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>290</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E2" s="4">
         <v>0.5</v>
@@ -13602,16 +13602,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E3" s="4">
         <v>0.3</v>
@@ -13637,104 +13637,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -13756,104 +13756,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/upload/input.xlsx
+++ b/upload/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ACD2A2-439E-4B4B-8644-0147C88EB27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD33E5F-F0B2-4E1D-8A21-1FB45336B2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Instructions" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$K$224</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="399">
   <si>
     <t>id</t>
   </si>
@@ -772,9 +772,6 @@
     <t>QF1 ВРУ Автопарковка</t>
   </si>
   <si>
-    <t>QF1 ЩР-ЗУ Электрозарядные</t>
-  </si>
-  <si>
     <t>QF1 ВРУ Супермаркет</t>
   </si>
   <si>
@@ -1169,6 +1166,69 @@
   </si>
   <si>
     <t>Учет Pi 1 с.ш. ART-03 PQRS, 5(10)A 5000/5  ГРЩ1</t>
+  </si>
+  <si>
+    <t>ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QS ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>Учет PQS ART-03 PQRS 600/5А</t>
+  </si>
+  <si>
+    <t>QF ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>1 с.ш. ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF1 1 с.ш. ЗУ1 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF4 1 с.ш. ЗУ4 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF3 1 с.ш. ЗУ3 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF2 1 с.ш. ЗУ2 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>Будка охраны</t>
+  </si>
+  <si>
+    <t>QF5 1 с.ш. ЗУ5 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF6 1 с.ш. ЗУ6 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF7 1 с.ш. ЗУ7 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>QF8 1 с.ш. ЗУ8 ЩР-ЗУ</t>
+  </si>
+  <si>
+    <t>ЗУ1</t>
+  </si>
+  <si>
+    <t>ЗУ2</t>
+  </si>
+  <si>
+    <t>ЗУ3</t>
+  </si>
+  <si>
+    <t>ЗУ4</t>
+  </si>
+  <si>
+    <t>ШР-Будка охраны</t>
+  </si>
+  <si>
+    <t>QF1 ШР-Будка охраны</t>
+  </si>
+  <si>
+    <t>ППГнг(А)-HF-3х2,5 L=20</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1306,11 +1366,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1367,9 +1440,6 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1381,6 +1451,50 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1721,13 +1835,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K983"/>
+  <dimension ref="A1:K981"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
-    <col min="2" max="2" width="22" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="24" style="2" customWidth="1"/>
     <col min="5" max="5" width="35.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.875" style="2" customWidth="1"/>
@@ -1773,40 +1886,40 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1">
-      <c r="A2" s="13">
+    <row r="2" spans="1:11">
+      <c r="A2" s="26">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="29">
         <v>1000</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="30"/>
+      <c r="K2" s="29" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1">
+    <row r="3" spans="1:11">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1823,7 +1936,7 @@
         <v>62</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G3" s="5">
         <v>630</v>
@@ -1839,7 +1952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26.25" hidden="1">
+    <row r="4" spans="1:11" ht="26.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1853,7 +1966,7 @@
         <v>157</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>59</v>
@@ -1872,7 +1985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1">
+    <row r="5" spans="1:11">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1880,7 +1993,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>13</v>
@@ -1905,7 +2018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.25" hidden="1">
+    <row r="6" spans="1:11" ht="26.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -1913,7 +2026,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>158</v>
@@ -1938,7 +2051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30" hidden="1">
+    <row r="7" spans="1:11" ht="30">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -1952,7 +2065,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="5">
@@ -1965,7 +2078,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>17</v>
@@ -1975,7 +2088,7 @@
       <c r="A8" s="13"/>
       <c r="B8" s="14"/>
       <c r="C8" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>13</v>
@@ -1992,46 +2105,46 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1">
-      <c r="A9" s="13">
+    <row r="9" spans="1:11">
+      <c r="A9" s="26">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="F9" s="15" t="s">
+      <c r="E9" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="29">
         <v>16</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="29">
         <v>3.5</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="26.25" hidden="1">
+      <c r="J9" s="30"/>
+      <c r="K9" s="29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="26.25">
       <c r="A10" s="13">
         <v>8</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>159</v>
@@ -2045,10 +2158,10 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="26.25">
       <c r="A11" s="13">
         <v>9</v>
       </c>
@@ -2072,10 +2185,10 @@
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="26.25">
       <c r="A12" s="13">
         <v>10</v>
       </c>
@@ -2099,10 +2212,10 @@
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
       <c r="K12" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="26.25">
       <c r="A13" s="13">
         <v>11</v>
       </c>
@@ -2116,7 +2229,7 @@
         <v>160</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>62</v>
@@ -2129,7 +2242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1">
+    <row r="14" spans="1:11">
       <c r="A14" s="13">
         <v>12</v>
       </c>
@@ -2137,7 +2250,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>13</v>
@@ -2156,34 +2269,34 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="26.25" hidden="1">
-      <c r="A15" s="13">
+    <row r="15" spans="1:11" ht="26.25">
+      <c r="A15" s="26">
         <v>13</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" hidden="1">
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30">
       <c r="A16" s="13">
         <v>14</v>
       </c>
@@ -2197,7 +2310,7 @@
         <v>159</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>62</v>
@@ -2206,25 +2319,25 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="13">
         <v>15</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="5"/>
@@ -2232,10 +2345,10 @@
       <c r="I17" s="5"/>
       <c r="J17" s="6"/>
       <c r="K17" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="13">
         <v>16</v>
       </c>
@@ -2243,7 +2356,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>159</v>
@@ -2259,10 +2372,10 @@
       <c r="I18" s="5"/>
       <c r="J18" s="6"/>
       <c r="K18" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="13">
         <v>17</v>
       </c>
@@ -2270,7 +2383,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>159</v>
@@ -2286,10 +2399,10 @@
       <c r="I19" s="5"/>
       <c r="J19" s="6"/>
       <c r="K19" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30">
       <c r="A20" s="13">
         <v>18</v>
       </c>
@@ -2312,13 +2425,13 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30">
       <c r="A21" s="13">
         <v>19</v>
       </c>
@@ -2341,13 +2454,13 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="13">
         <v>20</v>
       </c>
@@ -2370,13 +2483,13 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="26.25" hidden="1">
+    <row r="23" spans="1:11" ht="26.25">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -2390,7 +2503,7 @@
         <v>159</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>62</v>
@@ -2399,46 +2512,46 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="25.5" hidden="1">
-      <c r="A24" s="13">
+    <row r="24" spans="1:11" ht="25.5">
+      <c r="A24" s="26">
         <v>23</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="25.5" hidden="1">
+      <c r="E24" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="29" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="25.5">
       <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="23"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>159</v>
@@ -2446,7 +2559,7 @@
       <c r="E25" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="F25" s="23"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -2455,7 +2568,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1">
+    <row r="26" spans="1:11">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -2471,7 +2584,7 @@
       <c r="E26" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="23"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -2480,21 +2593,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="25.5" hidden="1">
+    <row r="27" spans="1:11" ht="25.5">
       <c r="A27" s="13">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
+      <c r="B27" s="22"/>
       <c r="C27" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="F27" s="23"/>
+        <v>301</v>
+      </c>
+      <c r="F27" s="22"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -2503,30 +2616,30 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1">
-      <c r="A28" s="13">
+    <row r="28" spans="1:11">
+      <c r="A28" s="26">
         <v>27</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="D28" s="21" t="s">
+      <c r="B28" s="35"/>
+      <c r="C28" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="23"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" hidden="1">
+      <c r="F28" s="35"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -2542,22 +2655,22 @@
       <c r="E29" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="23"/>
+      <c r="F29" s="22"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="6"/>
       <c r="K29" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="13">
         <v>29</v>
       </c>
-      <c r="B30" s="23"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>159</v>
@@ -2565,16 +2678,16 @@
       <c r="E30" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="23"/>
+      <c r="F30" s="22"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="6"/>
       <c r="K30" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -2590,16 +2703,16 @@
       <c r="E31" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="23"/>
+      <c r="F31" s="22"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="6"/>
       <c r="K31" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="30" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -2616,19 +2729,19 @@
         <v>74</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="30" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="30">
       <c r="A33" s="13">
         <v>32</v>
       </c>
@@ -2645,19 +2758,19 @@
         <v>74</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="30" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -2674,19 +2787,19 @@
         <v>74</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="26.25">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -2700,20 +2813,20 @@
         <v>159</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6"/>
       <c r="K35" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="26.25">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -2727,20 +2840,20 @@
         <v>159</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
       <c r="K36" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="26.25">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -2754,20 +2867,20 @@
         <v>159</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
       <c r="K37" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="26.25">
       <c r="A38" s="13">
         <v>37</v>
       </c>
@@ -2781,20 +2894,20 @@
         <v>159</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="6"/>
       <c r="K38" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="26.25">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -2808,20 +2921,20 @@
         <v>159</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="6"/>
       <c r="K39" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="26.25">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -2835,20 +2948,20 @@
         <v>159</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="6"/>
       <c r="K40" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="26.25">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -2862,20 +2975,20 @@
         <v>159</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="6"/>
       <c r="K41" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="26.25">
       <c r="A42" s="13">
         <v>41</v>
       </c>
@@ -2889,20 +3002,20 @@
         <v>159</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="6"/>
       <c r="K42" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="26.25">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -2916,20 +3029,20 @@
         <v>159</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>266</v>
+        <v>334</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>265</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="6"/>
       <c r="K43" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="26.25">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -2943,20 +3056,20 @@
         <v>159</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>266</v>
+        <v>335</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>265</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="26.25">
       <c r="A45" s="13">
         <v>44</v>
       </c>
@@ -2970,20 +3083,20 @@
         <v>159</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>266</v>
+        <v>354</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>265</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="6"/>
       <c r="K45" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="51.75" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="51.75">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -3000,17 +3113,17 @@
         <v>79</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="6"/>
       <c r="K46" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="26.25">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -3024,20 +3137,20 @@
         <v>159</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="6"/>
       <c r="K47" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="26.25">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -3051,20 +3164,20 @@
         <v>159</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="6"/>
       <c r="K48" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="26.25">
       <c r="A49" s="13">
         <v>48</v>
       </c>
@@ -3078,20 +3191,20 @@
         <v>159</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="6"/>
       <c r="K49" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="26.25">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -3105,20 +3218,20 @@
         <v>159</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="6"/>
       <c r="K50" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="26.25">
       <c r="A51" s="13">
         <v>50</v>
       </c>
@@ -3132,20 +3245,20 @@
         <v>159</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="6"/>
       <c r="K51" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="26.25">
       <c r="A52" s="13">
         <v>51</v>
       </c>
@@ -3159,20 +3272,20 @@
         <v>159</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="6"/>
       <c r="K52" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="26.25">
       <c r="A53" s="13">
         <v>52</v>
       </c>
@@ -3186,20 +3299,20 @@
         <v>159</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="6"/>
       <c r="K53" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="26.25">
       <c r="A54" s="13">
         <v>53</v>
       </c>
@@ -3213,20 +3326,20 @@
         <v>159</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="6"/>
       <c r="K54" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="26.25">
       <c r="A55" s="13">
         <v>54</v>
       </c>
@@ -3240,20 +3353,20 @@
         <v>159</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="6"/>
       <c r="K55" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="26.25">
       <c r="A56" s="13">
         <v>55</v>
       </c>
@@ -3267,20 +3380,20 @@
         <v>159</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="6"/>
       <c r="K56" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="26.25" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="26.25">
       <c r="A57" s="13">
         <v>56</v>
       </c>
@@ -3297,7 +3410,7 @@
         <v>201</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G57" s="5">
         <v>120</v>
@@ -3309,7 +3422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1">
+    <row r="58" spans="1:11">
       <c r="A58" s="13">
         <v>57</v>
       </c>
@@ -3338,7 +3451,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1">
+    <row r="59" spans="1:11">
       <c r="A59" s="13">
         <v>58</v>
       </c>
@@ -3367,7 +3480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1">
+    <row r="60" spans="1:11">
       <c r="A60" s="13">
         <v>59</v>
       </c>
@@ -3396,7 +3509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1">
+    <row r="61" spans="1:11">
       <c r="A61" s="13">
         <v>60</v>
       </c>
@@ -3425,7 +3538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1">
+    <row r="62" spans="1:11">
       <c r="A62" s="13">
         <v>61</v>
       </c>
@@ -3454,7 +3567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1">
+    <row r="63" spans="1:11">
       <c r="A63" s="13">
         <v>62</v>
       </c>
@@ -3483,7 +3596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1">
+    <row r="64" spans="1:11">
       <c r="A64" s="13">
         <v>63</v>
       </c>
@@ -3512,7 +3625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1">
+    <row r="65" spans="1:11">
       <c r="A65" s="13">
         <v>64</v>
       </c>
@@ -3541,7 +3654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1">
+    <row r="66" spans="1:11">
       <c r="A66" s="13">
         <v>65</v>
       </c>
@@ -3570,7 +3683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1">
+    <row r="67" spans="1:11">
       <c r="A67" s="13">
         <v>66</v>
       </c>
@@ -3599,7 +3712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1">
+    <row r="68" spans="1:11">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -3628,7 +3741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1">
+    <row r="69" spans="1:11">
       <c r="A69" s="13">
         <v>68</v>
       </c>
@@ -3657,7 +3770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1">
+    <row r="70" spans="1:11">
       <c r="A70" s="13">
         <v>69</v>
       </c>
@@ -3686,7 +3799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1">
+    <row r="71" spans="1:11">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -3715,7 +3828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1">
+    <row r="72" spans="1:11">
       <c r="A72" s="13">
         <v>71</v>
       </c>
@@ -3744,7 +3857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1">
+    <row r="73" spans="1:11">
       <c r="A73" s="13">
         <v>72</v>
       </c>
@@ -3773,7 +3886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1">
+    <row r="74" spans="1:11">
       <c r="A74" s="13">
         <v>73</v>
       </c>
@@ -3802,7 +3915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1">
+    <row r="75" spans="1:11">
       <c r="A75" s="13">
         <v>74</v>
       </c>
@@ -3831,7 +3944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1">
+    <row r="76" spans="1:11">
       <c r="A76" s="13">
         <v>75</v>
       </c>
@@ -3860,7 +3973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1">
+    <row r="77" spans="1:11">
       <c r="A77" s="13">
         <v>76</v>
       </c>
@@ -3889,7 +4002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="26.25" hidden="1">
+    <row r="78" spans="1:11" ht="26.25">
       <c r="A78" s="13">
         <v>77</v>
       </c>
@@ -3906,7 +4019,7 @@
         <v>77</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G78" s="5">
         <v>200</v>
@@ -3918,7 +4031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="26.25" hidden="1">
+    <row r="79" spans="1:11" ht="26.25">
       <c r="A79" s="13">
         <v>78</v>
       </c>
@@ -3935,7 +4048,7 @@
         <v>78</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -3945,7 +4058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1">
+    <row r="80" spans="1:11">
       <c r="A80" s="13">
         <v>79</v>
       </c>
@@ -3961,45 +4074,45 @@
       <c r="E80" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F80" s="25"/>
+      <c r="F80" s="24"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="64.5" hidden="1">
-      <c r="A81" s="13">
+    <row r="81" spans="1:11" ht="64.5">
+      <c r="A81" s="26">
         <v>80</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C81" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="D81" s="7" t="s">
+      <c r="C81" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="D81" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" hidden="1">
+      <c r="F81" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="G81" s="29"/>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="13">
         <v>81</v>
       </c>
@@ -4023,10 +4136,10 @@
       <c r="I82" s="5"/>
       <c r="J82" s="6"/>
       <c r="K82" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" s="13">
         <v>82</v>
       </c>
@@ -4050,10 +4163,10 @@
       <c r="I83" s="5"/>
       <c r="J83" s="6"/>
       <c r="K83" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" s="13">
         <v>83</v>
       </c>
@@ -4077,10 +4190,10 @@
       <c r="I84" s="5"/>
       <c r="J84" s="6"/>
       <c r="K84" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" s="13">
         <v>84</v>
       </c>
@@ -4104,10 +4217,10 @@
       <c r="I85" s="5"/>
       <c r="J85" s="6"/>
       <c r="K85" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" s="13">
         <v>85</v>
       </c>
@@ -4130,13 +4243,13 @@
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="13">
         <v>86</v>
       </c>
@@ -4159,13 +4272,13 @@
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="26.25">
       <c r="A88" s="13">
         <v>87</v>
       </c>
@@ -4182,17 +4295,17 @@
         <v>212</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="6"/>
       <c r="K88" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="26.25">
       <c r="A89" s="13">
         <v>88</v>
       </c>
@@ -4209,17 +4322,17 @@
         <v>87</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="6"/>
       <c r="K89" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="26.25">
       <c r="A90" s="13">
         <v>89</v>
       </c>
@@ -4236,17 +4349,17 @@
         <v>88</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="18"/>
       <c r="K90" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="26.25">
       <c r="A91" s="13">
         <v>90</v>
       </c>
@@ -4263,17 +4376,17 @@
         <v>89</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="18"/>
       <c r="K91" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="26.25">
       <c r="A92" s="13">
         <v>91</v>
       </c>
@@ -4290,17 +4403,17 @@
         <v>90</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="18"/>
       <c r="K92" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="26.25">
       <c r="A93" s="13">
         <v>92</v>
       </c>
@@ -4317,17 +4430,17 @@
         <v>91</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="18"/>
       <c r="K93" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="26.25">
       <c r="A94" s="13">
         <v>93</v>
       </c>
@@ -4344,17 +4457,17 @@
         <v>92</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="18"/>
       <c r="K94" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="26.25">
       <c r="A95" s="13">
         <v>94</v>
       </c>
@@ -4371,17 +4484,17 @@
         <v>93</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="18"/>
       <c r="K95" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="26.25">
       <c r="A96" s="13">
         <v>95</v>
       </c>
@@ -4398,17 +4511,17 @@
         <v>94</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="18"/>
       <c r="K96" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="26.25">
       <c r="A97" s="13">
         <v>96</v>
       </c>
@@ -4425,17 +4538,17 @@
         <v>95</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="18"/>
       <c r="K97" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="26.25">
       <c r="A98" s="13">
         <v>97</v>
       </c>
@@ -4452,17 +4565,17 @@
         <v>96</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="18"/>
       <c r="K98" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="26.25">
       <c r="A99" s="13">
         <v>98</v>
       </c>
@@ -4479,17 +4592,17 @@
         <v>97</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="18"/>
       <c r="K99" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="26.25">
       <c r="A100" s="13">
         <v>99</v>
       </c>
@@ -4506,17 +4619,17 @@
         <v>98</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="18"/>
       <c r="K100" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="26.25">
       <c r="A101" s="13">
         <v>100</v>
       </c>
@@ -4533,17 +4646,17 @@
         <v>99</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="18"/>
       <c r="K101" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="26.25">
       <c r="A102" s="13">
         <v>101</v>
       </c>
@@ -4560,17 +4673,17 @@
         <v>100</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="18"/>
       <c r="K102" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="26.25">
       <c r="A103" s="13">
         <v>102</v>
       </c>
@@ -4587,17 +4700,17 @@
         <v>101</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="18"/>
       <c r="K103" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="26.25">
       <c r="A104" s="13">
         <v>103</v>
       </c>
@@ -4614,17 +4727,17 @@
         <v>102</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="18"/>
       <c r="K104" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="26.25">
       <c r="A105" s="13">
         <v>104</v>
       </c>
@@ -4641,17 +4754,17 @@
         <v>103</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="18"/>
       <c r="K105" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="26.25">
       <c r="A106" s="13">
         <v>105</v>
       </c>
@@ -4668,17 +4781,17 @@
         <v>104</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="18"/>
       <c r="K106" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="26.25">
       <c r="A107" s="13">
         <v>106</v>
       </c>
@@ -4695,17 +4808,17 @@
         <v>105</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="18"/>
       <c r="K107" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="26.25">
       <c r="A108" s="13">
         <v>107</v>
       </c>
@@ -4722,17 +4835,17 @@
         <v>106</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="18"/>
       <c r="K108" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="26.25">
       <c r="A109" s="13">
         <v>108</v>
       </c>
@@ -4749,17 +4862,17 @@
         <v>107</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="18"/>
       <c r="K109" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="26.25">
       <c r="A110" s="13">
         <v>109</v>
       </c>
@@ -4776,17 +4889,17 @@
         <v>213</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="18"/>
       <c r="K110" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="26.25">
       <c r="A111" s="13">
         <v>110</v>
       </c>
@@ -4803,17 +4916,17 @@
         <v>214</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="18"/>
       <c r="K111" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="26.25">
       <c r="A112" s="13">
         <v>111</v>
       </c>
@@ -4830,17 +4943,17 @@
         <v>215</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="18"/>
       <c r="K112" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="26.25">
       <c r="A113" s="13">
         <v>112</v>
       </c>
@@ -4857,17 +4970,17 @@
         <v>216</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="18"/>
       <c r="K113" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="26.25">
       <c r="A114" s="13">
         <v>113</v>
       </c>
@@ -4884,17 +4997,17 @@
         <v>217</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="18"/>
       <c r="K114" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="26.25">
       <c r="A115" s="13">
         <v>114</v>
       </c>
@@ -4911,17 +5024,17 @@
         <v>218</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="18"/>
       <c r="K115" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="26.25">
       <c r="A116" s="13">
         <v>115</v>
       </c>
@@ -4938,17 +5051,17 @@
         <v>219</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="18"/>
       <c r="K116" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="26.25">
       <c r="A117" s="13">
         <v>116</v>
       </c>
@@ -4965,17 +5078,17 @@
         <v>220</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="18"/>
       <c r="K117" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="26.25">
       <c r="A118" s="13">
         <v>117</v>
       </c>
@@ -4992,17 +5105,17 @@
         <v>221</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="18"/>
       <c r="K118" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="26.25">
       <c r="A119" s="13">
         <v>118</v>
       </c>
@@ -5019,17 +5132,17 @@
         <v>222</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="18"/>
       <c r="K119" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="39" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="39">
       <c r="A120" s="13">
         <v>119</v>
       </c>
@@ -5046,17 +5159,17 @@
         <v>223</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="18"/>
       <c r="K120" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" s="13">
         <v>120</v>
       </c>
@@ -5066,20 +5179,20 @@
       <c r="C121" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D121" s="25"/>
+      <c r="D121" s="24"/>
       <c r="E121" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="F121" s="25"/>
+      <c r="F121" s="24"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="18"/>
       <c r="K121" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="64.5" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="64.5">
       <c r="A122" s="13">
         <v>121</v>
       </c>
@@ -5096,17 +5209,17 @@
         <v>225</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="18"/>
       <c r="K122" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="64.5" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="64.5">
       <c r="A123" s="13">
         <v>122</v>
       </c>
@@ -5123,17 +5236,17 @@
         <v>226</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="18"/>
       <c r="K123" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="51.75" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="51.75">
       <c r="A124" s="13">
         <v>123</v>
       </c>
@@ -5150,17 +5263,17 @@
         <v>227</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="18"/>
       <c r="K124" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="39" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="39">
       <c r="A125" s="13">
         <v>124</v>
       </c>
@@ -5177,17 +5290,17 @@
         <v>228</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="18"/>
       <c r="K125" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" s="13">
         <v>125</v>
       </c>
@@ -5197,20 +5310,20 @@
       <c r="C126" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D126" s="25"/>
+      <c r="D126" s="24"/>
       <c r="E126" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="F126" s="25"/>
+      <c r="F126" s="24"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="18"/>
       <c r="K126" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="26.25">
       <c r="A127" s="13">
         <v>126</v>
       </c>
@@ -5227,17 +5340,17 @@
         <v>229</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="18"/>
       <c r="K127" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="26.25">
       <c r="A128" s="13">
         <v>127</v>
       </c>
@@ -5254,17 +5367,17 @@
         <v>230</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="18"/>
       <c r="K128" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="26.25">
       <c r="A129" s="13">
         <v>128</v>
       </c>
@@ -5281,17 +5394,17 @@
         <v>231</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="18"/>
       <c r="K129" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130" s="13">
         <v>129</v>
       </c>
@@ -5301,20 +5414,20 @@
       <c r="C130" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D130" s="25"/>
+      <c r="D130" s="24"/>
       <c r="E130" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="F130" s="25"/>
+      <c r="F130" s="24"/>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="18"/>
       <c r="K130" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="26.25" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="26.25">
       <c r="A131" s="13">
         <v>130</v>
       </c>
@@ -5330,16 +5443,16 @@
       <c r="E131" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="F131" s="25"/>
+      <c r="F131" s="24"/>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="18"/>
       <c r="K131" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" hidden="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132" s="13">
         <v>132</v>
       </c>
@@ -5366,7 +5479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1">
+    <row r="133" spans="1:11">
       <c r="A133" s="13">
         <v>133</v>
       </c>
@@ -5393,7 +5506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="39" hidden="1">
+    <row r="134" spans="1:11" ht="39">
       <c r="A134" s="13">
         <v>134</v>
       </c>
@@ -5420,28 +5533,28 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="26.25" hidden="1">
-      <c r="A135" s="13">
+    <row r="135" spans="1:11" ht="26.25">
+      <c r="A135" s="26">
         <v>135</v>
       </c>
-      <c r="B135" s="6"/>
-      <c r="C135" s="9" t="s">
+      <c r="B135" s="30"/>
+      <c r="C135" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="D135" s="9" t="s">
+      <c r="D135" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="E135" s="9" t="s">
+      <c r="E135" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="F135" s="25"/>
-      <c r="G135" s="5"/>
-      <c r="H135" s="5"/>
-      <c r="I135" s="5"/>
-      <c r="J135" s="18"/>
-      <c r="K135" s="5"/>
-    </row>
-    <row r="136" spans="1:11" ht="26.25" hidden="1">
+      <c r="F135" s="38"/>
+      <c r="G135" s="29"/>
+      <c r="H135" s="29"/>
+      <c r="I135" s="29"/>
+      <c r="J135" s="31"/>
+      <c r="K135" s="29"/>
+    </row>
+    <row r="136" spans="1:11" ht="26.25">
       <c r="A136" s="13">
         <v>136</v>
       </c>
@@ -5466,7 +5579,7 @@
       <c r="J136" s="18"/>
       <c r="K136" s="5"/>
     </row>
-    <row r="137" spans="1:11" ht="26.25" hidden="1">
+    <row r="137" spans="1:11" ht="26.25">
       <c r="A137" s="13">
         <v>137</v>
       </c>
@@ -5491,7 +5604,7 @@
       <c r="J137" s="18"/>
       <c r="K137" s="5"/>
     </row>
-    <row r="138" spans="1:11" ht="26.25" hidden="1">
+    <row r="138" spans="1:11" ht="26.25">
       <c r="A138" s="13">
         <v>138</v>
       </c>
@@ -5516,7 +5629,7 @@
       <c r="J138" s="18"/>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="1:11" ht="26.25" hidden="1">
+    <row r="139" spans="1:11" ht="26.25">
       <c r="A139" s="13">
         <v>139</v>
       </c>
@@ -5541,7 +5654,7 @@
       <c r="J139" s="18"/>
       <c r="K139" s="5"/>
     </row>
-    <row r="140" spans="1:11" ht="26.25" hidden="1">
+    <row r="140" spans="1:11" ht="26.25">
       <c r="A140" s="13">
         <v>140</v>
       </c>
@@ -5566,7 +5679,7 @@
       <c r="J140" s="18"/>
       <c r="K140" s="5"/>
     </row>
-    <row r="141" spans="1:11" ht="26.25" hidden="1">
+    <row r="141" spans="1:11" ht="26.25">
       <c r="A141" s="13">
         <v>141</v>
       </c>
@@ -5591,7 +5704,7 @@
       <c r="J141" s="18"/>
       <c r="K141" s="5"/>
     </row>
-    <row r="142" spans="1:11" ht="26.25" hidden="1">
+    <row r="142" spans="1:11" ht="26.25">
       <c r="A142" s="13">
         <v>142</v>
       </c>
@@ -5616,7 +5729,7 @@
       <c r="J142" s="18"/>
       <c r="K142" s="5"/>
     </row>
-    <row r="143" spans="1:11" ht="26.25" hidden="1">
+    <row r="143" spans="1:11" ht="26.25">
       <c r="A143" s="13">
         <v>143</v>
       </c>
@@ -5641,7 +5754,7 @@
       <c r="J143" s="18"/>
       <c r="K143" s="5"/>
     </row>
-    <row r="144" spans="1:11" ht="26.25" hidden="1">
+    <row r="144" spans="1:11" ht="26.25">
       <c r="A144" s="13">
         <v>144</v>
       </c>
@@ -5666,7 +5779,7 @@
       <c r="J144" s="18"/>
       <c r="K144" s="5"/>
     </row>
-    <row r="145" spans="1:11" ht="26.25" hidden="1">
+    <row r="145" spans="1:11" ht="26.25">
       <c r="A145" s="13">
         <v>145</v>
       </c>
@@ -5691,7 +5804,7 @@
       <c r="J145" s="18"/>
       <c r="K145" s="5"/>
     </row>
-    <row r="146" spans="1:11" hidden="1">
+    <row r="146" spans="1:11">
       <c r="A146" s="13">
         <v>146</v>
       </c>
@@ -5701,7 +5814,7 @@
       <c r="C146" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D146" s="25"/>
+      <c r="D146" s="24"/>
       <c r="E146" s="9" t="s">
         <v>125</v>
       </c>
@@ -5714,7 +5827,7 @@
       <c r="J146" s="18"/>
       <c r="K146" s="5"/>
     </row>
-    <row r="147" spans="1:11" hidden="1">
+    <row r="147" spans="1:11">
       <c r="A147" s="13">
         <v>147</v>
       </c>
@@ -5724,7 +5837,7 @@
       <c r="C147" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D147" s="25"/>
+      <c r="D147" s="24"/>
       <c r="E147" s="9" t="s">
         <v>126</v>
       </c>
@@ -5737,7 +5850,7 @@
       <c r="J147" s="18"/>
       <c r="K147" s="5"/>
     </row>
-    <row r="148" spans="1:11" hidden="1">
+    <row r="148" spans="1:11">
       <c r="A148" s="13">
         <v>148</v>
       </c>
@@ -5747,7 +5860,7 @@
       <c r="C148" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D148" s="25"/>
+      <c r="D148" s="24"/>
       <c r="E148" s="9" t="s">
         <v>127</v>
       </c>
@@ -5760,7 +5873,7 @@
       <c r="J148" s="18"/>
       <c r="K148" s="5"/>
     </row>
-    <row r="149" spans="1:11" hidden="1">
+    <row r="149" spans="1:11">
       <c r="A149" s="13">
         <v>149</v>
       </c>
@@ -5770,7 +5883,7 @@
       <c r="C149" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D149" s="25"/>
+      <c r="D149" s="24"/>
       <c r="E149" s="9" t="s">
         <v>128</v>
       </c>
@@ -5783,7 +5896,7 @@
       <c r="J149" s="18"/>
       <c r="K149" s="5"/>
     </row>
-    <row r="150" spans="1:11" hidden="1">
+    <row r="150" spans="1:11">
       <c r="A150" s="13">
         <v>150</v>
       </c>
@@ -5793,7 +5906,7 @@
       <c r="C150" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D150" s="25"/>
+      <c r="D150" s="24"/>
       <c r="E150" s="9" t="s">
         <v>129</v>
       </c>
@@ -5806,7 +5919,7 @@
       <c r="J150" s="18"/>
       <c r="K150" s="5"/>
     </row>
-    <row r="151" spans="1:11" hidden="1">
+    <row r="151" spans="1:11">
       <c r="A151" s="13">
         <v>151</v>
       </c>
@@ -5816,7 +5929,7 @@
       <c r="C151" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D151" s="25"/>
+      <c r="D151" s="24"/>
       <c r="E151" s="9" t="s">
         <v>130</v>
       </c>
@@ -5829,7 +5942,7 @@
       <c r="J151" s="18"/>
       <c r="K151" s="5"/>
     </row>
-    <row r="152" spans="1:11" hidden="1">
+    <row r="152" spans="1:11">
       <c r="A152" s="13">
         <v>152</v>
       </c>
@@ -5839,7 +5952,7 @@
       <c r="C152" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D152" s="25"/>
+      <c r="D152" s="24"/>
       <c r="E152" s="9" t="s">
         <v>131</v>
       </c>
@@ -5852,7 +5965,7 @@
       <c r="J152" s="18"/>
       <c r="K152" s="5"/>
     </row>
-    <row r="153" spans="1:11" hidden="1">
+    <row r="153" spans="1:11">
       <c r="A153" s="13">
         <v>153</v>
       </c>
@@ -5862,7 +5975,7 @@
       <c r="C153" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D153" s="25"/>
+      <c r="D153" s="24"/>
       <c r="E153" s="9" t="s">
         <v>132</v>
       </c>
@@ -5875,7 +5988,7 @@
       <c r="J153" s="18"/>
       <c r="K153" s="5"/>
     </row>
-    <row r="154" spans="1:11" hidden="1">
+    <row r="154" spans="1:11">
       <c r="A154" s="13">
         <v>154</v>
       </c>
@@ -5885,7 +5998,7 @@
       <c r="C154" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D154" s="25"/>
+      <c r="D154" s="24"/>
       <c r="E154" s="9" t="s">
         <v>133</v>
       </c>
@@ -5898,7 +6011,7 @@
       <c r="J154" s="18"/>
       <c r="K154" s="5"/>
     </row>
-    <row r="155" spans="1:11" hidden="1">
+    <row r="155" spans="1:11">
       <c r="A155" s="13">
         <v>155</v>
       </c>
@@ -5908,7 +6021,7 @@
       <c r="C155" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D155" s="25"/>
+      <c r="D155" s="24"/>
       <c r="E155" s="9" t="s">
         <v>134</v>
       </c>
@@ -5921,7 +6034,7 @@
       <c r="J155" s="18"/>
       <c r="K155" s="5"/>
     </row>
-    <row r="156" spans="1:11" hidden="1">
+    <row r="156" spans="1:11">
       <c r="A156" s="13">
         <v>156</v>
       </c>
@@ -5931,7 +6044,7 @@
       <c r="C156" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D156" s="25"/>
+      <c r="D156" s="24"/>
       <c r="E156" s="9" t="s">
         <v>135</v>
       </c>
@@ -5944,7 +6057,7 @@
       <c r="J156" s="18"/>
       <c r="K156" s="5"/>
     </row>
-    <row r="157" spans="1:11" ht="26.25" hidden="1">
+    <row r="157" spans="1:11" ht="26.25">
       <c r="A157" s="13">
         <v>157</v>
       </c>
@@ -5969,7 +6082,7 @@
       <c r="J157" s="18"/>
       <c r="K157" s="5"/>
     </row>
-    <row r="158" spans="1:11" ht="26.25" hidden="1">
+    <row r="158" spans="1:11" ht="26.25">
       <c r="A158" s="13">
         <v>158</v>
       </c>
@@ -5994,7 +6107,7 @@
       <c r="J158" s="18"/>
       <c r="K158" s="5"/>
     </row>
-    <row r="159" spans="1:11" ht="26.25" hidden="1">
+    <row r="159" spans="1:11" ht="26.25">
       <c r="A159" s="13">
         <v>159</v>
       </c>
@@ -6019,7 +6132,7 @@
       <c r="J159" s="18"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="1:11" ht="26.25" hidden="1">
+    <row r="160" spans="1:11" ht="26.25">
       <c r="A160" s="13">
         <v>160</v>
       </c>
@@ -6044,7 +6157,7 @@
       <c r="J160" s="18"/>
       <c r="K160" s="5"/>
     </row>
-    <row r="161" spans="1:11" ht="26.25" hidden="1">
+    <row r="161" spans="1:11" ht="26.25">
       <c r="A161" s="13">
         <v>161</v>
       </c>
@@ -6069,7 +6182,7 @@
       <c r="J161" s="18"/>
       <c r="K161" s="5"/>
     </row>
-    <row r="162" spans="1:11" ht="26.25" hidden="1">
+    <row r="162" spans="1:11" ht="26.25">
       <c r="A162" s="13">
         <v>162</v>
       </c>
@@ -6094,7 +6207,7 @@
       <c r="J162" s="18"/>
       <c r="K162" s="5"/>
     </row>
-    <row r="163" spans="1:11" ht="26.25" hidden="1">
+    <row r="163" spans="1:11" ht="26.25">
       <c r="A163" s="13">
         <v>163</v>
       </c>
@@ -6119,7 +6232,7 @@
       <c r="J163" s="18"/>
       <c r="K163" s="5"/>
     </row>
-    <row r="164" spans="1:11" ht="26.25" hidden="1">
+    <row r="164" spans="1:11" ht="26.25">
       <c r="A164" s="13">
         <v>164</v>
       </c>
@@ -6144,7 +6257,7 @@
       <c r="J164" s="18"/>
       <c r="K164" s="5"/>
     </row>
-    <row r="165" spans="1:11" ht="26.25" hidden="1">
+    <row r="165" spans="1:11" ht="26.25">
       <c r="A165" s="13">
         <v>165</v>
       </c>
@@ -6169,7 +6282,7 @@
       <c r="J165" s="18"/>
       <c r="K165" s="5"/>
     </row>
-    <row r="166" spans="1:11" ht="26.25" hidden="1">
+    <row r="166" spans="1:11" ht="26.25">
       <c r="A166" s="13">
         <v>166</v>
       </c>
@@ -6194,7 +6307,7 @@
       <c r="J166" s="18"/>
       <c r="K166" s="5"/>
     </row>
-    <row r="167" spans="1:11" ht="26.25" hidden="1">
+    <row r="167" spans="1:11" ht="26.25">
       <c r="A167" s="13">
         <v>167</v>
       </c>
@@ -6219,7 +6332,7 @@
       <c r="J167" s="18"/>
       <c r="K167" s="5"/>
     </row>
-    <row r="168" spans="1:11" ht="39" hidden="1">
+    <row r="168" spans="1:11" ht="39">
       <c r="A168" s="13">
         <v>168</v>
       </c>
@@ -6246,7 +6359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="26.25" hidden="1">
+    <row r="169" spans="1:11" ht="26.25">
       <c r="A169" s="13">
         <v>169</v>
       </c>
@@ -6273,7 +6386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1">
+    <row r="170" spans="1:11">
       <c r="A170" s="13">
         <v>170</v>
       </c>
@@ -6283,9 +6396,9 @@
       <c r="C170" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D170" s="25"/>
-      <c r="E170" s="26" t="s">
-        <v>331</v>
+      <c r="D170" s="24"/>
+      <c r="E170" s="25" t="s">
+        <v>330</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>138</v>
@@ -6298,7 +6411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1">
+    <row r="171" spans="1:11">
       <c r="A171" s="13">
         <v>171</v>
       </c>
@@ -6308,9 +6421,9 @@
       <c r="C171" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D171" s="25"/>
-      <c r="E171" s="26" t="s">
-        <v>332</v>
+      <c r="D171" s="24"/>
+      <c r="E171" s="25" t="s">
+        <v>331</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>139</v>
@@ -6323,7 +6436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="26.25" hidden="1">
+    <row r="172" spans="1:11" ht="26.25">
       <c r="A172" s="13">
         <v>172</v>
       </c>
@@ -6336,8 +6449,8 @@
       <c r="D172" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E172" s="9" t="s">
-        <v>246</v>
+      <c r="E172" s="10" t="s">
+        <v>379</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>140</v>
@@ -6350,7 +6463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="26.25" hidden="1">
+    <row r="173" spans="1:11" ht="26.25">
       <c r="A173" s="13">
         <v>173</v>
       </c>
@@ -6364,7 +6477,7 @@
         <v>189</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>141</v>
@@ -6377,7 +6490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="26.25" hidden="1">
+    <row r="174" spans="1:11" ht="26.25">
       <c r="A174" s="13">
         <v>174</v>
       </c>
@@ -6391,7 +6504,7 @@
         <v>190</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>142</v>
@@ -6404,7 +6517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="39" hidden="1">
+    <row r="175" spans="1:11" ht="39">
       <c r="A175" s="13">
         <v>175</v>
       </c>
@@ -6418,7 +6531,7 @@
         <v>191</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>143</v>
@@ -6431,7 +6544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1">
+    <row r="176" spans="1:11">
       <c r="A176" s="13">
         <v>176</v>
       </c>
@@ -6445,7 +6558,7 @@
         <v>192</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>144</v>
@@ -6458,7 +6571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="26.25" hidden="1">
+    <row r="177" spans="1:11" ht="26.25">
       <c r="A177" s="13">
         <v>177</v>
       </c>
@@ -6472,7 +6585,7 @@
         <v>193</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>145</v>
@@ -6485,7 +6598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="39" hidden="1">
+    <row r="178" spans="1:11" ht="39">
       <c r="A178" s="13">
         <v>178</v>
       </c>
@@ -6499,7 +6612,7 @@
         <v>194</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>146</v>
@@ -6512,7 +6625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="26.25" hidden="1">
+    <row r="179" spans="1:11" ht="26.25">
       <c r="A179" s="13">
         <v>179</v>
       </c>
@@ -6526,7 +6639,7 @@
         <v>195</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>147</v>
@@ -6539,7 +6652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1">
+    <row r="180" spans="1:11">
       <c r="A180" s="13">
         <v>180</v>
       </c>
@@ -6549,9 +6662,9 @@
       <c r="C180" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D180" s="25"/>
-      <c r="E180" s="26" t="s">
-        <v>333</v>
+      <c r="D180" s="24"/>
+      <c r="E180" s="25" t="s">
+        <v>332</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>148</v>
@@ -6564,7 +6677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1">
+    <row r="181" spans="1:11">
       <c r="A181" s="13">
         <v>181</v>
       </c>
@@ -6574,9 +6687,9 @@
       <c r="C181" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D181" s="25"/>
-      <c r="E181" s="26" t="s">
-        <v>334</v>
+      <c r="D181" s="24"/>
+      <c r="E181" s="25" t="s">
+        <v>333</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>149</v>
@@ -6589,7 +6702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1">
+    <row r="182" spans="1:11">
       <c r="A182" s="13">
         <v>182</v>
       </c>
@@ -6603,7 +6716,7 @@
         <v>185</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>150</v>
@@ -6616,7 +6729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="26.25" hidden="1">
+    <row r="183" spans="1:11" ht="26.25">
       <c r="A183" s="13">
         <v>183</v>
       </c>
@@ -6630,7 +6743,7 @@
         <v>196</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>151</v>
@@ -6643,7 +6756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="26.25" hidden="1">
+    <row r="184" spans="1:11" ht="26.25">
       <c r="A184" s="13">
         <v>184</v>
       </c>
@@ -6657,7 +6770,7 @@
         <v>197</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>152</v>
@@ -6670,7 +6783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="39" hidden="1">
+    <row r="185" spans="1:11" ht="39">
       <c r="A185" s="13">
         <v>185</v>
       </c>
@@ -6684,7 +6797,7 @@
         <v>198</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>153</v>
@@ -6697,7 +6810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="26.25" hidden="1">
+    <row r="186" spans="1:11" ht="26.25">
       <c r="A186" s="13">
         <v>186</v>
       </c>
@@ -6711,7 +6824,7 @@
         <v>199</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>154</v>
@@ -6724,7 +6837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1">
+    <row r="187" spans="1:11">
       <c r="A187" s="13">
         <v>187</v>
       </c>
@@ -6738,7 +6851,7 @@
         <v>192</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>155</v>
@@ -6751,7 +6864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1">
+    <row r="188" spans="1:11">
       <c r="A188" s="13">
         <v>188</v>
       </c>
@@ -6759,13 +6872,13 @@
         <v>11</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F188" s="11"/>
       <c r="G188" s="5">
@@ -6778,7 +6891,7 @@
       <c r="J188" s="8"/>
       <c r="K188" s="5"/>
     </row>
-    <row r="189" spans="1:11" hidden="1">
+    <row r="189" spans="1:11">
       <c r="A189" s="13">
         <v>189</v>
       </c>
@@ -6786,13 +6899,13 @@
         <v>11</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F189" s="8"/>
       <c r="G189" s="5">
@@ -6804,10 +6917,10 @@
       <c r="I189" s="5"/>
       <c r="J189" s="8"/>
       <c r="K189" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
       <c r="A190" s="13">
         <v>190</v>
       </c>
@@ -6815,13 +6928,13 @@
         <v>11</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="5">
@@ -6833,10 +6946,10 @@
       <c r="I190" s="5"/>
       <c r="J190" s="8"/>
       <c r="K190" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
       <c r="A191" s="13">
         <v>191</v>
       </c>
@@ -6844,13 +6957,13 @@
         <v>11</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F191" s="8"/>
       <c r="G191" s="5">
@@ -6862,10 +6975,10 @@
       <c r="I191" s="5"/>
       <c r="J191" s="8"/>
       <c r="K191" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
       <c r="A192" s="13">
         <v>192</v>
       </c>
@@ -6873,13 +6986,13 @@
         <v>11</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="5">
@@ -6891,10 +7004,10 @@
       <c r="I192" s="5"/>
       <c r="J192" s="8"/>
       <c r="K192" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
       <c r="A193" s="13">
         <v>193</v>
       </c>
@@ -6902,13 +7015,13 @@
         <v>11</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F193" s="8"/>
       <c r="G193" s="5">
@@ -6920,10 +7033,10 @@
       <c r="I193" s="5"/>
       <c r="J193" s="8"/>
       <c r="K193" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
       <c r="A194" s="13">
         <v>194</v>
       </c>
@@ -6931,13 +7044,13 @@
         <v>11</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="5">
@@ -6949,10 +7062,10 @@
       <c r="I194" s="5"/>
       <c r="J194" s="8"/>
       <c r="K194" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
       <c r="A195" s="13">
         <v>195</v>
       </c>
@@ -6960,13 +7073,13 @@
         <v>11</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="5">
@@ -6978,10 +7091,10 @@
       <c r="I195" s="5"/>
       <c r="J195" s="8"/>
       <c r="K195" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
       <c r="A196" s="13">
         <v>196</v>
       </c>
@@ -6989,13 +7102,13 @@
         <v>11</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="5">
@@ -7007,10 +7120,10 @@
       <c r="I196" s="5"/>
       <c r="J196" s="8"/>
       <c r="K196" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
       <c r="A197" s="13">
         <v>197</v>
       </c>
@@ -7018,13 +7131,13 @@
         <v>11</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="5">
@@ -7036,10 +7149,10 @@
       <c r="I197" s="5"/>
       <c r="J197" s="8"/>
       <c r="K197" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
       <c r="A198" s="13">
         <v>199</v>
       </c>
@@ -7047,13 +7160,13 @@
         <v>11</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="5">
@@ -7065,10 +7178,10 @@
       <c r="I198" s="5"/>
       <c r="J198" s="8"/>
       <c r="K198" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
       <c r="A199" s="13">
         <v>200</v>
       </c>
@@ -7076,13 +7189,13 @@
         <v>11</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F199" s="8"/>
       <c r="G199" s="5">
@@ -7094,10 +7207,10 @@
       <c r="I199" s="5"/>
       <c r="J199" s="8"/>
       <c r="K199" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
       <c r="A200" s="13">
         <v>201</v>
       </c>
@@ -7105,13 +7218,13 @@
         <v>11</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="5">
@@ -7123,10 +7236,10 @@
       <c r="I200" s="5"/>
       <c r="J200" s="8"/>
       <c r="K200" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
       <c r="A201" s="13">
         <v>202</v>
       </c>
@@ -7134,13 +7247,13 @@
         <v>11</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="5">
@@ -7152,10 +7265,10 @@
       <c r="I201" s="5"/>
       <c r="J201" s="8"/>
       <c r="K201" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
       <c r="A202" s="13">
         <v>203</v>
       </c>
@@ -7163,13 +7276,13 @@
         <v>11</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="5">
@@ -7181,10 +7294,10 @@
       <c r="I202" s="5"/>
       <c r="J202" s="8"/>
       <c r="K202" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
       <c r="A203" s="13">
         <v>204</v>
       </c>
@@ -7192,13 +7305,13 @@
         <v>11</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F203" s="8"/>
       <c r="G203" s="5">
@@ -7210,10 +7323,10 @@
       <c r="I203" s="5"/>
       <c r="J203" s="8"/>
       <c r="K203" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
       <c r="A204" s="13">
         <v>205</v>
       </c>
@@ -7221,13 +7334,13 @@
         <v>11</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F204" s="8"/>
       <c r="G204" s="5">
@@ -7239,10 +7352,10 @@
       <c r="I204" s="5"/>
       <c r="J204" s="8"/>
       <c r="K204" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="205" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
       <c r="A205" s="13">
         <v>206</v>
       </c>
@@ -7250,13 +7363,13 @@
         <v>11</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F205" s="8"/>
       <c r="G205" s="5">
@@ -7268,10 +7381,10 @@
       <c r="I205" s="5"/>
       <c r="J205" s="8"/>
       <c r="K205" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
       <c r="A206" s="13">
         <v>207</v>
       </c>
@@ -7279,13 +7392,13 @@
         <v>11</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="5">
@@ -7297,24 +7410,24 @@
       <c r="I206" s="5"/>
       <c r="J206" s="8"/>
       <c r="K206" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" hidden="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
       <c r="A207" s="13">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D207" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F207" s="8"/>
       <c r="G207" s="5">
@@ -7326,144 +7439,457 @@
       <c r="I207" s="5"/>
       <c r="J207" s="8"/>
       <c r="K207" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="208" spans="1:11">
-      <c r="B208" s="1"/>
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-      <c r="F208" s="1"/>
-      <c r="J208" s="1"/>
-    </row>
-    <row r="209" spans="2:10">
-      <c r="B209" s="1"/>
-      <c r="C209" s="3"/>
-      <c r="D209" s="3"/>
-      <c r="E209" s="3"/>
-      <c r="F209" s="1"/>
-      <c r="J209" s="1"/>
-    </row>
-    <row r="210" spans="2:10">
-      <c r="B210" s="1"/>
-      <c r="C210" s="3"/>
-      <c r="D210" s="3"/>
-      <c r="E210" s="3"/>
-      <c r="F210" s="1"/>
-      <c r="J210" s="1"/>
-    </row>
-    <row r="211" spans="2:10">
-      <c r="B211" s="1"/>
-      <c r="C211" s="3"/>
-      <c r="D211" s="3"/>
-      <c r="E211" s="3"/>
-      <c r="F211" s="1"/>
-      <c r="J211" s="1"/>
-    </row>
-    <row r="212" spans="2:10">
-      <c r="B212" s="1"/>
-      <c r="C212" s="3"/>
-      <c r="D212" s="3"/>
-      <c r="E212" s="3"/>
-      <c r="F212" s="1"/>
-      <c r="J212" s="1"/>
-    </row>
-    <row r="213" spans="2:10">
-      <c r="B213" s="1"/>
-      <c r="C213" s="3"/>
-      <c r="D213" s="3"/>
-      <c r="E213" s="3"/>
-      <c r="F213" s="1"/>
-      <c r="J213" s="1"/>
-    </row>
-    <row r="214" spans="2:10">
-      <c r="B214" s="1"/>
-      <c r="C214" s="3"/>
-      <c r="D214" s="3"/>
-      <c r="E214" s="3"/>
-      <c r="F214" s="1"/>
-      <c r="J214" s="1"/>
-    </row>
-    <row r="215" spans="2:10">
-      <c r="B215" s="1"/>
-      <c r="C215" s="3"/>
-      <c r="D215" s="3"/>
-      <c r="E215" s="3"/>
-      <c r="F215" s="1"/>
-      <c r="J215" s="1"/>
-    </row>
-    <row r="216" spans="2:10">
-      <c r="B216" s="1"/>
-      <c r="C216" s="3"/>
-      <c r="D216" s="3"/>
-      <c r="E216" s="3"/>
-      <c r="F216" s="1"/>
-      <c r="J216" s="1"/>
-    </row>
-    <row r="217" spans="2:10">
-      <c r="B217" s="1"/>
-      <c r="C217" s="3"/>
-      <c r="D217" s="3"/>
-      <c r="E217" s="3"/>
-      <c r="F217" s="1"/>
-      <c r="J217" s="1"/>
-    </row>
-    <row r="218" spans="2:10">
-      <c r="B218" s="1"/>
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-      <c r="F218" s="1"/>
-      <c r="J218" s="1"/>
-    </row>
-    <row r="219" spans="2:10">
-      <c r="B219" s="1"/>
-      <c r="C219" s="3"/>
-      <c r="D219" s="3"/>
-      <c r="E219" s="3"/>
-      <c r="F219" s="1"/>
-      <c r="J219" s="1"/>
-    </row>
-    <row r="220" spans="2:10">
-      <c r="B220" s="1"/>
-      <c r="C220" s="3"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-      <c r="F220" s="1"/>
-      <c r="J220" s="1"/>
-    </row>
-    <row r="221" spans="2:10">
-      <c r="B221" s="1"/>
-      <c r="C221" s="3"/>
-      <c r="D221" s="3"/>
-      <c r="E221" s="3"/>
-      <c r="F221" s="1"/>
-      <c r="J221" s="1"/>
-    </row>
-    <row r="222" spans="2:10">
-      <c r="B222" s="1"/>
-      <c r="C222" s="3"/>
-      <c r="D222" s="3"/>
-      <c r="E222" s="3"/>
-      <c r="F222" s="1"/>
-      <c r="J222" s="1"/>
-    </row>
-    <row r="223" spans="2:10">
-      <c r="B223" s="1"/>
-      <c r="C223" s="3"/>
-      <c r="D223" s="3"/>
-      <c r="E223" s="3"/>
-      <c r="F223" s="1"/>
-      <c r="J223" s="1"/>
-    </row>
-    <row r="224" spans="2:10">
-      <c r="B224" s="1"/>
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
-      <c r="F224" s="1"/>
-      <c r="J224" s="1"/>
+      <c r="A208" s="13">
+        <v>207</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="F208" s="8"/>
+      <c r="G208" s="5"/>
+      <c r="H208" s="5"/>
+      <c r="I208" s="5"/>
+      <c r="J208" s="8"/>
+      <c r="K208" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11">
+      <c r="A209" s="13">
+        <v>207</v>
+      </c>
+      <c r="B209" s="8"/>
+      <c r="C209" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="F209" s="40"/>
+      <c r="G209" s="5"/>
+      <c r="H209" s="5"/>
+      <c r="I209" s="5"/>
+      <c r="J209" s="8"/>
+      <c r="K209" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" s="13">
+        <v>207</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="D210" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E210" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="F210" s="8">
+        <v>630</v>
+      </c>
+      <c r="G210" s="5">
+        <v>630</v>
+      </c>
+      <c r="H210" s="5"/>
+      <c r="I210" s="5"/>
+      <c r="J210" s="8"/>
+      <c r="K210" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" s="13">
+        <v>207</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D211" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E211" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="F211" s="8"/>
+      <c r="G211" s="5"/>
+      <c r="H211" s="5"/>
+      <c r="I211" s="5"/>
+      <c r="J211" s="8"/>
+      <c r="K211" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="A212" s="13">
+        <v>207</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C212" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D212" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E212" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="F212" s="8"/>
+      <c r="G212" s="5"/>
+      <c r="H212" s="5"/>
+      <c r="I212" s="5"/>
+      <c r="J212" s="8"/>
+      <c r="K212" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" s="13">
+        <v>207</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E213" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="F213" s="8"/>
+      <c r="G213" s="5"/>
+      <c r="H213" s="5"/>
+      <c r="I213" s="5"/>
+      <c r="J213" s="8"/>
+      <c r="K213" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="A214" s="13">
+        <v>207</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E214" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="F214" s="8"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
+      <c r="J214" s="8"/>
+      <c r="K214" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="A215" s="13">
+        <v>207</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F215" s="8"/>
+      <c r="G215" s="5"/>
+      <c r="H215" s="5"/>
+      <c r="I215" s="5"/>
+      <c r="J215" s="8"/>
+      <c r="K215" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="A216" s="13">
+        <v>207</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C216" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="F216" s="8"/>
+      <c r="G216" s="5"/>
+      <c r="H216" s="5"/>
+      <c r="I216" s="5"/>
+      <c r="J216" s="8"/>
+      <c r="K216" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="A217" s="13">
+        <v>207</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C217" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E217" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="F217" s="8"/>
+      <c r="G217" s="5"/>
+      <c r="H217" s="5"/>
+      <c r="I217" s="5"/>
+      <c r="J217" s="8"/>
+      <c r="K217" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11">
+      <c r="A218" s="13">
+        <v>207</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C218" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D218" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E218" s="39" t="s">
+        <v>391</v>
+      </c>
+      <c r="F218" s="8"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+      <c r="I218" s="5"/>
+      <c r="J218" s="8"/>
+      <c r="K218" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="A219" s="13">
+        <v>207</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E219" s="39" t="s">
+        <v>392</v>
+      </c>
+      <c r="F219" s="8"/>
+      <c r="G219" s="8">
+        <v>80</v>
+      </c>
+      <c r="H219" s="5">
+        <v>20</v>
+      </c>
+      <c r="I219" s="5"/>
+      <c r="J219" s="8"/>
+      <c r="K219" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11">
+      <c r="A220" s="13">
+        <v>207</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E220" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="F220" s="8"/>
+      <c r="G220" s="8">
+        <v>80</v>
+      </c>
+      <c r="H220" s="5">
+        <v>20</v>
+      </c>
+      <c r="I220" s="5"/>
+      <c r="J220" s="8"/>
+      <c r="K220" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="A221" s="13">
+        <v>207</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E221" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="F221" s="8"/>
+      <c r="G221" s="8">
+        <v>80</v>
+      </c>
+      <c r="H221" s="5">
+        <v>20</v>
+      </c>
+      <c r="I221" s="5"/>
+      <c r="J221" s="8"/>
+      <c r="K221" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="A222" s="13">
+        <v>207</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="D222" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E222" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="F222" s="8"/>
+      <c r="G222" s="8">
+        <v>80</v>
+      </c>
+      <c r="H222" s="5">
+        <v>20</v>
+      </c>
+      <c r="I222" s="5"/>
+      <c r="J222" s="8"/>
+      <c r="K222" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="A223" s="13">
+        <v>207</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="F223" s="8"/>
+      <c r="G223" s="8">
+        <v>80</v>
+      </c>
+      <c r="H223" s="5"/>
+      <c r="I223" s="5"/>
+      <c r="J223" s="8"/>
+      <c r="K223" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" s="13">
+        <v>207</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="D224" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="E224" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="F224" s="8"/>
+      <c r="G224" s="41">
+        <v>20</v>
+      </c>
+      <c r="H224" s="5">
+        <v>3</v>
+      </c>
+      <c r="I224" s="5"/>
+      <c r="J224" s="8"/>
+      <c r="K224" s="5" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="225" spans="2:10">
       <c r="B225" s="1"/>
@@ -13521,30 +13947,8 @@
       <c r="F981" s="1"/>
       <c r="J981" s="1"/>
     </row>
-    <row r="982" spans="2:10">
-      <c r="B982" s="1"/>
-      <c r="C982" s="3"/>
-      <c r="D982" s="3"/>
-      <c r="E982" s="3"/>
-      <c r="F982" s="1"/>
-      <c r="J982" s="1"/>
-    </row>
-    <row r="983" spans="2:10">
-      <c r="B983" s="1"/>
-      <c r="C983" s="3"/>
-      <c r="D983" s="3"/>
-      <c r="E983" s="3"/>
-      <c r="F983" s="1"/>
-      <c r="J983" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K207" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Учет Pi 1 с.ш. ГРЩ1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K224" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -13571,30 +13975,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E2" s="4">
         <v>0.5</v>
@@ -13602,16 +14006,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E3" s="4">
         <v>0.3</v>
@@ -13637,104 +14041,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -13756,104 +14160,104 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/upload/input.xlsx
+++ b/upload/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Desktop\электрохозяйство\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A39326B-8423-4A19-BE4B-EBC4977F2457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148B3968-F730-4DB4-9346-003B6C8650DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Networkall" sheetId="1" r:id="rId1"/>
@@ -1654,7 +1654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1690,7 +1690,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1792,6 +1791,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2163,36 +2168,36 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="B2" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="G2" s="30"/>
+      <c r="G2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="K2" s="43">
+      <c r="K2" s="42">
         <v>1000</v>
       </c>
-      <c r="L2" s="43" t="s">
+      <c r="L2" s="42" t="s">
         <v>374</v>
       </c>
       <c r="M2" s="2">
@@ -2212,22 +2217,22 @@
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="G3" s="27"/>
+      <c r="G3" s="26"/>
       <c r="J3" s="5" t="s">
         <v>367</v>
       </c>
@@ -2242,22 +2247,22 @@
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="27"/>
+      <c r="G4" s="26"/>
       <c r="J4" s="5" t="s">
         <v>367</v>
       </c>
@@ -2281,22 +2286,22 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="26"/>
       <c r="J5" s="5" t="s">
         <v>368</v>
       </c>
@@ -2311,22 +2316,22 @@
       <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="J6" s="5" t="s">
         <v>368</v>
       </c>
@@ -2347,20 +2352,20 @@
       <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="40" t="s">
+      <c r="F7" s="35"/>
+      <c r="G7" s="39" t="s">
         <v>362</v>
       </c>
       <c r="J7" s="5" t="s">
@@ -2375,18 +2380,18 @@
     </row>
     <row r="8" spans="1:16" ht="39" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="19" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="27"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="26"/>
       <c r="J8" s="5" t="s">
         <v>368</v>
       </c>
@@ -2394,32 +2399,32 @@
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="J9" s="43" t="s">
+      <c r="G9" s="29"/>
+      <c r="J9" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="42">
         <v>16</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="42">
         <v>3.5</v>
       </c>
     </row>
@@ -2427,18 +2432,18 @@
       <c r="A10" s="9">
         <v>8</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="27"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="26"/>
       <c r="J10" s="5" t="s">
         <v>369</v>
       </c>
@@ -2449,22 +2454,22 @@
       <c r="A11" s="9">
         <v>9</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="26"/>
       <c r="J11" s="5" t="s">
         <v>369</v>
       </c>
@@ -2475,22 +2480,22 @@
       <c r="A12" s="9">
         <v>10</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="J12" s="5" t="s">
         <v>369</v>
       </c>
@@ -2501,22 +2506,22 @@
       <c r="A13" s="9">
         <v>11</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="26"/>
       <c r="J13" s="5" t="s">
         <v>367</v>
       </c>
@@ -2536,22 +2541,22 @@
       <c r="A14" s="9">
         <v>12</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="26"/>
       <c r="J14" s="5" t="s">
         <v>368</v>
       </c>
@@ -2559,51 +2564,51 @@
       <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>13</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="41"/>
-      <c r="J15" s="43" t="s">
+      <c r="G15" s="40"/>
+      <c r="J15" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
     </row>
     <row r="16" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>14</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="B16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>363</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -2616,18 +2621,18 @@
       <c r="A17" s="9">
         <v>15</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="19" t="s">
+      <c r="B17" s="19"/>
+      <c r="C17" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="27"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="26"/>
       <c r="J17" s="5" t="s">
         <v>369</v>
       </c>
@@ -2638,22 +2643,22 @@
       <c r="A18" s="9">
         <v>16</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="26"/>
       <c r="J18" s="5" t="s">
         <v>369</v>
       </c>
@@ -2664,22 +2669,22 @@
       <c r="A19" s="9">
         <v>17</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="27"/>
+      <c r="G19" s="26"/>
       <c r="J19" s="5" t="s">
         <v>369</v>
       </c>
@@ -2690,22 +2695,22 @@
       <c r="A20" s="9">
         <v>18</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>363</v>
       </c>
       <c r="J20" s="5" t="s">
@@ -2718,22 +2723,22 @@
       <c r="A21" s="9">
         <v>19</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="39" t="s">
         <v>363</v>
       </c>
       <c r="J21" s="5" t="s">
@@ -2746,22 +2751,22 @@
       <c r="A22" s="9">
         <v>20</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="B22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="26" t="s">
         <v>30</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -2774,22 +2779,22 @@
       <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="B23" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="26" t="s">
         <v>30</v>
       </c>
       <c r="J23" s="5" t="s">
@@ -2799,30 +2804,30 @@
       <c r="L23" s="5"/>
     </row>
     <row r="24" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>23</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="G24" s="42"/>
-      <c r="J24" s="43" t="s">
+      <c r="G24" s="41"/>
+      <c r="J24" s="42" t="s">
         <v>370</v>
       </c>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
       <c r="M24">
         <v>135</v>
       </c>
@@ -2837,18 +2842,18 @@
       <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="24" t="s">
+      <c r="B25" s="22"/>
+      <c r="C25" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="27"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="26"/>
       <c r="J25" s="5" t="s">
         <v>368</v>
       </c>
@@ -2859,20 +2864,20 @@
       <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="F26" s="23"/>
-      <c r="G26" s="27"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="26"/>
       <c r="J26" s="5" t="s">
         <v>368</v>
       </c>
@@ -2883,18 +2888,18 @@
       <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="24" t="s">
+      <c r="B27" s="22"/>
+      <c r="C27" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="27"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="26"/>
       <c r="J27" s="5" t="s">
         <v>368</v>
       </c>
@@ -2902,45 +2907,45 @@
       <c r="L27" s="5"/>
     </row>
     <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>27</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="22" t="s">
+      <c r="B28" s="25"/>
+      <c r="C28" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="26"/>
-      <c r="G28" s="30"/>
-      <c r="J28" s="43" t="s">
+      <c r="F28" s="25"/>
+      <c r="G28" s="29"/>
+      <c r="J28" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="K28" s="43"/>
-      <c r="L28" s="43"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>28</v>
       </c>
-      <c r="B29" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="27"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="26"/>
       <c r="J29" s="5" t="s">
         <v>369</v>
       </c>
@@ -2951,18 +2956,18 @@
       <c r="A30" s="9">
         <v>29</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="24" t="s">
+      <c r="B30" s="22"/>
+      <c r="C30" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="23"/>
-      <c r="G30" s="27"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="26"/>
       <c r="J30" s="5" t="s">
         <v>369</v>
       </c>
@@ -2973,20 +2978,20 @@
       <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="24" t="s">
+      <c r="B31" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="27"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="26"/>
       <c r="J31" s="5" t="s">
         <v>369</v>
       </c>
@@ -2997,22 +3002,22 @@
       <c r="A32" s="9">
         <v>31</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="G32" s="27" t="s">
+      <c r="G32" s="26" t="s">
         <v>364</v>
       </c>
       <c r="J32" s="5" t="s">
@@ -3025,22 +3030,22 @@
       <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="G33" s="27" t="s">
+      <c r="G33" s="26" t="s">
         <v>364</v>
       </c>
       <c r="J33" s="5" t="s">
@@ -3053,22 +3058,22 @@
       <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="28" t="s">
+      <c r="B34" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="G34" s="27" t="s">
+      <c r="G34" s="26" t="s">
         <v>364</v>
       </c>
       <c r="J34" s="5" t="s">
@@ -3081,22 +3086,22 @@
       <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="26"/>
       <c r="J35" s="5" t="s">
         <v>369</v>
       </c>
@@ -3107,22 +3112,22 @@
       <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="28" t="s">
+      <c r="E36" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="J36" s="5" t="s">
         <v>369</v>
       </c>
@@ -3133,22 +3138,22 @@
       <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="28" t="s">
+      <c r="E37" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G37" s="27"/>
+      <c r="G37" s="26"/>
       <c r="J37" s="5" t="s">
         <v>369</v>
       </c>
@@ -3159,22 +3164,22 @@
       <c r="A38" s="9">
         <v>37</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G38" s="27"/>
+      <c r="G38" s="26"/>
       <c r="J38" s="5" t="s">
         <v>369</v>
       </c>
@@ -3185,22 +3190,22 @@
       <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="28" t="s">
+      <c r="E39" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G39" s="27"/>
+      <c r="G39" s="26"/>
       <c r="J39" s="5" t="s">
         <v>369</v>
       </c>
@@ -3211,22 +3216,22 @@
       <c r="A40" s="9">
         <v>39</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E40" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G40" s="27"/>
+      <c r="G40" s="26"/>
       <c r="J40" s="5" t="s">
         <v>369</v>
       </c>
@@ -3237,22 +3242,22 @@
       <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="E41" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G41" s="27"/>
+      <c r="G41" s="26"/>
       <c r="J41" s="5" t="s">
         <v>369</v>
       </c>
@@ -3263,22 +3268,22 @@
       <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G42" s="27"/>
+      <c r="G42" s="26"/>
       <c r="J42" s="5" t="s">
         <v>369</v>
       </c>
@@ -3289,22 +3294,22 @@
       <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C43" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="28" t="s">
+      <c r="E43" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="G43" s="27"/>
+      <c r="G43" s="26"/>
       <c r="J43" s="5" t="s">
         <v>369</v>
       </c>
@@ -3315,22 +3320,22 @@
       <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="28" t="s">
+      <c r="E44" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="G44" s="27"/>
+      <c r="G44" s="26"/>
       <c r="J44" s="5" t="s">
         <v>369</v>
       </c>
@@ -3341,22 +3346,22 @@
       <c r="A45" s="9">
         <v>44</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="29" t="s">
+      <c r="E45" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="F45" s="37" t="s">
+      <c r="F45" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="G45" s="27"/>
+      <c r="G45" s="26"/>
       <c r="J45" s="5" t="s">
         <v>369</v>
       </c>
@@ -3367,22 +3372,22 @@
       <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="29" t="s">
+      <c r="B46" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="D46" s="29" t="s">
+      <c r="D46" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="E46" s="29" t="s">
+      <c r="E46" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="28" t="s">
         <v>340</v>
       </c>
-      <c r="G46" s="27"/>
+      <c r="G46" s="26"/>
       <c r="J46" s="5" t="s">
         <v>369</v>
       </c>
@@ -3402,22 +3407,22 @@
       <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="29" t="s">
+      <c r="E47" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G47" s="27"/>
+      <c r="G47" s="26"/>
       <c r="J47" s="5" t="s">
         <v>369</v>
       </c>
@@ -3428,22 +3433,22 @@
       <c r="A48" s="9">
         <v>47</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="D48" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="29" t="s">
+      <c r="E48" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G48" s="27"/>
+      <c r="G48" s="26"/>
       <c r="J48" s="5" t="s">
         <v>369</v>
       </c>
@@ -3454,22 +3459,22 @@
       <c r="A49" s="9">
         <v>48</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D49" s="29" t="s">
+      <c r="D49" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E49" s="29" t="s">
+      <c r="E49" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="F49" s="29" t="s">
+      <c r="F49" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G49" s="27"/>
+      <c r="G49" s="26"/>
       <c r="J49" s="5" t="s">
         <v>369</v>
       </c>
@@ -3480,22 +3485,22 @@
       <c r="A50" s="9">
         <v>49</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E50" s="29" t="s">
+      <c r="E50" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F50" s="29" t="s">
+      <c r="F50" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G50" s="27"/>
+      <c r="G50" s="26"/>
       <c r="J50" s="5" t="s">
         <v>369</v>
       </c>
@@ -3506,22 +3511,22 @@
       <c r="A51" s="9">
         <v>50</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="29" t="s">
+      <c r="D51" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="F51" s="29" t="s">
+      <c r="F51" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G51" s="27"/>
+      <c r="G51" s="26"/>
       <c r="J51" s="5" t="s">
         <v>369</v>
       </c>
@@ -3532,22 +3537,22 @@
       <c r="A52" s="9">
         <v>51</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E52" s="29" t="s">
+      <c r="E52" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="F52" s="29" t="s">
+      <c r="F52" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G52" s="27"/>
+      <c r="G52" s="26"/>
       <c r="J52" s="5" t="s">
         <v>369</v>
       </c>
@@ -3558,22 +3563,22 @@
       <c r="A53" s="9">
         <v>52</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D53" s="29" t="s">
+      <c r="D53" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="29" t="s">
+      <c r="E53" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="F53" s="29" t="s">
+      <c r="F53" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G53" s="27"/>
+      <c r="G53" s="26"/>
       <c r="J53" s="5" t="s">
         <v>369</v>
       </c>
@@ -3584,22 +3589,22 @@
       <c r="A54" s="9">
         <v>53</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D54" s="29" t="s">
+      <c r="D54" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E54" s="29" t="s">
+      <c r="E54" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G54" s="27"/>
+      <c r="G54" s="26"/>
       <c r="J54" s="5" t="s">
         <v>369</v>
       </c>
@@ -3610,22 +3615,22 @@
       <c r="A55" s="9">
         <v>54</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="F55" s="29" t="s">
+      <c r="F55" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G55" s="27"/>
+      <c r="G55" s="26"/>
       <c r="J55" s="5" t="s">
         <v>369</v>
       </c>
@@ -3636,48 +3641,48 @@
       <c r="A56" s="9">
         <v>55</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="G56" s="27"/>
+      <c r="G56" s="26"/>
       <c r="J56" s="5" t="s">
         <v>369</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="1:12" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>56</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="29" t="s">
+      <c r="F57" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="G57" s="27"/>
+      <c r="G57" s="26"/>
       <c r="J57" s="5" t="s">
         <v>368</v>
       </c>
@@ -3690,22 +3695,22 @@
       <c r="A58" s="9">
         <v>57</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="29" t="s">
+      <c r="D58" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E58" s="29" t="s">
+      <c r="E58" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="F58" s="29" t="s">
+      <c r="F58" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="G58" s="27"/>
+      <c r="G58" s="26"/>
       <c r="J58" s="5" t="s">
         <v>368</v>
       </c>
@@ -3718,22 +3723,22 @@
       <c r="A59" s="9">
         <v>58</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="29" t="s">
+      <c r="D59" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E59" s="29" t="s">
+      <c r="E59" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="F59" s="29" t="s">
+      <c r="F59" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="G59" s="27"/>
+      <c r="G59" s="26"/>
       <c r="J59" s="5" t="s">
         <v>368</v>
       </c>
@@ -3746,22 +3751,22 @@
       <c r="A60" s="9">
         <v>59</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E60" s="29" t="s">
+      <c r="E60" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="F60" s="29" t="s">
+      <c r="F60" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="G60" s="27"/>
+      <c r="G60" s="26"/>
       <c r="J60" s="5" t="s">
         <v>368</v>
       </c>
@@ -3774,22 +3779,22 @@
       <c r="A61" s="9">
         <v>60</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="29" t="s">
+      <c r="D61" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F61" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="G61" s="27"/>
+      <c r="G61" s="26"/>
       <c r="J61" s="5" t="s">
         <v>368</v>
       </c>
@@ -3802,22 +3807,22 @@
       <c r="A62" s="9">
         <v>61</v>
       </c>
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="F62" s="29" t="s">
+      <c r="F62" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="G62" s="27"/>
+      <c r="G62" s="26"/>
       <c r="J62" s="5" t="s">
         <v>368</v>
       </c>
@@ -3830,22 +3835,22 @@
       <c r="A63" s="9">
         <v>62</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="29" t="s">
+      <c r="D63" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F63" s="29" t="s">
+      <c r="F63" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="G63" s="27"/>
+      <c r="G63" s="26"/>
       <c r="J63" s="5" t="s">
         <v>368</v>
       </c>
@@ -3858,22 +3863,22 @@
       <c r="A64" s="9">
         <v>63</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="F64" s="29" t="s">
+      <c r="F64" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="G64" s="27"/>
+      <c r="G64" s="26"/>
       <c r="J64" s="5" t="s">
         <v>368</v>
       </c>
@@ -3886,22 +3891,22 @@
       <c r="A65" s="9">
         <v>64</v>
       </c>
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="F65" s="29" t="s">
+      <c r="F65" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="G65" s="27"/>
+      <c r="G65" s="26"/>
       <c r="J65" s="5" t="s">
         <v>368</v>
       </c>
@@ -3914,22 +3919,22 @@
       <c r="A66" s="9">
         <v>65</v>
       </c>
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E66" s="29" t="s">
+      <c r="E66" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="F66" s="29" t="s">
+      <c r="F66" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="G66" s="27"/>
+      <c r="G66" s="26"/>
       <c r="J66" s="5" t="s">
         <v>368</v>
       </c>
@@ -3942,22 +3947,22 @@
       <c r="A67" s="9">
         <v>66</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E67" s="29" t="s">
+      <c r="E67" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="29" t="s">
+      <c r="F67" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="G67" s="27"/>
+      <c r="G67" s="26"/>
       <c r="J67" s="5" t="s">
         <v>368</v>
       </c>
@@ -3970,22 +3975,22 @@
       <c r="A68" s="9">
         <v>67</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E68" s="29" t="s">
+      <c r="E68" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="G68" s="27"/>
+      <c r="G68" s="26"/>
       <c r="J68" s="5" t="s">
         <v>368</v>
       </c>
@@ -3998,22 +4003,22 @@
       <c r="A69" s="9">
         <v>68</v>
       </c>
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D69" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="F69" s="29" t="s">
+      <c r="F69" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="27"/>
+      <c r="G69" s="26"/>
       <c r="J69" s="5" t="s">
         <v>368</v>
       </c>
@@ -4026,22 +4031,22 @@
       <c r="A70" s="9">
         <v>69</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D70" s="29" t="s">
+      <c r="D70" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="E70" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="G70" s="27"/>
+      <c r="G70" s="26"/>
       <c r="J70" s="5" t="s">
         <v>368</v>
       </c>
@@ -4054,22 +4059,22 @@
       <c r="A71" s="9">
         <v>70</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="29" t="s">
+      <c r="E71" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="G71" s="27"/>
+      <c r="G71" s="26"/>
       <c r="J71" s="5" t="s">
         <v>368</v>
       </c>
@@ -4082,22 +4087,22 @@
       <c r="A72" s="9">
         <v>71</v>
       </c>
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D72" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E72" s="29" t="s">
+      <c r="E72" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="F72" s="29" t="s">
+      <c r="F72" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="G72" s="27"/>
+      <c r="G72" s="26"/>
       <c r="J72" s="5" t="s">
         <v>368</v>
       </c>
@@ -4110,22 +4115,22 @@
       <c r="A73" s="9">
         <v>72</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D73" s="29" t="s">
+      <c r="D73" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E73" s="29" t="s">
+      <c r="E73" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="G73" s="27"/>
+      <c r="G73" s="26"/>
       <c r="J73" s="5" t="s">
         <v>368</v>
       </c>
@@ -4138,22 +4143,22 @@
       <c r="A74" s="9">
         <v>73</v>
       </c>
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D74" s="29" t="s">
+      <c r="D74" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E74" s="29" t="s">
+      <c r="E74" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="G74" s="27"/>
+      <c r="G74" s="26"/>
       <c r="J74" s="5" t="s">
         <v>368</v>
       </c>
@@ -4166,22 +4171,22 @@
       <c r="A75" s="9">
         <v>74</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D75" s="29" t="s">
+      <c r="D75" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E75" s="29" t="s">
+      <c r="E75" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F75" s="29" t="s">
+      <c r="F75" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="G75" s="27"/>
+      <c r="G75" s="26"/>
       <c r="J75" s="5" t="s">
         <v>368</v>
       </c>
@@ -4194,22 +4199,22 @@
       <c r="A76" s="9">
         <v>75</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D76" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="F76" s="29" t="s">
+      <c r="F76" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="G76" s="27"/>
+      <c r="G76" s="26"/>
       <c r="J76" s="5" t="s">
         <v>368</v>
       </c>
@@ -4222,22 +4227,22 @@
       <c r="A77" s="9">
         <v>76</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D77" s="29" t="s">
+      <c r="D77" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E77" s="29" t="s">
+      <c r="E77" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="29" t="s">
+      <c r="F77" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="G77" s="27"/>
+      <c r="G77" s="26"/>
       <c r="J77" s="5" t="s">
         <v>368</v>
       </c>
@@ -4246,26 +4251,26 @@
       </c>
       <c r="L77" s="5"/>
     </row>
-    <row r="78" spans="1:12" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>77</v>
       </c>
-      <c r="B78" s="27" t="s">
+      <c r="B78" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D78" s="29" t="s">
+      <c r="D78" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E78" s="29" t="s">
+      <c r="E78" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="G78" s="27"/>
+      <c r="G78" s="26"/>
       <c r="J78" s="5" t="s">
         <v>368</v>
       </c>
@@ -4274,26 +4279,26 @@
       </c>
       <c r="L78" s="5"/>
     </row>
-    <row r="79" spans="1:12" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="39" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>78</v>
       </c>
-      <c r="B79" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C79" s="29" t="s">
+      <c r="B79" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C79" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="29" t="s">
+      <c r="D79" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E79" s="29" t="s">
+      <c r="E79" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="F79" s="29" t="s">
+      <c r="F79" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="G79" s="27"/>
+      <c r="G79" s="26"/>
       <c r="J79" s="5" t="s">
         <v>368</v>
       </c>
@@ -4304,20 +4309,20 @@
       <c r="A80" s="9">
         <v>79</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="29" t="s">
+      <c r="D80" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E80" s="29" t="s">
+      <c r="E80" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="F80" s="32"/>
-      <c r="G80" s="27" t="s">
+      <c r="F80" s="31"/>
+      <c r="G80" s="26" t="s">
         <v>365</v>
       </c>
       <c r="J80" s="5" t="s">
@@ -4327,30 +4332,30 @@
       <c r="L80" s="5"/>
     </row>
     <row r="81" spans="1:15" ht="90" x14ac:dyDescent="0.25">
-      <c r="A81" s="15">
+      <c r="A81" s="14">
         <v>80</v>
       </c>
-      <c r="B81" s="30" t="s">
+      <c r="B81" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="C81" s="31" t="s">
+      <c r="C81" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="D81" s="31" t="s">
+      <c r="D81" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="E81" s="31" t="s">
+      <c r="E81" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="F81" s="31" t="s">
+      <c r="F81" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="G81" s="30"/>
-      <c r="J81" s="43" t="s">
+      <c r="G81" s="29"/>
+      <c r="J81" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="K81" s="43"/>
-      <c r="L81" s="43"/>
+      <c r="K81" s="42"/>
+      <c r="L81" s="42"/>
       <c r="M81">
         <v>5</v>
       </c>
@@ -4365,22 +4370,22 @@
       <c r="A82" s="9">
         <v>81</v>
       </c>
-      <c r="B82" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="29" t="s">
+      <c r="B82" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C82" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="D82" s="29" t="s">
+      <c r="D82" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E82" s="29" t="s">
+      <c r="E82" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="F82" s="29" t="s">
+      <c r="F82" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G82" s="27"/>
+      <c r="G82" s="26"/>
       <c r="J82" s="5" t="s">
         <v>371</v>
       </c>
@@ -4391,22 +4396,22 @@
       <c r="A83" s="9">
         <v>82</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="D83" s="29" t="s">
+      <c r="D83" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E83" s="29" t="s">
+      <c r="E83" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="F83" s="29" t="s">
+      <c r="F83" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="G83" s="27"/>
+      <c r="G83" s="26"/>
       <c r="J83" s="5" t="s">
         <v>371</v>
       </c>
@@ -4417,22 +4422,22 @@
       <c r="A84" s="9">
         <v>83</v>
       </c>
-      <c r="B84" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C84" s="29" t="s">
+      <c r="B84" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C84" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="D84" s="29" t="s">
+      <c r="D84" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E84" s="29" t="s">
+      <c r="E84" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="F84" s="29" t="s">
+      <c r="F84" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G84" s="27"/>
+      <c r="G84" s="26"/>
       <c r="J84" s="5" t="s">
         <v>371</v>
       </c>
@@ -4443,22 +4448,22 @@
       <c r="A85" s="9">
         <v>84</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="D85" s="29" t="s">
+      <c r="D85" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E85" s="29" t="s">
+      <c r="E85" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="F85" s="29" t="s">
+      <c r="F85" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="G85" s="27"/>
+      <c r="G85" s="26"/>
       <c r="J85" s="5" t="s">
         <v>371</v>
       </c>
@@ -4469,22 +4474,22 @@
       <c r="A86" s="9">
         <v>85</v>
       </c>
-      <c r="B86" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C86" s="29" t="s">
+      <c r="B86" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C86" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="D86" s="29" t="s">
+      <c r="D86" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="F86" s="29" t="s">
+      <c r="F86" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G86" s="27" t="s">
+      <c r="G86" s="26" t="s">
         <v>366</v>
       </c>
       <c r="J86" s="5" t="s">
@@ -4497,22 +4502,22 @@
       <c r="A87" s="9">
         <v>86</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="D87" s="29" t="s">
+      <c r="D87" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="F87" s="29" t="s">
+      <c r="F87" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="G87" s="27" t="s">
+      <c r="G87" s="26" t="s">
         <v>366</v>
       </c>
       <c r="J87" s="5" t="s">
@@ -4525,22 +4530,22 @@
       <c r="A88" s="9">
         <v>87</v>
       </c>
-      <c r="B88" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C88" s="29" t="s">
+      <c r="B88" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C88" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D88" s="29" t="s">
+      <c r="D88" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="F88" s="29" t="s">
+      <c r="F88" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G88" s="27"/>
+      <c r="G88" s="26"/>
       <c r="J88" s="5" t="s">
         <v>371</v>
       </c>
@@ -4551,22 +4556,22 @@
       <c r="A89" s="9">
         <v>88</v>
       </c>
-      <c r="B89" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C89" s="29" t="s">
+      <c r="B89" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C89" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="29" t="s">
+      <c r="D89" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E89" s="29" t="s">
+      <c r="E89" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="F89" s="29" t="s">
+      <c r="F89" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G89" s="27"/>
+      <c r="G89" s="26"/>
       <c r="J89" s="5" t="s">
         <v>371</v>
       </c>
@@ -4577,22 +4582,22 @@
       <c r="A90" s="9">
         <v>89</v>
       </c>
-      <c r="B90" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C90" s="29" t="s">
+      <c r="B90" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C90" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D90" s="29" t="s">
+      <c r="D90" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E90" s="29" t="s">
+      <c r="E90" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="F90" s="29" t="s">
+      <c r="F90" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G90" s="40"/>
+      <c r="G90" s="39"/>
       <c r="J90" s="5" t="s">
         <v>371</v>
       </c>
@@ -4603,22 +4608,22 @@
       <c r="A91" s="9">
         <v>90</v>
       </c>
-      <c r="B91" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C91" s="29" t="s">
+      <c r="B91" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C91" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D91" s="29" t="s">
+      <c r="D91" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E91" s="29" t="s">
+      <c r="E91" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="F91" s="29" t="s">
+      <c r="F91" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G91" s="40"/>
+      <c r="G91" s="39"/>
       <c r="J91" s="5" t="s">
         <v>371</v>
       </c>
@@ -4629,22 +4634,22 @@
       <c r="A92" s="9">
         <v>91</v>
       </c>
-      <c r="B92" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C92" s="29" t="s">
+      <c r="B92" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C92" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D92" s="29" t="s">
+      <c r="D92" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E92" s="29" t="s">
+      <c r="E92" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="F92" s="29" t="s">
+      <c r="F92" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G92" s="40"/>
+      <c r="G92" s="39"/>
       <c r="J92" s="5" t="s">
         <v>371</v>
       </c>
@@ -4655,22 +4660,22 @@
       <c r="A93" s="9">
         <v>92</v>
       </c>
-      <c r="B93" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C93" s="29" t="s">
+      <c r="B93" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C93" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D93" s="29" t="s">
+      <c r="D93" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E93" s="29" t="s">
+      <c r="E93" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="F93" s="29" t="s">
+      <c r="F93" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G93" s="40"/>
+      <c r="G93" s="39"/>
       <c r="J93" s="5" t="s">
         <v>371</v>
       </c>
@@ -4681,22 +4686,22 @@
       <c r="A94" s="9">
         <v>93</v>
       </c>
-      <c r="B94" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C94" s="29" t="s">
+      <c r="B94" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C94" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D94" s="29" t="s">
+      <c r="D94" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E94" s="29" t="s">
+      <c r="E94" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="F94" s="29" t="s">
+      <c r="F94" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G94" s="40"/>
+      <c r="G94" s="39"/>
       <c r="J94" s="5" t="s">
         <v>371</v>
       </c>
@@ -4707,22 +4712,22 @@
       <c r="A95" s="9">
         <v>94</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C95" s="29" t="s">
+      <c r="B95" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C95" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D95" s="29" t="s">
+      <c r="D95" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E95" s="29" t="s">
+      <c r="E95" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="F95" s="29" t="s">
+      <c r="F95" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G95" s="40"/>
+      <c r="G95" s="39"/>
       <c r="J95" s="5" t="s">
         <v>371</v>
       </c>
@@ -4733,22 +4738,22 @@
       <c r="A96" s="9">
         <v>95</v>
       </c>
-      <c r="B96" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C96" s="29" t="s">
+      <c r="B96" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C96" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D96" s="29" t="s">
+      <c r="D96" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E96" s="29" t="s">
+      <c r="E96" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="F96" s="29" t="s">
+      <c r="F96" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G96" s="40"/>
+      <c r="G96" s="39"/>
       <c r="J96" s="5" t="s">
         <v>371</v>
       </c>
@@ -4759,22 +4764,22 @@
       <c r="A97" s="9">
         <v>96</v>
       </c>
-      <c r="B97" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C97" s="29" t="s">
+      <c r="B97" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C97" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D97" s="29" t="s">
+      <c r="D97" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E97" s="29" t="s">
+      <c r="E97" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="F97" s="29" t="s">
+      <c r="F97" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G97" s="40"/>
+      <c r="G97" s="39"/>
       <c r="J97" s="5" t="s">
         <v>371</v>
       </c>
@@ -4785,22 +4790,22 @@
       <c r="A98" s="9">
         <v>97</v>
       </c>
-      <c r="B98" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C98" s="29" t="s">
+      <c r="B98" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C98" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D98" s="29" t="s">
+      <c r="D98" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E98" s="29" t="s">
+      <c r="E98" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="F98" s="29" t="s">
+      <c r="F98" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G98" s="40"/>
+      <c r="G98" s="39"/>
       <c r="J98" s="5" t="s">
         <v>371</v>
       </c>
@@ -4811,22 +4816,22 @@
       <c r="A99" s="9">
         <v>98</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C99" s="29" t="s">
+      <c r="C99" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D99" s="29" t="s">
+      <c r="D99" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E99" s="29" t="s">
+      <c r="E99" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="F99" s="29" t="s">
+      <c r="F99" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G99" s="40"/>
+      <c r="G99" s="39"/>
       <c r="J99" s="5" t="s">
         <v>371</v>
       </c>
@@ -4837,22 +4842,22 @@
       <c r="A100" s="9">
         <v>99</v>
       </c>
-      <c r="B100" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C100" s="29" t="s">
+      <c r="B100" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C100" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D100" s="29" t="s">
+      <c r="D100" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E100" s="29" t="s">
+      <c r="E100" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="F100" s="29" t="s">
+      <c r="F100" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G100" s="40"/>
+      <c r="G100" s="39"/>
       <c r="J100" s="5" t="s">
         <v>371</v>
       </c>
@@ -4863,22 +4868,22 @@
       <c r="A101" s="9">
         <v>100</v>
       </c>
-      <c r="B101" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C101" s="29" t="s">
+      <c r="B101" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C101" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D101" s="29" t="s">
+      <c r="D101" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E101" s="29" t="s">
+      <c r="E101" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="F101" s="29" t="s">
+      <c r="F101" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G101" s="40"/>
+      <c r="G101" s="39"/>
       <c r="J101" s="5" t="s">
         <v>371</v>
       </c>
@@ -4889,22 +4894,22 @@
       <c r="A102" s="9">
         <v>101</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C102" s="29" t="s">
+      <c r="B102" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C102" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D102" s="29" t="s">
+      <c r="D102" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E102" s="29" t="s">
+      <c r="E102" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="F102" s="29" t="s">
+      <c r="F102" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G102" s="40"/>
+      <c r="G102" s="39"/>
       <c r="J102" s="5" t="s">
         <v>371</v>
       </c>
@@ -4915,22 +4920,22 @@
       <c r="A103" s="9">
         <v>102</v>
       </c>
-      <c r="B103" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C103" s="29" t="s">
+      <c r="B103" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C103" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D103" s="29" t="s">
+      <c r="D103" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E103" s="29" t="s">
+      <c r="E103" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="F103" s="29" t="s">
+      <c r="F103" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G103" s="40"/>
+      <c r="G103" s="39"/>
       <c r="J103" s="5" t="s">
         <v>371</v>
       </c>
@@ -4941,22 +4946,22 @@
       <c r="A104" s="9">
         <v>103</v>
       </c>
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D104" s="29" t="s">
+      <c r="D104" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E104" s="29" t="s">
+      <c r="E104" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="F104" s="29" t="s">
+      <c r="F104" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G104" s="40"/>
+      <c r="G104" s="39"/>
       <c r="J104" s="5" t="s">
         <v>371</v>
       </c>
@@ -4967,22 +4972,22 @@
       <c r="A105" s="9">
         <v>104</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C105" s="29" t="s">
+      <c r="B105" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C105" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D105" s="29" t="s">
+      <c r="D105" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E105" s="29" t="s">
+      <c r="E105" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="F105" s="29" t="s">
+      <c r="F105" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G105" s="40"/>
+      <c r="G105" s="39"/>
       <c r="J105" s="5" t="s">
         <v>371</v>
       </c>
@@ -4993,22 +4998,22 @@
       <c r="A106" s="9">
         <v>105</v>
       </c>
-      <c r="B106" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C106" s="29" t="s">
+      <c r="B106" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C106" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D106" s="29" t="s">
+      <c r="D106" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E106" s="29" t="s">
+      <c r="E106" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="F106" s="29" t="s">
+      <c r="F106" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G106" s="40"/>
+      <c r="G106" s="39"/>
       <c r="J106" s="5" t="s">
         <v>371</v>
       </c>
@@ -5019,22 +5024,22 @@
       <c r="A107" s="9">
         <v>106</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C107" s="29" t="s">
+      <c r="B107" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C107" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D107" s="29" t="s">
+      <c r="D107" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E107" s="29" t="s">
+      <c r="E107" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="F107" s="29" t="s">
+      <c r="F107" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G107" s="40"/>
+      <c r="G107" s="39"/>
       <c r="J107" s="5" t="s">
         <v>371</v>
       </c>
@@ -5045,22 +5050,22 @@
       <c r="A108" s="9">
         <v>107</v>
       </c>
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D108" s="29" t="s">
+      <c r="D108" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E108" s="29" t="s">
+      <c r="E108" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="F108" s="29" t="s">
+      <c r="F108" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G108" s="40"/>
+      <c r="G108" s="39"/>
       <c r="J108" s="5" t="s">
         <v>371</v>
       </c>
@@ -5071,22 +5076,22 @@
       <c r="A109" s="9">
         <v>108</v>
       </c>
-      <c r="B109" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C109" s="29" t="s">
+      <c r="B109" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C109" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D109" s="29" t="s">
+      <c r="D109" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E109" s="29" t="s">
+      <c r="E109" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="F109" s="29" t="s">
+      <c r="F109" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G109" s="40"/>
+      <c r="G109" s="39"/>
       <c r="J109" s="5" t="s">
         <v>371</v>
       </c>
@@ -5097,22 +5102,22 @@
       <c r="A110" s="9">
         <v>109</v>
       </c>
-      <c r="B110" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C110" s="29" t="s">
+      <c r="B110" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="29" t="s">
+      <c r="D110" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="E110" s="29" t="s">
+      <c r="E110" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F110" s="29" t="s">
+      <c r="F110" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="G110" s="40"/>
+      <c r="G110" s="39"/>
       <c r="J110" s="5" t="s">
         <v>371</v>
       </c>
@@ -5123,22 +5128,22 @@
       <c r="A111" s="9">
         <v>110</v>
       </c>
-      <c r="B111" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C111" s="29" t="s">
+      <c r="B111" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C111" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="D111" s="29" t="s">
+      <c r="D111" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E111" s="29" t="s">
+      <c r="E111" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="F111" s="29" t="s">
+      <c r="F111" s="28" t="s">
         <v>345</v>
       </c>
-      <c r="G111" s="40"/>
+      <c r="G111" s="39"/>
       <c r="J111" s="5" t="s">
         <v>371</v>
       </c>
@@ -5158,22 +5163,22 @@
       <c r="A112" s="9">
         <v>111</v>
       </c>
-      <c r="B112" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C112" s="29" t="s">
+      <c r="B112" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="D112" s="28" t="s">
+      <c r="D112" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="E112" s="29" t="s">
+      <c r="E112" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="F112" s="29" t="s">
+      <c r="F112" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="G112" s="40"/>
+      <c r="G112" s="39"/>
       <c r="J112" s="5" t="s">
         <v>371</v>
       </c>
@@ -5193,22 +5198,22 @@
       <c r="A113" s="9">
         <v>112</v>
       </c>
-      <c r="B113" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C113" s="29" t="s">
+      <c r="B113" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C113" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="D113" s="28" t="s">
+      <c r="D113" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="E113" s="29" t="s">
+      <c r="E113" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="F113" s="29" t="s">
+      <c r="F113" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="G113" s="40"/>
+      <c r="G113" s="39"/>
       <c r="J113" s="5" t="s">
         <v>371</v>
       </c>
@@ -5228,22 +5233,22 @@
       <c r="A114" s="9">
         <v>113</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C114" s="29" t="s">
+      <c r="B114" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D114" s="28" t="s">
+      <c r="D114" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="E114" s="29" t="s">
+      <c r="E114" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="F114" s="29" t="s">
+      <c r="F114" s="28" t="s">
         <v>348</v>
       </c>
-      <c r="G114" s="40"/>
+      <c r="G114" s="39"/>
       <c r="J114" s="5" t="s">
         <v>371</v>
       </c>
@@ -5263,22 +5268,22 @@
       <c r="A115" s="9">
         <v>114</v>
       </c>
-      <c r="B115" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C115" s="29" t="s">
+      <c r="B115" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C115" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="D115" s="28" t="s">
+      <c r="D115" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="E115" s="29" t="s">
+      <c r="E115" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="F115" s="29" t="s">
+      <c r="F115" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="G115" s="40"/>
+      <c r="G115" s="39"/>
       <c r="J115" s="5" t="s">
         <v>371</v>
       </c>
@@ -5298,22 +5303,22 @@
       <c r="A116" s="9">
         <v>115</v>
       </c>
-      <c r="B116" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C116" s="29" t="s">
+      <c r="B116" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C116" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="D116" s="28" t="s">
+      <c r="D116" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="E116" s="29" t="s">
+      <c r="E116" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="F116" s="29" t="s">
+      <c r="F116" s="28" t="s">
         <v>350</v>
       </c>
-      <c r="G116" s="40"/>
+      <c r="G116" s="39"/>
       <c r="J116" s="5" t="s">
         <v>371</v>
       </c>
@@ -5333,22 +5338,22 @@
       <c r="A117" s="9">
         <v>116</v>
       </c>
-      <c r="B117" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C117" s="29" t="s">
+      <c r="B117" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C117" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="D117" s="28" t="s">
+      <c r="D117" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="E117" s="29" t="s">
+      <c r="E117" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="F117" s="29" t="s">
+      <c r="F117" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="G117" s="40"/>
+      <c r="G117" s="39"/>
       <c r="J117" s="5" t="s">
         <v>371</v>
       </c>
@@ -5368,22 +5373,22 @@
       <c r="A118" s="9">
         <v>117</v>
       </c>
-      <c r="B118" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C118" s="29" t="s">
+      <c r="B118" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C118" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="D118" s="28" t="s">
+      <c r="D118" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E118" s="29" t="s">
+      <c r="E118" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="F118" s="29" t="s">
+      <c r="F118" s="28" t="s">
         <v>352</v>
       </c>
-      <c r="G118" s="40"/>
+      <c r="G118" s="39"/>
       <c r="J118" s="5" t="s">
         <v>371</v>
       </c>
@@ -5403,22 +5408,22 @@
       <c r="A119" s="9">
         <v>118</v>
       </c>
-      <c r="B119" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C119" s="29" t="s">
+      <c r="B119" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C119" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D119" s="28" t="s">
+      <c r="D119" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="E119" s="29" t="s">
+      <c r="E119" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="F119" s="29" t="s">
+      <c r="F119" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="G119" s="40"/>
+      <c r="G119" s="39"/>
       <c r="J119" s="5" t="s">
         <v>371</v>
       </c>
@@ -5434,26 +5439,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" ht="39" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>119</v>
       </c>
-      <c r="B120" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C120" s="29" t="s">
+      <c r="B120" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C120" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D120" s="28" t="s">
+      <c r="D120" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="E120" s="29" t="s">
+      <c r="E120" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="F120" s="29" t="s">
+      <c r="F120" s="28" t="s">
         <v>354</v>
       </c>
-      <c r="G120" s="40"/>
+      <c r="G120" s="39"/>
       <c r="J120" s="5" t="s">
         <v>371</v>
       </c>
@@ -5473,18 +5478,18 @@
       <c r="A121" s="9">
         <v>120</v>
       </c>
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C121" s="29" t="s">
+      <c r="C121" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="D121" s="32"/>
-      <c r="E121" s="28" t="s">
+      <c r="D121" s="31"/>
+      <c r="E121" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="F121" s="32"/>
-      <c r="G121" s="40"/>
+      <c r="F121" s="31"/>
+      <c r="G121" s="39"/>
       <c r="J121" s="5" t="s">
         <v>371</v>
       </c>
@@ -5495,22 +5500,22 @@
       <c r="A122" s="9">
         <v>121</v>
       </c>
-      <c r="B122" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C122" s="29" t="s">
+      <c r="B122" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C122" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="D122" s="28" t="s">
+      <c r="D122" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="E122" s="29" t="s">
+      <c r="E122" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="F122" s="29" t="s">
+      <c r="F122" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="G122" s="40"/>
+      <c r="G122" s="39"/>
       <c r="J122" s="5" t="s">
         <v>371</v>
       </c>
@@ -5530,22 +5535,22 @@
       <c r="A123" s="9">
         <v>122</v>
       </c>
-      <c r="B123" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C123" s="29" t="s">
+      <c r="B123" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C123" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="D123" s="28" t="s">
+      <c r="D123" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="E123" s="29" t="s">
+      <c r="E123" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="F123" s="29" t="s">
+      <c r="F123" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="G123" s="40"/>
+      <c r="G123" s="39"/>
       <c r="J123" s="5" t="s">
         <v>371</v>
       </c>
@@ -5565,22 +5570,22 @@
       <c r="A124" s="9">
         <v>123</v>
       </c>
-      <c r="B124" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C124" s="29" t="s">
+      <c r="B124" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="D124" s="28" t="s">
+      <c r="D124" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E124" s="29" t="s">
+      <c r="E124" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F124" s="29" t="s">
+      <c r="F124" s="28" t="s">
         <v>357</v>
       </c>
-      <c r="G124" s="40"/>
+      <c r="G124" s="39"/>
       <c r="J124" s="5" t="s">
         <v>371</v>
       </c>
@@ -5596,26 +5601,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="77.25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>124</v>
       </c>
-      <c r="B125" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C125" s="29" t="s">
+      <c r="B125" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="D125" s="28" t="s">
+      <c r="D125" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="E125" s="29" t="s">
+      <c r="E125" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="F125" s="29" t="s">
+      <c r="F125" s="28" t="s">
         <v>358</v>
       </c>
-      <c r="G125" s="40"/>
+      <c r="G125" s="39"/>
       <c r="J125" s="5" t="s">
         <v>371</v>
       </c>
@@ -5635,18 +5640,18 @@
       <c r="A126" s="9">
         <v>125</v>
       </c>
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C126" s="29" t="s">
+      <c r="C126" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="D126" s="32"/>
-      <c r="E126" s="28" t="s">
+      <c r="D126" s="31"/>
+      <c r="E126" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="F126" s="32"/>
-      <c r="G126" s="40"/>
+      <c r="F126" s="31"/>
+      <c r="G126" s="39"/>
       <c r="J126" s="5" t="s">
         <v>371</v>
       </c>
@@ -5657,22 +5662,22 @@
       <c r="A127" s="9">
         <v>126</v>
       </c>
-      <c r="B127" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C127" s="29" t="s">
+      <c r="B127" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C127" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D127" s="28" t="s">
+      <c r="D127" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="E127" s="29" t="s">
+      <c r="E127" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="F127" s="29" t="s">
+      <c r="F127" s="28" t="s">
         <v>359</v>
       </c>
-      <c r="G127" s="40"/>
+      <c r="G127" s="39"/>
       <c r="J127" s="5" t="s">
         <v>371</v>
       </c>
@@ -5692,22 +5697,22 @@
       <c r="A128" s="9">
         <v>127</v>
       </c>
-      <c r="B128" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C128" s="29" t="s">
+      <c r="B128" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C128" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="D128" s="28" t="s">
+      <c r="D128" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="E128" s="29" t="s">
+      <c r="E128" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="F128" s="29" t="s">
+      <c r="F128" s="28" t="s">
         <v>360</v>
       </c>
-      <c r="G128" s="40"/>
+      <c r="G128" s="39"/>
       <c r="J128" s="5" t="s">
         <v>371</v>
       </c>
@@ -5718,22 +5723,22 @@
       <c r="A129" s="9">
         <v>128</v>
       </c>
-      <c r="B129" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C129" s="29" t="s">
+      <c r="B129" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="D129" s="28" t="s">
+      <c r="D129" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="E129" s="29" t="s">
+      <c r="E129" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="F129" s="29" t="s">
+      <c r="F129" s="28" t="s">
         <v>361</v>
       </c>
-      <c r="G129" s="40"/>
+      <c r="G129" s="39"/>
       <c r="J129" s="5" t="s">
         <v>371</v>
       </c>
@@ -5753,18 +5758,18 @@
       <c r="A130" s="9">
         <v>129</v>
       </c>
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C130" s="29" t="s">
+      <c r="C130" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="D130" s="32"/>
-      <c r="E130" s="28" t="s">
+      <c r="D130" s="31"/>
+      <c r="E130" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="F130" s="32"/>
-      <c r="G130" s="40"/>
+      <c r="F130" s="31"/>
+      <c r="G130" s="39"/>
       <c r="J130" s="5" t="s">
         <v>371</v>
       </c>
@@ -5775,20 +5780,20 @@
       <c r="A131" s="9">
         <v>130</v>
       </c>
-      <c r="B131" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C131" s="29" t="s">
+      <c r="B131" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C131" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="D131" s="28" t="s">
+      <c r="D131" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="E131" s="28" t="s">
+      <c r="E131" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="F131" s="32"/>
-      <c r="G131" s="40"/>
+      <c r="F131" s="31"/>
+      <c r="G131" s="39"/>
       <c r="J131" s="5" t="s">
         <v>371</v>
       </c>
@@ -5808,22 +5813,22 @@
       <c r="A132" s="9">
         <v>132</v>
       </c>
-      <c r="B132" s="27" t="s">
+      <c r="B132" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C132" s="28" t="s">
+      <c r="C132" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="D132" s="28" t="s">
+      <c r="D132" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E132" s="28" t="s">
+      <c r="E132" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="F132" s="28" t="s">
+      <c r="F132" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="G132" s="40"/>
+      <c r="G132" s="39"/>
       <c r="J132" s="5" t="s">
         <v>368</v>
       </c>
@@ -5834,22 +5839,22 @@
       <c r="A133" s="9">
         <v>133</v>
       </c>
-      <c r="B133" s="27" t="s">
+      <c r="B133" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C133" s="28" t="s">
+      <c r="C133" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="D133" s="28" t="s">
+      <c r="D133" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E133" s="28" t="s">
+      <c r="E133" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="F133" s="28" t="s">
+      <c r="F133" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="G133" s="40"/>
+      <c r="G133" s="39"/>
       <c r="J133" s="5" t="s">
         <v>368</v>
       </c>
@@ -5860,22 +5865,22 @@
       <c r="A134" s="9">
         <v>134</v>
       </c>
-      <c r="B134" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C134" s="28" t="s">
+      <c r="B134" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="D134" s="28" t="s">
+      <c r="D134" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E134" s="28" t="s">
+      <c r="E134" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="F134" s="28" t="s">
+      <c r="F134" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G134" s="40"/>
+      <c r="G134" s="39"/>
       <c r="J134" s="5" t="s">
         <v>368</v>
       </c>
@@ -5883,45 +5888,45 @@
       <c r="L134" s="5"/>
     </row>
     <row r="135" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A135" s="15">
+      <c r="A135" s="14">
         <v>135</v>
       </c>
-      <c r="B135" s="30"/>
-      <c r="C135" s="33" t="s">
+      <c r="B135" s="29"/>
+      <c r="C135" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="D135" s="33" t="s">
+      <c r="D135" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="E135" s="33" t="s">
+      <c r="E135" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="F135" s="38"/>
-      <c r="G135" s="41"/>
-      <c r="J135" s="43"/>
-      <c r="K135" s="43"/>
-      <c r="L135" s="43"/>
+      <c r="F135" s="37"/>
+      <c r="G135" s="40"/>
+      <c r="J135" s="42"/>
+      <c r="K135" s="42"/>
+      <c r="L135" s="42"/>
     </row>
     <row r="136" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>136</v>
       </c>
-      <c r="B136" s="27" t="s">
+      <c r="B136" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C136" s="28" t="s">
+      <c r="C136" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="D136" s="28" t="s">
+      <c r="D136" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E136" s="28" t="s">
+      <c r="E136" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="F136" s="28" t="s">
+      <c r="F136" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G136" s="40"/>
+      <c r="G136" s="39"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
@@ -5930,22 +5935,22 @@
       <c r="A137" s="9">
         <v>137</v>
       </c>
-      <c r="B137" s="27" t="s">
+      <c r="B137" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C137" s="28" t="s">
+      <c r="C137" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="D137" s="28" t="s">
+      <c r="D137" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E137" s="28" t="s">
+      <c r="E137" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="F137" s="28" t="s">
+      <c r="F137" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G137" s="40"/>
+      <c r="G137" s="39"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
@@ -5954,22 +5959,22 @@
       <c r="A138" s="9">
         <v>138</v>
       </c>
-      <c r="B138" s="27" t="s">
+      <c r="B138" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C138" s="28" t="s">
+      <c r="C138" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="D138" s="28" t="s">
+      <c r="D138" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E138" s="28" t="s">
+      <c r="E138" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="F138" s="28" t="s">
+      <c r="F138" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G138" s="40"/>
+      <c r="G138" s="39"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
       <c r="L138" s="5"/>
@@ -5978,22 +5983,22 @@
       <c r="A139" s="9">
         <v>139</v>
       </c>
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C139" s="28" t="s">
+      <c r="C139" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="D139" s="28" t="s">
+      <c r="D139" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E139" s="28" t="s">
+      <c r="E139" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="F139" s="28" t="s">
+      <c r="F139" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G139" s="40"/>
+      <c r="G139" s="39"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
       <c r="L139" s="5"/>
@@ -6002,22 +6007,22 @@
       <c r="A140" s="9">
         <v>140</v>
       </c>
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C140" s="28" t="s">
+      <c r="C140" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="D140" s="28" t="s">
+      <c r="D140" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E140" s="28" t="s">
+      <c r="E140" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="F140" s="28" t="s">
+      <c r="F140" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G140" s="40"/>
+      <c r="G140" s="39"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
       <c r="L140" s="5"/>
@@ -6026,22 +6031,22 @@
       <c r="A141" s="9">
         <v>141</v>
       </c>
-      <c r="B141" s="27" t="s">
+      <c r="B141" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C141" s="28" t="s">
+      <c r="C141" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="D141" s="28" t="s">
+      <c r="D141" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E141" s="28" t="s">
+      <c r="E141" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="F141" s="28" t="s">
+      <c r="F141" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G141" s="40"/>
+      <c r="G141" s="39"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
       <c r="L141" s="5"/>
@@ -6050,22 +6055,22 @@
       <c r="A142" s="9">
         <v>142</v>
       </c>
-      <c r="B142" s="27" t="s">
+      <c r="B142" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="C142" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="D142" s="28" t="s">
+      <c r="D142" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E142" s="28" t="s">
+      <c r="E142" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="F142" s="28" t="s">
+      <c r="F142" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G142" s="40"/>
+      <c r="G142" s="39"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
       <c r="L142" s="5"/>
@@ -6074,22 +6079,22 @@
       <c r="A143" s="9">
         <v>143</v>
       </c>
-      <c r="B143" s="27" t="s">
+      <c r="B143" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C143" s="28" t="s">
+      <c r="C143" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="D143" s="28" t="s">
+      <c r="D143" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E143" s="28" t="s">
+      <c r="E143" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="F143" s="28" t="s">
+      <c r="F143" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G143" s="40"/>
+      <c r="G143" s="39"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
       <c r="L143" s="5"/>
@@ -6098,22 +6103,22 @@
       <c r="A144" s="9">
         <v>144</v>
       </c>
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C144" s="28" t="s">
+      <c r="C144" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="D144" s="28" t="s">
+      <c r="D144" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E144" s="28" t="s">
+      <c r="E144" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="F144" s="28" t="s">
+      <c r="F144" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G144" s="40"/>
+      <c r="G144" s="39"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
       <c r="L144" s="5"/>
@@ -6122,22 +6127,22 @@
       <c r="A145" s="9">
         <v>145</v>
       </c>
-      <c r="B145" s="27" t="s">
+      <c r="B145" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C145" s="28" t="s">
+      <c r="C145" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="D145" s="28" t="s">
+      <c r="D145" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E145" s="28" t="s">
+      <c r="E145" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="F145" s="28" t="s">
+      <c r="F145" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="40"/>
+      <c r="G145" s="39"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
@@ -6146,20 +6151,20 @@
       <c r="A146" s="9">
         <v>146</v>
       </c>
-      <c r="B146" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C146" s="28" t="s">
+      <c r="B146" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C146" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="D146" s="32"/>
-      <c r="E146" s="28" t="s">
+      <c r="D146" s="31"/>
+      <c r="E146" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="F146" s="28" t="s">
+      <c r="F146" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G146" s="40"/>
+      <c r="G146" s="39"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
@@ -6168,20 +6173,20 @@
       <c r="A147" s="9">
         <v>147</v>
       </c>
-      <c r="B147" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C147" s="28" t="s">
+      <c r="B147" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C147" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="D147" s="32"/>
-      <c r="E147" s="28" t="s">
+      <c r="D147" s="31"/>
+      <c r="E147" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="F147" s="28" t="s">
+      <c r="F147" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G147" s="40"/>
+      <c r="G147" s="39"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
@@ -6190,20 +6195,20 @@
       <c r="A148" s="9">
         <v>148</v>
       </c>
-      <c r="B148" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C148" s="28" t="s">
+      <c r="B148" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C148" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="D148" s="32"/>
-      <c r="E148" s="28" t="s">
+      <c r="D148" s="31"/>
+      <c r="E148" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="F148" s="28" t="s">
+      <c r="F148" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G148" s="40"/>
+      <c r="G148" s="39"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
@@ -6212,20 +6217,20 @@
       <c r="A149" s="9">
         <v>149</v>
       </c>
-      <c r="B149" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C149" s="28" t="s">
+      <c r="B149" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C149" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="D149" s="32"/>
-      <c r="E149" s="28" t="s">
+      <c r="D149" s="31"/>
+      <c r="E149" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="F149" s="28" t="s">
+      <c r="F149" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G149" s="40"/>
+      <c r="G149" s="39"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
@@ -6234,20 +6239,20 @@
       <c r="A150" s="9">
         <v>150</v>
       </c>
-      <c r="B150" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C150" s="28" t="s">
+      <c r="B150" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C150" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="D150" s="32"/>
-      <c r="E150" s="28" t="s">
+      <c r="D150" s="31"/>
+      <c r="E150" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="F150" s="28" t="s">
+      <c r="F150" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G150" s="40"/>
+      <c r="G150" s="39"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
@@ -6256,20 +6261,20 @@
       <c r="A151" s="9">
         <v>151</v>
       </c>
-      <c r="B151" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C151" s="28" t="s">
+      <c r="B151" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C151" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="D151" s="32"/>
-      <c r="E151" s="28" t="s">
+      <c r="D151" s="31"/>
+      <c r="E151" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="F151" s="28" t="s">
+      <c r="F151" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G151" s="40"/>
+      <c r="G151" s="39"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
@@ -6278,20 +6283,20 @@
       <c r="A152" s="9">
         <v>152</v>
       </c>
-      <c r="B152" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C152" s="28" t="s">
+      <c r="B152" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C152" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="D152" s="32"/>
-      <c r="E152" s="28" t="s">
+      <c r="D152" s="31"/>
+      <c r="E152" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="F152" s="28" t="s">
+      <c r="F152" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G152" s="40"/>
+      <c r="G152" s="39"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
@@ -6300,20 +6305,20 @@
       <c r="A153" s="9">
         <v>153</v>
       </c>
-      <c r="B153" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C153" s="28" t="s">
+      <c r="B153" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C153" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="D153" s="32"/>
-      <c r="E153" s="28" t="s">
+      <c r="D153" s="31"/>
+      <c r="E153" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="F153" s="28" t="s">
+      <c r="F153" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G153" s="40"/>
+      <c r="G153" s="39"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
@@ -6322,20 +6327,20 @@
       <c r="A154" s="9">
         <v>154</v>
       </c>
-      <c r="B154" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C154" s="28" t="s">
+      <c r="B154" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C154" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="D154" s="32"/>
-      <c r="E154" s="28" t="s">
+      <c r="D154" s="31"/>
+      <c r="E154" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="F154" s="28" t="s">
+      <c r="F154" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G154" s="40"/>
+      <c r="G154" s="39"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
@@ -6344,20 +6349,20 @@
       <c r="A155" s="9">
         <v>155</v>
       </c>
-      <c r="B155" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C155" s="28" t="s">
+      <c r="B155" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C155" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="D155" s="32"/>
-      <c r="E155" s="28" t="s">
+      <c r="D155" s="31"/>
+      <c r="E155" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="F155" s="28" t="s">
+      <c r="F155" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G155" s="40"/>
+      <c r="G155" s="39"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
@@ -6366,20 +6371,20 @@
       <c r="A156" s="9">
         <v>156</v>
       </c>
-      <c r="B156" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C156" s="28" t="s">
+      <c r="B156" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C156" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="D156" s="32"/>
-      <c r="E156" s="28" t="s">
+      <c r="D156" s="31"/>
+      <c r="E156" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="F156" s="28" t="s">
+      <c r="F156" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G156" s="40"/>
+      <c r="G156" s="39"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
@@ -6388,22 +6393,22 @@
       <c r="A157" s="9">
         <v>157</v>
       </c>
-      <c r="B157" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C157" s="28" t="s">
+      <c r="B157" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="D157" s="28" t="s">
+      <c r="D157" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E157" s="28" t="s">
+      <c r="E157" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="F157" s="28" t="s">
+      <c r="F157" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="G157" s="40"/>
+      <c r="G157" s="39"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
@@ -6412,22 +6417,22 @@
       <c r="A158" s="9">
         <v>158</v>
       </c>
-      <c r="B158" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C158" s="28" t="s">
+      <c r="B158" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C158" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="D158" s="28" t="s">
+      <c r="D158" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E158" s="28" t="s">
+      <c r="E158" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="F158" s="28" t="s">
+      <c r="F158" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="G158" s="40"/>
+      <c r="G158" s="39"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
@@ -6436,22 +6441,22 @@
       <c r="A159" s="9">
         <v>159</v>
       </c>
-      <c r="B159" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C159" s="28" t="s">
+      <c r="B159" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C159" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="D159" s="28" t="s">
+      <c r="D159" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E159" s="28" t="s">
+      <c r="E159" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="F159" s="28" t="s">
+      <c r="F159" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="G159" s="40"/>
+      <c r="G159" s="39"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
@@ -6460,22 +6465,22 @@
       <c r="A160" s="9">
         <v>160</v>
       </c>
-      <c r="B160" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C160" s="28" t="s">
+      <c r="B160" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C160" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="D160" s="28" t="s">
+      <c r="D160" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E160" s="28" t="s">
+      <c r="E160" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="F160" s="28" t="s">
+      <c r="F160" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="G160" s="40"/>
+      <c r="G160" s="39"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
@@ -6484,22 +6489,22 @@
       <c r="A161" s="9">
         <v>161</v>
       </c>
-      <c r="B161" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C161" s="28" t="s">
+      <c r="B161" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C161" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="D161" s="28" t="s">
+      <c r="D161" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E161" s="28" t="s">
+      <c r="E161" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="F161" s="28" t="s">
+      <c r="F161" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="G161" s="40"/>
+      <c r="G161" s="39"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
@@ -6508,22 +6513,22 @@
       <c r="A162" s="9">
         <v>162</v>
       </c>
-      <c r="B162" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C162" s="28" t="s">
+      <c r="B162" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C162" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="D162" s="28" t="s">
+      <c r="D162" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E162" s="28" t="s">
+      <c r="E162" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="F162" s="28" t="s">
+      <c r="F162" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="G162" s="40"/>
+      <c r="G162" s="39"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
       <c r="L162" s="5"/>
@@ -6532,22 +6537,22 @@
       <c r="A163" s="9">
         <v>163</v>
       </c>
-      <c r="B163" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C163" s="28" t="s">
+      <c r="B163" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C163" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="D163" s="28" t="s">
+      <c r="D163" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E163" s="28" t="s">
+      <c r="E163" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="F163" s="28" t="s">
+      <c r="F163" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="G163" s="40"/>
+      <c r="G163" s="39"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
       <c r="L163" s="5"/>
@@ -6556,22 +6561,22 @@
       <c r="A164" s="9">
         <v>164</v>
       </c>
-      <c r="B164" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C164" s="28" t="s">
+      <c r="B164" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C164" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="D164" s="28" t="s">
+      <c r="D164" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E164" s="28" t="s">
+      <c r="E164" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="F164" s="28" t="s">
+      <c r="F164" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="G164" s="40"/>
+      <c r="G164" s="39"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
@@ -6580,22 +6585,22 @@
       <c r="A165" s="9">
         <v>165</v>
       </c>
-      <c r="B165" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C165" s="28" t="s">
+      <c r="B165" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C165" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="D165" s="28" t="s">
+      <c r="D165" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E165" s="28" t="s">
+      <c r="E165" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="F165" s="28" t="s">
+      <c r="F165" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="G165" s="40"/>
+      <c r="G165" s="39"/>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
       <c r="L165" s="5"/>
@@ -6604,22 +6609,22 @@
       <c r="A166" s="9">
         <v>166</v>
       </c>
-      <c r="B166" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C166" s="28" t="s">
+      <c r="B166" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C166" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="D166" s="28" t="s">
+      <c r="D166" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E166" s="28" t="s">
+      <c r="E166" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="F166" s="28" t="s">
+      <c r="F166" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="G166" s="40"/>
+      <c r="G166" s="39"/>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
@@ -6628,22 +6633,22 @@
       <c r="A167" s="9">
         <v>167</v>
       </c>
-      <c r="B167" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C167" s="28" t="s">
+      <c r="B167" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C167" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="D167" s="28" t="s">
+      <c r="D167" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E167" s="28" t="s">
+      <c r="E167" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="F167" s="28" t="s">
+      <c r="F167" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="G167" s="40"/>
+      <c r="G167" s="39"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
@@ -6652,22 +6657,22 @@
       <c r="A168" s="9">
         <v>168</v>
       </c>
-      <c r="B168" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C168" s="28" t="s">
+      <c r="B168" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C168" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="D168" s="28" t="s">
+      <c r="D168" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E168" s="28" t="s">
+      <c r="E168" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="F168" s="28" t="s">
+      <c r="F168" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="G168" s="40"/>
+      <c r="G168" s="39"/>
       <c r="J168" s="5" t="s">
         <v>368</v>
       </c>
@@ -6687,22 +6692,22 @@
       <c r="A169" s="9">
         <v>169</v>
       </c>
-      <c r="B169" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C169" s="28" t="s">
+      <c r="B169" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C169" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="D169" s="28" t="s">
+      <c r="D169" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="E169" s="28" t="s">
+      <c r="E169" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="F169" s="28" t="s">
+      <c r="F169" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="G169" s="40"/>
+      <c r="G169" s="39"/>
       <c r="J169" s="5" t="s">
         <v>368</v>
       </c>
@@ -6722,20 +6727,20 @@
       <c r="A170" s="9">
         <v>170</v>
       </c>
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C170" s="28" t="s">
+      <c r="C170" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="D170" s="32"/>
-      <c r="E170" s="28" t="s">
+      <c r="D170" s="31"/>
+      <c r="E170" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="F170" s="28" t="s">
+      <c r="F170" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="G170" s="40"/>
+      <c r="G170" s="39"/>
       <c r="J170" s="5" t="s">
         <v>368</v>
       </c>
@@ -6746,20 +6751,20 @@
       <c r="A171" s="9">
         <v>171</v>
       </c>
-      <c r="B171" s="27" t="s">
+      <c r="B171" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C171" s="28" t="s">
+      <c r="C171" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="D171" s="32"/>
-      <c r="E171" s="28" t="s">
+      <c r="D171" s="31"/>
+      <c r="E171" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="F171" s="28" t="s">
+      <c r="F171" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="G171" s="40"/>
+      <c r="G171" s="39"/>
       <c r="J171" s="5" t="s">
         <v>368</v>
       </c>
@@ -6770,22 +6775,22 @@
       <c r="A172" s="9">
         <v>172</v>
       </c>
-      <c r="B172" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C172" s="28" t="s">
+      <c r="B172" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C172" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D172" s="28" t="s">
+      <c r="D172" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="E172" s="34" t="s">
+      <c r="E172" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="F172" s="28" t="s">
+      <c r="F172" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="G172" s="40"/>
+      <c r="G172" s="39"/>
       <c r="J172" s="5" t="s">
         <v>368</v>
       </c>
@@ -6796,22 +6801,22 @@
       <c r="A173" s="9">
         <v>173</v>
       </c>
-      <c r="B173" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C173" s="28" t="s">
+      <c r="B173" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C173" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="D173" s="28" t="s">
+      <c r="D173" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="E173" s="28" t="s">
+      <c r="E173" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="F173" s="28" t="s">
+      <c r="F173" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="G173" s="40"/>
+      <c r="G173" s="39"/>
       <c r="J173" s="5" t="s">
         <v>368</v>
       </c>
@@ -6822,22 +6827,22 @@
       <c r="A174" s="9">
         <v>174</v>
       </c>
-      <c r="B174" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C174" s="28" t="s">
+      <c r="B174" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C174" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="D174" s="28" t="s">
+      <c r="D174" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="E174" s="28" t="s">
+      <c r="E174" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="F174" s="28" t="s">
+      <c r="F174" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="G174" s="40"/>
+      <c r="G174" s="39"/>
       <c r="J174" s="5" t="s">
         <v>368</v>
       </c>
@@ -6848,22 +6853,22 @@
       <c r="A175" s="9">
         <v>175</v>
       </c>
-      <c r="B175" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C175" s="28" t="s">
+      <c r="B175" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C175" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="D175" s="28" t="s">
+      <c r="D175" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="E175" s="28" t="s">
+      <c r="E175" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="F175" s="28" t="s">
+      <c r="F175" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="G175" s="40"/>
+      <c r="G175" s="39"/>
       <c r="J175" s="5" t="s">
         <v>368</v>
       </c>
@@ -6874,22 +6879,22 @@
       <c r="A176" s="9">
         <v>176</v>
       </c>
-      <c r="B176" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C176" s="28" t="s">
+      <c r="B176" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C176" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="D176" s="28" t="s">
+      <c r="D176" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="E176" s="28" t="s">
+      <c r="E176" s="27" t="s">
         <v>264</v>
       </c>
-      <c r="F176" s="28" t="s">
+      <c r="F176" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="G176" s="40"/>
+      <c r="G176" s="39"/>
       <c r="J176" s="5" t="s">
         <v>368</v>
       </c>
@@ -6900,22 +6905,22 @@
       <c r="A177" s="9">
         <v>177</v>
       </c>
-      <c r="B177" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C177" s="28" t="s">
+      <c r="B177" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C177" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="D177" s="28" t="s">
+      <c r="D177" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="E177" s="28" t="s">
+      <c r="E177" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="F177" s="28" t="s">
+      <c r="F177" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="G177" s="40"/>
+      <c r="G177" s="39"/>
       <c r="J177" s="5" t="s">
         <v>368</v>
       </c>
@@ -6926,22 +6931,22 @@
       <c r="A178" s="9">
         <v>178</v>
       </c>
-      <c r="B178" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C178" s="28" t="s">
+      <c r="B178" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C178" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="D178" s="28" t="s">
+      <c r="D178" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="E178" s="28" t="s">
+      <c r="E178" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="F178" s="28" t="s">
+      <c r="F178" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="G178" s="40"/>
+      <c r="G178" s="39"/>
       <c r="J178" s="5" t="s">
         <v>368</v>
       </c>
@@ -6961,22 +6966,22 @@
       <c r="A179" s="9">
         <v>179</v>
       </c>
-      <c r="B179" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C179" s="28" t="s">
+      <c r="B179" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C179" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="D179" s="28" t="s">
+      <c r="D179" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="E179" s="28" t="s">
+      <c r="E179" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="F179" s="28" t="s">
+      <c r="F179" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="G179" s="40"/>
+      <c r="G179" s="39"/>
       <c r="J179" s="5" t="s">
         <v>368</v>
       </c>
@@ -6996,20 +7001,20 @@
       <c r="A180" s="9">
         <v>180</v>
       </c>
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C180" s="28" t="s">
+      <c r="C180" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="D180" s="32"/>
-      <c r="E180" s="28" t="s">
+      <c r="D180" s="31"/>
+      <c r="E180" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="F180" s="28" t="s">
+      <c r="F180" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="G180" s="40"/>
+      <c r="G180" s="39"/>
       <c r="J180" s="5" t="s">
         <v>368</v>
       </c>
@@ -7020,20 +7025,20 @@
       <c r="A181" s="9">
         <v>181</v>
       </c>
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C181" s="28" t="s">
+      <c r="C181" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="D181" s="32"/>
-      <c r="E181" s="28" t="s">
+      <c r="D181" s="31"/>
+      <c r="E181" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="F181" s="28" t="s">
+      <c r="F181" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="G181" s="40"/>
+      <c r="G181" s="39"/>
       <c r="J181" s="5" t="s">
         <v>368</v>
       </c>
@@ -7044,22 +7049,22 @@
       <c r="A182" s="9">
         <v>182</v>
       </c>
-      <c r="B182" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C182" s="28" t="s">
+      <c r="B182" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C182" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="D182" s="28" t="s">
+      <c r="D182" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E182" s="28" t="s">
+      <c r="E182" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="F182" s="28" t="s">
+      <c r="F182" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="G182" s="40"/>
+      <c r="G182" s="39"/>
       <c r="J182" s="5" t="s">
         <v>368</v>
       </c>
@@ -7070,22 +7075,22 @@
       <c r="A183" s="9">
         <v>183</v>
       </c>
-      <c r="B183" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C183" s="28" t="s">
+      <c r="B183" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C183" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="D183" s="28" t="s">
+      <c r="D183" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="E183" s="28" t="s">
+      <c r="E183" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="F183" s="28" t="s">
+      <c r="F183" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="G183" s="40"/>
+      <c r="G183" s="39"/>
       <c r="J183" s="5" t="s">
         <v>368</v>
       </c>
@@ -7096,22 +7101,22 @@
       <c r="A184" s="9">
         <v>184</v>
       </c>
-      <c r="B184" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C184" s="28" t="s">
+      <c r="B184" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C184" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="D184" s="28" t="s">
+      <c r="D184" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="E184" s="28" t="s">
+      <c r="E184" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="F184" s="28" t="s">
+      <c r="F184" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="G184" s="40"/>
+      <c r="G184" s="39"/>
       <c r="J184" s="5" t="s">
         <v>368</v>
       </c>
@@ -7122,22 +7127,22 @@
       <c r="A185" s="9">
         <v>185</v>
       </c>
-      <c r="B185" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C185" s="28" t="s">
+      <c r="B185" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C185" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="D185" s="28" t="s">
+      <c r="D185" s="27" t="s">
         <v>287</v>
       </c>
-      <c r="E185" s="28" t="s">
+      <c r="E185" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="F185" s="28" t="s">
+      <c r="F185" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="G185" s="40"/>
+      <c r="G185" s="39"/>
       <c r="J185" s="5" t="s">
         <v>368</v>
       </c>
@@ -7148,22 +7153,22 @@
       <c r="A186" s="9">
         <v>186</v>
       </c>
-      <c r="B186" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C186" s="28" t="s">
+      <c r="B186" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C186" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="D186" s="28" t="s">
+      <c r="D186" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="E186" s="28" t="s">
+      <c r="E186" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="F186" s="28" t="s">
+      <c r="F186" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="G186" s="40"/>
+      <c r="G186" s="39"/>
       <c r="J186" s="5" t="s">
         <v>368</v>
       </c>
@@ -7174,22 +7179,22 @@
       <c r="A187" s="9">
         <v>187</v>
       </c>
-      <c r="B187" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C187" s="28" t="s">
+      <c r="B187" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C187" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="D187" s="28" t="s">
+      <c r="D187" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="E187" s="28" t="s">
+      <c r="E187" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="F187" s="28" t="s">
+      <c r="F187" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="G187" s="40"/>
+      <c r="G187" s="39"/>
       <c r="J187" s="5" t="s">
         <v>368</v>
       </c>
@@ -7200,20 +7205,20 @@
       <c r="A188" s="9">
         <v>188</v>
       </c>
-      <c r="B188" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C188" s="28" t="s">
+      <c r="B188" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C188" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D188" s="34" t="s">
+      <c r="D188" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E188" s="34" t="s">
+      <c r="E188" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="F188" s="39"/>
-      <c r="G188" s="35"/>
+      <c r="F188" s="38"/>
+      <c r="G188" s="34"/>
       <c r="J188" s="5"/>
       <c r="K188" s="5">
         <v>63</v>
@@ -7226,20 +7231,20 @@
       <c r="A189" s="9">
         <v>189</v>
       </c>
-      <c r="B189" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C189" s="28" t="s">
+      <c r="B189" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C189" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="D189" s="34" t="s">
+      <c r="D189" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E189" s="34" t="s">
+      <c r="E189" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="F189" s="35"/>
-      <c r="G189" s="35"/>
+      <c r="F189" s="34"/>
+      <c r="G189" s="34"/>
       <c r="J189" s="5" t="s">
         <v>369</v>
       </c>
@@ -7254,20 +7259,20 @@
       <c r="A190" s="9">
         <v>190</v>
       </c>
-      <c r="B190" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C190" s="28" t="s">
+      <c r="B190" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C190" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D190" s="34" t="s">
+      <c r="D190" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E190" s="34" t="s">
+      <c r="E190" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="F190" s="35"/>
-      <c r="G190" s="35"/>
+      <c r="F190" s="34"/>
+      <c r="G190" s="34"/>
       <c r="J190" s="5" t="s">
         <v>369</v>
       </c>
@@ -7282,20 +7287,20 @@
       <c r="A191" s="9">
         <v>191</v>
       </c>
-      <c r="B191" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C191" s="28" t="s">
+      <c r="B191" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C191" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="D191" s="34" t="s">
+      <c r="D191" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E191" s="34" t="s">
+      <c r="E191" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="F191" s="35"/>
-      <c r="G191" s="35"/>
+      <c r="F191" s="34"/>
+      <c r="G191" s="34"/>
       <c r="J191" s="5" t="s">
         <v>369</v>
       </c>
@@ -7310,20 +7315,20 @@
       <c r="A192" s="9">
         <v>192</v>
       </c>
-      <c r="B192" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C192" s="28" t="s">
+      <c r="B192" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C192" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D192" s="34" t="s">
+      <c r="D192" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E192" s="34" t="s">
+      <c r="E192" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="F192" s="35"/>
-      <c r="G192" s="35"/>
+      <c r="F192" s="34"/>
+      <c r="G192" s="34"/>
       <c r="J192" s="5" t="s">
         <v>369</v>
       </c>
@@ -7338,20 +7343,20 @@
       <c r="A193" s="9">
         <v>193</v>
       </c>
-      <c r="B193" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C193" s="28" t="s">
+      <c r="B193" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C193" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="D193" s="34" t="s">
+      <c r="D193" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E193" s="34" t="s">
+      <c r="E193" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="F193" s="35"/>
-      <c r="G193" s="35"/>
+      <c r="F193" s="34"/>
+      <c r="G193" s="34"/>
       <c r="J193" s="5" t="s">
         <v>369</v>
       </c>
@@ -7366,20 +7371,20 @@
       <c r="A194" s="9">
         <v>194</v>
       </c>
-      <c r="B194" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C194" s="28" t="s">
+      <c r="B194" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C194" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D194" s="34" t="s">
+      <c r="D194" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E194" s="34" t="s">
+      <c r="E194" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="F194" s="35"/>
-      <c r="G194" s="35"/>
+      <c r="F194" s="34"/>
+      <c r="G194" s="34"/>
       <c r="J194" s="5" t="s">
         <v>369</v>
       </c>
@@ -7394,20 +7399,20 @@
       <c r="A195" s="9">
         <v>195</v>
       </c>
-      <c r="B195" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C195" s="28" t="s">
+      <c r="B195" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C195" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D195" s="34" t="s">
+      <c r="D195" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E195" s="34" t="s">
+      <c r="E195" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="F195" s="35"/>
-      <c r="G195" s="35"/>
+      <c r="F195" s="34"/>
+      <c r="G195" s="34"/>
       <c r="J195" s="5" t="s">
         <v>369</v>
       </c>
@@ -7422,20 +7427,20 @@
       <c r="A196" s="9">
         <v>196</v>
       </c>
-      <c r="B196" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C196" s="28" t="s">
+      <c r="B196" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C196" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D196" s="34" t="s">
+      <c r="D196" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E196" s="34" t="s">
+      <c r="E196" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="F196" s="35"/>
-      <c r="G196" s="35"/>
+      <c r="F196" s="34"/>
+      <c r="G196" s="34"/>
       <c r="J196" s="5" t="s">
         <v>369</v>
       </c>
@@ -7450,20 +7455,20 @@
       <c r="A197" s="9">
         <v>197</v>
       </c>
-      <c r="B197" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C197" s="28" t="s">
+      <c r="B197" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C197" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="D197" s="34" t="s">
+      <c r="D197" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E197" s="34" t="s">
+      <c r="E197" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="F197" s="35"/>
-      <c r="G197" s="35"/>
+      <c r="F197" s="34"/>
+      <c r="G197" s="34"/>
       <c r="J197" s="5" t="s">
         <v>369</v>
       </c>
@@ -7478,20 +7483,20 @@
       <c r="A198" s="9">
         <v>199</v>
       </c>
-      <c r="B198" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C198" s="29" t="s">
+      <c r="B198" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C198" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="D198" s="34" t="s">
+      <c r="D198" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E198" s="34" t="s">
+      <c r="E198" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="F198" s="35"/>
-      <c r="G198" s="35"/>
+      <c r="F198" s="34"/>
+      <c r="G198" s="34"/>
       <c r="J198" s="5" t="s">
         <v>369</v>
       </c>
@@ -7506,20 +7511,20 @@
       <c r="A199" s="9">
         <v>200</v>
       </c>
-      <c r="B199" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C199" s="29" t="s">
+      <c r="B199" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C199" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="D199" s="34" t="s">
+      <c r="D199" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E199" s="34" t="s">
+      <c r="E199" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="F199" s="35"/>
-      <c r="G199" s="35"/>
+      <c r="F199" s="34"/>
+      <c r="G199" s="34"/>
       <c r="J199" s="5" t="s">
         <v>369</v>
       </c>
@@ -7534,20 +7539,20 @@
       <c r="A200" s="9">
         <v>201</v>
       </c>
-      <c r="B200" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C200" s="29" t="s">
+      <c r="B200" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C200" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="D200" s="34" t="s">
+      <c r="D200" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E200" s="34" t="s">
+      <c r="E200" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="F200" s="35"/>
-      <c r="G200" s="35"/>
+      <c r="F200" s="34"/>
+      <c r="G200" s="34"/>
       <c r="J200" s="5" t="s">
         <v>369</v>
       </c>
@@ -7562,20 +7567,20 @@
       <c r="A201" s="9">
         <v>202</v>
       </c>
-      <c r="B201" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C201" s="29" t="s">
+      <c r="B201" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C201" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="D201" s="34" t="s">
+      <c r="D201" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E201" s="34" t="s">
+      <c r="E201" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="F201" s="35"/>
-      <c r="G201" s="35"/>
+      <c r="F201" s="34"/>
+      <c r="G201" s="34"/>
       <c r="J201" s="5" t="s">
         <v>369</v>
       </c>
@@ -7590,20 +7595,20 @@
       <c r="A202" s="9">
         <v>203</v>
       </c>
-      <c r="B202" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C202" s="29" t="s">
+      <c r="B202" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C202" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="D202" s="34" t="s">
+      <c r="D202" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E202" s="34" t="s">
+      <c r="E202" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="F202" s="35"/>
-      <c r="G202" s="35"/>
+      <c r="F202" s="34"/>
+      <c r="G202" s="34"/>
       <c r="J202" s="5" t="s">
         <v>369</v>
       </c>
@@ -7618,20 +7623,20 @@
       <c r="A203" s="9">
         <v>204</v>
       </c>
-      <c r="B203" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C203" s="29" t="s">
+      <c r="B203" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C203" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="D203" s="34" t="s">
+      <c r="D203" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E203" s="34" t="s">
+      <c r="E203" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="F203" s="35"/>
-      <c r="G203" s="35"/>
+      <c r="F203" s="34"/>
+      <c r="G203" s="34"/>
       <c r="J203" s="5" t="s">
         <v>369</v>
       </c>
@@ -7646,20 +7651,20 @@
       <c r="A204" s="9">
         <v>205</v>
       </c>
-      <c r="B204" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C204" s="29" t="s">
+      <c r="B204" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C204" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="D204" s="34" t="s">
+      <c r="D204" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E204" s="34" t="s">
+      <c r="E204" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="F204" s="35"/>
-      <c r="G204" s="35"/>
+      <c r="F204" s="34"/>
+      <c r="G204" s="34"/>
       <c r="J204" s="5" t="s">
         <v>369</v>
       </c>
@@ -7674,20 +7679,20 @@
       <c r="A205" s="9">
         <v>206</v>
       </c>
-      <c r="B205" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C205" s="29" t="s">
+      <c r="B205" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C205" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="D205" s="34" t="s">
+      <c r="D205" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E205" s="34" t="s">
+      <c r="E205" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="F205" s="35"/>
-      <c r="G205" s="35"/>
+      <c r="F205" s="34"/>
+      <c r="G205" s="34"/>
       <c r="J205" s="5" t="s">
         <v>369</v>
       </c>
@@ -7702,20 +7707,20 @@
       <c r="A206" s="9">
         <v>207</v>
       </c>
-      <c r="B206" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C206" s="29" t="s">
+      <c r="B206" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C206" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="D206" s="34" t="s">
+      <c r="D206" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E206" s="34" t="s">
+      <c r="E206" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="F206" s="35"/>
-      <c r="G206" s="35"/>
+      <c r="F206" s="34"/>
+      <c r="G206" s="34"/>
       <c r="J206" s="5" t="s">
         <v>369</v>
       </c>
@@ -7730,20 +7735,20 @@
       <c r="A207" s="9">
         <v>207</v>
       </c>
-      <c r="B207" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C207" s="29" t="s">
+      <c r="B207" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C207" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D207" s="34" t="s">
+      <c r="D207" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="E207" s="34" t="s">
+      <c r="E207" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="F207" s="35"/>
-      <c r="G207" s="35"/>
+      <c r="F207" s="34"/>
+      <c r="G207" s="34"/>
       <c r="J207" s="5" t="s">
         <v>369</v>
       </c>
@@ -7758,20 +7763,20 @@
       <c r="A208" s="9">
         <v>207</v>
       </c>
-      <c r="B208" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C208" s="34" t="s">
+      <c r="B208" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C208" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="D208" s="34" t="s">
+      <c r="D208" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E208" s="34" t="s">
+      <c r="E208" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="F208" s="35"/>
-      <c r="G208" s="35"/>
+      <c r="F208" s="34"/>
+      <c r="G208" s="34"/>
       <c r="J208" s="5" t="s">
         <v>372</v>
       </c>
@@ -7782,18 +7787,18 @@
       <c r="A209" s="9">
         <v>207</v>
       </c>
-      <c r="B209" s="35"/>
-      <c r="C209" s="34" t="s">
+      <c r="B209" s="34"/>
+      <c r="C209" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D209" s="34" t="s">
+      <c r="D209" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E209" s="34" t="s">
+      <c r="E209" s="33" t="s">
         <v>316</v>
       </c>
       <c r="F209" s="5"/>
-      <c r="G209" s="35"/>
+      <c r="G209" s="34"/>
       <c r="J209" s="5" t="s">
         <v>372</v>
       </c>
@@ -7804,22 +7809,22 @@
       <c r="A210" s="9">
         <v>207</v>
       </c>
-      <c r="B210" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C210" s="34" t="s">
+      <c r="B210" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C210" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="D210" s="34" t="s">
+      <c r="D210" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E210" s="34" t="s">
+      <c r="E210" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="F210" s="35">
+      <c r="F210" s="34">
         <v>630</v>
       </c>
-      <c r="G210" s="35"/>
+      <c r="G210" s="34"/>
       <c r="J210" s="5" t="s">
         <v>372</v>
       </c>
@@ -7832,20 +7837,20 @@
       <c r="A211" s="9">
         <v>207</v>
       </c>
-      <c r="B211" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C211" s="34" t="s">
+      <c r="B211" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C211" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D211" s="34" t="s">
+      <c r="D211" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E211" s="34" t="s">
+      <c r="E211" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="F211" s="35"/>
-      <c r="G211" s="35"/>
+      <c r="F211" s="34"/>
+      <c r="G211" s="34"/>
       <c r="J211" s="5" t="s">
         <v>372</v>
       </c>
@@ -7856,20 +7861,20 @@
       <c r="A212" s="9">
         <v>207</v>
       </c>
-      <c r="B212" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C212" s="34" t="s">
+      <c r="B212" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C212" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D212" s="34" t="s">
+      <c r="D212" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E212" s="34" t="s">
+      <c r="E212" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="F212" s="35"/>
-      <c r="G212" s="35"/>
+      <c r="F212" s="34"/>
+      <c r="G212" s="34"/>
       <c r="J212" s="5" t="s">
         <v>372</v>
       </c>
@@ -7880,20 +7885,20 @@
       <c r="A213" s="9">
         <v>207</v>
       </c>
-      <c r="B213" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C213" s="34" t="s">
+      <c r="B213" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C213" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D213" s="34" t="s">
+      <c r="D213" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E213" s="34" t="s">
+      <c r="E213" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="F213" s="35"/>
-      <c r="G213" s="35"/>
+      <c r="F213" s="34"/>
+      <c r="G213" s="34"/>
       <c r="J213" s="5" t="s">
         <v>372</v>
       </c>
@@ -7904,20 +7909,20 @@
       <c r="A214" s="9">
         <v>207</v>
       </c>
-      <c r="B214" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C214" s="34" t="s">
+      <c r="B214" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C214" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D214" s="34" t="s">
+      <c r="D214" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E214" s="34" t="s">
+      <c r="E214" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="F214" s="35"/>
-      <c r="G214" s="35"/>
+      <c r="F214" s="34"/>
+      <c r="G214" s="34"/>
       <c r="J214" s="5" t="s">
         <v>372</v>
       </c>
@@ -7928,20 +7933,20 @@
       <c r="A215" s="9">
         <v>207</v>
       </c>
-      <c r="B215" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C215" s="34" t="s">
+      <c r="B215" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C215" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D215" s="34" t="s">
+      <c r="D215" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E215" s="34" t="s">
+      <c r="E215" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="F215" s="35"/>
-      <c r="G215" s="35"/>
+      <c r="F215" s="34"/>
+      <c r="G215" s="34"/>
       <c r="J215" s="5" t="s">
         <v>372</v>
       </c>
@@ -7952,20 +7957,20 @@
       <c r="A216" s="9">
         <v>207</v>
       </c>
-      <c r="B216" s="27" t="s">
+      <c r="B216" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C216" s="34" t="s">
+      <c r="C216" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D216" s="34" t="s">
+      <c r="D216" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E216" s="34" t="s">
+      <c r="E216" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="F216" s="35"/>
-      <c r="G216" s="35"/>
+      <c r="F216" s="34"/>
+      <c r="G216" s="34"/>
       <c r="J216" s="5" t="s">
         <v>372</v>
       </c>
@@ -7976,20 +7981,20 @@
       <c r="A217" s="9">
         <v>207</v>
       </c>
-      <c r="B217" s="27" t="s">
+      <c r="B217" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C217" s="34" t="s">
+      <c r="C217" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D217" s="34" t="s">
+      <c r="D217" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E217" s="34" t="s">
+      <c r="E217" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="F217" s="35"/>
-      <c r="G217" s="35"/>
+      <c r="F217" s="34"/>
+      <c r="G217" s="34"/>
       <c r="J217" s="5" t="s">
         <v>372</v>
       </c>
@@ -8000,20 +8005,20 @@
       <c r="A218" s="9">
         <v>207</v>
       </c>
-      <c r="B218" s="27" t="s">
+      <c r="B218" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C218" s="34" t="s">
+      <c r="C218" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D218" s="34" t="s">
+      <c r="D218" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E218" s="34" t="s">
+      <c r="E218" s="33" t="s">
         <v>325</v>
       </c>
-      <c r="F218" s="35"/>
-      <c r="G218" s="35"/>
+      <c r="F218" s="34"/>
+      <c r="G218" s="34"/>
       <c r="J218" s="5" t="s">
         <v>372</v>
       </c>
@@ -8024,24 +8029,24 @@
       <c r="A219" s="9">
         <v>207</v>
       </c>
-      <c r="B219" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C219" s="34" t="s">
+      <c r="B219" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C219" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="D219" s="34" t="s">
+      <c r="D219" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E219" s="34" t="s">
+      <c r="E219" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="F219" s="35"/>
-      <c r="G219" s="35"/>
+      <c r="F219" s="34"/>
+      <c r="G219" s="34"/>
       <c r="J219" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="K219" s="35">
+      <c r="K219" s="34">
         <v>80</v>
       </c>
       <c r="L219" s="5">
@@ -8052,24 +8057,24 @@
       <c r="A220" s="9">
         <v>207</v>
       </c>
-      <c r="B220" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C220" s="34" t="s">
+      <c r="B220" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C220" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="D220" s="34" t="s">
+      <c r="D220" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E220" s="34" t="s">
+      <c r="E220" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="F220" s="35"/>
-      <c r="G220" s="35"/>
+      <c r="F220" s="34"/>
+      <c r="G220" s="34"/>
       <c r="J220" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="K220" s="35">
+      <c r="K220" s="34">
         <v>80</v>
       </c>
       <c r="L220" s="5">
@@ -8080,24 +8085,24 @@
       <c r="A221" s="9">
         <v>207</v>
       </c>
-      <c r="B221" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C221" s="34" t="s">
+      <c r="B221" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C221" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="D221" s="34" t="s">
+      <c r="D221" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E221" s="34" t="s">
+      <c r="E221" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="F221" s="35"/>
-      <c r="G221" s="35"/>
+      <c r="F221" s="34"/>
+      <c r="G221" s="34"/>
       <c r="J221" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="K221" s="35">
+      <c r="K221" s="34">
         <v>80</v>
       </c>
       <c r="L221" s="5">
@@ -8108,24 +8113,24 @@
       <c r="A222" s="9">
         <v>207</v>
       </c>
-      <c r="B222" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C222" s="34" t="s">
+      <c r="B222" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C222" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="D222" s="34" t="s">
+      <c r="D222" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E222" s="34" t="s">
+      <c r="E222" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="F222" s="35"/>
-      <c r="G222" s="35"/>
+      <c r="F222" s="34"/>
+      <c r="G222" s="34"/>
       <c r="J222" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="K222" s="35">
+      <c r="K222" s="34">
         <v>80</v>
       </c>
       <c r="L222" s="5">
@@ -8136,24 +8141,24 @@
       <c r="A223" s="9">
         <v>207</v>
       </c>
-      <c r="B223" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C223" s="34" t="s">
+      <c r="B223" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C223" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="D223" s="34" t="s">
+      <c r="D223" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E223" s="34" t="s">
+      <c r="E223" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="F223" s="35"/>
-      <c r="G223" s="35"/>
+      <c r="F223" s="34"/>
+      <c r="G223" s="34"/>
       <c r="J223" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="K223" s="35">
+      <c r="K223" s="34">
         <v>80</v>
       </c>
       <c r="L223" s="5"/>
@@ -8162,24 +8167,24 @@
       <c r="A224" s="9">
         <v>207</v>
       </c>
-      <c r="B224" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C224" s="34" t="s">
+      <c r="B224" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C224" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="D224" s="34" t="s">
+      <c r="D224" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="E224" s="34" t="s">
+      <c r="E224" s="33" t="s">
         <v>332</v>
       </c>
-      <c r="F224" s="35"/>
-      <c r="G224" s="35"/>
+      <c r="F224" s="34"/>
+      <c r="G224" s="34"/>
       <c r="J224" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="K224" s="35">
+      <c r="K224" s="34">
         <v>20</v>
       </c>
       <c r="L224" s="5">
@@ -8196,113 +8201,113 @@
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J225" s="44" t="s">
+      <c r="J225" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="B226" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C226" s="45" t="s">
+      <c r="B226" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C226" s="44" t="s">
         <v>380</v>
       </c>
-      <c r="D226" s="34" t="s">
+      <c r="D226" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E226" s="46" t="s">
+      <c r="E226" s="45" t="s">
         <v>382</v>
       </c>
       <c r="F226" t="s">
         <v>381</v>
       </c>
-      <c r="J226" s="44" t="s">
+      <c r="J226" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="C227" s="46" t="s">
+      <c r="C227" s="45" t="s">
         <v>382</v>
       </c>
-      <c r="D227" s="47" t="s">
+      <c r="D227" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="E227" s="45" t="s">
+      <c r="E227" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="J227" s="44" t="s">
+      <c r="J227" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
-      <c r="C228" s="48" t="s">
+      <c r="C228" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="D228" s="34" t="s">
+      <c r="D228" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E228" s="48" t="s">
+      <c r="E228" s="47" t="s">
         <v>384</v>
       </c>
       <c r="F228" s="5"/>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
-      <c r="I228" s="48" t="s">
+      <c r="I228" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J228" s="44" t="s">
+      <c r="J228" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
-      <c r="C229" s="48" t="s">
+      <c r="C229" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="D229" s="34" t="s">
+      <c r="D229" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E229" s="48" t="s">
+      <c r="E229" s="47" t="s">
         <v>385</v>
       </c>
       <c r="F229" s="5"/>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
-      <c r="I229" s="48" t="s">
+      <c r="I229" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J229" s="44" t="s">
+      <c r="J229" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="5"/>
-      <c r="B230" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C230" s="48" t="s">
+      <c r="B230" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C230" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="D230" s="34" t="s">
+      <c r="D230" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E230" s="48" t="s">
+      <c r="E230" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="F230" s="48">
+      <c r="F230" s="47">
         <v>500</v>
       </c>
-      <c r="G230" s="48" t="s">
+      <c r="G230" s="47" t="s">
         <v>394</v>
       </c>
       <c r="H230" s="5"/>
-      <c r="I230" s="48" t="s">
+      <c r="I230" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J230" s="44" t="s">
+      <c r="J230" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -8311,82 +8316,82 @@
       <c r="B231" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C231" s="48" t="s">
+      <c r="C231" s="47" t="s">
         <v>385</v>
       </c>
-      <c r="D231" s="34" t="s">
+      <c r="D231" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E231" s="48" t="s">
+      <c r="E231" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="F231" s="48">
+      <c r="F231" s="47">
         <v>500</v>
       </c>
-      <c r="G231" s="48" t="s">
+      <c r="G231" s="47" t="s">
         <v>396</v>
       </c>
       <c r="H231" s="5"/>
-      <c r="I231" s="48" t="s">
+      <c r="I231" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J231" s="44" t="s">
+      <c r="J231" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A232" s="5"/>
-      <c r="B232" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C232" s="48" t="s">
+      <c r="B232" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C232" s="47" t="s">
         <v>389</v>
       </c>
-      <c r="D232" s="34" t="s">
+      <c r="D232" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E232" s="49" t="s">
+      <c r="E232" s="48" t="s">
         <v>390</v>
       </c>
       <c r="F232" s="5"/>
       <c r="G232" s="5"/>
       <c r="H232" s="5"/>
-      <c r="I232" s="48" t="s">
+      <c r="I232" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J232" s="44" t="s">
+      <c r="J232" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
-      <c r="C233" s="49" t="s">
+      <c r="C233" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="D233" s="34" t="s">
+      <c r="D233" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E233" s="48" t="s">
+      <c r="E233" s="47" t="s">
         <v>391</v>
       </c>
       <c r="F233" s="5"/>
       <c r="G233" s="5"/>
       <c r="H233" s="5"/>
-      <c r="I233" s="48" t="s">
+      <c r="I233" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J233" s="44" t="s">
+      <c r="J233" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
-      <c r="C234" s="48" t="s">
+      <c r="C234" s="47" t="s">
         <v>391</v>
       </c>
-      <c r="D234" s="34" t="s">
+      <c r="D234" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E234" s="5" t="s">
@@ -8395,20 +8400,20 @@
       <c r="F234" s="5"/>
       <c r="G234" s="5"/>
       <c r="H234" s="5"/>
-      <c r="I234" s="48" t="s">
+      <c r="I234" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J234" s="44" t="s">
+      <c r="J234" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
-      <c r="C235" s="48" t="s">
+      <c r="C235" s="47" t="s">
         <v>391</v>
       </c>
-      <c r="D235" s="34" t="s">
+      <c r="D235" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E235" s="5" t="s">
@@ -8417,10 +8422,10 @@
       <c r="F235" s="5"/>
       <c r="G235" s="5"/>
       <c r="H235" s="5"/>
-      <c r="I235" s="48" t="s">
+      <c r="I235" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J235" s="44" t="s">
+      <c r="J235" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -8432,782 +8437,782 @@
       <c r="C236" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="D236" s="34" t="s">
+      <c r="D236" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E236" s="48" t="s">
+      <c r="E236" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="F236" s="48">
+      <c r="F236" s="47">
         <v>500</v>
       </c>
-      <c r="G236" s="48" t="s">
+      <c r="G236" s="47" t="s">
         <v>395</v>
       </c>
       <c r="H236" s="5"/>
-      <c r="I236" s="48" t="s">
+      <c r="I236" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J236" s="44" t="s">
+      <c r="J236" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="5"/>
-      <c r="B237" s="35" t="s">
+      <c r="B237" s="34" t="s">
         <v>55</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="D237" s="34" t="s">
+      <c r="D237" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E237" s="48" t="s">
+      <c r="E237" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="F237" s="48">
+      <c r="F237" s="47">
         <v>500</v>
       </c>
-      <c r="G237" s="48" t="s">
+      <c r="G237" s="47" t="s">
         <v>396</v>
       </c>
       <c r="H237" s="5"/>
-      <c r="I237" s="48" t="s">
+      <c r="I237" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="J237" s="44" t="s">
+      <c r="J237" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C238" s="48" t="s">
+      <c r="C238" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D238" s="34" t="s">
+      <c r="D238" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E238" t="s">
         <v>438</v>
       </c>
-      <c r="I238" s="45" t="s">
+      <c r="I238" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J238" s="44" t="s">
+      <c r="J238" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C239" s="48" t="s">
+      <c r="C239" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D239" s="34" t="s">
+      <c r="D239" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E239" t="s">
         <v>439</v>
       </c>
-      <c r="I239" s="45" t="s">
+      <c r="I239" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J239" s="44" t="s">
+      <c r="J239" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C240" s="48" t="s">
+      <c r="C240" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D240" s="34" t="s">
+      <c r="D240" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E240" t="s">
         <v>397</v>
       </c>
-      <c r="I240" s="45" t="s">
+      <c r="I240" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J240" s="44" t="s">
+      <c r="J240" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="241" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C241" s="48" t="s">
+      <c r="C241" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D241" s="34" t="s">
+      <c r="D241" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E241" t="s">
         <v>398</v>
       </c>
-      <c r="I241" s="45" t="s">
+      <c r="I241" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J241" s="44" t="s">
+      <c r="J241" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="242" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C242" s="48" t="s">
+      <c r="C242" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D242" s="34" t="s">
+      <c r="D242" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E242" t="s">
         <v>399</v>
       </c>
-      <c r="I242" s="45" t="s">
+      <c r="I242" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J242" s="44" t="s">
+      <c r="J242" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="243" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C243" s="48" t="s">
+      <c r="C243" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D243" s="34" t="s">
+      <c r="D243" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E243" t="s">
         <v>400</v>
       </c>
-      <c r="I243" s="45" t="s">
+      <c r="I243" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J243" s="44" t="s">
+      <c r="J243" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="244" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C244" s="48" t="s">
+      <c r="C244" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D244" s="34" t="s">
+      <c r="D244" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E244" t="s">
         <v>401</v>
       </c>
-      <c r="I244" s="45" t="s">
+      <c r="I244" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J244" s="44" t="s">
+      <c r="J244" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="245" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C245" s="48" t="s">
+      <c r="C245" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D245" s="34" t="s">
+      <c r="D245" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E245" t="s">
         <v>402</v>
       </c>
-      <c r="I245" s="45" t="s">
+      <c r="I245" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J245" s="44" t="s">
+      <c r="J245" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="246" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C246" s="48" t="s">
+      <c r="C246" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D246" s="34" t="s">
+      <c r="D246" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E246" t="s">
         <v>403</v>
       </c>
-      <c r="I246" s="45" t="s">
+      <c r="I246" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J246" s="44" t="s">
+      <c r="J246" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="247" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C247" s="48" t="s">
+      <c r="C247" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D247" s="34" t="s">
+      <c r="D247" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E247" t="s">
         <v>404</v>
       </c>
-      <c r="I247" s="45" t="s">
+      <c r="I247" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J247" s="44" t="s">
+      <c r="J247" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="248" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C248" s="48" t="s">
+      <c r="C248" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D248" s="34" t="s">
+      <c r="D248" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E248" t="s">
         <v>405</v>
       </c>
-      <c r="I248" s="45" t="s">
+      <c r="I248" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J248" s="44" t="s">
+      <c r="J248" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="249" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C249" s="48" t="s">
+      <c r="C249" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D249" s="34" t="s">
+      <c r="D249" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E249" t="s">
         <v>406</v>
       </c>
-      <c r="I249" s="45" t="s">
+      <c r="I249" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J249" s="44" t="s">
+      <c r="J249" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="250" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C250" s="48" t="s">
+      <c r="C250" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D250" s="34" t="s">
+      <c r="D250" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E250" t="s">
         <v>407</v>
       </c>
-      <c r="I250" s="45" t="s">
+      <c r="I250" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J250" s="44" t="s">
+      <c r="J250" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="251" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C251" s="48" t="s">
+      <c r="C251" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D251" s="34" t="s">
+      <c r="D251" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E251" t="s">
         <v>408</v>
       </c>
-      <c r="I251" s="45" t="s">
+      <c r="I251" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J251" s="44" t="s">
+      <c r="J251" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="252" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C252" s="48" t="s">
+      <c r="C252" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D252" s="34" t="s">
+      <c r="D252" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E252" t="s">
         <v>409</v>
       </c>
-      <c r="I252" s="45" t="s">
+      <c r="I252" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J252" s="44" t="s">
+      <c r="J252" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="253" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C253" s="48" t="s">
+      <c r="C253" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D253" s="34" t="s">
+      <c r="D253" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E253" t="s">
         <v>410</v>
       </c>
-      <c r="I253" s="45" t="s">
+      <c r="I253" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J253" s="44" t="s">
+      <c r="J253" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="254" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C254" s="48" t="s">
+      <c r="C254" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D254" s="34" t="s">
+      <c r="D254" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E254" t="s">
         <v>411</v>
       </c>
-      <c r="I254" s="45" t="s">
+      <c r="I254" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J254" s="44" t="s">
+      <c r="J254" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="255" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C255" s="48" t="s">
+      <c r="C255" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D255" s="34" t="s">
+      <c r="D255" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E255" t="s">
         <v>412</v>
       </c>
-      <c r="I255" s="45" t="s">
+      <c r="I255" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J255" s="44" t="s">
+      <c r="J255" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="256" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C256" s="48" t="s">
+      <c r="C256" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D256" s="34" t="s">
+      <c r="D256" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E256" t="s">
         <v>413</v>
       </c>
-      <c r="I256" s="45" t="s">
+      <c r="I256" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J256" s="44" t="s">
+      <c r="J256" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="257" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C257" s="48" t="s">
+      <c r="C257" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="D257" s="34" t="s">
+      <c r="D257" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E257" t="s">
         <v>414</v>
       </c>
-      <c r="I257" s="45" t="s">
+      <c r="I257" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J257" s="44" t="s">
+      <c r="J257" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="258" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C258" s="48" t="s">
+      <c r="C258" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D258" s="34" t="s">
+      <c r="D258" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E258" t="s">
         <v>415</v>
       </c>
-      <c r="I258" s="45" t="s">
+      <c r="I258" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J258" s="44" t="s">
+      <c r="J258" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="259" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C259" s="48" t="s">
+      <c r="C259" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D259" s="34" t="s">
+      <c r="D259" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E259" t="s">
         <v>416</v>
       </c>
-      <c r="I259" s="45" t="s">
+      <c r="I259" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J259" s="44" t="s">
+      <c r="J259" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="260" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C260" s="48" t="s">
+      <c r="C260" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D260" s="34" t="s">
+      <c r="D260" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E260" t="s">
         <v>417</v>
       </c>
-      <c r="I260" s="45" t="s">
+      <c r="I260" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J260" s="44" t="s">
+      <c r="J260" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="261" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C261" s="48" t="s">
+      <c r="C261" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D261" s="34" t="s">
+      <c r="D261" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E261" t="s">
         <v>418</v>
       </c>
-      <c r="I261" s="45" t="s">
+      <c r="I261" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J261" s="44" t="s">
+      <c r="J261" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="262" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C262" s="48" t="s">
+      <c r="C262" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D262" s="34" t="s">
+      <c r="D262" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E262" t="s">
         <v>419</v>
       </c>
-      <c r="I262" s="45" t="s">
+      <c r="I262" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J262" s="44" t="s">
+      <c r="J262" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="263" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C263" s="48" t="s">
+      <c r="C263" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D263" s="34" t="s">
+      <c r="D263" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E263" t="s">
         <v>420</v>
       </c>
-      <c r="I263" s="45" t="s">
+      <c r="I263" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J263" s="44" t="s">
+      <c r="J263" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="264" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C264" s="48" t="s">
+      <c r="C264" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D264" s="34" t="s">
+      <c r="D264" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E264" t="s">
         <v>421</v>
       </c>
-      <c r="I264" s="45" t="s">
+      <c r="I264" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J264" s="44" t="s">
+      <c r="J264" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="265" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C265" s="48" t="s">
+      <c r="C265" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D265" s="34" t="s">
+      <c r="D265" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E265" t="s">
         <v>422</v>
       </c>
-      <c r="I265" s="45" t="s">
+      <c r="I265" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J265" s="44" t="s">
+      <c r="J265" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="266" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C266" s="48" t="s">
+      <c r="C266" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D266" s="34" t="s">
+      <c r="D266" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E266" t="s">
         <v>423</v>
       </c>
-      <c r="I266" s="45" t="s">
+      <c r="I266" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J266" s="44" t="s">
+      <c r="J266" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="267" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C267" s="48" t="s">
+      <c r="C267" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D267" s="34" t="s">
+      <c r="D267" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E267" t="s">
         <v>424</v>
       </c>
-      <c r="I267" s="45" t="s">
+      <c r="I267" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J267" s="44" t="s">
+      <c r="J267" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="268" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C268" s="48" t="s">
+      <c r="C268" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D268" s="34" t="s">
+      <c r="D268" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E268" t="s">
         <v>425</v>
       </c>
-      <c r="I268" s="45" t="s">
+      <c r="I268" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J268" s="44" t="s">
+      <c r="J268" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="269" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C269" s="48" t="s">
+      <c r="C269" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D269" s="34" t="s">
+      <c r="D269" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E269" t="s">
         <v>426</v>
       </c>
-      <c r="I269" s="45" t="s">
+      <c r="I269" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J269" s="44" t="s">
+      <c r="J269" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="270" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C270" s="48" t="s">
+      <c r="C270" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D270" s="34" t="s">
+      <c r="D270" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E270" t="s">
         <v>427</v>
       </c>
-      <c r="I270" s="45" t="s">
+      <c r="I270" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J270" s="44" t="s">
+      <c r="J270" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="271" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C271" s="48" t="s">
+      <c r="C271" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D271" s="34" t="s">
+      <c r="D271" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E271" t="s">
         <v>428</v>
       </c>
-      <c r="I271" s="45" t="s">
+      <c r="I271" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J271" s="44" t="s">
+      <c r="J271" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="272" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C272" s="48" t="s">
+      <c r="C272" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D272" s="34" t="s">
+      <c r="D272" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E272" t="s">
         <v>429</v>
       </c>
-      <c r="I272" s="45" t="s">
+      <c r="I272" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J272" s="44" t="s">
+      <c r="J272" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="273" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C273" s="48" t="s">
+      <c r="C273" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D273" s="34" t="s">
+      <c r="D273" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E273" t="s">
         <v>430</v>
       </c>
-      <c r="I273" s="45" t="s">
+      <c r="I273" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J273" s="44" t="s">
+      <c r="J273" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="274" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C274" s="48" t="s">
+      <c r="C274" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D274" s="34" t="s">
+      <c r="D274" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E274" t="s">
         <v>431</v>
       </c>
-      <c r="I274" s="45" t="s">
+      <c r="I274" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J274" s="44" t="s">
+      <c r="J274" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="275" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C275" s="48" t="s">
+      <c r="C275" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D275" s="34" t="s">
+      <c r="D275" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E275" t="s">
         <v>432</v>
       </c>
-      <c r="I275" s="45" t="s">
+      <c r="I275" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J275" s="44" t="s">
+      <c r="J275" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="276" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C276" s="48" t="s">
+      <c r="C276" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D276" s="34" t="s">
+      <c r="D276" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E276" t="s">
         <v>433</v>
       </c>
-      <c r="I276" s="45" t="s">
+      <c r="I276" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J276" s="44" t="s">
+      <c r="J276" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="277" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C277" s="48" t="s">
+      <c r="C277" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D277" s="34" t="s">
+      <c r="D277" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E277" t="s">
         <v>434</v>
       </c>
-      <c r="I277" s="45" t="s">
+      <c r="I277" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J277" s="44" t="s">
+      <c r="J277" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="278" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C278" s="48" t="s">
+      <c r="C278" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D278" s="34" t="s">
+      <c r="D278" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E278" t="s">
         <v>435</v>
       </c>
-      <c r="I278" s="45" t="s">
+      <c r="I278" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J278" s="44" t="s">
+      <c r="J278" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="279" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C279" s="48" t="s">
+      <c r="C279" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D279" s="34" t="s">
+      <c r="D279" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E279" t="s">
         <v>436</v>
       </c>
-      <c r="I279" s="45" t="s">
+      <c r="I279" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J279" s="44" t="s">
+      <c r="J279" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="280" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C280" s="48" t="s">
+      <c r="C280" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="D280" s="34" t="s">
+      <c r="D280" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E280" t="s">
         <v>437</v>
       </c>
-      <c r="I280" s="45" t="s">
+      <c r="I280" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J280" s="44" t="s">
+      <c r="J280" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9221,10 +9226,10 @@
       <c r="E281" t="s">
         <v>448</v>
       </c>
-      <c r="I281" s="45" t="s">
+      <c r="I281" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J281" s="44" t="s">
+      <c r="J281" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9238,10 +9243,10 @@
       <c r="E282" t="s">
         <v>449</v>
       </c>
-      <c r="I282" s="45" t="s">
+      <c r="I282" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J282" s="44" t="s">
+      <c r="J282" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9255,10 +9260,10 @@
       <c r="E283" t="s">
         <v>450</v>
       </c>
-      <c r="I283" s="45" t="s">
+      <c r="I283" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J283" s="44" t="s">
+      <c r="J283" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9272,10 +9277,10 @@
       <c r="E284" t="s">
         <v>451</v>
       </c>
-      <c r="I284" s="45" t="s">
+      <c r="I284" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J284" s="44" t="s">
+      <c r="J284" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9289,10 +9294,10 @@
       <c r="E285" t="s">
         <v>452</v>
       </c>
-      <c r="I285" s="45" t="s">
+      <c r="I285" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J285" s="44" t="s">
+      <c r="J285" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9306,10 +9311,10 @@
       <c r="E286" t="s">
         <v>453</v>
       </c>
-      <c r="I286" s="45" t="s">
+      <c r="I286" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J286" s="44" t="s">
+      <c r="J286" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9323,10 +9328,10 @@
       <c r="E287" t="s">
         <v>454</v>
       </c>
-      <c r="I287" s="45" t="s">
+      <c r="I287" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J287" s="44" t="s">
+      <c r="J287" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9340,10 +9345,10 @@
       <c r="E288" t="s">
         <v>455</v>
       </c>
-      <c r="I288" s="45" t="s">
+      <c r="I288" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J288" s="44" t="s">
+      <c r="J288" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9357,10 +9362,10 @@
       <c r="E289" t="s">
         <v>456</v>
       </c>
-      <c r="I289" s="45" t="s">
+      <c r="I289" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J289" s="44" t="s">
+      <c r="J289" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9374,10 +9379,10 @@
       <c r="E290" t="s">
         <v>457</v>
       </c>
-      <c r="I290" s="45" t="s">
+      <c r="I290" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J290" s="44" t="s">
+      <c r="J290" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9391,10 +9396,10 @@
       <c r="E291" t="s">
         <v>458</v>
       </c>
-      <c r="I291" s="45" t="s">
+      <c r="I291" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J291" s="44" t="s">
+      <c r="J291" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9408,10 +9413,10 @@
       <c r="E292" t="s">
         <v>459</v>
       </c>
-      <c r="I292" s="45" t="s">
+      <c r="I292" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J292" s="44" t="s">
+      <c r="J292" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9425,10 +9430,10 @@
       <c r="E293" t="s">
         <v>460</v>
       </c>
-      <c r="I293" s="45" t="s">
+      <c r="I293" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J293" s="44" t="s">
+      <c r="J293" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9442,10 +9447,10 @@
       <c r="E294" t="s">
         <v>461</v>
       </c>
-      <c r="I294" s="45" t="s">
+      <c r="I294" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J294" s="44" t="s">
+      <c r="J294" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9459,10 +9464,10 @@
       <c r="E295" t="s">
         <v>462</v>
       </c>
-      <c r="I295" s="45" t="s">
+      <c r="I295" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J295" s="44" t="s">
+      <c r="J295" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9470,10 +9475,10 @@
       <c r="C296" t="s">
         <v>410</v>
       </c>
-      <c r="I296" s="45" t="s">
+      <c r="I296" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J296" s="44" t="s">
+      <c r="J296" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9481,10 +9486,10 @@
       <c r="C297" t="s">
         <v>411</v>
       </c>
-      <c r="I297" s="45" t="s">
+      <c r="I297" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J297" s="44" t="s">
+      <c r="J297" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9492,10 +9497,10 @@
       <c r="C298" t="s">
         <v>412</v>
       </c>
-      <c r="I298" s="45" t="s">
+      <c r="I298" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J298" s="44" t="s">
+      <c r="J298" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9503,10 +9508,10 @@
       <c r="C299" t="s">
         <v>413</v>
       </c>
-      <c r="I299" s="45" t="s">
+      <c r="I299" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J299" s="44" t="s">
+      <c r="J299" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9514,10 +9519,10 @@
       <c r="C300" t="s">
         <v>414</v>
       </c>
-      <c r="I300" s="45" t="s">
+      <c r="I300" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J300" s="44" t="s">
+      <c r="J300" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9531,10 +9536,10 @@
       <c r="E301" t="s">
         <v>448</v>
       </c>
-      <c r="I301" s="45" t="s">
+      <c r="I301" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J301" s="44" t="s">
+      <c r="J301" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9548,10 +9553,10 @@
       <c r="E302" t="s">
         <v>463</v>
       </c>
-      <c r="I302" s="45" t="s">
+      <c r="I302" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J302" s="44" t="s">
+      <c r="J302" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9565,10 +9570,10 @@
       <c r="E303" t="s">
         <v>464</v>
       </c>
-      <c r="I303" s="45" t="s">
+      <c r="I303" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J303" s="44" t="s">
+      <c r="J303" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9582,10 +9587,10 @@
       <c r="E304" t="s">
         <v>465</v>
       </c>
-      <c r="I304" s="45" t="s">
+      <c r="I304" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J304" s="44" t="s">
+      <c r="J304" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9599,10 +9604,10 @@
       <c r="E305" t="s">
         <v>466</v>
       </c>
-      <c r="I305" s="45" t="s">
+      <c r="I305" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J305" s="44" t="s">
+      <c r="J305" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9616,10 +9621,10 @@
       <c r="E306" t="s">
         <v>467</v>
       </c>
-      <c r="I306" s="45" t="s">
+      <c r="I306" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J306" s="44" t="s">
+      <c r="J306" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9633,10 +9638,10 @@
       <c r="E307" t="s">
         <v>468</v>
       </c>
-      <c r="I307" s="45" t="s">
+      <c r="I307" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J307" s="44" t="s">
+      <c r="J307" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9650,10 +9655,10 @@
       <c r="E308" t="s">
         <v>469</v>
       </c>
-      <c r="I308" s="45" t="s">
+      <c r="I308" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J308" s="44" t="s">
+      <c r="J308" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9661,10 +9666,10 @@
       <c r="C309" t="s">
         <v>423</v>
       </c>
-      <c r="I309" s="45" t="s">
+      <c r="I309" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J309" s="44" t="s">
+      <c r="J309" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9672,10 +9677,10 @@
       <c r="C310" t="s">
         <v>424</v>
       </c>
-      <c r="I310" s="45" t="s">
+      <c r="I310" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J310" s="44" t="s">
+      <c r="J310" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9689,10 +9694,10 @@
       <c r="E311" t="s">
         <v>470</v>
       </c>
-      <c r="I311" s="45" t="s">
+      <c r="I311" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J311" s="44" t="s">
+      <c r="J311" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9703,10 +9708,10 @@
       <c r="D312" t="s">
         <v>441</v>
       </c>
-      <c r="I312" s="45" t="s">
+      <c r="I312" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J312" s="44" t="s">
+      <c r="J312" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9717,10 +9722,10 @@
       <c r="D313" t="s">
         <v>441</v>
       </c>
-      <c r="I313" s="45" t="s">
+      <c r="I313" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J313" s="44" t="s">
+      <c r="J313" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9731,10 +9736,10 @@
       <c r="D314" t="s">
         <v>441</v>
       </c>
-      <c r="I314" s="45" t="s">
+      <c r="I314" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J314" s="44" t="s">
+      <c r="J314" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9745,10 +9750,10 @@
       <c r="D315" t="s">
         <v>447</v>
       </c>
-      <c r="I315" s="45" t="s">
+      <c r="I315" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J315" s="44" t="s">
+      <c r="J315" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9759,10 +9764,10 @@
       <c r="D316" t="s">
         <v>447</v>
       </c>
-      <c r="I316" s="45" t="s">
+      <c r="I316" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J316" s="44" t="s">
+      <c r="J316" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9773,10 +9778,10 @@
       <c r="D317" t="s">
         <v>446</v>
       </c>
-      <c r="I317" s="45" t="s">
+      <c r="I317" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J317" s="44" t="s">
+      <c r="J317" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9787,10 +9792,10 @@
       <c r="D318" t="s">
         <v>443</v>
       </c>
-      <c r="I318" s="45" t="s">
+      <c r="I318" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J318" s="44" t="s">
+      <c r="J318" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9801,10 +9806,10 @@
       <c r="D319" t="s">
         <v>441</v>
       </c>
-      <c r="I319" s="45" t="s">
+      <c r="I319" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J319" s="44" t="s">
+      <c r="J319" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9815,10 +9820,10 @@
       <c r="D320" t="s">
         <v>441</v>
       </c>
-      <c r="I320" s="45" t="s">
+      <c r="I320" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J320" s="44" t="s">
+      <c r="J320" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9829,10 +9834,10 @@
       <c r="D321" t="s">
         <v>444</v>
       </c>
-      <c r="I321" s="45" t="s">
+      <c r="I321" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J321" s="44" t="s">
+      <c r="J321" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9843,10 +9848,10 @@
       <c r="D322" t="s">
         <v>444</v>
       </c>
-      <c r="I322" s="45" t="s">
+      <c r="I322" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J322" s="44" t="s">
+      <c r="J322" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -9854,138 +9859,138 @@
       <c r="C323" t="s">
         <v>437</v>
       </c>
-      <c r="I323" s="45" t="s">
+      <c r="I323" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J323" s="44" t="s">
+      <c r="J323" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="324" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I324" s="45" t="s">
+      <c r="I324" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J324" s="44" t="s">
+      <c r="J324" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="325" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I325" s="45" t="s">
+      <c r="I325" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J325" s="44" t="s">
+      <c r="J325" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="326" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I326" s="45" t="s">
+      <c r="I326" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J326" s="44" t="s">
+      <c r="J326" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="327" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I327" s="45" t="s">
+      <c r="I327" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J327" s="44" t="s">
+      <c r="J327" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="328" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I328" s="45" t="s">
+      <c r="I328" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J328" s="44" t="s">
+      <c r="J328" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="329" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I329" s="45" t="s">
+      <c r="I329" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J329" s="44" t="s">
+      <c r="J329" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="330" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I330" s="45" t="s">
+      <c r="I330" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J330" s="44" t="s">
+      <c r="J330" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="331" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I331" s="45" t="s">
+      <c r="I331" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J331" s="44" t="s">
+      <c r="J331" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="332" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I332" s="45" t="s">
+      <c r="I332" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J332" s="44" t="s">
+      <c r="J332" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="333" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I333" s="45" t="s">
+      <c r="I333" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J333" s="44" t="s">
+      <c r="J333" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="334" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I334" s="45" t="s">
+      <c r="I334" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J334" s="44" t="s">
+      <c r="J334" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="335" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I335" s="45" t="s">
+      <c r="I335" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J335" s="44" t="s">
+      <c r="J335" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="336" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I336" s="45" t="s">
+      <c r="I336" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J336" s="44" t="s">
+      <c r="J336" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="337" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I337" s="45" t="s">
+      <c r="I337" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J337" s="44" t="s">
+      <c r="J337" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="338" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I338" s="45" t="s">
+      <c r="I338" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J338" s="44" t="s">
+      <c r="J338" s="43" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="339" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I339" s="45" t="s">
+      <c r="I339" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="J339" s="44" t="s">
+      <c r="J339" s="43" t="s">
         <v>379</v>
       </c>
     </row>
@@ -10048,10 +10053,10 @@
       <c r="E2" s="8">
         <v>19</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>12.6</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>0.114</v>
       </c>
       <c r="H2" s="6" t="s">
@@ -11896,27 +11901,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C77E5E48-C390-4456-ADB7-BF328E6A6938}">
   <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="50" t="s">
         <v>22</v>
       </c>
     </row>

--- a/upload/input.xlsx
+++ b/upload/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gass_y\Desktop\электрохозяйство\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17E83AE-895A-40A8-9EFC-B613AE22232D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C289C044-6D0D-4416-BF52-4E65023AA2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15480" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Networkall" sheetId="6" r:id="rId1"/>
@@ -21,6 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CableReference!$A$1:$H$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Networkall!$A$1:$W$364</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="458">
   <si>
     <t>№</t>
   </si>
@@ -1416,13 +1417,16 @@
   </si>
   <si>
     <t>Категория</t>
+  </si>
+  <si>
+    <t>ППГнг(А)-HF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1520,6 +1524,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1559,7 +1569,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1582,11 +1592,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1663,6 +1684,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1972,7 +1996,7 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
@@ -2111,12 +2135,14 @@
       <c r="S2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="1">
-        <v>85</v>
+      <c r="T2" s="29">
+        <v>0.4</v>
       </c>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
-      <c r="W2" s="28"/>
+      <c r="W2" s="1">
+        <v>85</v>
+      </c>
     </row>
     <row r="3" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
@@ -2160,12 +2186,14 @@
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="1">
-        <v>75</v>
+      <c r="T3" s="29">
+        <v>0.22</v>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
-      <c r="W3" s="28"/>
+      <c r="W3" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="4" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
@@ -2205,7 +2233,7 @@
         <v>140</v>
       </c>
       <c r="Q4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>53</v>
@@ -2213,12 +2241,14 @@
       <c r="S4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="T4" s="1">
-        <v>270</v>
+      <c r="T4" s="29">
+        <v>0.22</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="28"/>
+      <c r="W4" s="1">
+        <v>270</v>
+      </c>
     </row>
     <row r="5" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
@@ -2260,10 +2290,12 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+      <c r="T5" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="28"/>
+      <c r="W5" s="3"/>
     </row>
     <row r="6" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
@@ -2309,10 +2341,12 @@
       <c r="S6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="T6" s="3"/>
+      <c r="T6" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="28"/>
+      <c r="W6" s="3"/>
     </row>
     <row r="7" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
@@ -2358,10 +2392,12 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
+      <c r="T7" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-      <c r="W7" s="28"/>
+      <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A8" s="28"/>
@@ -2393,10 +2429,12 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
+      <c r="T8" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-      <c r="W8" s="28"/>
+      <c r="W8" s="3"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
@@ -2436,10 +2474,12 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
+      <c r="T9" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="28"/>
+      <c r="W9" s="3"/>
     </row>
     <row r="10" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
@@ -2475,10 +2515,12 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+      <c r="T10" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="28"/>
+      <c r="W10" s="3"/>
     </row>
     <row r="11" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
@@ -2516,10 +2558,12 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
+      <c r="T11" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="28"/>
+      <c r="W11" s="3"/>
     </row>
     <row r="12" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
@@ -2557,10 +2601,12 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="T12" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="28"/>
+      <c r="W12" s="3"/>
     </row>
     <row r="13" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
@@ -2597,17 +2643,21 @@
       <c r="P13" s="3">
         <v>160</v>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="3">
+        <v>5</v>
+      </c>
       <c r="R13" s="3" t="s">
         <v>53</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="T13" s="3"/>
+      <c r="T13" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
-      <c r="W13" s="28"/>
+      <c r="W13" s="3"/>
     </row>
     <row r="14" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
@@ -2643,10 +2693,12 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
+      <c r="T14" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
-      <c r="W14" s="28"/>
+      <c r="W14" s="3"/>
     </row>
     <row r="15" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="28">
@@ -2684,10 +2736,12 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="T15" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
-      <c r="W15" s="28"/>
+      <c r="W15" s="3"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="28">
@@ -2725,10 +2779,12 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
+      <c r="T16" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-      <c r="W16" s="28"/>
+      <c r="W16" s="3"/>
     </row>
     <row r="17" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A17" s="28">
@@ -2764,10 +2820,12 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
+      <c r="T17" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
-      <c r="W17" s="28"/>
+      <c r="W17" s="3"/>
     </row>
     <row r="18" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="28">
@@ -2805,10 +2863,12 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
+      <c r="T18" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="28"/>
+      <c r="W18" s="3"/>
     </row>
     <row r="19" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="28">
@@ -2846,10 +2906,12 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+      <c r="T19" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-      <c r="W19" s="28"/>
+      <c r="W19" s="3"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
@@ -2887,10 +2949,12 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
+      <c r="T20" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="W20" s="28"/>
+      <c r="W20" s="3"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
@@ -2928,10 +2992,12 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="T21" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="W21" s="28"/>
+      <c r="W21" s="3"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
@@ -2967,10 +3033,12 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
+      <c r="T22" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="28"/>
+      <c r="W22" s="3"/>
     </row>
     <row r="23" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
@@ -3016,10 +3084,12 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
+      <c r="T23" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
-      <c r="W23" s="28"/>
+      <c r="W23" s="3"/>
     </row>
     <row r="24" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
@@ -3058,17 +3128,21 @@
       <c r="P24" s="3">
         <v>135</v>
       </c>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3">
+        <v>5</v>
+      </c>
       <c r="R24" s="3" t="s">
         <v>86</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="T24" s="3"/>
+      <c r="T24" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
-      <c r="W24" s="28"/>
+      <c r="W24" s="3"/>
     </row>
     <row r="25" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
@@ -3102,10 +3176,12 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
+      <c r="T25" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
-      <c r="W25" s="28"/>
+      <c r="W25" s="3"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
@@ -3145,10 +3221,12 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
+      <c r="T26" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
-      <c r="W26" s="28"/>
+      <c r="W26" s="3"/>
     </row>
     <row r="27" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="28">
@@ -3182,10 +3260,12 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
+      <c r="T27" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
-      <c r="W27" s="28"/>
+      <c r="W27" s="3"/>
     </row>
     <row r="28" spans="1:23" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="28">
@@ -3221,10 +3301,12 @@
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
+      <c r="T28" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
-      <c r="W28" s="28"/>
+      <c r="W28" s="3"/>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="28">
@@ -3262,10 +3344,12 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
+      <c r="T29" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
-      <c r="W29" s="28"/>
+      <c r="W29" s="3"/>
     </row>
     <row r="30" spans="1:23" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
@@ -3301,10 +3385,12 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
+      <c r="T30" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
-      <c r="W30" s="28"/>
+      <c r="W30" s="3"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
@@ -3342,10 +3428,12 @@
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
+      <c r="T31" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
-      <c r="W31" s="28"/>
+      <c r="W31" s="3"/>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="28">
@@ -3383,10 +3471,12 @@
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
+      <c r="T32" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
-      <c r="W32" s="28"/>
+      <c r="W32" s="3"/>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
@@ -3424,10 +3514,12 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
+      <c r="T33" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
-      <c r="W33" s="28"/>
+      <c r="W33" s="3"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
@@ -3465,10 +3557,12 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
+      <c r="T34" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
-      <c r="W34" s="28"/>
+      <c r="W34" s="3"/>
     </row>
     <row r="35" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
@@ -3506,10 +3600,12 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
+      <c r="T35" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
-      <c r="W35" s="28"/>
+      <c r="W35" s="3"/>
     </row>
     <row r="36" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
@@ -3547,10 +3643,12 @@
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
+      <c r="T36" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
-      <c r="W36" s="28"/>
+      <c r="W36" s="3"/>
     </row>
     <row r="37" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
@@ -3588,10 +3686,12 @@
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
+      <c r="T37" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
-      <c r="W37" s="28"/>
+      <c r="W37" s="3"/>
     </row>
     <row r="38" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
@@ -3629,10 +3729,12 @@
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
+      <c r="T38" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="28"/>
+      <c r="W38" s="3"/>
     </row>
     <row r="39" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
@@ -3670,10 +3772,12 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
+      <c r="T39" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="28"/>
+      <c r="W39" s="3"/>
     </row>
     <row r="40" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="28">
@@ -3711,10 +3815,12 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
+      <c r="T40" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-      <c r="W40" s="28"/>
+      <c r="W40" s="3"/>
     </row>
     <row r="41" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="28">
@@ -3752,10 +3858,12 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
+      <c r="T41" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
-      <c r="W41" s="28"/>
+      <c r="W41" s="3"/>
     </row>
     <row r="42" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="28">
@@ -3793,10 +3901,12 @@
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
+      <c r="T42" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
-      <c r="W42" s="28"/>
+      <c r="W42" s="3"/>
     </row>
     <row r="43" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="28">
@@ -3834,10 +3944,12 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
+      <c r="T43" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
-      <c r="W43" s="28"/>
+      <c r="W43" s="3"/>
     </row>
     <row r="44" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="28">
@@ -3875,10 +3987,12 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
+      <c r="T44" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
-      <c r="W44" s="28"/>
+      <c r="W44" s="3"/>
     </row>
     <row r="45" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="28">
@@ -3916,10 +4030,12 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
+      <c r="T45" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
-      <c r="W45" s="28"/>
+      <c r="W45" s="3"/>
     </row>
     <row r="46" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A46" s="28">
@@ -3956,17 +4072,21 @@
       <c r="P46" s="3">
         <v>50</v>
       </c>
-      <c r="Q46" s="3"/>
+      <c r="Q46" s="3">
+        <v>5</v>
+      </c>
       <c r="R46" s="3">
         <v>12</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T46" s="3"/>
+      <c r="T46" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="28"/>
+      <c r="W46" s="3"/>
     </row>
     <row r="47" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="28">
@@ -4004,10 +4124,12 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
+      <c r="T47" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
-      <c r="W47" s="28"/>
+      <c r="W47" s="3"/>
     </row>
     <row r="48" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="28">
@@ -4045,10 +4167,12 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
+      <c r="T48" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
-      <c r="W48" s="28"/>
+      <c r="W48" s="3"/>
     </row>
     <row r="49" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="28">
@@ -4086,10 +4210,12 @@
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
+      <c r="T49" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
-      <c r="W49" s="28"/>
+      <c r="W49" s="3"/>
     </row>
     <row r="50" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="28">
@@ -4127,10 +4253,12 @@
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
+      <c r="T50" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
-      <c r="W50" s="28"/>
+      <c r="W50" s="3"/>
     </row>
     <row r="51" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="28">
@@ -4168,10 +4296,12 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
+      <c r="T51" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
-      <c r="W51" s="28"/>
+      <c r="W51" s="3"/>
     </row>
     <row r="52" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="28">
@@ -4209,10 +4339,12 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
+      <c r="T52" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
-      <c r="W52" s="28"/>
+      <c r="W52" s="3"/>
     </row>
     <row r="53" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="28">
@@ -4250,10 +4382,12 @@
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
+      <c r="T53" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
-      <c r="W53" s="28"/>
+      <c r="W53" s="3"/>
     </row>
     <row r="54" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="28">
@@ -4291,10 +4425,12 @@
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
+      <c r="T54" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
-      <c r="W54" s="28"/>
+      <c r="W54" s="3"/>
     </row>
     <row r="55" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="28">
@@ -4332,10 +4468,12 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
+      <c r="T55" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-      <c r="W55" s="28"/>
+      <c r="W55" s="3"/>
     </row>
     <row r="56" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="28">
@@ -4373,10 +4511,12 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
+      <c r="T56" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-      <c r="W56" s="28"/>
+      <c r="W56" s="3"/>
     </row>
     <row r="57" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="28">
@@ -4410,10 +4550,12 @@
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
+      <c r="T57" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
-      <c r="W57" s="28"/>
+      <c r="W57" s="3"/>
     </row>
     <row r="58" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="28">
@@ -4447,10 +4589,12 @@
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
+      <c r="T58" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
-      <c r="W58" s="28"/>
+      <c r="W58" s="3"/>
     </row>
     <row r="59" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="28">
@@ -4484,10 +4628,12 @@
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
+      <c r="T59" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
-      <c r="W59" s="28"/>
+      <c r="W59" s="3"/>
     </row>
     <row r="60" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="28">
@@ -4521,10 +4667,12 @@
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
+      <c r="T60" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
-      <c r="W60" s="28"/>
+      <c r="W60" s="3"/>
     </row>
     <row r="61" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="28">
@@ -4558,10 +4706,12 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
-      <c r="T61" s="3"/>
+      <c r="T61" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
-      <c r="W61" s="28"/>
+      <c r="W61" s="3"/>
     </row>
     <row r="62" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="28">
@@ -4595,10 +4745,12 @@
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
+      <c r="T62" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
-      <c r="W62" s="28"/>
+      <c r="W62" s="3"/>
     </row>
     <row r="63" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="28">
@@ -4632,10 +4784,12 @@
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
+      <c r="T63" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
-      <c r="W63" s="28"/>
+      <c r="W63" s="3"/>
     </row>
     <row r="64" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="28">
@@ -4669,10 +4823,12 @@
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
+      <c r="T64" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
-      <c r="W64" s="28"/>
+      <c r="W64" s="3"/>
     </row>
     <row r="65" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="28">
@@ -4706,10 +4862,12 @@
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
+      <c r="T65" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
-      <c r="W65" s="28"/>
+      <c r="W65" s="3"/>
     </row>
     <row r="66" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="28">
@@ -4743,10 +4901,12 @@
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
-      <c r="T66" s="3"/>
+      <c r="T66" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
-      <c r="W66" s="28"/>
+      <c r="W66" s="3"/>
     </row>
     <row r="67" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="28">
@@ -4780,10 +4940,12 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
+      <c r="T67" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-      <c r="W67" s="28"/>
+      <c r="W67" s="3"/>
     </row>
     <row r="68" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="28">
@@ -4817,10 +4979,12 @@
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
+      <c r="T68" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
-      <c r="W68" s="28"/>
+      <c r="W68" s="3"/>
     </row>
     <row r="69" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="28">
@@ -4854,10 +5018,12 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
+      <c r="T69" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
-      <c r="W69" s="28"/>
+      <c r="W69" s="3"/>
     </row>
     <row r="70" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="28">
@@ -4891,10 +5057,12 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
+      <c r="T70" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
-      <c r="W70" s="28"/>
+      <c r="W70" s="3"/>
     </row>
     <row r="71" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="28">
@@ -4928,10 +5096,12 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
+      <c r="T71" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
-      <c r="W71" s="28"/>
+      <c r="W71" s="3"/>
     </row>
     <row r="72" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="28">
@@ -4965,10 +5135,12 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
+      <c r="T72" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
-      <c r="W72" s="28"/>
+      <c r="W72" s="3"/>
     </row>
     <row r="73" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="28">
@@ -5002,10 +5174,12 @@
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
+      <c r="T73" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
-      <c r="W73" s="28"/>
+      <c r="W73" s="3"/>
     </row>
     <row r="74" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="28">
@@ -5039,10 +5213,12 @@
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
+      <c r="T74" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
-      <c r="W74" s="28"/>
+      <c r="W74" s="3"/>
     </row>
     <row r="75" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="28">
@@ -5076,10 +5252,12 @@
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
+      <c r="T75" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
-      <c r="W75" s="28"/>
+      <c r="W75" s="3"/>
     </row>
     <row r="76" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="28">
@@ -5113,10 +5291,12 @@
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
-      <c r="T76" s="3"/>
+      <c r="T76" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
-      <c r="W76" s="28"/>
+      <c r="W76" s="3"/>
     </row>
     <row r="77" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="28">
@@ -5150,10 +5330,12 @@
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
+      <c r="T77" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
-      <c r="W77" s="28"/>
+      <c r="W77" s="3"/>
     </row>
     <row r="78" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="28">
@@ -5187,10 +5369,12 @@
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
-      <c r="T78" s="3"/>
+      <c r="T78" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
-      <c r="W78" s="28"/>
+      <c r="W78" s="3"/>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="28">
@@ -5230,10 +5414,12 @@
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
+      <c r="T79" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U79" s="3"/>
       <c r="V79" s="3"/>
-      <c r="W79" s="28"/>
+      <c r="W79" s="3"/>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="28">
@@ -5277,10 +5463,12 @@
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
-      <c r="T80" s="3"/>
+      <c r="T80" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
-      <c r="W80" s="28"/>
+      <c r="W80" s="3"/>
     </row>
     <row r="81" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A81" s="28">
@@ -5317,17 +5505,21 @@
       <c r="P81" s="3">
         <v>5</v>
       </c>
-      <c r="Q81" s="3"/>
+      <c r="Q81" s="3">
+        <v>5</v>
+      </c>
       <c r="R81" s="3">
         <v>120</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T81" s="3"/>
+      <c r="T81" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U81" s="3"/>
       <c r="V81" s="3"/>
-      <c r="W81" s="28"/>
+      <c r="W81" s="3"/>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="28">
@@ -5365,10 +5557,12 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-      <c r="T82" s="3"/>
+      <c r="T82" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-      <c r="W82" s="28"/>
+      <c r="W82" s="3"/>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="28">
@@ -5406,10 +5600,12 @@
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
-      <c r="T83" s="3"/>
+      <c r="T83" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
-      <c r="W83" s="28"/>
+      <c r="W83" s="3"/>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="28">
@@ -5447,10 +5643,12 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
-      <c r="T84" s="3"/>
+      <c r="T84" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
-      <c r="W84" s="28"/>
+      <c r="W84" s="3"/>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="28">
@@ -5488,10 +5686,12 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
+      <c r="T85" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
-      <c r="W85" s="28"/>
+      <c r="W85" s="3"/>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="28">
@@ -5529,10 +5729,12 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
-      <c r="T86" s="3"/>
+      <c r="T86" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
-      <c r="W86" s="28"/>
+      <c r="W86" s="3"/>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="28">
@@ -5570,10 +5772,12 @@
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
-      <c r="T87" s="3"/>
+      <c r="T87" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
-      <c r="W87" s="28"/>
+      <c r="W87" s="3"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="28">
@@ -5611,10 +5815,12 @@
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
-      <c r="T88" s="3"/>
+      <c r="T88" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
-      <c r="W88" s="28"/>
+      <c r="W88" s="3"/>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="28">
@@ -5652,10 +5858,12 @@
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
-      <c r="T89" s="3"/>
+      <c r="T89" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U89" s="3"/>
       <c r="V89" s="3"/>
-      <c r="W89" s="28"/>
+      <c r="W89" s="3"/>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="28">
@@ -5693,10 +5901,12 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-      <c r="T90" s="3"/>
+      <c r="T90" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-      <c r="W90" s="28"/>
+      <c r="W90" s="3"/>
     </row>
     <row r="91" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A91" s="28">
@@ -5734,10 +5944,12 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
-      <c r="T91" s="3"/>
+      <c r="T91" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U91" s="3"/>
       <c r="V91" s="3"/>
-      <c r="W91" s="28"/>
+      <c r="W91" s="3"/>
     </row>
     <row r="92" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A92" s="28">
@@ -5775,10 +5987,12 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
-      <c r="T92" s="3"/>
+      <c r="T92" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U92" s="3"/>
       <c r="V92" s="3"/>
-      <c r="W92" s="28"/>
+      <c r="W92" s="3"/>
     </row>
     <row r="93" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A93" s="28">
@@ -5816,10 +6030,12 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
-      <c r="T93" s="3"/>
+      <c r="T93" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U93" s="3"/>
       <c r="V93" s="3"/>
-      <c r="W93" s="28"/>
+      <c r="W93" s="3"/>
     </row>
     <row r="94" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A94" s="28">
@@ -5857,10 +6073,12 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
-      <c r="T94" s="3"/>
+      <c r="T94" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
-      <c r="W94" s="28"/>
+      <c r="W94" s="3"/>
     </row>
     <row r="95" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A95" s="28">
@@ -5898,10 +6116,12 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-      <c r="T95" s="3"/>
+      <c r="T95" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-      <c r="W95" s="28"/>
+      <c r="W95" s="3"/>
     </row>
     <row r="96" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A96" s="28">
@@ -5939,10 +6159,12 @@
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
-      <c r="T96" s="3"/>
+      <c r="T96" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U96" s="3"/>
       <c r="V96" s="3"/>
-      <c r="W96" s="28"/>
+      <c r="W96" s="3"/>
     </row>
     <row r="97" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A97" s="28">
@@ -5980,10 +6202,12 @@
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
-      <c r="T97" s="3"/>
+      <c r="T97" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U97" s="3"/>
       <c r="V97" s="3"/>
-      <c r="W97" s="28"/>
+      <c r="W97" s="3"/>
     </row>
     <row r="98" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A98" s="28">
@@ -6021,10 +6245,12 @@
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
-      <c r="T98" s="3"/>
+      <c r="T98" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U98" s="3"/>
       <c r="V98" s="3"/>
-      <c r="W98" s="28"/>
+      <c r="W98" s="3"/>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="28">
@@ -6062,10 +6288,12 @@
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
-      <c r="T99" s="3"/>
+      <c r="T99" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U99" s="3"/>
       <c r="V99" s="3"/>
-      <c r="W99" s="28"/>
+      <c r="W99" s="3"/>
     </row>
     <row r="100" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A100" s="28">
@@ -6103,10 +6331,12 @@
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
-      <c r="T100" s="3"/>
+      <c r="T100" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U100" s="3"/>
       <c r="V100" s="3"/>
-      <c r="W100" s="28"/>
+      <c r="W100" s="3"/>
     </row>
     <row r="101" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A101" s="28">
@@ -6144,10 +6374,12 @@
       <c r="Q101" s="3"/>
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
-      <c r="T101" s="3"/>
+      <c r="T101" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U101" s="3"/>
       <c r="V101" s="3"/>
-      <c r="W101" s="28"/>
+      <c r="W101" s="3"/>
     </row>
     <row r="102" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A102" s="28">
@@ -6185,10 +6417,12 @@
       <c r="Q102" s="3"/>
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
-      <c r="T102" s="3"/>
+      <c r="T102" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U102" s="3"/>
       <c r="V102" s="3"/>
-      <c r="W102" s="28"/>
+      <c r="W102" s="3"/>
     </row>
     <row r="103" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A103" s="28">
@@ -6226,10 +6460,12 @@
       <c r="Q103" s="3"/>
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
-      <c r="T103" s="3"/>
+      <c r="T103" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U103" s="3"/>
       <c r="V103" s="3"/>
-      <c r="W103" s="28"/>
+      <c r="W103" s="3"/>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="28">
@@ -6267,10 +6503,12 @@
       <c r="Q104" s="3"/>
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
-      <c r="T104" s="3"/>
+      <c r="T104" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U104" s="3"/>
       <c r="V104" s="3"/>
-      <c r="W104" s="28"/>
+      <c r="W104" s="3"/>
     </row>
     <row r="105" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A105" s="28">
@@ -6308,10 +6546,12 @@
       <c r="Q105" s="3"/>
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
-      <c r="T105" s="3"/>
+      <c r="T105" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U105" s="3"/>
       <c r="V105" s="3"/>
-      <c r="W105" s="28"/>
+      <c r="W105" s="3"/>
     </row>
     <row r="106" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A106" s="28">
@@ -6349,10 +6589,12 @@
       <c r="Q106" s="3"/>
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
-      <c r="T106" s="3"/>
+      <c r="T106" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U106" s="3"/>
       <c r="V106" s="3"/>
-      <c r="W106" s="28"/>
+      <c r="W106" s="3"/>
     </row>
     <row r="107" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A107" s="28">
@@ -6390,10 +6632,12 @@
       <c r="Q107" s="3"/>
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
-      <c r="T107" s="3"/>
+      <c r="T107" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U107" s="3"/>
       <c r="V107" s="3"/>
-      <c r="W107" s="28"/>
+      <c r="W107" s="3"/>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="28">
@@ -6431,10 +6675,12 @@
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
-      <c r="T108" s="3"/>
+      <c r="T108" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U108" s="3"/>
       <c r="V108" s="3"/>
-      <c r="W108" s="28"/>
+      <c r="W108" s="3"/>
     </row>
     <row r="109" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A109" s="28">
@@ -6472,10 +6718,12 @@
       <c r="Q109" s="3"/>
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
-      <c r="T109" s="3"/>
+      <c r="T109" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U109" s="3"/>
       <c r="V109" s="3"/>
-      <c r="W109" s="28"/>
+      <c r="W109" s="3"/>
     </row>
     <row r="110" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A110" s="28">
@@ -6513,10 +6761,12 @@
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
-      <c r="T110" s="3"/>
+      <c r="T110" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U110" s="3"/>
       <c r="V110" s="3"/>
-      <c r="W110" s="28"/>
+      <c r="W110" s="3"/>
     </row>
     <row r="111" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A111" s="28">
@@ -6562,12 +6812,14 @@
       <c r="S111" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T111" s="3">
-        <v>16</v>
+      <c r="T111" s="29">
+        <v>0.4</v>
       </c>
       <c r="U111" s="3"/>
       <c r="V111" s="3"/>
-      <c r="W111" s="28"/>
+      <c r="W111" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="112" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A112" s="28">
@@ -6613,12 +6865,14 @@
       <c r="S112" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T112" s="3">
-        <v>16</v>
+      <c r="T112" s="29">
+        <v>0.4</v>
       </c>
       <c r="U112" s="3"/>
       <c r="V112" s="3"/>
-      <c r="W112" s="28"/>
+      <c r="W112" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="113" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A113" s="28">
@@ -6655,17 +6909,21 @@
       <c r="P113" s="3">
         <v>60</v>
       </c>
-      <c r="Q113" s="3"/>
+      <c r="Q113" s="3">
+        <v>5</v>
+      </c>
       <c r="R113" s="3">
         <v>16</v>
       </c>
       <c r="S113" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T113" s="3"/>
+      <c r="T113" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U113" s="3"/>
       <c r="V113" s="3"/>
-      <c r="W113" s="28"/>
+      <c r="W113" s="3"/>
     </row>
     <row r="114" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A114" s="28">
@@ -6711,12 +6969,14 @@
       <c r="S114" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T114" s="3">
-        <v>16</v>
+      <c r="T114" s="29">
+        <v>0.4</v>
       </c>
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
-      <c r="W114" s="28"/>
+      <c r="W114" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="115" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A115" s="28">
@@ -6762,12 +7022,14 @@
       <c r="S115" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T115" s="3">
-        <v>16</v>
+      <c r="T115" s="29">
+        <v>0.4</v>
       </c>
       <c r="U115" s="3"/>
       <c r="V115" s="3"/>
-      <c r="W115" s="28"/>
+      <c r="W115" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="116" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A116" s="28">
@@ -6813,12 +7075,14 @@
       <c r="S116" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T116" s="3">
-        <v>16</v>
+      <c r="T116" s="29">
+        <v>0.4</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="3"/>
-      <c r="W116" s="28"/>
+      <c r="W116" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="117" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A117" s="28">
@@ -6864,12 +7128,14 @@
       <c r="S117" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T117" s="3">
-        <v>25</v>
+      <c r="T117" s="29">
+        <v>0.4</v>
       </c>
       <c r="U117" s="3"/>
       <c r="V117" s="3"/>
-      <c r="W117" s="28"/>
+      <c r="W117" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="118" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A118" s="28">
@@ -6915,12 +7181,14 @@
       <c r="S118" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T118" s="3">
-        <v>25</v>
+      <c r="T118" s="29">
+        <v>0.4</v>
       </c>
       <c r="U118" s="3"/>
       <c r="V118" s="3"/>
-      <c r="W118" s="28"/>
+      <c r="W118" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="119" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A119" s="28">
@@ -6966,12 +7234,14 @@
       <c r="S119" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T119" s="3">
-        <v>25</v>
+      <c r="T119" s="29">
+        <v>0.4</v>
       </c>
       <c r="U119" s="3"/>
       <c r="V119" s="3"/>
-      <c r="W119" s="28"/>
+      <c r="W119" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="120" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A120" s="28">
@@ -7017,12 +7287,14 @@
       <c r="S120" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T120" s="3">
-        <v>16</v>
+      <c r="T120" s="29">
+        <v>0.4</v>
       </c>
       <c r="U120" s="3"/>
       <c r="V120" s="3"/>
-      <c r="W120" s="28"/>
+      <c r="W120" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="28">
@@ -7058,10 +7330,12 @@
       <c r="Q121" s="3"/>
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
-      <c r="T121" s="3"/>
+      <c r="T121" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U121" s="3"/>
       <c r="V121" s="3"/>
-      <c r="W121" s="28"/>
+      <c r="W121" s="3"/>
     </row>
     <row r="122" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A122" s="28">
@@ -7107,12 +7381,14 @@
       <c r="S122" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T122" s="3">
-        <v>16</v>
+      <c r="T122" s="29">
+        <v>0.4</v>
       </c>
       <c r="U122" s="3"/>
       <c r="V122" s="3"/>
-      <c r="W122" s="28"/>
+      <c r="W122" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="123" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A123" s="28">
@@ -7158,12 +7434,14 @@
       <c r="S123" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T123" s="3">
-        <v>16</v>
+      <c r="T123" s="29">
+        <v>0.4</v>
       </c>
       <c r="U123" s="3"/>
       <c r="V123" s="3"/>
-      <c r="W123" s="28"/>
+      <c r="W123" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="124" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A124" s="28">
@@ -7209,12 +7487,14 @@
       <c r="S124" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T124" s="3">
-        <v>16</v>
+      <c r="T124" s="29">
+        <v>0.4</v>
       </c>
       <c r="U124" s="3"/>
       <c r="V124" s="3"/>
-      <c r="W124" s="28"/>
+      <c r="W124" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="125" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A125" s="28">
@@ -7260,12 +7540,14 @@
       <c r="S125" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T125" s="3">
-        <v>16</v>
+      <c r="T125" s="29">
+        <v>0.4</v>
       </c>
       <c r="U125" s="3"/>
       <c r="V125" s="3"/>
-      <c r="W125" s="28"/>
+      <c r="W125" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="28">
@@ -7301,10 +7583,12 @@
       <c r="Q126" s="3"/>
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
-      <c r="T126" s="3"/>
+      <c r="T126" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U126" s="3"/>
       <c r="V126" s="3"/>
-      <c r="W126" s="28"/>
+      <c r="W126" s="3"/>
     </row>
     <row r="127" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A127" s="28">
@@ -7350,12 +7634,14 @@
       <c r="S127" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T127" s="3">
-        <v>16</v>
+      <c r="T127" s="29">
+        <v>0.4</v>
       </c>
       <c r="U127" s="3"/>
       <c r="V127" s="3"/>
-      <c r="W127" s="28"/>
+      <c r="W127" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="128" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A128" s="28">
@@ -7393,10 +7679,12 @@
       <c r="Q128" s="3"/>
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
-      <c r="T128" s="3"/>
+      <c r="T128" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U128" s="3"/>
       <c r="V128" s="3"/>
-      <c r="W128" s="28"/>
+      <c r="W128" s="3"/>
     </row>
     <row r="129" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A129" s="28">
@@ -7442,12 +7730,14 @@
       <c r="S129" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T129" s="3">
-        <v>32</v>
+      <c r="T129" s="29">
+        <v>0.4</v>
       </c>
       <c r="U129" s="3"/>
       <c r="V129" s="3"/>
-      <c r="W129" s="28"/>
+      <c r="W129" s="3">
+        <v>32</v>
+      </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="28">
@@ -7483,10 +7773,12 @@
       <c r="Q130" s="3"/>
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
-      <c r="T130" s="3"/>
+      <c r="T130" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U130" s="3"/>
       <c r="V130" s="3"/>
-      <c r="W130" s="28"/>
+      <c r="W130" s="3"/>
     </row>
     <row r="131" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A131" s="28">
@@ -7532,12 +7824,14 @@
       <c r="S131" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T131" s="3">
-        <v>16</v>
+      <c r="T131" s="29">
+        <v>0.4</v>
       </c>
       <c r="U131" s="3"/>
       <c r="V131" s="3"/>
-      <c r="W131" s="28"/>
+      <c r="W131" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="132" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="28">
@@ -7577,10 +7871,12 @@
       <c r="Q132" s="3"/>
       <c r="R132" s="3"/>
       <c r="S132" s="3"/>
-      <c r="T132" s="3"/>
+      <c r="T132" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U132" s="3"/>
       <c r="V132" s="3"/>
-      <c r="W132" s="28"/>
+      <c r="W132" s="3"/>
     </row>
     <row r="133" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="28">
@@ -7620,10 +7916,12 @@
       <c r="Q133" s="3"/>
       <c r="R133" s="3"/>
       <c r="S133" s="3"/>
-      <c r="T133" s="3"/>
+      <c r="T133" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U133" s="3"/>
       <c r="V133" s="3"/>
-      <c r="W133" s="28"/>
+      <c r="W133" s="3"/>
     </row>
     <row r="134" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A134" s="28">
@@ -7673,12 +7971,14 @@
       <c r="S134" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T134" s="3">
-        <v>2500</v>
+      <c r="T134" s="29">
+        <v>0.4</v>
       </c>
       <c r="U134" s="3"/>
       <c r="V134" s="3"/>
-      <c r="W134" s="28"/>
+      <c r="W134" s="3">
+        <v>2500</v>
+      </c>
     </row>
     <row r="135" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A135" s="28">
@@ -7720,12 +8020,14 @@
       <c r="S135" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T135" s="3">
-        <v>16</v>
+      <c r="T135" s="29">
+        <v>0.4</v>
       </c>
       <c r="U135" s="3"/>
       <c r="V135" s="3"/>
-      <c r="W135" s="28"/>
+      <c r="W135" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="136" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="28">
@@ -7769,12 +8071,14 @@
       <c r="S136" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T136" s="3">
-        <v>16</v>
+      <c r="T136" s="29">
+        <v>0.4</v>
       </c>
       <c r="U136" s="3"/>
       <c r="V136" s="3"/>
-      <c r="W136" s="28"/>
+      <c r="W136" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="137" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="28">
@@ -7818,12 +8122,14 @@
       <c r="S137" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T137" s="3">
-        <v>16</v>
+      <c r="T137" s="29">
+        <v>0.4</v>
       </c>
       <c r="U137" s="3"/>
       <c r="V137" s="3"/>
-      <c r="W137" s="28"/>
+      <c r="W137" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="138" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="28">
@@ -7867,12 +8173,14 @@
       <c r="S138" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T138" s="3">
-        <v>16</v>
+      <c r="T138" s="29">
+        <v>0.4</v>
       </c>
       <c r="U138" s="3"/>
       <c r="V138" s="3"/>
-      <c r="W138" s="28"/>
+      <c r="W138" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="139" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="28">
@@ -7916,12 +8224,14 @@
       <c r="S139" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T139" s="3">
-        <v>16</v>
+      <c r="T139" s="29">
+        <v>0.4</v>
       </c>
       <c r="U139" s="3"/>
       <c r="V139" s="3"/>
-      <c r="W139" s="28"/>
+      <c r="W139" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="140" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="28">
@@ -7965,12 +8275,14 @@
       <c r="S140" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T140" s="3">
-        <v>16</v>
+      <c r="T140" s="29">
+        <v>0.4</v>
       </c>
       <c r="U140" s="3"/>
       <c r="V140" s="3"/>
-      <c r="W140" s="28"/>
+      <c r="W140" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="141" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="28">
@@ -8014,12 +8326,14 @@
       <c r="S141" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T141" s="3">
-        <v>16</v>
+      <c r="T141" s="29">
+        <v>0.4</v>
       </c>
       <c r="U141" s="3"/>
       <c r="V141" s="3"/>
-      <c r="W141" s="28"/>
+      <c r="W141" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="142" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="28">
@@ -8063,12 +8377,14 @@
       <c r="S142" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T142" s="3">
-        <v>16</v>
+      <c r="T142" s="29">
+        <v>0.4</v>
       </c>
       <c r="U142" s="3"/>
       <c r="V142" s="3"/>
-      <c r="W142" s="28"/>
+      <c r="W142" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="143" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="28">
@@ -8112,12 +8428,14 @@
       <c r="S143" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T143" s="3">
-        <v>16</v>
+      <c r="T143" s="29">
+        <v>0.4</v>
       </c>
       <c r="U143" s="3"/>
       <c r="V143" s="3"/>
-      <c r="W143" s="28"/>
+      <c r="W143" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="144" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="28">
@@ -8161,12 +8479,14 @@
       <c r="S144" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T144" s="3">
-        <v>16</v>
+      <c r="T144" s="29">
+        <v>0.4</v>
       </c>
       <c r="U144" s="3"/>
       <c r="V144" s="3"/>
-      <c r="W144" s="28"/>
+      <c r="W144" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="145" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="28">
@@ -8210,12 +8530,14 @@
       <c r="S145" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T145" s="3">
-        <v>16</v>
+      <c r="T145" s="29">
+        <v>0.4</v>
       </c>
       <c r="U145" s="3"/>
       <c r="V145" s="3"/>
-      <c r="W145" s="28"/>
+      <c r="W145" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="146" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A146" s="28">
@@ -8257,12 +8579,14 @@
       <c r="S146" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T146" s="3">
-        <v>16</v>
+      <c r="T146" s="29">
+        <v>0.4</v>
       </c>
       <c r="U146" s="3"/>
       <c r="V146" s="3"/>
-      <c r="W146" s="28"/>
+      <c r="W146" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="147" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A147" s="28">
@@ -8304,12 +8628,14 @@
       <c r="S147" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T147" s="3">
-        <v>16</v>
+      <c r="T147" s="29">
+        <v>0.4</v>
       </c>
       <c r="U147" s="3"/>
       <c r="V147" s="3"/>
-      <c r="W147" s="28"/>
+      <c r="W147" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="148" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A148" s="28">
@@ -8351,12 +8677,14 @@
       <c r="S148" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T148" s="3">
-        <v>16</v>
+      <c r="T148" s="29">
+        <v>0.4</v>
       </c>
       <c r="U148" s="3"/>
       <c r="V148" s="3"/>
-      <c r="W148" s="28"/>
+      <c r="W148" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="149" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A149" s="28">
@@ -8398,12 +8726,14 @@
       <c r="S149" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T149" s="3">
-        <v>16</v>
+      <c r="T149" s="29">
+        <v>0.4</v>
       </c>
       <c r="U149" s="3"/>
       <c r="V149" s="3"/>
-      <c r="W149" s="28"/>
+      <c r="W149" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="150" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A150" s="28">
@@ -8445,12 +8775,14 @@
       <c r="S150" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T150" s="3">
-        <v>16</v>
+      <c r="T150" s="29">
+        <v>0.4</v>
       </c>
       <c r="U150" s="3"/>
       <c r="V150" s="3"/>
-      <c r="W150" s="28"/>
+      <c r="W150" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="151" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A151" s="28">
@@ -8492,12 +8824,14 @@
       <c r="S151" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T151" s="3">
-        <v>16</v>
+      <c r="T151" s="29">
+        <v>0.4</v>
       </c>
       <c r="U151" s="3"/>
       <c r="V151" s="3"/>
-      <c r="W151" s="28"/>
+      <c r="W151" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="152" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A152" s="28">
@@ -8539,12 +8873,14 @@
       <c r="S152" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T152" s="3">
-        <v>16</v>
+      <c r="T152" s="29">
+        <v>0.4</v>
       </c>
       <c r="U152" s="3"/>
       <c r="V152" s="3"/>
-      <c r="W152" s="28"/>
+      <c r="W152" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="153" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A153" s="28">
@@ -8586,12 +8922,14 @@
       <c r="S153" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T153" s="3">
-        <v>16</v>
+      <c r="T153" s="29">
+        <v>0.4</v>
       </c>
       <c r="U153" s="3"/>
       <c r="V153" s="3"/>
-      <c r="W153" s="28"/>
+      <c r="W153" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="154" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A154" s="28">
@@ -8633,12 +8971,14 @@
       <c r="S154" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T154" s="3">
-        <v>16</v>
+      <c r="T154" s="29">
+        <v>0.4</v>
       </c>
       <c r="U154" s="3"/>
       <c r="V154" s="3"/>
-      <c r="W154" s="28"/>
+      <c r="W154" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="155" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A155" s="28">
@@ -8680,12 +9020,14 @@
       <c r="S155" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T155" s="3">
-        <v>16</v>
+      <c r="T155" s="29">
+        <v>0.4</v>
       </c>
       <c r="U155" s="3"/>
       <c r="V155" s="3"/>
-      <c r="W155" s="28"/>
+      <c r="W155" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="156" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A156" s="28">
@@ -8727,12 +9069,14 @@
       <c r="S156" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T156" s="3">
-        <v>16</v>
+      <c r="T156" s="29">
+        <v>0.4</v>
       </c>
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
-      <c r="W156" s="28"/>
+      <c r="W156" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="157" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A157" s="28">
@@ -8776,12 +9120,14 @@
       <c r="S157" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T157" s="3">
-        <v>16</v>
+      <c r="T157" s="29">
+        <v>0.4</v>
       </c>
       <c r="U157" s="3"/>
       <c r="V157" s="3"/>
-      <c r="W157" s="28"/>
+      <c r="W157" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="158" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A158" s="28">
@@ -8825,12 +9171,14 @@
       <c r="S158" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T158" s="3">
-        <v>16</v>
+      <c r="T158" s="29">
+        <v>0.4</v>
       </c>
       <c r="U158" s="3"/>
       <c r="V158" s="3"/>
-      <c r="W158" s="28"/>
+      <c r="W158" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="159" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A159" s="28">
@@ -8874,12 +9222,14 @@
       <c r="S159" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T159" s="3">
-        <v>16</v>
+      <c r="T159" s="29">
+        <v>0.4</v>
       </c>
       <c r="U159" s="3"/>
       <c r="V159" s="3"/>
-      <c r="W159" s="28"/>
+      <c r="W159" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="160" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A160" s="28">
@@ -8923,12 +9273,14 @@
       <c r="S160" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T160" s="3">
-        <v>16</v>
+      <c r="T160" s="29">
+        <v>0.4</v>
       </c>
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
-      <c r="W160" s="28"/>
+      <c r="W160" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="161" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A161" s="28">
@@ -8972,12 +9324,14 @@
       <c r="S161" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T161" s="3">
-        <v>16</v>
+      <c r="T161" s="29">
+        <v>0.4</v>
       </c>
       <c r="U161" s="3"/>
       <c r="V161" s="3"/>
-      <c r="W161" s="28"/>
+      <c r="W161" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="162" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A162" s="28">
@@ -9021,12 +9375,14 @@
       <c r="S162" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T162" s="3">
-        <v>16</v>
+      <c r="T162" s="29">
+        <v>0.4</v>
       </c>
       <c r="U162" s="3"/>
       <c r="V162" s="3"/>
-      <c r="W162" s="28"/>
+      <c r="W162" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="163" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A163" s="28">
@@ -9070,12 +9426,14 @@
       <c r="S163" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T163" s="3">
-        <v>16</v>
+      <c r="T163" s="29">
+        <v>0.4</v>
       </c>
       <c r="U163" s="3"/>
       <c r="V163" s="3"/>
-      <c r="W163" s="28"/>
+      <c r="W163" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="164" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A164" s="28">
@@ -9119,12 +9477,14 @@
       <c r="S164" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T164" s="3">
-        <v>16</v>
+      <c r="T164" s="29">
+        <v>0.4</v>
       </c>
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
-      <c r="W164" s="28"/>
+      <c r="W164" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="165" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A165" s="28">
@@ -9168,12 +9528,14 @@
       <c r="S165" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T165" s="3">
-        <v>16</v>
+      <c r="T165" s="29">
+        <v>0.4</v>
       </c>
       <c r="U165" s="3"/>
       <c r="V165" s="3"/>
-      <c r="W165" s="28"/>
+      <c r="W165" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="166" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A166" s="28">
@@ -9217,12 +9579,14 @@
       <c r="S166" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T166" s="3">
-        <v>16</v>
+      <c r="T166" s="29">
+        <v>0.4</v>
       </c>
       <c r="U166" s="3"/>
       <c r="V166" s="3"/>
-      <c r="W166" s="28"/>
+      <c r="W166" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="167" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A167" s="28">
@@ -9266,12 +9630,14 @@
       <c r="S167" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T167" s="3">
-        <v>16</v>
+      <c r="T167" s="29">
+        <v>0.4</v>
       </c>
       <c r="U167" s="3"/>
       <c r="V167" s="3"/>
-      <c r="W167" s="28"/>
+      <c r="W167" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="168" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A168" s="28">
@@ -9321,10 +9687,12 @@
       <c r="S168" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T168" s="3"/>
+      <c r="T168" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U168" s="3"/>
       <c r="V168" s="3"/>
-      <c r="W168" s="28"/>
+      <c r="W168" s="3"/>
     </row>
     <row r="169" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A169" s="28">
@@ -9374,10 +9742,12 @@
       <c r="S169" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T169" s="3"/>
+      <c r="T169" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U169" s="3"/>
       <c r="V169" s="3"/>
-      <c r="W169" s="28"/>
+      <c r="W169" s="3"/>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="28">
@@ -9417,10 +9787,12 @@
       <c r="Q170" s="3"/>
       <c r="R170" s="3"/>
       <c r="S170" s="3"/>
-      <c r="T170" s="3"/>
+      <c r="T170" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U170" s="3"/>
       <c r="V170" s="3"/>
-      <c r="W170" s="28"/>
+      <c r="W170" s="3"/>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="28">
@@ -9460,10 +9832,12 @@
       <c r="Q171" s="3"/>
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
-      <c r="T171" s="3"/>
+      <c r="T171" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U171" s="3"/>
       <c r="V171" s="3"/>
-      <c r="W171" s="28"/>
+      <c r="W171" s="3"/>
     </row>
     <row r="172" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A172" s="28">
@@ -9513,10 +9887,12 @@
       <c r="S172" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T172" s="3"/>
+      <c r="T172" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U172" s="3"/>
       <c r="V172" s="3"/>
-      <c r="W172" s="28"/>
+      <c r="W172" s="3"/>
     </row>
     <row r="173" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A173" s="28">
@@ -9564,12 +9940,14 @@
       <c r="S173" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T173" s="3">
-        <v>630</v>
+      <c r="T173" s="29">
+        <v>0.4</v>
       </c>
       <c r="U173" s="3"/>
       <c r="V173" s="3"/>
-      <c r="W173" s="28"/>
+      <c r="W173" s="3">
+        <v>630</v>
+      </c>
     </row>
     <row r="174" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A174" s="28">
@@ -9617,12 +9995,14 @@
       <c r="S174" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T174" s="3">
-        <v>800</v>
+      <c r="T174" s="29">
+        <v>0.4</v>
       </c>
       <c r="U174" s="3"/>
       <c r="V174" s="3"/>
-      <c r="W174" s="28"/>
+      <c r="W174" s="3">
+        <v>800</v>
+      </c>
     </row>
     <row r="175" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A175" s="28">
@@ -9670,12 +10050,14 @@
       <c r="S175" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T175" s="3">
-        <v>2500</v>
+      <c r="T175" s="29">
+        <v>0.4</v>
       </c>
       <c r="U175" s="3"/>
       <c r="V175" s="3"/>
-      <c r="W175" s="28"/>
+      <c r="W175" s="3">
+        <v>2500</v>
+      </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="28">
@@ -9719,12 +10101,14 @@
       <c r="S176" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T176" s="3">
-        <v>800</v>
+      <c r="T176" s="29">
+        <v>0.4</v>
       </c>
       <c r="U176" s="3"/>
       <c r="V176" s="3"/>
-      <c r="W176" s="28"/>
+      <c r="W176" s="3">
+        <v>800</v>
+      </c>
     </row>
     <row r="177" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A177" s="28">
@@ -9765,17 +10149,23 @@
       <c r="P177" s="3">
         <v>10</v>
       </c>
-      <c r="Q177" s="3"/>
-      <c r="R177" s="3"/>
+      <c r="Q177" s="3">
+        <v>5</v>
+      </c>
+      <c r="R177" s="3">
+        <v>2.5</v>
+      </c>
       <c r="S177" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T177" s="3">
-        <v>1250</v>
+      <c r="T177" s="29">
+        <v>0.4</v>
       </c>
       <c r="U177" s="3"/>
       <c r="V177" s="3"/>
-      <c r="W177" s="28"/>
+      <c r="W177" s="3">
+        <v>1250</v>
+      </c>
     </row>
     <row r="178" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A178" s="28">
@@ -9825,10 +10215,12 @@
       <c r="S178" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T178" s="3"/>
+      <c r="T178" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U178" s="3"/>
       <c r="V178" s="3"/>
-      <c r="W178" s="28"/>
+      <c r="W178" s="3"/>
     </row>
     <row r="179" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A179" s="28">
@@ -9878,10 +10270,12 @@
       <c r="S179" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T179" s="3"/>
+      <c r="T179" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U179" s="3"/>
       <c r="V179" s="3"/>
-      <c r="W179" s="28"/>
+      <c r="W179" s="3"/>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="28">
@@ -9927,10 +10321,12 @@
       <c r="S180" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T180" s="3"/>
+      <c r="T180" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U180" s="3"/>
       <c r="V180" s="3"/>
-      <c r="W180" s="28"/>
+      <c r="W180" s="3"/>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" s="28">
@@ -9976,10 +10372,12 @@
       <c r="S181" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T181" s="3"/>
+      <c r="T181" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U181" s="3"/>
       <c r="V181" s="3"/>
-      <c r="W181" s="28"/>
+      <c r="W181" s="3"/>
     </row>
     <row r="182" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A182" s="28">
@@ -10027,10 +10425,12 @@
       <c r="S182" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T182" s="3"/>
+      <c r="T182" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U182" s="3"/>
       <c r="V182" s="3"/>
-      <c r="W182" s="28"/>
+      <c r="W182" s="3"/>
     </row>
     <row r="183" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A183" s="28">
@@ -10078,12 +10478,14 @@
       <c r="S183" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T183" s="3">
-        <v>630</v>
+      <c r="T183" s="29">
+        <v>0.4</v>
       </c>
       <c r="U183" s="3"/>
       <c r="V183" s="3"/>
-      <c r="W183" s="28"/>
+      <c r="W183" s="3">
+        <v>630</v>
+      </c>
     </row>
     <row r="184" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A184" s="28">
@@ -10131,12 +10533,14 @@
       <c r="S184" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T184" s="3">
-        <v>800</v>
+      <c r="T184" s="29">
+        <v>0.4</v>
       </c>
       <c r="U184" s="3"/>
       <c r="V184" s="3"/>
-      <c r="W184" s="28"/>
+      <c r="W184" s="3">
+        <v>800</v>
+      </c>
     </row>
     <row r="185" spans="1:23" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A185" s="28">
@@ -10184,12 +10588,14 @@
       <c r="S185" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T185" s="3">
-        <v>2500</v>
+      <c r="T185" s="29">
+        <v>0.4</v>
       </c>
       <c r="U185" s="3"/>
       <c r="V185" s="3"/>
-      <c r="W185" s="28"/>
+      <c r="W185" s="3">
+        <v>2500</v>
+      </c>
     </row>
     <row r="186" spans="1:23" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A186" s="28">
@@ -10237,12 +10643,14 @@
       <c r="S186" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T186" s="3">
-        <v>2500</v>
+      <c r="T186" s="29">
+        <v>0.4</v>
       </c>
       <c r="U186" s="3"/>
       <c r="V186" s="3"/>
-      <c r="W186" s="28"/>
+      <c r="W186" s="3">
+        <v>2500</v>
+      </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="28">
@@ -10286,12 +10694,14 @@
       <c r="S187" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T187" s="3">
-        <v>800</v>
+      <c r="T187" s="29">
+        <v>0.4</v>
       </c>
       <c r="U187" s="3"/>
       <c r="V187" s="3"/>
-      <c r="W187" s="28"/>
+      <c r="W187" s="3">
+        <v>800</v>
+      </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="28">
@@ -10339,12 +10749,14 @@
       <c r="S188" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T188" s="3">
-        <v>16</v>
+      <c r="T188" s="29">
+        <v>0.4</v>
       </c>
       <c r="U188" s="3"/>
       <c r="V188" s="3"/>
-      <c r="W188" s="28"/>
+      <c r="W188" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="28">
@@ -10394,12 +10806,14 @@
       <c r="S189" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T189" s="3">
-        <v>16</v>
+      <c r="T189" s="29">
+        <v>0.4</v>
       </c>
       <c r="U189" s="3"/>
       <c r="V189" s="3"/>
-      <c r="W189" s="28"/>
+      <c r="W189" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="190" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A190" s="28">
@@ -10449,12 +10863,14 @@
       <c r="S190" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T190" s="3">
-        <v>16</v>
+      <c r="T190" s="29">
+        <v>0.4</v>
       </c>
       <c r="U190" s="3"/>
       <c r="V190" s="3"/>
-      <c r="W190" s="28"/>
+      <c r="W190" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="191" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A191" s="28">
@@ -10504,12 +10920,14 @@
       <c r="S191" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T191" s="3">
-        <v>16</v>
+      <c r="T191" s="29">
+        <v>0.4</v>
       </c>
       <c r="U191" s="3"/>
       <c r="V191" s="3"/>
-      <c r="W191" s="28"/>
+      <c r="W191" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="192" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A192" s="28">
@@ -10559,12 +10977,14 @@
       <c r="S192" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T192" s="3">
-        <v>16</v>
+      <c r="T192" s="29">
+        <v>0.4</v>
       </c>
       <c r="U192" s="3"/>
       <c r="V192" s="3"/>
-      <c r="W192" s="28"/>
+      <c r="W192" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="193" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A193" s="28">
@@ -10614,12 +11034,14 @@
       <c r="S193" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T193" s="3">
-        <v>16</v>
+      <c r="T193" s="29">
+        <v>0.4</v>
       </c>
       <c r="U193" s="3"/>
       <c r="V193" s="3"/>
-      <c r="W193" s="28"/>
+      <c r="W193" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="28">
@@ -10669,12 +11091,14 @@
       <c r="S194" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T194" s="3">
-        <v>16</v>
+      <c r="T194" s="29">
+        <v>0.4</v>
       </c>
       <c r="U194" s="3"/>
       <c r="V194" s="3"/>
-      <c r="W194" s="28"/>
+      <c r="W194" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="195" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A195" s="28">
@@ -10724,12 +11148,14 @@
       <c r="S195" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T195" s="3">
-        <v>16</v>
+      <c r="T195" s="29">
+        <v>0.4</v>
       </c>
       <c r="U195" s="3"/>
       <c r="V195" s="3"/>
-      <c r="W195" s="28"/>
+      <c r="W195" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="28">
@@ -10779,12 +11205,14 @@
       <c r="S196" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T196" s="3">
-        <v>16</v>
+      <c r="T196" s="29">
+        <v>0.4</v>
       </c>
       <c r="U196" s="3"/>
       <c r="V196" s="3"/>
-      <c r="W196" s="28"/>
+      <c r="W196" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="28">
@@ -10834,12 +11262,14 @@
       <c r="S197" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T197" s="3">
-        <v>16</v>
+      <c r="T197" s="29">
+        <v>0.4</v>
       </c>
       <c r="U197" s="3"/>
       <c r="V197" s="3"/>
-      <c r="W197" s="28"/>
+      <c r="W197" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="198" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A198" s="28">
@@ -10889,12 +11319,14 @@
       <c r="S198" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T198" s="3">
-        <v>16</v>
+      <c r="T198" s="29">
+        <v>0.4</v>
       </c>
       <c r="U198" s="3"/>
       <c r="V198" s="3"/>
-      <c r="W198" s="28"/>
+      <c r="W198" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="199" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A199" s="28">
@@ -10944,12 +11376,14 @@
       <c r="S199" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T199" s="3">
-        <v>16</v>
+      <c r="T199" s="29">
+        <v>0.4</v>
       </c>
       <c r="U199" s="3"/>
       <c r="V199" s="3"/>
-      <c r="W199" s="28"/>
+      <c r="W199" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="200" spans="1:23" ht="39" x14ac:dyDescent="0.25">
       <c r="A200" s="28">
@@ -10999,12 +11433,14 @@
       <c r="S200" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T200" s="3">
-        <v>16</v>
+      <c r="T200" s="29">
+        <v>0.4</v>
       </c>
       <c r="U200" s="3"/>
       <c r="V200" s="3"/>
-      <c r="W200" s="28"/>
+      <c r="W200" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="201" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A201" s="28">
@@ -11054,12 +11490,14 @@
       <c r="S201" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T201" s="3">
-        <v>16</v>
+      <c r="T201" s="29">
+        <v>0.4</v>
       </c>
       <c r="U201" s="3"/>
       <c r="V201" s="3"/>
-      <c r="W201" s="28"/>
+      <c r="W201" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="202" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A202" s="28">
@@ -11109,12 +11547,14 @@
       <c r="S202" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T202" s="3">
-        <v>16</v>
+      <c r="T202" s="29">
+        <v>0.4</v>
       </c>
       <c r="U202" s="3"/>
       <c r="V202" s="3"/>
-      <c r="W202" s="28"/>
+      <c r="W202" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="28">
@@ -11164,12 +11604,14 @@
       <c r="S203" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T203" s="3">
-        <v>16</v>
+      <c r="T203" s="29">
+        <v>0.4</v>
       </c>
       <c r="U203" s="3"/>
       <c r="V203" s="3"/>
-      <c r="W203" s="28"/>
+      <c r="W203" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="204" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A204" s="28">
@@ -11219,12 +11661,14 @@
       <c r="S204" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T204" s="3">
-        <v>16</v>
+      <c r="T204" s="29">
+        <v>0.4</v>
       </c>
       <c r="U204" s="3"/>
       <c r="V204" s="3"/>
-      <c r="W204" s="28"/>
+      <c r="W204" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="205" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A205" s="28">
@@ -11274,12 +11718,14 @@
       <c r="S205" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T205" s="3">
-        <v>16</v>
+      <c r="T205" s="29">
+        <v>0.4</v>
       </c>
       <c r="U205" s="3"/>
       <c r="V205" s="3"/>
-      <c r="W205" s="28"/>
+      <c r="W205" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="206" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A206" s="28">
@@ -11329,12 +11775,14 @@
       <c r="S206" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T206" s="3">
-        <v>16</v>
+      <c r="T206" s="29">
+        <v>0.4</v>
       </c>
       <c r="U206" s="3"/>
       <c r="V206" s="3"/>
-      <c r="W206" s="28"/>
+      <c r="W206" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="207" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A207" s="28">
@@ -11384,12 +11832,14 @@
       <c r="S207" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T207" s="3">
-        <v>16</v>
+      <c r="T207" s="29">
+        <v>0.4</v>
       </c>
       <c r="U207" s="3"/>
       <c r="V207" s="3"/>
-      <c r="W207" s="28"/>
+      <c r="W207" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" s="28">
@@ -11427,10 +11877,12 @@
       <c r="Q208" s="3"/>
       <c r="R208" s="3"/>
       <c r="S208" s="3"/>
-      <c r="T208" s="3"/>
+      <c r="T208" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U208" s="3"/>
       <c r="V208" s="3"/>
-      <c r="W208" s="28"/>
+      <c r="W208" s="3"/>
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" s="28">
@@ -11466,10 +11918,12 @@
       <c r="Q209" s="3"/>
       <c r="R209" s="3"/>
       <c r="S209" s="3"/>
-      <c r="T209" s="3"/>
+      <c r="T209" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U209" s="3"/>
       <c r="V209" s="3"/>
-      <c r="W209" s="28"/>
+      <c r="W209" s="3"/>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" s="28">
@@ -11509,10 +11963,12 @@
       <c r="Q210" s="3"/>
       <c r="R210" s="3"/>
       <c r="S210" s="3"/>
-      <c r="T210" s="3"/>
+      <c r="T210" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U210" s="3"/>
       <c r="V210" s="3"/>
-      <c r="W210" s="28"/>
+      <c r="W210" s="3"/>
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" s="28">
@@ -11550,10 +12006,12 @@
       <c r="Q211" s="3"/>
       <c r="R211" s="3"/>
       <c r="S211" s="3"/>
-      <c r="T211" s="3"/>
+      <c r="T211" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U211" s="3"/>
       <c r="V211" s="3"/>
-      <c r="W211" s="28"/>
+      <c r="W211" s="3"/>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="28">
@@ -11591,10 +12049,12 @@
       <c r="Q212" s="3"/>
       <c r="R212" s="3"/>
       <c r="S212" s="3"/>
-      <c r="T212" s="3"/>
+      <c r="T212" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U212" s="3"/>
       <c r="V212" s="3"/>
-      <c r="W212" s="28"/>
+      <c r="W212" s="3"/>
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" s="28">
@@ -11632,10 +12092,12 @@
       <c r="Q213" s="3"/>
       <c r="R213" s="3"/>
       <c r="S213" s="3"/>
-      <c r="T213" s="3"/>
+      <c r="T213" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U213" s="3"/>
       <c r="V213" s="3"/>
-      <c r="W213" s="28"/>
+      <c r="W213" s="3"/>
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" s="28">
@@ -11673,10 +12135,12 @@
       <c r="Q214" s="3"/>
       <c r="R214" s="3"/>
       <c r="S214" s="3"/>
-      <c r="T214" s="3"/>
+      <c r="T214" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U214" s="3"/>
       <c r="V214" s="3"/>
-      <c r="W214" s="28"/>
+      <c r="W214" s="3"/>
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" s="28">
@@ -11714,10 +12178,12 @@
       <c r="Q215" s="3"/>
       <c r="R215" s="3"/>
       <c r="S215" s="3"/>
-      <c r="T215" s="3"/>
+      <c r="T215" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U215" s="3"/>
       <c r="V215" s="3"/>
-      <c r="W215" s="28"/>
+      <c r="W215" s="3"/>
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" s="28">
@@ -11755,10 +12221,12 @@
       <c r="Q216" s="3"/>
       <c r="R216" s="3"/>
       <c r="S216" s="3"/>
-      <c r="T216" s="3"/>
+      <c r="T216" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U216" s="3"/>
       <c r="V216" s="3"/>
-      <c r="W216" s="28"/>
+      <c r="W216" s="3"/>
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="28">
@@ -11796,10 +12264,12 @@
       <c r="Q217" s="3"/>
       <c r="R217" s="3"/>
       <c r="S217" s="3"/>
-      <c r="T217" s="3"/>
+      <c r="T217" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U217" s="3"/>
       <c r="V217" s="3"/>
-      <c r="W217" s="28"/>
+      <c r="W217" s="3"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="28">
@@ -11837,10 +12307,12 @@
       <c r="Q218" s="3"/>
       <c r="R218" s="3"/>
       <c r="S218" s="3"/>
-      <c r="T218" s="3"/>
+      <c r="T218" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U218" s="3"/>
       <c r="V218" s="3"/>
-      <c r="W218" s="28"/>
+      <c r="W218" s="3"/>
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" s="28">
@@ -11880,10 +12352,12 @@
       <c r="Q219" s="3"/>
       <c r="R219" s="3"/>
       <c r="S219" s="3"/>
-      <c r="T219" s="3"/>
+      <c r="T219" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U219" s="3"/>
       <c r="V219" s="3"/>
-      <c r="W219" s="28"/>
+      <c r="W219" s="3"/>
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" s="28">
@@ -11923,10 +12397,12 @@
       <c r="Q220" s="3"/>
       <c r="R220" s="3"/>
       <c r="S220" s="3"/>
-      <c r="T220" s="3"/>
+      <c r="T220" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U220" s="3"/>
       <c r="V220" s="3"/>
-      <c r="W220" s="28"/>
+      <c r="W220" s="3"/>
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" s="28">
@@ -11966,10 +12442,12 @@
       <c r="Q221" s="3"/>
       <c r="R221" s="3"/>
       <c r="S221" s="3"/>
-      <c r="T221" s="3"/>
+      <c r="T221" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U221" s="3"/>
       <c r="V221" s="3"/>
-      <c r="W221" s="28"/>
+      <c r="W221" s="3"/>
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" s="28">
@@ -12009,10 +12487,12 @@
       <c r="Q222" s="3"/>
       <c r="R222" s="3"/>
       <c r="S222" s="3"/>
-      <c r="T222" s="3"/>
+      <c r="T222" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U222" s="3"/>
       <c r="V222" s="3"/>
-      <c r="W222" s="28"/>
+      <c r="W222" s="3"/>
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" s="28">
@@ -12052,10 +12532,12 @@
       <c r="Q223" s="3"/>
       <c r="R223" s="3"/>
       <c r="S223" s="3"/>
-      <c r="T223" s="3"/>
+      <c r="T223" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U223" s="3"/>
       <c r="V223" s="3"/>
-      <c r="W223" s="28"/>
+      <c r="W223" s="3"/>
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="28">
@@ -12105,12 +12587,14 @@
       <c r="S224" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T224" s="3">
-        <v>16</v>
+      <c r="T224" s="29">
+        <v>0.4</v>
       </c>
       <c r="U224" s="3"/>
       <c r="V224" s="3"/>
-      <c r="W224" s="28"/>
+      <c r="W224" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="225" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A225" s="28">
@@ -12148,10 +12632,12 @@
       <c r="Q225" s="3"/>
       <c r="R225" s="3"/>
       <c r="S225" s="3"/>
-      <c r="T225" s="3"/>
+      <c r="T225" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U225" s="3"/>
       <c r="V225" s="3"/>
-      <c r="W225" s="28"/>
+      <c r="W225" s="3"/>
     </row>
     <row r="226" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A226" s="28">
@@ -12187,10 +12673,12 @@
       <c r="Q226" s="3"/>
       <c r="R226" s="3"/>
       <c r="S226" s="3"/>
-      <c r="T226" s="3"/>
+      <c r="T226" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U226" s="3"/>
       <c r="V226" s="3"/>
-      <c r="W226" s="28"/>
+      <c r="W226" s="3"/>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="28">
@@ -12228,10 +12716,12 @@
       <c r="Q227" s="3"/>
       <c r="R227" s="3"/>
       <c r="S227" s="3"/>
-      <c r="T227" s="3"/>
+      <c r="T227" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U227" s="3"/>
       <c r="V227" s="3"/>
-      <c r="W227" s="28"/>
+      <c r="W227" s="3"/>
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="28">
@@ -12269,10 +12759,12 @@
       <c r="Q228" s="3"/>
       <c r="R228" s="3"/>
       <c r="S228" s="3"/>
-      <c r="T228" s="3"/>
+      <c r="T228" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U228" s="3"/>
       <c r="V228" s="3"/>
-      <c r="W228" s="28"/>
+      <c r="W228" s="3"/>
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="28">
@@ -12312,10 +12804,12 @@
       <c r="Q229" s="3"/>
       <c r="R229" s="3"/>
       <c r="S229" s="3"/>
-      <c r="T229" s="3"/>
+      <c r="T229" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U229" s="3"/>
       <c r="V229" s="3"/>
-      <c r="W229" s="28"/>
+      <c r="W229" s="3"/>
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="28">
@@ -12355,10 +12849,12 @@
       <c r="Q230" s="3"/>
       <c r="R230" s="3"/>
       <c r="S230" s="3"/>
-      <c r="T230" s="3"/>
+      <c r="T230" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U230" s="3"/>
       <c r="V230" s="3"/>
-      <c r="W230" s="28"/>
+      <c r="W230" s="3"/>
     </row>
     <row r="231" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A231" s="28">
@@ -12398,10 +12894,12 @@
       <c r="Q231" s="3"/>
       <c r="R231" s="3"/>
       <c r="S231" s="3"/>
-      <c r="T231" s="3"/>
+      <c r="T231" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U231" s="3"/>
       <c r="V231" s="3"/>
-      <c r="W231" s="28"/>
+      <c r="W231" s="3"/>
     </row>
     <row r="232" spans="1:23" ht="51" x14ac:dyDescent="0.25">
       <c r="A232" s="28">
@@ -12439,10 +12937,12 @@
       <c r="Q232" s="3"/>
       <c r="R232" s="3"/>
       <c r="S232" s="3"/>
-      <c r="T232" s="3"/>
+      <c r="T232" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U232" s="3"/>
       <c r="V232" s="3"/>
-      <c r="W232" s="28"/>
+      <c r="W232" s="3"/>
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="28">
@@ -12480,10 +12980,12 @@
       <c r="Q233" s="3"/>
       <c r="R233" s="3"/>
       <c r="S233" s="3"/>
-      <c r="T233" s="3"/>
+      <c r="T233" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U233" s="3"/>
       <c r="V233" s="3"/>
-      <c r="W233" s="28"/>
+      <c r="W233" s="3"/>
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="28">
@@ -12521,10 +13023,12 @@
       <c r="Q234" s="3"/>
       <c r="R234" s="3"/>
       <c r="S234" s="3"/>
-      <c r="T234" s="3"/>
+      <c r="T234" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U234" s="3"/>
       <c r="V234" s="3"/>
-      <c r="W234" s="28"/>
+      <c r="W234" s="3"/>
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="28">
@@ -12564,10 +13068,12 @@
       <c r="Q235" s="3"/>
       <c r="R235" s="3"/>
       <c r="S235" s="3"/>
-      <c r="T235" s="3"/>
+      <c r="T235" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U235" s="3"/>
       <c r="V235" s="3"/>
-      <c r="W235" s="28"/>
+      <c r="W235" s="3"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="28">
@@ -12607,10 +13113,12 @@
       <c r="Q236" s="3"/>
       <c r="R236" s="3"/>
       <c r="S236" s="3"/>
-      <c r="T236" s="3"/>
+      <c r="T236" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U236" s="3"/>
       <c r="V236" s="3"/>
-      <c r="W236" s="28"/>
+      <c r="W236" s="3"/>
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="28">
@@ -12648,10 +13156,12 @@
       <c r="Q237" s="3"/>
       <c r="R237" s="3"/>
       <c r="S237" s="3"/>
-      <c r="T237" s="3"/>
+      <c r="T237" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U237" s="3"/>
       <c r="V237" s="3"/>
-      <c r="W237" s="28"/>
+      <c r="W237" s="3"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="28">
@@ -12689,10 +13199,12 @@
       <c r="Q238" s="3"/>
       <c r="R238" s="3"/>
       <c r="S238" s="3"/>
-      <c r="T238" s="3"/>
+      <c r="T238" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U238" s="3"/>
       <c r="V238" s="3"/>
-      <c r="W238" s="28"/>
+      <c r="W238" s="3"/>
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="28">
@@ -12730,10 +13242,12 @@
       <c r="Q239" s="3"/>
       <c r="R239" s="3"/>
       <c r="S239" s="3"/>
-      <c r="T239" s="3"/>
+      <c r="T239" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U239" s="3"/>
       <c r="V239" s="3"/>
-      <c r="W239" s="28"/>
+      <c r="W239" s="3"/>
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="28">
@@ -12771,10 +13285,12 @@
       <c r="Q240" s="3"/>
       <c r="R240" s="3"/>
       <c r="S240" s="3"/>
-      <c r="T240" s="3"/>
+      <c r="T240" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U240" s="3"/>
       <c r="V240" s="3"/>
-      <c r="W240" s="28"/>
+      <c r="W240" s="3"/>
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="28">
@@ -12812,10 +13328,12 @@
       <c r="Q241" s="3"/>
       <c r="R241" s="3"/>
       <c r="S241" s="3"/>
-      <c r="T241" s="3"/>
+      <c r="T241" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U241" s="3"/>
       <c r="V241" s="3"/>
-      <c r="W241" s="28"/>
+      <c r="W241" s="3"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="28">
@@ -12853,10 +13371,12 @@
       <c r="Q242" s="3"/>
       <c r="R242" s="3"/>
       <c r="S242" s="3"/>
-      <c r="T242" s="3"/>
+      <c r="T242" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U242" s="3"/>
       <c r="V242" s="3"/>
-      <c r="W242" s="28"/>
+      <c r="W242" s="3"/>
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="28">
@@ -12894,10 +13414,12 @@
       <c r="Q243" s="3"/>
       <c r="R243" s="3"/>
       <c r="S243" s="3"/>
-      <c r="T243" s="3"/>
+      <c r="T243" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U243" s="3"/>
       <c r="V243" s="3"/>
-      <c r="W243" s="28"/>
+      <c r="W243" s="3"/>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="28">
@@ -12935,10 +13457,12 @@
       <c r="Q244" s="3"/>
       <c r="R244" s="3"/>
       <c r="S244" s="3"/>
-      <c r="T244" s="3"/>
+      <c r="T244" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U244" s="3"/>
       <c r="V244" s="3"/>
-      <c r="W244" s="28"/>
+      <c r="W244" s="3"/>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="28">
@@ -12976,10 +13500,12 @@
       <c r="Q245" s="3"/>
       <c r="R245" s="3"/>
       <c r="S245" s="3"/>
-      <c r="T245" s="3"/>
+      <c r="T245" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U245" s="3"/>
       <c r="V245" s="3"/>
-      <c r="W245" s="28"/>
+      <c r="W245" s="3"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="28">
@@ -13017,10 +13543,12 @@
       <c r="Q246" s="3"/>
       <c r="R246" s="3"/>
       <c r="S246" s="3"/>
-      <c r="T246" s="3"/>
+      <c r="T246" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U246" s="3"/>
       <c r="V246" s="3"/>
-      <c r="W246" s="28"/>
+      <c r="W246" s="3"/>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="28">
@@ -13058,10 +13586,12 @@
       <c r="Q247" s="3"/>
       <c r="R247" s="3"/>
       <c r="S247" s="3"/>
-      <c r="T247" s="3"/>
+      <c r="T247" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U247" s="3"/>
       <c r="V247" s="3"/>
-      <c r="W247" s="28"/>
+      <c r="W247" s="3"/>
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="28">
@@ -13099,10 +13629,12 @@
       <c r="Q248" s="3"/>
       <c r="R248" s="3"/>
       <c r="S248" s="3"/>
-      <c r="T248" s="3"/>
+      <c r="T248" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U248" s="3"/>
       <c r="V248" s="3"/>
-      <c r="W248" s="28"/>
+      <c r="W248" s="3"/>
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="28">
@@ -13140,10 +13672,12 @@
       <c r="Q249" s="3"/>
       <c r="R249" s="3"/>
       <c r="S249" s="3"/>
-      <c r="T249" s="3"/>
+      <c r="T249" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U249" s="3"/>
       <c r="V249" s="3"/>
-      <c r="W249" s="28"/>
+      <c r="W249" s="3"/>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="28">
@@ -13181,10 +13715,12 @@
       <c r="Q250" s="3"/>
       <c r="R250" s="3"/>
       <c r="S250" s="3"/>
-      <c r="T250" s="3"/>
+      <c r="T250" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U250" s="3"/>
       <c r="V250" s="3"/>
-      <c r="W250" s="28"/>
+      <c r="W250" s="3"/>
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="28">
@@ -13222,10 +13758,12 @@
       <c r="Q251" s="3"/>
       <c r="R251" s="3"/>
       <c r="S251" s="3"/>
-      <c r="T251" s="3"/>
+      <c r="T251" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U251" s="3"/>
       <c r="V251" s="3"/>
-      <c r="W251" s="28"/>
+      <c r="W251" s="3"/>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="28">
@@ -13263,10 +13801,12 @@
       <c r="Q252" s="3"/>
       <c r="R252" s="3"/>
       <c r="S252" s="3"/>
-      <c r="T252" s="3"/>
+      <c r="T252" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U252" s="3"/>
       <c r="V252" s="3"/>
-      <c r="W252" s="28"/>
+      <c r="W252" s="3"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="28">
@@ -13304,10 +13844,12 @@
       <c r="Q253" s="3"/>
       <c r="R253" s="3"/>
       <c r="S253" s="3"/>
-      <c r="T253" s="3"/>
+      <c r="T253" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U253" s="3"/>
       <c r="V253" s="3"/>
-      <c r="W253" s="28"/>
+      <c r="W253" s="3"/>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="28">
@@ -13345,10 +13887,12 @@
       <c r="Q254" s="3"/>
       <c r="R254" s="3"/>
       <c r="S254" s="3"/>
-      <c r="T254" s="3"/>
+      <c r="T254" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U254" s="3"/>
       <c r="V254" s="3"/>
-      <c r="W254" s="28"/>
+      <c r="W254" s="3"/>
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="28">
@@ -13386,10 +13930,12 @@
       <c r="Q255" s="3"/>
       <c r="R255" s="3"/>
       <c r="S255" s="3"/>
-      <c r="T255" s="3"/>
+      <c r="T255" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U255" s="3"/>
       <c r="V255" s="3"/>
-      <c r="W255" s="28"/>
+      <c r="W255" s="3"/>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="28">
@@ -13427,10 +13973,12 @@
       <c r="Q256" s="3"/>
       <c r="R256" s="3"/>
       <c r="S256" s="3"/>
-      <c r="T256" s="3"/>
+      <c r="T256" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U256" s="3"/>
       <c r="V256" s="3"/>
-      <c r="W256" s="28"/>
+      <c r="W256" s="3"/>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="28">
@@ -13468,10 +14016,12 @@
       <c r="Q257" s="3"/>
       <c r="R257" s="3"/>
       <c r="S257" s="3"/>
-      <c r="T257" s="3"/>
+      <c r="T257" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U257" s="3"/>
       <c r="V257" s="3"/>
-      <c r="W257" s="28"/>
+      <c r="W257" s="3"/>
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="28">
@@ -13509,10 +14059,12 @@
       <c r="Q258" s="3"/>
       <c r="R258" s="3"/>
       <c r="S258" s="3"/>
-      <c r="T258" s="3"/>
+      <c r="T258" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U258" s="3"/>
       <c r="V258" s="3"/>
-      <c r="W258" s="28"/>
+      <c r="W258" s="3"/>
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="28">
@@ -13550,10 +14102,12 @@
       <c r="Q259" s="3"/>
       <c r="R259" s="3"/>
       <c r="S259" s="3"/>
-      <c r="T259" s="3"/>
+      <c r="T259" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U259" s="3"/>
       <c r="V259" s="3"/>
-      <c r="W259" s="28"/>
+      <c r="W259" s="3"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="28">
@@ -13591,10 +14145,12 @@
       <c r="Q260" s="3"/>
       <c r="R260" s="3"/>
       <c r="S260" s="3"/>
-      <c r="T260" s="3"/>
+      <c r="T260" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U260" s="3"/>
       <c r="V260" s="3"/>
-      <c r="W260" s="28"/>
+      <c r="W260" s="3"/>
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" s="28">
@@ -13632,10 +14188,12 @@
       <c r="Q261" s="3"/>
       <c r="R261" s="3"/>
       <c r="S261" s="3"/>
-      <c r="T261" s="3"/>
+      <c r="T261" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U261" s="3"/>
       <c r="V261" s="3"/>
-      <c r="W261" s="28"/>
+      <c r="W261" s="3"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" s="28">
@@ -13673,10 +14231,12 @@
       <c r="Q262" s="3"/>
       <c r="R262" s="3"/>
       <c r="S262" s="3"/>
-      <c r="T262" s="3"/>
+      <c r="T262" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U262" s="3"/>
       <c r="V262" s="3"/>
-      <c r="W262" s="28"/>
+      <c r="W262" s="3"/>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" s="28">
@@ -13714,10 +14274,12 @@
       <c r="Q263" s="3"/>
       <c r="R263" s="3"/>
       <c r="S263" s="3"/>
-      <c r="T263" s="3"/>
+      <c r="T263" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U263" s="3"/>
       <c r="V263" s="3"/>
-      <c r="W263" s="28"/>
+      <c r="W263" s="3"/>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" s="28">
@@ -13755,10 +14317,12 @@
       <c r="Q264" s="3"/>
       <c r="R264" s="3"/>
       <c r="S264" s="3"/>
-      <c r="T264" s="3"/>
+      <c r="T264" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U264" s="3"/>
       <c r="V264" s="3"/>
-      <c r="W264" s="28"/>
+      <c r="W264" s="3"/>
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" s="28">
@@ -13796,10 +14360,12 @@
       <c r="Q265" s="3"/>
       <c r="R265" s="3"/>
       <c r="S265" s="3"/>
-      <c r="T265" s="3"/>
+      <c r="T265" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U265" s="3"/>
       <c r="V265" s="3"/>
-      <c r="W265" s="28"/>
+      <c r="W265" s="3"/>
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" s="28">
@@ -13837,10 +14403,12 @@
       <c r="Q266" s="3"/>
       <c r="R266" s="3"/>
       <c r="S266" s="3"/>
-      <c r="T266" s="3"/>
+      <c r="T266" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U266" s="3"/>
       <c r="V266" s="3"/>
-      <c r="W266" s="28"/>
+      <c r="W266" s="3"/>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" s="28">
@@ -13878,10 +14446,12 @@
       <c r="Q267" s="3"/>
       <c r="R267" s="3"/>
       <c r="S267" s="3"/>
-      <c r="T267" s="3"/>
+      <c r="T267" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U267" s="3"/>
       <c r="V267" s="3"/>
-      <c r="W267" s="28"/>
+      <c r="W267" s="3"/>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" s="28">
@@ -13919,10 +14489,12 @@
       <c r="Q268" s="3"/>
       <c r="R268" s="3"/>
       <c r="S268" s="3"/>
-      <c r="T268" s="3"/>
+      <c r="T268" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U268" s="3"/>
       <c r="V268" s="3"/>
-      <c r="W268" s="28"/>
+      <c r="W268" s="3"/>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" s="28">
@@ -13960,10 +14532,12 @@
       <c r="Q269" s="3"/>
       <c r="R269" s="3"/>
       <c r="S269" s="3"/>
-      <c r="T269" s="3"/>
+      <c r="T269" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U269" s="3"/>
       <c r="V269" s="3"/>
-      <c r="W269" s="28"/>
+      <c r="W269" s="3"/>
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" s="28">
@@ -14001,10 +14575,12 @@
       <c r="Q270" s="3"/>
       <c r="R270" s="3"/>
       <c r="S270" s="3"/>
-      <c r="T270" s="3"/>
+      <c r="T270" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U270" s="3"/>
       <c r="V270" s="3"/>
-      <c r="W270" s="28"/>
+      <c r="W270" s="3"/>
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" s="28">
@@ -14042,10 +14618,12 @@
       <c r="Q271" s="3"/>
       <c r="R271" s="3"/>
       <c r="S271" s="3"/>
-      <c r="T271" s="3"/>
+      <c r="T271" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U271" s="3"/>
       <c r="V271" s="3"/>
-      <c r="W271" s="28"/>
+      <c r="W271" s="3"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" s="28">
@@ -14083,10 +14661,12 @@
       <c r="Q272" s="3"/>
       <c r="R272" s="3"/>
       <c r="S272" s="3"/>
-      <c r="T272" s="3"/>
+      <c r="T272" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U272" s="3"/>
       <c r="V272" s="3"/>
-      <c r="W272" s="28"/>
+      <c r="W272" s="3"/>
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" s="28">
@@ -14124,10 +14704,12 @@
       <c r="Q273" s="3"/>
       <c r="R273" s="3"/>
       <c r="S273" s="3"/>
-      <c r="T273" s="3"/>
+      <c r="T273" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U273" s="3"/>
       <c r="V273" s="3"/>
-      <c r="W273" s="28"/>
+      <c r="W273" s="3"/>
     </row>
     <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" s="28">
@@ -14165,10 +14747,12 @@
       <c r="Q274" s="3"/>
       <c r="R274" s="3"/>
       <c r="S274" s="3"/>
-      <c r="T274" s="3"/>
+      <c r="T274" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U274" s="3"/>
       <c r="V274" s="3"/>
-      <c r="W274" s="28"/>
+      <c r="W274" s="3"/>
     </row>
     <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" s="28">
@@ -14206,10 +14790,12 @@
       <c r="Q275" s="3"/>
       <c r="R275" s="3"/>
       <c r="S275" s="3"/>
-      <c r="T275" s="3"/>
+      <c r="T275" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U275" s="3"/>
       <c r="V275" s="3"/>
-      <c r="W275" s="28"/>
+      <c r="W275" s="3"/>
     </row>
     <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" s="28">
@@ -14247,10 +14833,12 @@
       <c r="Q276" s="3"/>
       <c r="R276" s="3"/>
       <c r="S276" s="3"/>
-      <c r="T276" s="3"/>
+      <c r="T276" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U276" s="3"/>
       <c r="V276" s="3"/>
-      <c r="W276" s="28"/>
+      <c r="W276" s="3"/>
     </row>
     <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" s="28">
@@ -14288,10 +14876,12 @@
       <c r="Q277" s="3"/>
       <c r="R277" s="3"/>
       <c r="S277" s="3"/>
-      <c r="T277" s="3"/>
+      <c r="T277" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U277" s="3"/>
       <c r="V277" s="3"/>
-      <c r="W277" s="28"/>
+      <c r="W277" s="3"/>
     </row>
     <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" s="28">
@@ -14329,10 +14919,12 @@
       <c r="Q278" s="3"/>
       <c r="R278" s="3"/>
       <c r="S278" s="3"/>
-      <c r="T278" s="3"/>
+      <c r="T278" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U278" s="3"/>
       <c r="V278" s="3"/>
-      <c r="W278" s="28"/>
+      <c r="W278" s="3"/>
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" s="28">
@@ -14370,10 +14962,12 @@
       <c r="Q279" s="3"/>
       <c r="R279" s="3"/>
       <c r="S279" s="3"/>
-      <c r="T279" s="3"/>
+      <c r="T279" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U279" s="3"/>
       <c r="V279" s="3"/>
-      <c r="W279" s="28"/>
+      <c r="W279" s="3"/>
     </row>
     <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" s="28">
@@ -14425,10 +15019,12 @@
       <c r="S280" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T280" s="3"/>
+      <c r="T280" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U280" s="3"/>
       <c r="V280" s="3"/>
-      <c r="W280" s="28"/>
+      <c r="W280" s="3"/>
     </row>
     <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" s="28">
@@ -14471,13 +15067,21 @@
       <c r="P281" s="3">
         <v>32</v>
       </c>
-      <c r="Q281" s="3"/>
-      <c r="R281" s="3"/>
-      <c r="S281" s="3"/>
-      <c r="T281" s="3"/>
+      <c r="Q281" s="3">
+        <v>5</v>
+      </c>
+      <c r="R281" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S281" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T281" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U281" s="3"/>
       <c r="V281" s="3"/>
-      <c r="W281" s="28"/>
+      <c r="W281" s="3"/>
     </row>
     <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" s="28">
@@ -14520,13 +15124,21 @@
       <c r="P282" s="3">
         <v>29</v>
       </c>
-      <c r="Q282" s="3"/>
-      <c r="R282" s="3"/>
-      <c r="S282" s="3"/>
-      <c r="T282" s="3"/>
+      <c r="Q282" s="3">
+        <v>5</v>
+      </c>
+      <c r="R282" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S282" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T282" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U282" s="3"/>
       <c r="V282" s="3"/>
-      <c r="W282" s="28"/>
+      <c r="W282" s="3"/>
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" s="28">
@@ -14569,13 +15181,21 @@
       <c r="P283" s="3">
         <v>10</v>
       </c>
-      <c r="Q283" s="3"/>
-      <c r="R283" s="3"/>
-      <c r="S283" s="3"/>
-      <c r="T283" s="3"/>
+      <c r="Q283" s="3">
+        <v>5</v>
+      </c>
+      <c r="R283" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S283" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T283" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U283" s="3"/>
       <c r="V283" s="3"/>
-      <c r="W283" s="28"/>
+      <c r="W283" s="3"/>
     </row>
     <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" s="28">
@@ -14618,13 +15238,21 @@
       <c r="P284" s="3">
         <v>50</v>
       </c>
-      <c r="Q284" s="3"/>
-      <c r="R284" s="3"/>
-      <c r="S284" s="3"/>
-      <c r="T284" s="3"/>
+      <c r="Q284" s="3">
+        <v>5</v>
+      </c>
+      <c r="R284" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S284" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T284" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U284" s="3"/>
       <c r="V284" s="3"/>
-      <c r="W284" s="28"/>
+      <c r="W284" s="3"/>
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" s="28">
@@ -14667,13 +15295,21 @@
       <c r="P285" s="3">
         <v>10</v>
       </c>
-      <c r="Q285" s="3"/>
-      <c r="R285" s="3"/>
-      <c r="S285" s="3"/>
-      <c r="T285" s="3"/>
+      <c r="Q285" s="3">
+        <v>5</v>
+      </c>
+      <c r="R285" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S285" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T285" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U285" s="3"/>
       <c r="V285" s="3"/>
-      <c r="W285" s="28"/>
+      <c r="W285" s="3"/>
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" s="28">
@@ -14716,13 +15352,21 @@
       <c r="P286" s="3">
         <v>8</v>
       </c>
-      <c r="Q286" s="3"/>
-      <c r="R286" s="3"/>
-      <c r="S286" s="3"/>
-      <c r="T286" s="3"/>
+      <c r="Q286" s="3">
+        <v>5</v>
+      </c>
+      <c r="R286" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S286" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T286" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U286" s="3"/>
       <c r="V286" s="3"/>
-      <c r="W286" s="28"/>
+      <c r="W286" s="3"/>
     </row>
     <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" s="28">
@@ -14765,13 +15409,21 @@
       <c r="P287" s="3">
         <v>8</v>
       </c>
-      <c r="Q287" s="3"/>
-      <c r="R287" s="3"/>
-      <c r="S287" s="3"/>
-      <c r="T287" s="3"/>
+      <c r="Q287" s="3">
+        <v>5</v>
+      </c>
+      <c r="R287" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S287" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T287" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U287" s="3"/>
       <c r="V287" s="3"/>
-      <c r="W287" s="28"/>
+      <c r="W287" s="3"/>
     </row>
     <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" s="28">
@@ -14814,13 +15466,21 @@
       <c r="P288" s="3">
         <v>34</v>
       </c>
-      <c r="Q288" s="3"/>
-      <c r="R288" s="3"/>
-      <c r="S288" s="3"/>
-      <c r="T288" s="3"/>
+      <c r="Q288" s="3">
+        <v>5</v>
+      </c>
+      <c r="R288" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S288" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T288" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U288" s="3"/>
       <c r="V288" s="3"/>
-      <c r="W288" s="28"/>
+      <c r="W288" s="3"/>
     </row>
     <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" s="28">
@@ -14863,13 +15523,21 @@
       <c r="P289" s="3">
         <v>34</v>
       </c>
-      <c r="Q289" s="3"/>
-      <c r="R289" s="3"/>
-      <c r="S289" s="3"/>
-      <c r="T289" s="3"/>
+      <c r="Q289" s="3">
+        <v>5</v>
+      </c>
+      <c r="R289" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S289" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T289" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U289" s="3"/>
       <c r="V289" s="3"/>
-      <c r="W289" s="28"/>
+      <c r="W289" s="3"/>
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" s="28">
@@ -14921,10 +15589,12 @@
       <c r="S290" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T290" s="3"/>
+      <c r="T290" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U290" s="3"/>
       <c r="V290" s="3"/>
-      <c r="W290" s="28"/>
+      <c r="W290" s="3"/>
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" s="28">
@@ -14967,13 +15637,21 @@
       <c r="P291" s="3">
         <v>55</v>
       </c>
-      <c r="Q291" s="3"/>
-      <c r="R291" s="3"/>
-      <c r="S291" s="3"/>
-      <c r="T291" s="3"/>
+      <c r="Q291" s="3">
+        <v>5</v>
+      </c>
+      <c r="R291" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S291" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T291" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U291" s="3"/>
       <c r="V291" s="3"/>
-      <c r="W291" s="28"/>
+      <c r="W291" s="3"/>
     </row>
     <row r="292" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A292" s="28">
@@ -15016,13 +15694,21 @@
       <c r="P292" s="3">
         <v>131</v>
       </c>
-      <c r="Q292" s="3"/>
-      <c r="R292" s="3"/>
-      <c r="S292" s="3"/>
-      <c r="T292" s="3"/>
+      <c r="Q292" s="3">
+        <v>5</v>
+      </c>
+      <c r="R292" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S292" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T292" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U292" s="3"/>
       <c r="V292" s="3"/>
-      <c r="W292" s="28"/>
+      <c r="W292" s="3"/>
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A293" s="28">
@@ -15065,13 +15751,21 @@
       <c r="P293" s="3">
         <v>65</v>
       </c>
-      <c r="Q293" s="3"/>
-      <c r="R293" s="3"/>
-      <c r="S293" s="3"/>
-      <c r="T293" s="3"/>
+      <c r="Q293" s="3">
+        <v>5</v>
+      </c>
+      <c r="R293" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S293" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T293" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U293" s="3"/>
       <c r="V293" s="3"/>
-      <c r="W293" s="28"/>
+      <c r="W293" s="3"/>
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A294" s="28">
@@ -15114,13 +15808,21 @@
       <c r="P294" s="3">
         <v>10</v>
       </c>
-      <c r="Q294" s="3"/>
-      <c r="R294" s="3"/>
-      <c r="S294" s="3"/>
-      <c r="T294" s="3"/>
+      <c r="Q294" s="3">
+        <v>5</v>
+      </c>
+      <c r="R294" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S294" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T294" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U294" s="3"/>
       <c r="V294" s="3"/>
-      <c r="W294" s="28"/>
+      <c r="W294" s="3"/>
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A295" s="28">
@@ -15154,10 +15856,12 @@
       <c r="Q295" s="3"/>
       <c r="R295" s="3"/>
       <c r="S295" s="3"/>
-      <c r="T295" s="3"/>
+      <c r="T295" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U295" s="3"/>
       <c r="V295" s="3"/>
-      <c r="W295" s="28"/>
+      <c r="W295" s="3"/>
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A296" s="28">
@@ -15191,10 +15895,12 @@
       <c r="Q296" s="3"/>
       <c r="R296" s="3"/>
       <c r="S296" s="3"/>
-      <c r="T296" s="3"/>
+      <c r="T296" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U296" s="3"/>
       <c r="V296" s="3"/>
-      <c r="W296" s="28"/>
+      <c r="W296" s="3"/>
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A297" s="28">
@@ -15228,10 +15934,12 @@
       <c r="Q297" s="3"/>
       <c r="R297" s="3"/>
       <c r="S297" s="3"/>
-      <c r="T297" s="3"/>
+      <c r="T297" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U297" s="3"/>
       <c r="V297" s="3"/>
-      <c r="W297" s="28"/>
+      <c r="W297" s="3"/>
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A298" s="28">
@@ -15265,10 +15973,12 @@
       <c r="Q298" s="3"/>
       <c r="R298" s="3"/>
       <c r="S298" s="3"/>
-      <c r="T298" s="3"/>
+      <c r="T298" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U298" s="3"/>
       <c r="V298" s="3"/>
-      <c r="W298" s="28"/>
+      <c r="W298" s="3"/>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A299" s="28">
@@ -15302,10 +16012,12 @@
       <c r="Q299" s="3"/>
       <c r="R299" s="3"/>
       <c r="S299" s="3"/>
-      <c r="T299" s="3"/>
+      <c r="T299" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U299" s="3"/>
       <c r="V299" s="3"/>
-      <c r="W299" s="28"/>
+      <c r="W299" s="3"/>
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A300" s="28">
@@ -15348,13 +16060,21 @@
       <c r="P300" s="3">
         <v>100</v>
       </c>
-      <c r="Q300" s="3"/>
-      <c r="R300" s="3"/>
-      <c r="S300" s="3"/>
-      <c r="T300" s="3"/>
+      <c r="Q300" s="3">
+        <v>5</v>
+      </c>
+      <c r="R300" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S300" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T300" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U300" s="3"/>
       <c r="V300" s="3"/>
-      <c r="W300" s="28"/>
+      <c r="W300" s="3"/>
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A301" s="28">
@@ -15397,13 +16117,21 @@
       <c r="P301" s="3">
         <v>25</v>
       </c>
-      <c r="Q301" s="3"/>
-      <c r="R301" s="3"/>
-      <c r="S301" s="3"/>
-      <c r="T301" s="3"/>
+      <c r="Q301" s="3">
+        <v>5</v>
+      </c>
+      <c r="R301" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S301" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T301" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U301" s="3"/>
       <c r="V301" s="3"/>
-      <c r="W301" s="28"/>
+      <c r="W301" s="3"/>
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A302" s="28">
@@ -15446,13 +16174,21 @@
       <c r="P302" s="3">
         <v>55</v>
       </c>
-      <c r="Q302" s="3"/>
-      <c r="R302" s="3"/>
-      <c r="S302" s="3"/>
-      <c r="T302" s="3"/>
+      <c r="Q302" s="3">
+        <v>5</v>
+      </c>
+      <c r="R302" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S302" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T302" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U302" s="3"/>
       <c r="V302" s="3"/>
-      <c r="W302" s="28"/>
+      <c r="W302" s="3"/>
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A303" s="28">
@@ -15495,13 +16231,21 @@
       <c r="P303" s="3">
         <v>60</v>
       </c>
-      <c r="Q303" s="3"/>
-      <c r="R303" s="3"/>
-      <c r="S303" s="3"/>
-      <c r="T303" s="3"/>
+      <c r="Q303" s="3">
+        <v>5</v>
+      </c>
+      <c r="R303" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S303" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T303" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U303" s="3"/>
       <c r="V303" s="3"/>
-      <c r="W303" s="28"/>
+      <c r="W303" s="3"/>
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A304" s="28">
@@ -15544,13 +16288,21 @@
       <c r="P304" s="3">
         <v>34</v>
       </c>
-      <c r="Q304" s="3"/>
-      <c r="R304" s="3"/>
-      <c r="S304" s="3"/>
-      <c r="T304" s="3"/>
+      <c r="Q304" s="3">
+        <v>5</v>
+      </c>
+      <c r="R304" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S304" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T304" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U304" s="3"/>
       <c r="V304" s="3"/>
-      <c r="W304" s="28"/>
+      <c r="W304" s="3"/>
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A305" s="28">
@@ -15593,13 +16345,21 @@
       <c r="P305" s="3">
         <v>34</v>
       </c>
-      <c r="Q305" s="3"/>
-      <c r="R305" s="3"/>
-      <c r="S305" s="3"/>
-      <c r="T305" s="3"/>
+      <c r="Q305" s="3">
+        <v>5</v>
+      </c>
+      <c r="R305" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S305" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T305" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U305" s="3"/>
       <c r="V305" s="3"/>
-      <c r="W305" s="28"/>
+      <c r="W305" s="3"/>
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A306" s="28">
@@ -15642,13 +16402,21 @@
       <c r="P306" s="3">
         <v>85</v>
       </c>
-      <c r="Q306" s="3"/>
-      <c r="R306" s="3"/>
-      <c r="S306" s="3"/>
-      <c r="T306" s="3"/>
+      <c r="Q306" s="3">
+        <v>5</v>
+      </c>
+      <c r="R306" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S306" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T306" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U306" s="3"/>
       <c r="V306" s="3"/>
-      <c r="W306" s="28"/>
+      <c r="W306" s="3"/>
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A307" s="28">
@@ -15691,13 +16459,21 @@
       <c r="P307" s="3">
         <v>86</v>
       </c>
-      <c r="Q307" s="3"/>
-      <c r="R307" s="3"/>
-      <c r="S307" s="3"/>
-      <c r="T307" s="3"/>
+      <c r="Q307" s="3">
+        <v>5</v>
+      </c>
+      <c r="R307" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S307" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T307" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U307" s="3"/>
       <c r="V307" s="3"/>
-      <c r="W307" s="28"/>
+      <c r="W307" s="3"/>
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A308" s="28">
@@ -15734,13 +16510,21 @@
       <c r="P308" s="3">
         <v>74</v>
       </c>
-      <c r="Q308" s="3"/>
-      <c r="R308" s="3"/>
-      <c r="S308" s="3"/>
-      <c r="T308" s="3"/>
+      <c r="Q308" s="3">
+        <v>5</v>
+      </c>
+      <c r="R308" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S308" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T308" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U308" s="3"/>
       <c r="V308" s="3"/>
-      <c r="W308" s="28"/>
+      <c r="W308" s="3"/>
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A309" s="28">
@@ -15777,13 +16561,21 @@
       <c r="P309" s="3">
         <v>26</v>
       </c>
-      <c r="Q309" s="3"/>
-      <c r="R309" s="3"/>
-      <c r="S309" s="3"/>
-      <c r="T309" s="3"/>
+      <c r="Q309" s="3">
+        <v>5</v>
+      </c>
+      <c r="R309" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S309" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T309" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U309" s="3"/>
       <c r="V309" s="3"/>
-      <c r="W309" s="28"/>
+      <c r="W309" s="3"/>
     </row>
     <row r="310" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A310" s="28">
@@ -15826,13 +16618,21 @@
       <c r="P310" s="3">
         <v>70</v>
       </c>
-      <c r="Q310" s="3"/>
-      <c r="R310" s="3"/>
-      <c r="S310" s="3"/>
-      <c r="T310" s="3"/>
+      <c r="Q310" s="3">
+        <v>5</v>
+      </c>
+      <c r="R310" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S310" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T310" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U310" s="3"/>
       <c r="V310" s="3"/>
-      <c r="W310" s="28"/>
+      <c r="W310" s="3"/>
     </row>
     <row r="311" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A311" s="28">
@@ -15875,13 +16675,21 @@
       <c r="P311" s="3">
         <v>90</v>
       </c>
-      <c r="Q311" s="3"/>
-      <c r="R311" s="3"/>
-      <c r="S311" s="3"/>
-      <c r="T311" s="3"/>
+      <c r="Q311" s="3">
+        <v>5</v>
+      </c>
+      <c r="R311" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S311" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T311" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U311" s="3"/>
       <c r="V311" s="3"/>
-      <c r="W311" s="28"/>
+      <c r="W311" s="3"/>
     </row>
     <row r="312" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A312" s="28">
@@ -15924,13 +16732,21 @@
       <c r="P312" s="3">
         <v>92</v>
       </c>
-      <c r="Q312" s="3"/>
-      <c r="R312" s="3"/>
-      <c r="S312" s="3"/>
-      <c r="T312" s="3"/>
+      <c r="Q312" s="3">
+        <v>5</v>
+      </c>
+      <c r="R312" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S312" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T312" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U312" s="3"/>
       <c r="V312" s="3"/>
-      <c r="W312" s="28"/>
+      <c r="W312" s="3"/>
     </row>
     <row r="313" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A313" s="28">
@@ -15973,13 +16789,21 @@
       <c r="P313" s="3">
         <v>108</v>
       </c>
-      <c r="Q313" s="3"/>
-      <c r="R313" s="3"/>
-      <c r="S313" s="3"/>
-      <c r="T313" s="3"/>
+      <c r="Q313" s="3">
+        <v>5</v>
+      </c>
+      <c r="R313" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S313" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T313" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U313" s="3"/>
       <c r="V313" s="3"/>
-      <c r="W313" s="28"/>
+      <c r="W313" s="3"/>
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A314" s="28">
@@ -16031,10 +16855,12 @@
       <c r="S314" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T314" s="3"/>
+      <c r="T314" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U314" s="3"/>
       <c r="V314" s="3"/>
-      <c r="W314" s="28"/>
+      <c r="W314" s="3"/>
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A315" s="28">
@@ -16086,12 +16912,14 @@
       <c r="S315" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T315" s="3">
-        <v>16</v>
+      <c r="T315" s="29">
+        <v>0.22</v>
       </c>
       <c r="U315" s="3"/>
       <c r="V315" s="3"/>
-      <c r="W315" s="28"/>
+      <c r="W315" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A316" s="28">
@@ -16134,13 +16962,21 @@
       <c r="P316" s="3">
         <v>130</v>
       </c>
-      <c r="Q316" s="3"/>
-      <c r="R316" s="3"/>
-      <c r="S316" s="3"/>
-      <c r="T316" s="3"/>
+      <c r="Q316" s="3">
+        <v>5</v>
+      </c>
+      <c r="R316" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S316" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T316" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U316" s="3"/>
       <c r="V316" s="3"/>
-      <c r="W316" s="28"/>
+      <c r="W316" s="3"/>
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A317" s="28">
@@ -16183,13 +17019,21 @@
       <c r="P317" s="3">
         <v>35</v>
       </c>
-      <c r="Q317" s="3"/>
-      <c r="R317" s="3"/>
-      <c r="S317" s="3"/>
-      <c r="T317" s="3"/>
+      <c r="Q317" s="3">
+        <v>5</v>
+      </c>
+      <c r="R317" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S317" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T317" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U317" s="3"/>
       <c r="V317" s="3"/>
-      <c r="W317" s="28"/>
+      <c r="W317" s="3"/>
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A318" s="28">
@@ -16232,13 +17076,21 @@
       <c r="P318" s="3">
         <v>15</v>
       </c>
-      <c r="Q318" s="3"/>
-      <c r="R318" s="3"/>
-      <c r="S318" s="3"/>
-      <c r="T318" s="3"/>
+      <c r="Q318" s="3">
+        <v>5</v>
+      </c>
+      <c r="R318" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S318" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T318" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U318" s="3"/>
       <c r="V318" s="3"/>
-      <c r="W318" s="28"/>
+      <c r="W318" s="3"/>
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A319" s="28">
@@ -16281,13 +17133,21 @@
       <c r="P319" s="3">
         <v>92</v>
       </c>
-      <c r="Q319" s="3"/>
-      <c r="R319" s="3"/>
-      <c r="S319" s="3"/>
-      <c r="T319" s="3"/>
+      <c r="Q319" s="3">
+        <v>5</v>
+      </c>
+      <c r="R319" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S319" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T319" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U319" s="3"/>
       <c r="V319" s="3"/>
-      <c r="W319" s="28"/>
+      <c r="W319" s="3"/>
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A320" s="28">
@@ -16309,7 +17169,9 @@
       <c r="I320" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="J320" s="3"/>
+      <c r="J320" s="3">
+        <v>7</v>
+      </c>
       <c r="K320" s="1">
         <v>4.5</v>
       </c>
@@ -16323,10 +17185,12 @@
       <c r="Q320" s="3"/>
       <c r="R320" s="3"/>
       <c r="S320" s="3"/>
-      <c r="T320" s="3"/>
+      <c r="T320" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U320" s="3"/>
       <c r="V320" s="3"/>
-      <c r="W320" s="28"/>
+      <c r="W320" s="3"/>
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A321" s="28">
@@ -16348,7 +17212,9 @@
       <c r="I321" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="J321" s="3"/>
+      <c r="J321" s="3">
+        <v>7</v>
+      </c>
       <c r="K321" s="1">
         <v>4.5</v>
       </c>
@@ -16362,10 +17228,12 @@
       <c r="Q321" s="3"/>
       <c r="R321" s="3"/>
       <c r="S321" s="3"/>
-      <c r="T321" s="3"/>
+      <c r="T321" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U321" s="3"/>
       <c r="V321" s="3"/>
-      <c r="W321" s="28"/>
+      <c r="W321" s="3"/>
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" s="17"/>
@@ -16375,21 +17243,19 @@
       <c r="C322" s="17" t="s">
         <v>398</v>
       </c>
-      <c r="D322" s="17" t="s">
-        <v>46</v>
+      <c r="D322" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E322" s="17" t="str">
         <f>"нагрузка "&amp;C322</f>
         <v>нагрузка QF1 ВРУ-ИТП</v>
       </c>
-      <c r="F322" s="15" t="s">
+      <c r="H322" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G322" s="3" t="s">
+      <c r="I322" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H322" s="17"/>
-      <c r="I322" s="18"/>
       <c r="J322" s="18"/>
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
@@ -16398,11 +17264,21 @@
         <v>38</v>
       </c>
       <c r="O322" s="17"/>
-      <c r="P322" s="17"/>
-      <c r="Q322" s="17"/>
-      <c r="R322" s="17"/>
-      <c r="S322" s="17"/>
-      <c r="T322" s="17"/>
+      <c r="P322" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q322" s="3">
+        <v>5</v>
+      </c>
+      <c r="R322" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S322" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T322" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U322" s="3"/>
       <c r="V322" s="3"/>
       <c r="W322" s="17"/>
@@ -16415,21 +17291,19 @@
       <c r="C323" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="D323" s="17" t="s">
-        <v>46</v>
+      <c r="D323" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E323" s="17" t="str">
         <f t="shared" ref="E323:E354" si="0">"нагрузка "&amp;C323</f>
         <v>нагрузка QF1 ЩУЛ1</v>
       </c>
-      <c r="F323" s="15" t="s">
+      <c r="H323" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G323" s="3" t="s">
+      <c r="I323" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H323" s="17"/>
-      <c r="I323" s="18"/>
       <c r="J323" s="18"/>
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
@@ -16438,11 +17312,21 @@
         <v>16</v>
       </c>
       <c r="O323" s="17"/>
-      <c r="P323" s="17"/>
-      <c r="Q323" s="17"/>
-      <c r="R323" s="17"/>
-      <c r="S323" s="17"/>
-      <c r="T323" s="17"/>
+      <c r="P323" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q323" s="3">
+        <v>5</v>
+      </c>
+      <c r="R323" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S323" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T323" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U323" s="3"/>
       <c r="V323" s="3"/>
       <c r="W323" s="17"/>
@@ -16455,21 +17339,19 @@
       <c r="C324" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="D324" s="17" t="s">
-        <v>46</v>
+      <c r="D324" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E324" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩУЛ2</v>
       </c>
-      <c r="F324" s="15" t="s">
+      <c r="H324" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G324" s="3" t="s">
+      <c r="I324" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H324" s="17"/>
-      <c r="I324" s="18"/>
       <c r="J324" s="18"/>
       <c r="K324" s="17"/>
       <c r="L324" s="17"/>
@@ -16478,11 +17360,21 @@
         <v>16</v>
       </c>
       <c r="O324" s="17"/>
-      <c r="P324" s="17"/>
-      <c r="Q324" s="17"/>
-      <c r="R324" s="17"/>
-      <c r="S324" s="17"/>
-      <c r="T324" s="17"/>
+      <c r="P324" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q324" s="3">
+        <v>5</v>
+      </c>
+      <c r="R324" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S324" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T324" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U324" s="3"/>
       <c r="V324" s="3"/>
       <c r="W324" s="17"/>
@@ -16495,21 +17387,19 @@
       <c r="C325" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="D325" s="17" t="s">
-        <v>46</v>
+      <c r="D325" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E325" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-0</v>
       </c>
-      <c r="F325" s="15" t="s">
+      <c r="H325" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G325" s="3" t="s">
+      <c r="I325" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H325" s="17"/>
-      <c r="I325" s="18"/>
       <c r="J325" s="18"/>
       <c r="K325" s="17"/>
       <c r="L325" s="17"/>
@@ -16518,11 +17408,21 @@
         <v>7</v>
       </c>
       <c r="O325" s="17"/>
-      <c r="P325" s="17"/>
-      <c r="Q325" s="17"/>
-      <c r="R325" s="17"/>
-      <c r="S325" s="17"/>
-      <c r="T325" s="17"/>
+      <c r="P325" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q325" s="3">
+        <v>5</v>
+      </c>
+      <c r="R325" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S325" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T325" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U325" s="3"/>
       <c r="V325" s="3"/>
       <c r="W325" s="17"/>
@@ -16535,21 +17435,19 @@
       <c r="C326" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="D326" s="17" t="s">
-        <v>46</v>
+      <c r="D326" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E326" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-01</v>
       </c>
-      <c r="F326" s="15" t="s">
+      <c r="H326" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G326" s="3" t="s">
+      <c r="I326" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H326" s="17"/>
-      <c r="I326" s="18"/>
       <c r="J326" s="18"/>
       <c r="K326" s="17"/>
       <c r="L326" s="17"/>
@@ -16558,11 +17456,21 @@
         <v>5</v>
       </c>
       <c r="O326" s="17"/>
-      <c r="P326" s="17"/>
-      <c r="Q326" s="17"/>
-      <c r="R326" s="17"/>
-      <c r="S326" s="17"/>
-      <c r="T326" s="17"/>
+      <c r="P326" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q326" s="3">
+        <v>5</v>
+      </c>
+      <c r="R326" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S326" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T326" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U326" s="3"/>
       <c r="V326" s="3"/>
       <c r="W326" s="17"/>
@@ -16575,21 +17483,19 @@
       <c r="C327" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="D327" s="17" t="s">
-        <v>46</v>
+      <c r="D327" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E327" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩВ-0</v>
       </c>
-      <c r="F327" s="15" t="s">
+      <c r="H327" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G327" s="3" t="s">
+      <c r="I327" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H327" s="17"/>
-      <c r="I327" s="18"/>
       <c r="J327" s="18"/>
       <c r="K327" s="17"/>
       <c r="L327" s="17"/>
@@ -16598,11 +17504,21 @@
         <v>5</v>
       </c>
       <c r="O327" s="17"/>
-      <c r="P327" s="17"/>
-      <c r="Q327" s="17"/>
-      <c r="R327" s="17"/>
-      <c r="S327" s="17"/>
-      <c r="T327" s="17"/>
+      <c r="P327" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q327" s="3">
+        <v>5</v>
+      </c>
+      <c r="R327" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S327" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T327" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U327" s="3"/>
       <c r="V327" s="3"/>
       <c r="W327" s="17"/>
@@ -16615,21 +17531,19 @@
       <c r="C328" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="D328" s="17" t="s">
-        <v>46</v>
+      <c r="D328" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E328" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩУ-НО</v>
       </c>
-      <c r="F328" s="15" t="s">
+      <c r="H328" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G328" s="3" t="s">
+      <c r="I328" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H328" s="17"/>
-      <c r="I328" s="18"/>
       <c r="J328" s="18"/>
       <c r="K328" s="17"/>
       <c r="L328" s="17"/>
@@ -16638,11 +17552,21 @@
         <v>10</v>
       </c>
       <c r="O328" s="17"/>
-      <c r="P328" s="17"/>
-      <c r="Q328" s="17"/>
-      <c r="R328" s="17"/>
-      <c r="S328" s="17"/>
-      <c r="T328" s="17"/>
+      <c r="P328" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q328" s="3">
+        <v>5</v>
+      </c>
+      <c r="R328" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S328" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T328" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U328" s="3"/>
       <c r="V328" s="3"/>
       <c r="W328" s="17"/>
@@ -16655,21 +17579,19 @@
       <c r="C329" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="D329" s="17" t="s">
-        <v>46</v>
+      <c r="D329" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E329" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩУ-НТ</v>
       </c>
-      <c r="F329" s="15" t="s">
+      <c r="H329" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G329" s="3" t="s">
+      <c r="I329" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H329" s="17"/>
-      <c r="I329" s="18"/>
       <c r="J329" s="18"/>
       <c r="K329" s="17"/>
       <c r="L329" s="17"/>
@@ -16678,11 +17600,21 @@
         <v>10</v>
       </c>
       <c r="O329" s="17"/>
-      <c r="P329" s="17"/>
-      <c r="Q329" s="17"/>
-      <c r="R329" s="17"/>
-      <c r="S329" s="17"/>
-      <c r="T329" s="17"/>
+      <c r="P329" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q329" s="3">
+        <v>5</v>
+      </c>
+      <c r="R329" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S329" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T329" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U329" s="3"/>
       <c r="V329" s="3"/>
       <c r="W329" s="17"/>
@@ -16695,21 +17627,19 @@
       <c r="C330" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="D330" s="17" t="s">
-        <v>46</v>
+      <c r="D330" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E330" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩУ-ХЦ2</v>
       </c>
-      <c r="F330" s="15" t="s">
+      <c r="H330" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G330" s="3" t="s">
+      <c r="I330" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H330" s="17"/>
-      <c r="I330" s="18"/>
       <c r="J330" s="18"/>
       <c r="K330" s="17"/>
       <c r="L330" s="17"/>
@@ -16718,11 +17648,21 @@
         <v>3</v>
       </c>
       <c r="O330" s="17"/>
-      <c r="P330" s="17"/>
-      <c r="Q330" s="17"/>
-      <c r="R330" s="17"/>
-      <c r="S330" s="17"/>
-      <c r="T330" s="17"/>
+      <c r="P330" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q330" s="3">
+        <v>5</v>
+      </c>
+      <c r="R330" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S330" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T330" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U330" s="3"/>
       <c r="V330" s="3"/>
       <c r="W330" s="17"/>
@@ -16735,21 +17675,19 @@
       <c r="C331" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="D331" s="17" t="s">
-        <v>46</v>
+      <c r="D331" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E331" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЧП1</v>
       </c>
-      <c r="F331" s="15" t="s">
+      <c r="H331" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G331" s="3" t="s">
+      <c r="I331" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H331" s="17"/>
-      <c r="I331" s="18"/>
       <c r="J331" s="18"/>
       <c r="K331" s="17"/>
       <c r="L331" s="17"/>
@@ -16758,11 +17696,21 @@
         <v>18.5</v>
       </c>
       <c r="O331" s="17"/>
-      <c r="P331" s="17"/>
-      <c r="Q331" s="17"/>
-      <c r="R331" s="17"/>
-      <c r="S331" s="17"/>
-      <c r="T331" s="17"/>
+      <c r="P331" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q331" s="3">
+        <v>5</v>
+      </c>
+      <c r="R331" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S331" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T331" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U331" s="3"/>
       <c r="V331" s="3"/>
       <c r="W331" s="17"/>
@@ -16775,21 +17723,19 @@
       <c r="C332" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="D332" s="17" t="s">
-        <v>46</v>
+      <c r="D332" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E332" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЧП2</v>
       </c>
-      <c r="F332" s="15" t="s">
+      <c r="H332" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G332" s="3" t="s">
+      <c r="I332" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H332" s="17"/>
-      <c r="I332" s="18"/>
       <c r="J332" s="18"/>
       <c r="K332" s="17"/>
       <c r="L332" s="17"/>
@@ -16798,11 +17744,21 @@
         <v>18.5</v>
       </c>
       <c r="O332" s="17"/>
-      <c r="P332" s="17"/>
-      <c r="Q332" s="17"/>
-      <c r="R332" s="17"/>
-      <c r="S332" s="17"/>
-      <c r="T332" s="17"/>
+      <c r="P332" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q332" s="3">
+        <v>5</v>
+      </c>
+      <c r="R332" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S332" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T332" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U332" s="3"/>
       <c r="V332" s="3"/>
       <c r="W332" s="17"/>
@@ -16815,21 +17771,19 @@
       <c r="C333" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="D333" s="17" t="s">
-        <v>46</v>
+      <c r="D333" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E333" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩУ-П10.3;В15</v>
       </c>
-      <c r="F333" s="15" t="s">
+      <c r="H333" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G333" s="3" t="s">
+      <c r="I333" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H333" s="17"/>
-      <c r="I333" s="18"/>
       <c r="J333" s="18"/>
       <c r="K333" s="17"/>
       <c r="L333" s="17"/>
@@ -16838,11 +17792,21 @@
         <v>0.4</v>
       </c>
       <c r="O333" s="17"/>
-      <c r="P333" s="17"/>
-      <c r="Q333" s="17"/>
-      <c r="R333" s="17"/>
-      <c r="S333" s="17"/>
-      <c r="T333" s="17"/>
+      <c r="P333" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q333" s="3">
+        <v>5</v>
+      </c>
+      <c r="R333" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S333" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T333" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U333" s="3"/>
       <c r="V333" s="3"/>
       <c r="W333" s="17"/>
@@ -16855,21 +17819,19 @@
       <c r="C334" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="D334" s="17" t="s">
-        <v>46</v>
+      <c r="D334" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E334" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 КП1</v>
       </c>
-      <c r="F334" s="15" t="s">
+      <c r="H334" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G334" s="3" t="s">
+      <c r="I334" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H334" s="17"/>
-      <c r="I334" s="18"/>
       <c r="J334" s="18"/>
       <c r="K334" s="17"/>
       <c r="L334" s="17"/>
@@ -16878,11 +17840,21 @@
         <v>10</v>
       </c>
       <c r="O334" s="17"/>
-      <c r="P334" s="17"/>
-      <c r="Q334" s="17"/>
-      <c r="R334" s="17"/>
-      <c r="S334" s="17"/>
-      <c r="T334" s="17"/>
+      <c r="P334" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q334" s="3">
+        <v>5</v>
+      </c>
+      <c r="R334" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S334" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T334" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U334" s="3"/>
       <c r="V334" s="3"/>
       <c r="W334" s="17"/>
@@ -16895,21 +17867,19 @@
       <c r="C335" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D335" s="17" t="s">
-        <v>46</v>
+      <c r="D335" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E335" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ШОТ1</v>
       </c>
-      <c r="F335" s="15" t="s">
+      <c r="H335" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G335" s="3" t="s">
+      <c r="I335" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H335" s="17"/>
-      <c r="I335" s="18"/>
       <c r="J335" s="18"/>
       <c r="K335" s="17"/>
       <c r="L335" s="17"/>
@@ -16918,11 +17888,21 @@
         <v>2.83</v>
       </c>
       <c r="O335" s="17"/>
-      <c r="P335" s="17"/>
-      <c r="Q335" s="17"/>
-      <c r="R335" s="17"/>
-      <c r="S335" s="17"/>
-      <c r="T335" s="17"/>
+      <c r="P335" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q335" s="3">
+        <v>5</v>
+      </c>
+      <c r="R335" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S335" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T335" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U335" s="3"/>
       <c r="V335" s="3"/>
       <c r="W335" s="17"/>
@@ -16935,21 +17915,19 @@
       <c r="C336" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="D336" s="17" t="s">
-        <v>46</v>
+      <c r="D336" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E336" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩУЭО1</v>
       </c>
-      <c r="F336" s="15" t="s">
+      <c r="H336" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G336" s="3" t="s">
+      <c r="I336" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H336" s="17"/>
-      <c r="I336" s="18"/>
       <c r="J336" s="18"/>
       <c r="K336" s="17"/>
       <c r="L336" s="17"/>
@@ -16958,11 +17936,21 @@
         <v>4.1749999999999998</v>
       </c>
       <c r="O336" s="17"/>
-      <c r="P336" s="17"/>
-      <c r="Q336" s="17"/>
-      <c r="R336" s="17"/>
-      <c r="S336" s="17"/>
-      <c r="T336" s="17"/>
+      <c r="P336" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q336" s="3">
+        <v>5</v>
+      </c>
+      <c r="R336" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S336" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T336" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U336" s="3"/>
       <c r="V336" s="3"/>
       <c r="W336" s="17"/>
@@ -16975,21 +17963,19 @@
       <c r="C337" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="D337" s="17" t="s">
-        <v>46</v>
+      <c r="D337" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E337" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ВРУ-ИТП</v>
       </c>
-      <c r="F337" s="15" t="s">
+      <c r="H337" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G337" s="3" t="s">
+      <c r="I337" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H337" s="17"/>
-      <c r="I337" s="18"/>
       <c r="J337" s="18"/>
       <c r="K337" s="17"/>
       <c r="L337" s="17"/>
@@ -16998,11 +17984,21 @@
         <v>37.270000000000003</v>
       </c>
       <c r="O337" s="17"/>
-      <c r="P337" s="17"/>
-      <c r="Q337" s="17"/>
-      <c r="R337" s="17"/>
-      <c r="S337" s="17"/>
-      <c r="T337" s="17"/>
+      <c r="P337" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q337" s="3">
+        <v>5</v>
+      </c>
+      <c r="R337" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S337" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T337" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U337" s="3"/>
       <c r="V337" s="3"/>
       <c r="W337" s="17"/>
@@ -17015,21 +18011,19 @@
       <c r="C338" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="D338" s="17" t="s">
-        <v>46</v>
+      <c r="D338" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E338" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЩУЛ3</v>
       </c>
-      <c r="F338" s="15" t="s">
+      <c r="H338" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G338" s="3" t="s">
+      <c r="I338" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H338" s="17"/>
-      <c r="I338" s="18"/>
       <c r="J338" s="18"/>
       <c r="K338" s="17"/>
       <c r="L338" s="17"/>
@@ -17038,11 +18032,21 @@
         <v>15</v>
       </c>
       <c r="O338" s="17"/>
-      <c r="P338" s="17"/>
-      <c r="Q338" s="17"/>
-      <c r="R338" s="17"/>
-      <c r="S338" s="17"/>
-      <c r="T338" s="17"/>
+      <c r="P338" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q338" s="3">
+        <v>5</v>
+      </c>
+      <c r="R338" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S338" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T338" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U338" s="3"/>
       <c r="V338" s="3"/>
       <c r="W338" s="17"/>
@@ -17055,21 +18059,19 @@
       <c r="C339" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="D339" s="17" t="s">
-        <v>46</v>
+      <c r="D339" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E339" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЩУ-Э1</v>
       </c>
-      <c r="F339" s="15" t="s">
+      <c r="H339" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G339" s="3" t="s">
+      <c r="I339" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H339" s="17"/>
-      <c r="I339" s="18"/>
       <c r="J339" s="18"/>
       <c r="K339" s="17"/>
       <c r="L339" s="17"/>
@@ -17078,11 +18080,21 @@
         <v>11</v>
       </c>
       <c r="O339" s="17"/>
-      <c r="P339" s="17"/>
-      <c r="Q339" s="17"/>
-      <c r="R339" s="17"/>
-      <c r="S339" s="17"/>
-      <c r="T339" s="17"/>
+      <c r="P339" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q339" s="3">
+        <v>5</v>
+      </c>
+      <c r="R339" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S339" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T339" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U339" s="3"/>
       <c r="V339" s="3"/>
       <c r="W339" s="17"/>
@@ -17095,21 +18107,19 @@
       <c r="C340" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="D340" s="17" t="s">
-        <v>46</v>
+      <c r="D340" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E340" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЩУ-Э2</v>
       </c>
-      <c r="F340" s="15" t="s">
+      <c r="H340" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G340" s="3" t="s">
+      <c r="I340" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H340" s="17"/>
-      <c r="I340" s="18"/>
       <c r="J340" s="18"/>
       <c r="K340" s="17"/>
       <c r="L340" s="17"/>
@@ -17118,11 +18128,21 @@
         <v>11</v>
       </c>
       <c r="O340" s="17"/>
-      <c r="P340" s="17"/>
-      <c r="Q340" s="17"/>
-      <c r="R340" s="17"/>
-      <c r="S340" s="17"/>
-      <c r="T340" s="17"/>
+      <c r="P340" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q340" s="3">
+        <v>5</v>
+      </c>
+      <c r="R340" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S340" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T340" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U340" s="3"/>
       <c r="V340" s="3"/>
       <c r="W340" s="17"/>
@@ -17135,21 +18155,19 @@
       <c r="C341" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="D341" s="17" t="s">
-        <v>46</v>
+      <c r="D341" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E341" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЧП3</v>
       </c>
-      <c r="F341" s="15" t="s">
+      <c r="H341" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G341" s="3" t="s">
+      <c r="I341" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H341" s="17"/>
-      <c r="I341" s="18"/>
       <c r="J341" s="18"/>
       <c r="K341" s="17"/>
       <c r="L341" s="17"/>
@@ -17158,11 +18176,21 @@
         <v>18.5</v>
       </c>
       <c r="O341" s="17"/>
-      <c r="P341" s="17"/>
-      <c r="Q341" s="17"/>
-      <c r="R341" s="17"/>
-      <c r="S341" s="17"/>
-      <c r="T341" s="17"/>
+      <c r="P341" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q341" s="3">
+        <v>5</v>
+      </c>
+      <c r="R341" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S341" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T341" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U341" s="3"/>
       <c r="V341" s="3"/>
       <c r="W341" s="17"/>
@@ -17175,21 +18203,19 @@
       <c r="C342" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="D342" s="17" t="s">
-        <v>46</v>
+      <c r="D342" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E342" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЧП4</v>
       </c>
-      <c r="F342" s="15" t="s">
+      <c r="H342" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G342" s="3" t="s">
+      <c r="I342" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H342" s="17"/>
-      <c r="I342" s="18"/>
       <c r="J342" s="18"/>
       <c r="K342" s="17"/>
       <c r="L342" s="17"/>
@@ -17198,11 +18224,21 @@
         <v>18.5</v>
       </c>
       <c r="O342" s="17"/>
-      <c r="P342" s="17"/>
-      <c r="Q342" s="17"/>
-      <c r="R342" s="17"/>
-      <c r="S342" s="17"/>
-      <c r="T342" s="17"/>
+      <c r="P342" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q342" s="3">
+        <v>5</v>
+      </c>
+      <c r="R342" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S342" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T342" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U342" s="3"/>
       <c r="V342" s="3"/>
       <c r="W342" s="17"/>
@@ -17215,21 +18251,19 @@
       <c r="C343" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="D343" s="17" t="s">
-        <v>46</v>
+      <c r="D343" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E343" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЩУ-КНС1</v>
       </c>
-      <c r="F343" s="15" t="s">
+      <c r="H343" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G343" s="3" t="s">
+      <c r="I343" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H343" s="17"/>
-      <c r="I343" s="18"/>
       <c r="J343" s="18"/>
       <c r="K343" s="17"/>
       <c r="L343" s="17"/>
@@ -17238,11 +18272,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="O343" s="17"/>
-      <c r="P343" s="17"/>
-      <c r="Q343" s="17"/>
-      <c r="R343" s="17"/>
-      <c r="S343" s="17"/>
-      <c r="T343" s="17"/>
+      <c r="P343" s="3">
+        <v>92</v>
+      </c>
+      <c r="Q343" s="3">
+        <v>5</v>
+      </c>
+      <c r="R343" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S343" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T343" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U343" s="3"/>
       <c r="V343" s="3"/>
       <c r="W343" s="17"/>
@@ -17255,21 +18299,19 @@
       <c r="C344" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="D344" s="17" t="s">
-        <v>46</v>
+      <c r="D344" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E344" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF2 ЩУ-КНС2</v>
       </c>
-      <c r="F344" s="15" t="s">
+      <c r="H344" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G344" s="3" t="s">
+      <c r="I344" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H344" s="17"/>
-      <c r="I344" s="18"/>
       <c r="J344" s="18"/>
       <c r="K344" s="17"/>
       <c r="L344" s="17"/>
@@ -17278,11 +18320,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="O344" s="17"/>
-      <c r="P344" s="17"/>
-      <c r="Q344" s="17"/>
-      <c r="R344" s="17"/>
-      <c r="S344" s="17"/>
-      <c r="T344" s="17"/>
+      <c r="P344" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q344" s="3">
+        <v>3</v>
+      </c>
+      <c r="R344" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S344" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T344" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U344" s="3"/>
       <c r="V344" s="3"/>
       <c r="W344" s="17"/>
@@ -17295,21 +18347,19 @@
       <c r="C345" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="D345" s="17" t="s">
-        <v>46</v>
+      <c r="D345" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E345" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ш1.5,ш1.6</v>
       </c>
-      <c r="F345" s="15" t="s">
+      <c r="H345" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G345" s="3" t="s">
+      <c r="I345" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H345" s="17"/>
-      <c r="I345" s="18"/>
       <c r="J345" s="18"/>
       <c r="K345" s="17"/>
       <c r="L345" s="17"/>
@@ -17318,11 +18368,21 @@
         <v>1.5</v>
       </c>
       <c r="O345" s="17"/>
-      <c r="P345" s="17"/>
-      <c r="Q345" s="17"/>
-      <c r="R345" s="17"/>
-      <c r="S345" s="17"/>
-      <c r="T345" s="17"/>
+      <c r="P345" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q345" s="3">
+        <v>3</v>
+      </c>
+      <c r="R345" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S345" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T345" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U345" s="3"/>
       <c r="V345" s="3"/>
       <c r="W345" s="17"/>
@@ -17335,21 +18395,19 @@
       <c r="C346" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="D346" s="17" t="s">
-        <v>46</v>
+      <c r="D346" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E346" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-С1</v>
       </c>
-      <c r="F346" s="15" t="s">
+      <c r="H346" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G346" s="3" t="s">
+      <c r="I346" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H346" s="17"/>
-      <c r="I346" s="18"/>
       <c r="J346" s="18"/>
       <c r="K346" s="17"/>
       <c r="L346" s="17"/>
@@ -17358,11 +18416,21 @@
         <v>14</v>
       </c>
       <c r="O346" s="17"/>
-      <c r="P346" s="17"/>
-      <c r="Q346" s="17"/>
-      <c r="R346" s="17"/>
-      <c r="S346" s="17"/>
-      <c r="T346" s="17"/>
+      <c r="P346" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q346" s="3">
+        <v>3</v>
+      </c>
+      <c r="R346" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S346" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T346" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U346" s="3"/>
       <c r="V346" s="3"/>
       <c r="W346" s="17"/>
@@ -17375,21 +18443,19 @@
       <c r="C347" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="D347" s="17" t="s">
-        <v>46</v>
+      <c r="D347" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E347" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-С2</v>
       </c>
-      <c r="F347" s="15" t="s">
+      <c r="H347" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G347" s="3" t="s">
+      <c r="I347" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H347" s="17"/>
-      <c r="I347" s="18"/>
       <c r="J347" s="18"/>
       <c r="K347" s="17"/>
       <c r="L347" s="17"/>
@@ -17398,11 +18464,21 @@
         <v>14</v>
       </c>
       <c r="O347" s="17"/>
-      <c r="P347" s="17"/>
-      <c r="Q347" s="17"/>
-      <c r="R347" s="17"/>
-      <c r="S347" s="17"/>
-      <c r="T347" s="17"/>
+      <c r="P347" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q347" s="3">
+        <v>3</v>
+      </c>
+      <c r="R347" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S347" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T347" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U347" s="3"/>
       <c r="V347" s="3"/>
       <c r="W347" s="17"/>
@@ -17415,21 +18491,19 @@
       <c r="C348" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="D348" s="17" t="s">
-        <v>46</v>
+      <c r="D348" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E348" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-С3</v>
       </c>
-      <c r="F348" s="15" t="s">
+      <c r="H348" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G348" s="3" t="s">
+      <c r="I348" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H348" s="17"/>
-      <c r="I348" s="18"/>
       <c r="J348" s="18"/>
       <c r="K348" s="17"/>
       <c r="L348" s="17"/>
@@ -17438,11 +18512,21 @@
         <v>20</v>
       </c>
       <c r="O348" s="17"/>
-      <c r="P348" s="17"/>
-      <c r="Q348" s="17"/>
-      <c r="R348" s="17"/>
-      <c r="S348" s="17"/>
-      <c r="T348" s="17"/>
+      <c r="P348" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q348" s="3">
+        <v>3</v>
+      </c>
+      <c r="R348" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S348" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T348" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U348" s="3"/>
       <c r="V348" s="3"/>
       <c r="W348" s="17"/>
@@ -17455,21 +18539,19 @@
       <c r="C349" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="D349" s="17" t="s">
-        <v>46</v>
+      <c r="D349" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E349" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка СКУД-01</v>
       </c>
-      <c r="F349" s="15" t="s">
+      <c r="H349" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G349" s="3" t="s">
+      <c r="I349" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H349" s="17"/>
-      <c r="I349" s="18"/>
       <c r="J349" s="18"/>
       <c r="K349" s="17"/>
       <c r="L349" s="17"/>
@@ -17478,11 +18560,21 @@
         <v>0.12</v>
       </c>
       <c r="O349" s="17"/>
-      <c r="P349" s="17"/>
-      <c r="Q349" s="17"/>
-      <c r="R349" s="17"/>
-      <c r="S349" s="17"/>
-      <c r="T349" s="17"/>
+      <c r="P349" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q349" s="3">
+        <v>3</v>
+      </c>
+      <c r="R349" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S349" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T349" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U349" s="3"/>
       <c r="V349" s="3"/>
       <c r="W349" s="17"/>
@@ -17495,21 +18587,19 @@
       <c r="C350" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="D350" s="17" t="s">
-        <v>46</v>
+      <c r="D350" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E350" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка СКУД-02</v>
       </c>
-      <c r="F350" s="15" t="s">
+      <c r="H350" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G350" s="3" t="s">
+      <c r="I350" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H350" s="17"/>
-      <c r="I350" s="18"/>
       <c r="J350" s="18"/>
       <c r="K350" s="17"/>
       <c r="L350" s="17"/>
@@ -17518,11 +18608,21 @@
         <v>0.18</v>
       </c>
       <c r="O350" s="17"/>
-      <c r="P350" s="17"/>
-      <c r="Q350" s="17"/>
-      <c r="R350" s="17"/>
-      <c r="S350" s="17"/>
-      <c r="T350" s="17"/>
+      <c r="P350" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q350" s="3">
+        <v>3</v>
+      </c>
+      <c r="R350" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S350" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T350" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U350" s="3"/>
       <c r="V350" s="3"/>
       <c r="W350" s="17"/>
@@ -17535,21 +18635,19 @@
       <c r="C351" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="D351" s="17" t="s">
-        <v>46</v>
+      <c r="D351" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E351" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ШУО1</v>
       </c>
-      <c r="F351" s="15" t="s">
+      <c r="H351" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G351" s="3" t="s">
+      <c r="I351" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H351" s="17"/>
-      <c r="I351" s="18"/>
       <c r="J351" s="18"/>
       <c r="K351" s="17"/>
       <c r="L351" s="17"/>
@@ -17558,11 +18656,21 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="O351" s="17"/>
-      <c r="P351" s="17"/>
-      <c r="Q351" s="17"/>
-      <c r="R351" s="17"/>
-      <c r="S351" s="17"/>
-      <c r="T351" s="17"/>
+      <c r="P351" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q351" s="3">
+        <v>3</v>
+      </c>
+      <c r="R351" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S351" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T351" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U351" s="3"/>
       <c r="V351" s="3"/>
       <c r="W351" s="17"/>
@@ -17575,21 +18683,19 @@
       <c r="C352" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="D352" s="17" t="s">
-        <v>46</v>
+      <c r="D352" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E352" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ШУ-ДН1</v>
       </c>
-      <c r="F352" s="15" t="s">
+      <c r="H352" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G352" s="3" t="s">
+      <c r="I352" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H352" s="17"/>
-      <c r="I352" s="18"/>
       <c r="J352" s="18"/>
       <c r="K352" s="17"/>
       <c r="L352" s="17"/>
@@ -17598,11 +18704,21 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="O352" s="17"/>
-      <c r="P352" s="17"/>
-      <c r="Q352" s="17"/>
-      <c r="R352" s="17"/>
-      <c r="S352" s="17"/>
-      <c r="T352" s="17"/>
+      <c r="P352" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q352" s="3">
+        <v>3</v>
+      </c>
+      <c r="R352" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S352" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T352" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U352" s="3"/>
       <c r="V352" s="3"/>
       <c r="W352" s="17"/>
@@ -17615,21 +18731,19 @@
       <c r="C353" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="D353" s="17" t="s">
-        <v>46</v>
+      <c r="D353" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E353" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-С4</v>
       </c>
-      <c r="F353" s="15" t="s">
+      <c r="H353" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G353" s="3" t="s">
+      <c r="I353" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H353" s="17"/>
-      <c r="I353" s="18"/>
       <c r="J353" s="18"/>
       <c r="K353" s="17"/>
       <c r="L353" s="17"/>
@@ -17638,11 +18752,21 @@
         <v>14</v>
       </c>
       <c r="O353" s="17"/>
-      <c r="P353" s="17"/>
-      <c r="Q353" s="17"/>
-      <c r="R353" s="17"/>
-      <c r="S353" s="17"/>
-      <c r="T353" s="17"/>
+      <c r="P353" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q353" s="3">
+        <v>3</v>
+      </c>
+      <c r="R353" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S353" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T353" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U353" s="3"/>
       <c r="V353" s="3"/>
       <c r="W353" s="17"/>
@@ -17655,21 +18779,19 @@
       <c r="C354" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="D354" s="17" t="s">
-        <v>46</v>
+      <c r="D354" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="E354" s="17" t="str">
         <f t="shared" si="0"/>
         <v>нагрузка QF1 ЩР-С5</v>
       </c>
-      <c r="F354" s="15" t="s">
+      <c r="H354" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="G354" s="3" t="s">
+      <c r="I354" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H354" s="17"/>
-      <c r="I354" s="18"/>
       <c r="J354" s="18"/>
       <c r="K354" s="17"/>
       <c r="L354" s="17"/>
@@ -17678,11 +18800,21 @@
         <v>14</v>
       </c>
       <c r="O354" s="17"/>
-      <c r="P354" s="17"/>
-      <c r="Q354" s="17"/>
-      <c r="R354" s="17"/>
-      <c r="S354" s="17"/>
-      <c r="T354" s="17"/>
+      <c r="P354" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q354" s="3">
+        <v>3</v>
+      </c>
+      <c r="R354" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="S354" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T354" s="29">
+        <v>0.22</v>
+      </c>
       <c r="U354" s="3"/>
       <c r="V354" s="3"/>
       <c r="W354" s="17"/>
@@ -17719,7 +18851,9 @@
       <c r="Q355" s="24"/>
       <c r="R355" s="24"/>
       <c r="S355" s="24"/>
-      <c r="T355" s="24"/>
+      <c r="T355" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U355" s="3"/>
       <c r="V355" s="3"/>
       <c r="W355" s="24"/>
@@ -17756,7 +18890,9 @@
       <c r="Q356" s="24"/>
       <c r="R356" s="24"/>
       <c r="S356" s="24"/>
-      <c r="T356" s="24"/>
+      <c r="T356" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U356" s="3"/>
       <c r="V356" s="3"/>
       <c r="W356" s="24"/>
@@ -17793,7 +18929,9 @@
       <c r="Q357" s="24"/>
       <c r="R357" s="24"/>
       <c r="S357" s="24"/>
-      <c r="T357" s="24"/>
+      <c r="T357" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U357" s="3"/>
       <c r="V357" s="3"/>
       <c r="W357" s="24"/>
@@ -17830,7 +18968,9 @@
       <c r="Q358" s="24"/>
       <c r="R358" s="24"/>
       <c r="S358" s="24"/>
-      <c r="T358" s="24"/>
+      <c r="T358" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U358" s="3"/>
       <c r="V358" s="3"/>
       <c r="W358" s="24"/>
@@ -17867,7 +19007,9 @@
       <c r="Q359" s="24"/>
       <c r="R359" s="24"/>
       <c r="S359" s="24"/>
-      <c r="T359" s="24"/>
+      <c r="T359" s="29">
+        <v>0.4</v>
+      </c>
       <c r="U359" s="3"/>
       <c r="V359" s="3"/>
       <c r="W359" s="24"/>
@@ -17920,12 +19062,14 @@
       <c r="S360" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="T360" s="24">
-        <v>16</v>
+      <c r="T360" s="29">
+        <v>0.22</v>
       </c>
       <c r="U360" s="3"/>
       <c r="V360" s="3"/>
-      <c r="W360" s="24"/>
+      <c r="W360" s="24">
+        <v>16</v>
+      </c>
     </row>
     <row r="361" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A361" s="24"/>
@@ -17975,12 +19119,14 @@
       <c r="S361" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="T361" s="24">
-        <v>16</v>
+      <c r="T361" s="29">
+        <v>0.22</v>
       </c>
       <c r="U361" s="3"/>
       <c r="V361" s="3"/>
-      <c r="W361" s="24"/>
+      <c r="W361" s="24">
+        <v>16</v>
+      </c>
     </row>
     <row r="362" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A362" s="24"/>
@@ -18030,12 +19176,14 @@
       <c r="S362" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="T362" s="24">
-        <v>16</v>
+      <c r="T362" s="29">
+        <v>0.22</v>
       </c>
       <c r="U362" s="3"/>
       <c r="V362" s="3"/>
-      <c r="W362" s="24"/>
+      <c r="W362" s="24">
+        <v>16</v>
+      </c>
     </row>
     <row r="363" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A363" s="24"/>
@@ -18085,12 +19233,14 @@
       <c r="S363" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="T363" s="24">
-        <v>16</v>
+      <c r="T363" s="29">
+        <v>0.22</v>
       </c>
       <c r="U363" s="3"/>
       <c r="V363" s="3"/>
-      <c r="W363" s="24"/>
+      <c r="W363" s="24">
+        <v>16</v>
+      </c>
     </row>
     <row r="364" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A364" s="24"/>
@@ -18140,14 +19290,18 @@
       <c r="S364" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="T364" s="24">
-        <v>20</v>
+      <c r="T364" s="29">
+        <v>0.22</v>
       </c>
       <c r="U364" s="3"/>
       <c r="V364" s="3"/>
-      <c r="W364" s="24"/>
+      <c r="W364" s="24">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W364" xr:uid="{88E9F15A-FCA2-4EE6-B338-EE60C91C0095}"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
